--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10480" activeTab="1"/>
+    <workbookView windowWidth="20750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="学生、老师" sheetId="5" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="109">
   <si>
     <t>姓名</t>
   </si>
@@ -174,6 +174,9 @@
     <t>洪鑫洋</t>
   </si>
   <si>
+    <t>记笔记</t>
+  </si>
+  <si>
     <t>游武毅</t>
   </si>
   <si>
@@ -265,6 +268,9 @@
   </si>
   <si>
     <t>地2</t>
+  </si>
+  <si>
+    <t>提纲、惩罚跳舞</t>
   </si>
   <si>
     <t>生1</t>
@@ -1077,7 +1083,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1128,6 +1134,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1701,72 +1713,75 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:2">
       <c r="A41" s="13" t="s">
         <v>47</v>
       </c>
+      <c r="B41" s="10" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D53" s="14"/>
       <c r="E53" s="15"/>
@@ -1775,10 +1790,10 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D54" s="14"/>
       <c r="E54" s="15"/>
@@ -1787,37 +1802,38 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B55" s="14"/>
       <c r="C55" s="16"/>
       <c r="D55" s="10" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="56" ht="52" spans="1:2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
       <c r="A56" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B56" s="10" t="s">
         <v>66</v>
       </c>
+      <c r="B56" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C56" s="18"/>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="B57" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="C57" s="18"/>
+      <c r="B57" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C57" s="20"/>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C58" s="14"/>
       <c r="D58" s="15"/>
@@ -1827,9 +1843,9 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B59" s="19"/>
+        <v>72</v>
+      </c>
+      <c r="B59" s="21"/>
       <c r="D59" s="14"/>
       <c r="E59" s="15"/>
       <c r="F59" s="15"/>
@@ -1837,57 +1853,60 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B60" s="14"/>
       <c r="C60" s="16"/>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B61" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="C61" s="18"/>
-      <c r="D61" s="19"/>
-      <c r="E61" s="19"/>
-      <c r="F61" s="19"/>
-      <c r="G61" s="19"/>
+      <c r="B61" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C61" s="20"/>
+      <c r="D61" s="21"/>
+      <c r="E61" s="21"/>
+      <c r="F61" s="21"/>
+      <c r="G61" s="21"/>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B62" s="14"/>
       <c r="C62" s="16"/>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B63" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="C63" s="18"/>
+      <c r="B63" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="C63" s="20"/>
       <c r="D63" s="14"/>
       <c r="E63" s="15"/>
       <c r="F63" s="15"/>
       <c r="G63" s="16"/>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:4">
       <c r="A64" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B64" s="14"/>
       <c r="C64" s="16"/>
+      <c r="D64" s="10" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="65" ht="26" spans="1:7">
       <c r="A65" s="9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C65" s="14"/>
       <c r="D65" s="15"/>
@@ -1897,11 +1916,11 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="B66" s="19"/>
+        <v>83</v>
+      </c>
+      <c r="B66" s="21"/>
       <c r="C66" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D66" s="14"/>
       <c r="E66" s="15"/>
@@ -1910,38 +1929,38 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B67" s="14"/>
       <c r="C67" s="16"/>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B68" s="14"/>
       <c r="C68" s="16"/>
       <c r="D68" s="10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="B69" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="C69" s="18"/>
+        <v>88</v>
+      </c>
+      <c r="B69" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="C69" s="20"/>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="B70" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="C70" s="18"/>
+        <v>90</v>
+      </c>
+      <c r="B70" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C70" s="20"/>
       <c r="D70" s="14"/>
       <c r="E70" s="15"/>
       <c r="F70" s="15"/>
@@ -1949,20 +1968,20 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B71" s="14"/>
       <c r="C71" s="16"/>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D72" s="14"/>
       <c r="E72" s="15"/>
@@ -1971,11 +1990,11 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="B73" s="19"/>
+        <v>96</v>
+      </c>
+      <c r="B73" s="21"/>
       <c r="C73" s="10" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D73" s="14"/>
       <c r="E73" s="15"/>
@@ -1984,12 +2003,12 @@
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D75" s="14"/>
       <c r="E75" s="15"/>
@@ -1998,22 +2017,25 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B76" s="14"/>
       <c r="C76" s="16"/>
     </row>
-    <row r="77" spans="1:1">
+    <row r="77" spans="1:3">
       <c r="A77" s="9" t="s">
-        <v>99</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="B77" s="17"/>
+      <c r="C77" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="27">
     <mergeCell ref="C38:G38"/>
     <mergeCell ref="D53:G53"/>
     <mergeCell ref="D54:G54"/>
     <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
     <mergeCell ref="B57:C57"/>
     <mergeCell ref="C58:G58"/>
     <mergeCell ref="D59:G59"/>
@@ -2035,6 +2057,7 @@
     <mergeCell ref="D73:G73"/>
     <mergeCell ref="D75:G75"/>
     <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
   </mergeCells>
   <conditionalFormatting sqref="A1">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
@@ -2081,31 +2104,31 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:1">

--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10480"/>
+    <workbookView windowWidth="9810" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="学生、老师" sheetId="5" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="147">
   <si>
     <t>姓名</t>
   </si>
@@ -60,18 +60,33 @@
     <t>林芷琪</t>
   </si>
   <si>
+    <t>猴、郑致辰</t>
+  </si>
+  <si>
     <t>郭沁诗</t>
   </si>
   <si>
     <t>黄丰泽</t>
   </si>
   <si>
+    <t>骂人</t>
+  </si>
+  <si>
     <t>江雨晴</t>
   </si>
   <si>
+    <t>恩芽小说</t>
+  </si>
+  <si>
     <t>孔祥懿</t>
   </si>
   <si>
+    <t>济南</t>
+  </si>
+  <si>
+    <t>祥懿又是你、午餐（芹菜炒肉、土豆丝、秋葵、番茄酱）课间吃饭、画画、捏人、炫耀、演讲、喵喵姐</t>
+  </si>
+  <si>
     <t>林钰颖</t>
   </si>
   <si>
@@ -81,6 +96,9 @@
     <t>叶弘毅</t>
   </si>
   <si>
+    <t>相同单词造句</t>
+  </si>
+  <si>
     <t>张雨希</t>
   </si>
   <si>
@@ -93,15 +111,24 @@
     <t>郑致辰</t>
   </si>
   <si>
+    <t>牛奶拌饭</t>
+  </si>
+  <si>
     <t>陈婕</t>
   </si>
   <si>
+    <t>柠檬水</t>
+  </si>
+  <si>
     <t>江允儿</t>
   </si>
   <si>
     <t>徐嘉明</t>
   </si>
   <si>
+    <t>物理学家、发明家</t>
+  </si>
+  <si>
     <t>俞昕辰</t>
   </si>
   <si>
@@ -111,18 +138,39 @@
     <t>廖成羲</t>
   </si>
   <si>
+    <t>嘴瓢</t>
+  </si>
+  <si>
+    <t>写背诵内容（工整到潦草、一竖一点）</t>
+  </si>
+  <si>
     <t>林奕扬</t>
   </si>
   <si>
+    <t>骚（腰部绕环）、讨饭、座椅丝滑、班主任林奕扬、换衣服、摇头</t>
+  </si>
+  <si>
+    <t>爆胎</t>
+  </si>
+  <si>
     <t>张桢烨</t>
   </si>
   <si>
     <t>朱奕辰</t>
   </si>
   <si>
+    <t>左撇子、郑炜“义父”、辞职劳委</t>
+  </si>
+  <si>
     <t>李映辰</t>
   </si>
   <si>
+    <t>睡觉、趴/坐桌子、画画</t>
+  </si>
+  <si>
+    <t>咬手指、拉杆包、张桢烨、点空调时开窗、英语小测上画画/写“看不懂”</t>
+  </si>
+  <si>
     <t>林梓颢</t>
   </si>
   <si>
@@ -132,15 +180,33 @@
     <t>郑炜</t>
   </si>
   <si>
+    <t>大文豪、奶奶</t>
+  </si>
+  <si>
+    <t>打羽毛球</t>
+  </si>
+  <si>
     <t>黄恩亚</t>
   </si>
   <si>
+    <t>体香、生殖系统、迟到、午餐、跑步、字迹、腿伸过道、基督教、恩典时期的亚当、近代史、头发（捂头）、私藏卷子、拉小提琴、脏话、叫人、外八</t>
+  </si>
+  <si>
+    <t>推北师大、磨鞋、获奖时笑、菜被人吃、秀鼓包</t>
+  </si>
+  <si>
     <t>林承钰</t>
   </si>
   <si>
     <t>郑熠菲</t>
   </si>
   <si>
+    <t>装</t>
+  </si>
+  <si>
+    <t>关山度熠菲</t>
+  </si>
+  <si>
     <t>方欣妍</t>
   </si>
   <si>
@@ -159,22 +225,40 @@
     <t>陈子岩</t>
   </si>
   <si>
+    <t>女明星</t>
+  </si>
+  <si>
     <t>陈睿卓</t>
   </si>
   <si>
+    <t>午餐（海参/小米粥）、唱歌、2辆车、装、小学毕业照</t>
+  </si>
+  <si>
     <t>杨依诺</t>
   </si>
   <si>
+    <t>“社会人”</t>
+  </si>
+  <si>
     <t>薛阅晨</t>
   </si>
   <si>
+    <t>嘴甜、郑永泽</t>
+  </si>
+  <si>
     <t>蔡华楷</t>
   </si>
   <si>
+    <t>口水</t>
+  </si>
+  <si>
+    <t>讨饭</t>
+  </si>
+  <si>
     <t>洪鑫洋</t>
   </si>
   <si>
-    <t>记笔记</t>
+    <t>早读（劝学/磨刀霍霍向鑫洋）、生物30分、记笔记</t>
   </si>
   <si>
     <t>游武毅</t>
@@ -183,9 +267,15 @@
     <t>崔宇臣</t>
   </si>
   <si>
+    <t>起立时小动作</t>
+  </si>
+  <si>
     <t>曾好</t>
   </si>
   <si>
+    <t>自带饭、身材、手机、历史、戴眼镜</t>
+  </si>
+  <si>
     <t>陆梓豪</t>
   </si>
   <si>
@@ -198,22 +288,34 @@
     <t>刘天馨</t>
   </si>
   <si>
+    <t>陆梓豪（作业/午餐/值日）</t>
+  </si>
+  <si>
     <t>黄桂芳</t>
   </si>
   <si>
     <t>李梦妍</t>
   </si>
   <si>
+    <t>狡猾、雕版印刷、抢东西、画粑粑、曾好、梳子/镜子/护手霜/增高鞋、梗（橙绿、盆地、六棱柱、考试成绩</t>
+  </si>
+  <si>
     <t>曹世强</t>
   </si>
   <si>
     <t>蒲林豪</t>
   </si>
   <si>
+    <t>杂技（脚架脖子）、文件袋放腿上、口水</t>
+  </si>
+  <si>
+    <t>画画</t>
+  </si>
+  <si>
     <t>语1</t>
   </si>
   <si>
-    <t>防伪标志、声音忽高忽低</t>
+    <t>防伪标志、声音忽高忽低、小测</t>
   </si>
   <si>
     <t>语2</t>
@@ -222,6 +324,9 @@
     <t>通报作业情况、抽西游记</t>
   </si>
   <si>
+    <t>名言</t>
+  </si>
+  <si>
     <t>语3</t>
   </si>
   <si>
@@ -249,6 +354,9 @@
     <t>政2</t>
   </si>
   <si>
+    <t>前5看视频</t>
+  </si>
+  <si>
     <t>政3</t>
   </si>
   <si>
@@ -267,6 +375,9 @@
     <t>知识点（Z1）、拍照、“重男轻女”、打人、作业要求</t>
   </si>
   <si>
+    <t>抄知识点、做素养提升</t>
+  </si>
+  <si>
     <t>地2</t>
   </si>
   <si>
@@ -303,7 +414,7 @@
     <t>美1</t>
   </si>
   <si>
-    <t>铅笔、繁体字、眼保健操、掉头、下课状态</t>
+    <t>铅笔、繁体字、眼保健操、掉头、下课状态、上课起立</t>
   </si>
   <si>
     <t>美2</t>
@@ -331,6 +442,9 @@
   </si>
   <si>
     <t>信2</t>
+  </si>
+  <si>
+    <t>电击</t>
   </si>
   <si>
     <t>段长</t>
@@ -772,7 +886,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -784,43 +898,6 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -956,7 +1033,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -968,34 +1045,34 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1083,7 +1160,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1126,29 +1203,14 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1518,546 +1580,653 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:3">
       <c r="A3" s="13" t="s">
         <v>9</v>
       </c>
+      <c r="C3" s="10" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
+        <v>12</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
+        <v>14</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" ht="52" spans="1:3">
       <c r="A7" s="13" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="13" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" s="13" t="s">
-        <v>16</v>
+        <v>21</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="13" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="13" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14" s="13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
+        <v>26</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>31</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="13" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" ht="26" spans="1:3">
       <c r="A20" s="13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
+        <v>35</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" ht="39" spans="1:3">
       <c r="A21" s="13" t="s">
-        <v>27</v>
+        <v>38</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="13" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" ht="26" spans="1:2">
       <c r="A23" s="13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
+        <v>42</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" ht="39" spans="1:3">
       <c r="A24" s="13" t="s">
-        <v>30</v>
+        <v>44</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="13" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="13" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27" s="13" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
+        <v>49</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" ht="78" spans="1:3">
       <c r="A28" s="13" t="s">
-        <v>34</v>
+        <v>52</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30" s="13" t="s">
-        <v>36</v>
+        <v>56</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="13" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="13" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="13" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="13" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="13" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
       <c r="A36" s="13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
+        <v>64</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="37" ht="26" spans="1:3">
       <c r="A37" s="13" t="s">
-        <v>43</v>
+        <v>66</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="13" t="s">
-        <v>44</v>
+        <v>68</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>69</v>
       </c>
       <c r="C38" s="14"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="16"/>
-    </row>
-    <row r="39" spans="1:1">
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39" s="13" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
+        <v>70</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40" s="13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
+        <v>72</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41" ht="26" spans="1:3">
       <c r="A41" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="B41" s="10" t="s">
-        <v>48</v>
+        <v>75</v>
+      </c>
+      <c r="B41" s="10"/>
+      <c r="C41" s="10" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="13" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
       <c r="A43" s="13" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
+        <v>78</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="44" ht="26" spans="1:2">
       <c r="A44" s="13" t="s">
-        <v>51</v>
+        <v>80</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="13" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="13" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
       <c r="A48" s="13" t="s">
-        <v>55</v>
+        <v>85</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="50" ht="52" spans="1:3">
       <c r="A50" s="13" t="s">
-        <v>57</v>
+        <v>88</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="13" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="52" ht="26" spans="1:3">
       <c r="A52" s="13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
+        <v>91</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="53" ht="26" spans="1:7">
       <c r="A53" s="9" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="D53" s="14"/>
-      <c r="E53" s="15"/>
-      <c r="F53" s="15"/>
-      <c r="G53" s="16"/>
+      <c r="E53" s="14"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="14"/>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="9" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>63</v>
+        <v>97</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>98</v>
       </c>
       <c r="D54" s="14"/>
-      <c r="E54" s="15"/>
-      <c r="F54" s="15"/>
-      <c r="G54" s="16"/>
+      <c r="E54" s="14"/>
+      <c r="F54" s="14"/>
+      <c r="G54" s="14"/>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="9" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="B55" s="14"/>
-      <c r="C55" s="16"/>
+      <c r="C55" s="14"/>
       <c r="D55" s="10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" ht="52" spans="1:3">
       <c r="A56" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="B56" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C56" s="18"/>
-    </row>
-    <row r="57" spans="1:3">
+        <v>101</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C56" s="7"/>
+    </row>
+    <row r="57" ht="117" spans="1:3">
       <c r="A57" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="B57" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="C57" s="20"/>
+        <v>103</v>
+      </c>
+      <c r="B57" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="C57" s="15"/>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="9" t="s">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="C58" s="14"/>
-      <c r="D58" s="15"/>
-      <c r="E58" s="15"/>
-      <c r="F58" s="15"/>
-      <c r="G58" s="16"/>
+      <c r="D58" s="14"/>
+      <c r="E58" s="14"/>
+      <c r="F58" s="14"/>
+      <c r="G58" s="14"/>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="B59" s="21"/>
+        <v>107</v>
+      </c>
+      <c r="B59" s="14"/>
+      <c r="C59" s="10" t="s">
+        <v>108</v>
+      </c>
       <c r="D59" s="14"/>
-      <c r="E59" s="15"/>
-      <c r="F59" s="15"/>
-      <c r="G59" s="16"/>
+      <c r="E59" s="14"/>
+      <c r="F59" s="14"/>
+      <c r="G59" s="14"/>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="9" t="s">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="B60" s="14"/>
-      <c r="C60" s="16"/>
+      <c r="C60" s="14"/>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="B61" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="C61" s="20"/>
-      <c r="D61" s="21"/>
-      <c r="E61" s="21"/>
-      <c r="F61" s="21"/>
-      <c r="G61" s="21"/>
+        <v>110</v>
+      </c>
+      <c r="B61" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C61" s="15"/>
+      <c r="D61" s="14"/>
+      <c r="E61" s="14"/>
+      <c r="F61" s="14"/>
+      <c r="G61" s="14"/>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="9" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="B62" s="14"/>
-      <c r="C62" s="16"/>
-    </row>
-    <row r="63" spans="1:7">
+      <c r="C62" s="14"/>
+    </row>
+    <row r="63" ht="26" spans="1:7">
       <c r="A63" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="B63" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="C63" s="20"/>
+        <v>113</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>115</v>
+      </c>
       <c r="D63" s="14"/>
-      <c r="E63" s="15"/>
-      <c r="F63" s="15"/>
-      <c r="G63" s="16"/>
+      <c r="E63" s="14"/>
+      <c r="F63" s="14"/>
+      <c r="G63" s="14"/>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="9" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="B64" s="14"/>
-      <c r="C64" s="16"/>
+      <c r="C64" s="14"/>
       <c r="D64" s="10" t="s">
-        <v>80</v>
+        <v>117</v>
       </c>
     </row>
     <row r="65" ht="26" spans="1:7">
       <c r="A65" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="B65" s="10" t="s">
-        <v>82</v>
+        <v>118</v>
+      </c>
+      <c r="B65" s="16" t="s">
+        <v>119</v>
       </c>
       <c r="C65" s="14"/>
-      <c r="D65" s="15"/>
-      <c r="E65" s="15"/>
-      <c r="F65" s="15"/>
-      <c r="G65" s="16"/>
+      <c r="D65" s="14"/>
+      <c r="E65" s="14"/>
+      <c r="F65" s="14"/>
+      <c r="G65" s="14"/>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="B66" s="21"/>
+        <v>120</v>
+      </c>
+      <c r="B66" s="14"/>
       <c r="C66" s="10" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="D66" s="14"/>
-      <c r="E66" s="15"/>
-      <c r="F66" s="15"/>
-      <c r="G66" s="16"/>
+      <c r="E66" s="14"/>
+      <c r="F66" s="14"/>
+      <c r="G66" s="14"/>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="9" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="B67" s="14"/>
-      <c r="C67" s="16"/>
+      <c r="C67" s="14"/>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="9" t="s">
-        <v>86</v>
+        <v>123</v>
       </c>
       <c r="B68" s="14"/>
-      <c r="C68" s="16"/>
+      <c r="C68" s="14"/>
       <c r="D68" s="10" t="s">
-        <v>87</v>
+        <v>124</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="B69" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="C69" s="20"/>
-    </row>
-    <row r="70" spans="1:7">
+        <v>125</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C69" s="7"/>
+    </row>
+    <row r="70" ht="26" spans="1:7">
       <c r="A70" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="B70" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="C70" s="20"/>
+        <v>127</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C70" s="7"/>
       <c r="D70" s="14"/>
-      <c r="E70" s="15"/>
-      <c r="F70" s="15"/>
-      <c r="G70" s="16"/>
+      <c r="E70" s="14"/>
+      <c r="F70" s="14"/>
+      <c r="G70" s="14"/>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="9" t="s">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="B71" s="14"/>
-      <c r="C71" s="16"/>
+      <c r="C71" s="14"/>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="9" t="s">
-        <v>93</v>
+        <v>130</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>94</v>
+        <v>131</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>95</v>
+        <v>132</v>
       </c>
       <c r="D72" s="14"/>
-      <c r="E72" s="15"/>
-      <c r="F72" s="15"/>
-      <c r="G72" s="16"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="14"/>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B73" s="21"/>
+        <v>133</v>
+      </c>
+      <c r="B73" s="14"/>
       <c r="C73" s="10" t="s">
-        <v>97</v>
+        <v>134</v>
       </c>
       <c r="D73" s="14"/>
-      <c r="E73" s="15"/>
-      <c r="F73" s="15"/>
-      <c r="G73" s="16"/>
+      <c r="E73" s="14"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="14"/>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="9" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="9" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="D75" s="14"/>
-      <c r="E75" s="15"/>
-      <c r="F75" s="15"/>
-      <c r="G75" s="16"/>
-    </row>
-    <row r="76" spans="1:3">
+      <c r="E75" s="14"/>
+      <c r="F75" s="14"/>
+      <c r="G75" s="14"/>
+    </row>
+    <row r="76" spans="1:4">
       <c r="A76" s="9" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="B76" s="14"/>
-      <c r="C76" s="16"/>
+      <c r="C76" s="14"/>
+      <c r="D76" s="10" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="B77" s="17"/>
-      <c r="C77" s="18"/>
+        <v>139</v>
+      </c>
+      <c r="B77" s="7"/>
+      <c r="C77" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="20">
     <mergeCell ref="C38:G38"/>
     <mergeCell ref="D53:G53"/>
     <mergeCell ref="D54:G54"/>
     <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
     <mergeCell ref="C58:G58"/>
     <mergeCell ref="D59:G59"/>
     <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
     <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
     <mergeCell ref="D63:G63"/>
     <mergeCell ref="B64:C64"/>
     <mergeCell ref="C65:G65"/>
     <mergeCell ref="D66:G66"/>
     <mergeCell ref="B67:C67"/>
     <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
     <mergeCell ref="D70:G70"/>
     <mergeCell ref="B71:C71"/>
     <mergeCell ref="D72:G72"/>
     <mergeCell ref="D73:G73"/>
     <mergeCell ref="D75:G75"/>
     <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
   </mergeCells>
   <conditionalFormatting sqref="A1">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
@@ -2104,31 +2273,31 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="6" t="s">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="6" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="6" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="6" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:1">

--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="9810" windowHeight="10480"/>
+    <workbookView windowWidth="20750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="学生、老师" sheetId="5" r:id="rId1"/>
@@ -69,7 +69,7 @@
     <t>黄丰泽</t>
   </si>
   <si>
-    <t>骂人</t>
+    <t>骂人、没错</t>
   </si>
   <si>
     <t>江雨晴</t>
@@ -84,7 +84,7 @@
     <t>济南</t>
   </si>
   <si>
-    <t>祥懿又是你、午餐（芹菜炒肉、土豆丝、秋葵、番茄酱）课间吃饭、画画、捏人、炫耀、演讲、喵喵姐</t>
+    <t>祥懿又是你、午餐（芹菜炒肉、土豆丝、秋葵、番茄酱）课间吃饭、画画、捏/咬/打人、炫耀、演讲、喵喵姐</t>
   </si>
   <si>
     <t>林钰颖</t>
@@ -330,7 +330,7 @@
     <t>语3</t>
   </si>
   <si>
-    <t>微信窗口藏下面</t>
+    <t>微信窗口藏下面、C读“系”</t>
   </si>
   <si>
     <t>数1</t>
@@ -1160,7 +1160,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1205,9 +1205,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1863,7 +1860,6 @@
       <c r="A41" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="B41" s="10"/>
       <c r="C41" s="10" t="s">
         <v>76</v>
       </c>
@@ -1991,10 +1987,10 @@
       <c r="A57" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="B57" s="15" t="s">
+      <c r="B57" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C57" s="15"/>
+      <c r="C57" s="7"/>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="9" t="s">
@@ -2033,10 +2029,10 @@
       <c r="A61" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="B61" s="15" t="s">
+      <c r="B61" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="C61" s="15"/>
+      <c r="C61" s="7"/>
       <c r="D61" s="14"/>
       <c r="E61" s="14"/>
       <c r="F61" s="14"/>
@@ -2078,7 +2074,7 @@
       <c r="A65" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="B65" s="16" t="s">
+      <c r="B65" s="15" t="s">
         <v>119</v>
       </c>
       <c r="C65" s="14"/>

--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="153">
   <si>
     <t>姓名</t>
   </si>
@@ -195,6 +195,9 @@
     <t>推北师大、磨鞋、获奖时笑、菜被人吃、秀鼓包</t>
   </si>
   <si>
+    <t>朋友圈（模糊图片）、粗笔写字</t>
+  </si>
+  <si>
     <t>林承钰</t>
   </si>
   <si>
@@ -297,7 +300,7 @@
     <t>李梦妍</t>
   </si>
   <si>
-    <t>狡猾、雕版印刷、抢东西、画粑粑、曾好、梳子/镜子/护手霜/增高鞋、梗（橙绿、盆地、六棱柱、考试成绩</t>
+    <t>狡猾、雕版印刷、抢东西、画粑粑、曾好、梳子/镜子/护手霜/增高鞋、梗（橙绿、盆地、六棱柱、考试成绩、大冒险</t>
   </si>
   <si>
     <t>曹世强</t>
@@ -345,6 +348,9 @@
     <t>小测（CTMO）、作业（抄几默几、积累本、AB本、订正）、one by one、笔记（活页、不要换笔、一课一页）、课前带读、作文本/草稿本/小绿（粉、黄、红）/预习、抄作业本、手机管理、做题标记、羽毛球、一人一包、学习小组、巡课、3条红领巾</t>
   </si>
   <si>
+    <t>请假13个工作日</t>
+  </si>
+  <si>
     <t>政1</t>
   </si>
   <si>
@@ -360,6 +366,9 @@
     <t>政3</t>
   </si>
   <si>
+    <t>啧</t>
+  </si>
+  <si>
     <t>史1</t>
   </si>
   <si>
@@ -469,6 +478,15 @@
   </si>
   <si>
     <t>么么脆鸡排、密封条、虫卵</t>
+  </si>
+  <si>
+    <t>热门游戏</t>
+  </si>
+  <si>
+    <t>五子棋、笔</t>
+  </si>
+  <si>
+    <t>水瓶</t>
   </si>
 </sst>
 </file>
@@ -1756,7 +1774,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" ht="78" spans="1:3">
+    <row r="28" ht="78" spans="1:4">
       <c r="A28" s="13" t="s">
         <v>52</v>
       </c>
@@ -1766,70 +1784,73 @@
       <c r="C28" s="10" t="s">
         <v>54</v>
       </c>
+      <c r="D28" s="10" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="37" ht="26" spans="1:3">
       <c r="A37" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C38" s="14"/>
       <c r="D38" s="14"/>
@@ -1839,110 +1860,110 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="41" ht="26" spans="1:3">
       <c r="A41" s="13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44" ht="26" spans="1:2">
       <c r="A44" s="13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="50" ht="52" spans="1:3">
       <c r="A50" s="13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="52" ht="26" spans="1:3">
       <c r="A52" s="13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="53" ht="26" spans="1:7">
       <c r="A53" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D53" s="14"/>
       <c r="E53" s="14"/>
@@ -1951,13 +1972,13 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D54" s="14"/>
       <c r="E54" s="14"/>
@@ -1966,38 +1987,41 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
       <c r="D55" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="56" ht="52" spans="1:3">
       <c r="A56" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C56" s="7"/>
     </row>
-    <row r="57" ht="117" spans="1:3">
+    <row r="57" ht="117" spans="1:4">
       <c r="A57" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C57" s="7"/>
+      <c r="D57" s="10" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C58" s="14"/>
       <c r="D58" s="14"/>
@@ -2007,30 +2031,33 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B59" s="14"/>
       <c r="C59" s="10" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D59" s="14"/>
       <c r="E59" s="14"/>
       <c r="F59" s="14"/>
       <c r="G59" s="14"/>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:4">
       <c r="A60" s="9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B60" s="14"/>
       <c r="C60" s="14"/>
+      <c r="D60" s="10" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="9" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C61" s="7"/>
       <c r="D61" s="14"/>
@@ -2040,20 +2067,20 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="9" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B62" s="14"/>
       <c r="C62" s="14"/>
     </row>
     <row r="63" ht="26" spans="1:7">
       <c r="A63" s="9" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D63" s="14"/>
       <c r="E63" s="14"/>
@@ -2062,20 +2089,20 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="9" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
       <c r="D64" s="10" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="65" ht="26" spans="1:7">
       <c r="A65" s="9" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C65" s="14"/>
       <c r="D65" s="14"/>
@@ -2085,11 +2112,11 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="9" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B66" s="14"/>
       <c r="C66" s="10" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D66" s="14"/>
       <c r="E66" s="14"/>
@@ -2098,36 +2125,36 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
       <c r="D68" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C69" s="7"/>
     </row>
     <row r="70" ht="26" spans="1:7">
       <c r="A70" s="9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C70" s="7"/>
       <c r="D70" s="14"/>
@@ -2137,20 +2164,20 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B71" s="14"/>
       <c r="C71" s="14"/>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="9" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D72" s="14"/>
       <c r="E72" s="14"/>
@@ -2159,11 +2186,11 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="9" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B73" s="14"/>
       <c r="C73" s="10" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D73" s="14"/>
       <c r="E73" s="14"/>
@@ -2172,12 +2199,12 @@
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="9" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="9" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D75" s="14"/>
       <c r="E75" s="14"/>
@@ -2186,17 +2213,17 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="9" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B76" s="14"/>
       <c r="C76" s="14"/>
       <c r="D76" s="10" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="9" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B77" s="7"/>
       <c r="C77" s="7"/>
@@ -2269,35 +2296,43 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="6" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="6" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="6" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="6"/>
+        <v>149</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="6"/>

--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="155">
   <si>
     <t>姓名</t>
   </si>
@@ -87,6 +87,9 @@
     <t>祥懿又是你、午餐（芹菜炒肉、土豆丝、秋葵、番茄酱）课间吃饭、画画、捏/咬/打人、炫耀、演讲、喵喵姐</t>
   </si>
   <si>
+    <t>萌、上课吃东西</t>
+  </si>
+  <si>
     <t>林钰颖</t>
   </si>
   <si>
@@ -237,6 +240,9 @@
     <t>午餐（海参/小米粥）、唱歌、2辆车、装、小学毕业照</t>
   </si>
   <si>
+    <t>对俞昕辰说要唱《再给我两分钟》</t>
+  </si>
+  <si>
     <t>杨依诺</t>
   </si>
   <si>
@@ -345,7 +351,7 @@
     <t>英1</t>
   </si>
   <si>
-    <t>小测（CTMO）、作业（抄几默几、积累本、AB本、订正）、one by one、笔记（活页、不要换笔、一课一页）、课前带读、作文本/草稿本/小绿（粉、黄、红）/预习、抄作业本、手机管理、做题标记、羽毛球、一人一包、学习小组、巡课、3条红领巾</t>
+    <t>小测（CTMO）、作业（抄几默几、积累本、AB本、订正）、one by one、笔记（活页、不要换笔、一课一页）、课前带读、作文本/草稿本/小绿（粉、黄、红）/预习、抄作业本、手机管理、做题标记、羽毛球、一人一包、学习小组、巡课、3条红领巾、AI视频</t>
   </si>
   <si>
     <t>请假13个工作日</t>
@@ -411,7 +417,7 @@
     <t>物1</t>
   </si>
   <si>
-    <t>读“m”</t>
+    <t>读“m”、写“解”</t>
   </si>
   <si>
     <t>体1</t>
@@ -453,7 +459,7 @@
     <t>信2</t>
   </si>
   <si>
-    <t>电击</t>
+    <t>电击小子、马赛克</t>
   </si>
   <si>
     <t>段长</t>
@@ -1624,7 +1630,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" ht="52" spans="1:3">
+    <row r="7" ht="52" spans="1:4">
       <c r="A7" s="13" t="s">
         <v>16</v>
       </c>
@@ -1634,223 +1640,229 @@
       <c r="C7" s="10" t="s">
         <v>18</v>
       </c>
+      <c r="D7" s="10" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" ht="26" spans="1:3">
       <c r="A20" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" ht="39" spans="1:3">
       <c r="A21" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" ht="26" spans="1:2">
       <c r="A23" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" ht="39" spans="1:3">
       <c r="A24" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" ht="78" spans="1:4">
       <c r="A28" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="37" ht="26" spans="1:3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="37" ht="26" spans="1:4">
       <c r="A37" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C38" s="14"/>
       <c r="D38" s="14"/>
@@ -1860,110 +1872,110 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41" ht="26" spans="1:3">
       <c r="A41" s="13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44" ht="26" spans="1:2">
       <c r="A44" s="13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="50" ht="52" spans="1:3">
       <c r="A50" s="13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="52" ht="26" spans="1:3">
       <c r="A52" s="13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="53" ht="26" spans="1:7">
       <c r="A53" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D53" s="14"/>
       <c r="E53" s="14"/>
@@ -1972,13 +1984,13 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D54" s="14"/>
       <c r="E54" s="14"/>
@@ -1987,41 +1999,41 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
       <c r="D55" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="56" ht="52" spans="1:3">
       <c r="A56" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C56" s="7"/>
     </row>
     <row r="57" ht="117" spans="1:4">
       <c r="A57" s="9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C57" s="7"/>
       <c r="D57" s="10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C58" s="14"/>
       <c r="D58" s="14"/>
@@ -2031,11 +2043,11 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B59" s="14"/>
       <c r="C59" s="10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D59" s="14"/>
       <c r="E59" s="14"/>
@@ -2044,20 +2056,20 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B60" s="14"/>
       <c r="C60" s="14"/>
       <c r="D60" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C61" s="7"/>
       <c r="D61" s="14"/>
@@ -2067,20 +2079,20 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B62" s="14"/>
       <c r="C62" s="14"/>
     </row>
     <row r="63" ht="26" spans="1:7">
       <c r="A63" s="9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D63" s="14"/>
       <c r="E63" s="14"/>
@@ -2089,20 +2101,20 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="9" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
       <c r="D64" s="10" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="65" ht="26" spans="1:7">
       <c r="A65" s="9" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C65" s="14"/>
       <c r="D65" s="14"/>
@@ -2112,11 +2124,11 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B66" s="14"/>
       <c r="C66" s="10" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D66" s="14"/>
       <c r="E66" s="14"/>
@@ -2125,36 +2137,36 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="9" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
       <c r="D68" s="10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C69" s="7"/>
     </row>
     <row r="70" ht="26" spans="1:7">
       <c r="A70" s="9" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C70" s="7"/>
       <c r="D70" s="14"/>
@@ -2164,20 +2176,20 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B71" s="14"/>
       <c r="C71" s="14"/>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="9" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D72" s="14"/>
       <c r="E72" s="14"/>
@@ -2186,11 +2198,11 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="9" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B73" s="14"/>
       <c r="C73" s="10" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D73" s="14"/>
       <c r="E73" s="14"/>
@@ -2199,12 +2211,12 @@
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="9" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D75" s="14"/>
       <c r="E75" s="14"/>
@@ -2213,17 +2225,17 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B76" s="14"/>
       <c r="C76" s="14"/>
       <c r="D76" s="10" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="9" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B77" s="7"/>
       <c r="C77" s="7"/>
@@ -2296,42 +2308,42 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:1">

--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="157">
   <si>
     <t>姓名</t>
   </si>
@@ -57,6 +57,9 @@
     <t>声音声音</t>
   </si>
   <si>
+    <t>江乐萱</t>
+  </si>
+  <si>
     <t>林芷琪</t>
   </si>
   <si>
@@ -87,7 +90,7 @@
     <t>祥懿又是你、午餐（芹菜炒肉、土豆丝、秋葵、番茄酱）课间吃饭、画画、捏/咬/打人、炫耀、演讲、喵喵姐</t>
   </si>
   <si>
-    <t>萌、上课吃东西</t>
+    <t>萌、上课吃东西、作业没写说没带、宣泄</t>
   </si>
   <si>
     <t>林钰颖</t>
@@ -111,6 +114,9 @@
     <t>郑永泽</t>
   </si>
   <si>
+    <t>阮贞铭（眼光）</t>
+  </si>
+  <si>
     <t>郑致辰</t>
   </si>
   <si>
@@ -354,7 +360,7 @@
     <t>小测（CTMO）、作业（抄几默几、积累本、AB本、订正）、one by one、笔记（活页、不要换笔、一课一页）、课前带读、作文本/草稿本/小绿（粉、黄、红）/预习、抄作业本、手机管理、做题标记、羽毛球、一人一包、学习小组、巡课、3条红领巾、AI视频</t>
   </si>
   <si>
-    <t>请假13个工作日</t>
+    <t>请假13个工作日（作业减、早读乱）、投屏打字</t>
   </si>
   <si>
     <t>政1</t>
@@ -372,7 +378,7 @@
     <t>政3</t>
   </si>
   <si>
-    <t>啧</t>
+    <t>啧+手势，对不对</t>
   </si>
   <si>
     <t>史1</t>
@@ -492,7 +498,7 @@
     <t>五子棋、笔</t>
   </si>
   <si>
-    <t>水瓶</t>
+    <t>水瓶、炸弹脚</t>
   </si>
 </sst>
 </file>
@@ -1593,276 +1599,282 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:3">
       <c r="A2" s="13" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>8</v>
       </c>
+      <c r="C2" s="10" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" ht="52" spans="1:4">
       <c r="A7" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" ht="26" spans="1:3">
       <c r="A20" s="13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" ht="39" spans="1:3">
       <c r="A21" s="13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" ht="26" spans="1:2">
       <c r="A23" s="13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" ht="39" spans="1:3">
       <c r="A24" s="13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" ht="78" spans="1:4">
       <c r="A28" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="13" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37" ht="26" spans="1:4">
       <c r="A37" s="13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C38" s="14"/>
       <c r="D38" s="14"/>
@@ -1872,110 +1884,110 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" ht="26" spans="1:3">
       <c r="A41" s="13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" ht="26" spans="1:2">
       <c r="A44" s="13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="13" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="50" ht="52" spans="1:3">
       <c r="A50" s="13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="52" ht="26" spans="1:3">
       <c r="A52" s="13" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="53" ht="26" spans="1:7">
       <c r="A53" s="9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D53" s="14"/>
       <c r="E53" s="14"/>
@@ -1984,13 +1996,13 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D54" s="14"/>
       <c r="E54" s="14"/>
@@ -1999,41 +2011,41 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
       <c r="D55" s="10" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="56" ht="52" spans="1:3">
       <c r="A56" s="9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C56" s="7"/>
     </row>
     <row r="57" ht="117" spans="1:4">
       <c r="A57" s="9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C57" s="7"/>
       <c r="D57" s="10" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C58" s="14"/>
       <c r="D58" s="14"/>
@@ -2043,11 +2055,11 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B59" s="14"/>
       <c r="C59" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D59" s="14"/>
       <c r="E59" s="14"/>
@@ -2056,20 +2068,20 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B60" s="14"/>
       <c r="C60" s="14"/>
       <c r="D60" s="10" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C61" s="7"/>
       <c r="D61" s="14"/>
@@ -2079,20 +2091,20 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B62" s="14"/>
       <c r="C62" s="14"/>
     </row>
     <row r="63" ht="26" spans="1:7">
       <c r="A63" s="9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D63" s="14"/>
       <c r="E63" s="14"/>
@@ -2101,20 +2113,20 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="9" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
       <c r="D64" s="10" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="65" ht="26" spans="1:7">
       <c r="A65" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C65" s="14"/>
       <c r="D65" s="14"/>
@@ -2124,11 +2136,11 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B66" s="14"/>
       <c r="C66" s="10" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D66" s="14"/>
       <c r="E66" s="14"/>
@@ -2137,36 +2149,36 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="9" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
       <c r="D68" s="10" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="9" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C69" s="7"/>
     </row>
     <row r="70" ht="26" spans="1:7">
       <c r="A70" s="9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C70" s="7"/>
       <c r="D70" s="14"/>
@@ -2176,20 +2188,20 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="9" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B71" s="14"/>
       <c r="C71" s="14"/>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="9" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D72" s="14"/>
       <c r="E72" s="14"/>
@@ -2198,11 +2210,11 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B73" s="14"/>
       <c r="C73" s="10" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D73" s="14"/>
       <c r="E73" s="14"/>
@@ -2211,12 +2223,12 @@
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D75" s="14"/>
       <c r="E75" s="14"/>
@@ -2225,17 +2237,17 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="9" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B76" s="14"/>
       <c r="C76" s="14"/>
       <c r="D76" s="10" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="9" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B77" s="7"/>
       <c r="C77" s="7"/>
@@ -2308,42 +2320,42 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:1">

--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="160">
   <si>
     <t>姓名</t>
   </si>
@@ -66,6 +66,9 @@
     <t>猴、郑致辰</t>
   </si>
   <si>
+    <t>带菜（给孔保管）</t>
+  </si>
+  <si>
     <t>郭沁诗</t>
   </si>
   <si>
@@ -90,7 +93,7 @@
     <t>祥懿又是你、午餐（芹菜炒肉、土豆丝、秋葵、番茄酱）课间吃饭、画画、捏/咬/打人、炫耀、演讲、喵喵姐</t>
   </si>
   <si>
-    <t>萌、上课吃东西、作业没写说没带、宣泄</t>
+    <t>萌、上课吃东西、作业没写说没带、宣泄、睡觉（低头/点头）</t>
   </si>
   <si>
     <t>林钰颖</t>
@@ -198,13 +201,13 @@
     <t>黄恩亚</t>
   </si>
   <si>
-    <t>体香、生殖系统、迟到、午餐、跑步、字迹、腿伸过道、基督教、恩典时期的亚当、近代史、头发（捂头）、私藏卷子、拉小提琴、脏话、叫人、外八</t>
+    <t>体香、生殖系统、迟到、午餐、跑步、字迹、腿伸过道、基督教、恩典时期的亚当、近代史、头发（捂头）、私藏卷子、拉小提琴、脏话、叫人、外八、开创黄话开端（塑料袋像避孕套）</t>
   </si>
   <si>
     <t>推北师大、磨鞋、获奖时笑、菜被人吃、秀鼓包</t>
   </si>
   <si>
-    <t>朋友圈（模糊图片）、粗笔写字</t>
+    <t>朋友圈（模糊图片）、马克笔写字</t>
   </si>
   <si>
     <t>林承钰</t>
@@ -499,6 +502,12 @@
   </si>
   <si>
     <t>水瓶、炸弹脚</t>
+  </si>
+  <si>
+    <t>金叵罗</t>
+  </si>
+  <si>
+    <t>睿昕咖啡</t>
   </si>
 </sst>
 </file>
@@ -1610,271 +1619,274 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>11</v>
       </c>
+      <c r="D3" s="10" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" ht="52" spans="1:4">
       <c r="A7" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" ht="26" spans="1:3">
       <c r="A20" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" ht="39" spans="1:3">
       <c r="A21" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" ht="26" spans="1:2">
       <c r="A23" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" ht="39" spans="1:3">
       <c r="A24" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="28" ht="78" spans="1:4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" ht="91" spans="1:4">
       <c r="A28" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37" ht="26" spans="1:4">
       <c r="A37" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C38" s="14"/>
       <c r="D38" s="14"/>
@@ -1884,110 +1896,110 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" ht="26" spans="1:3">
       <c r="A41" s="13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="44" ht="26" spans="1:2">
       <c r="A44" s="13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="50" ht="52" spans="1:3">
       <c r="A50" s="13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="52" ht="26" spans="1:3">
       <c r="A52" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="53" ht="26" spans="1:7">
       <c r="A53" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D53" s="14"/>
       <c r="E53" s="14"/>
@@ -1996,13 +2008,13 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D54" s="14"/>
       <c r="E54" s="14"/>
@@ -2011,41 +2023,41 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
       <c r="D55" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="56" ht="52" spans="1:3">
       <c r="A56" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C56" s="7"/>
     </row>
     <row r="57" ht="117" spans="1:4">
       <c r="A57" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C57" s="7"/>
       <c r="D57" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C58" s="14"/>
       <c r="D58" s="14"/>
@@ -2055,11 +2067,11 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B59" s="14"/>
       <c r="C59" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D59" s="14"/>
       <c r="E59" s="14"/>
@@ -2068,20 +2080,20 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B60" s="14"/>
       <c r="C60" s="14"/>
       <c r="D60" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C61" s="7"/>
       <c r="D61" s="14"/>
@@ -2091,20 +2103,20 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B62" s="14"/>
       <c r="C62" s="14"/>
     </row>
     <row r="63" ht="26" spans="1:7">
       <c r="A63" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D63" s="14"/>
       <c r="E63" s="14"/>
@@ -2113,20 +2125,20 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
       <c r="D64" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="65" ht="26" spans="1:7">
       <c r="A65" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C65" s="14"/>
       <c r="D65" s="14"/>
@@ -2136,11 +2148,11 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B66" s="14"/>
       <c r="C66" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D66" s="14"/>
       <c r="E66" s="14"/>
@@ -2149,36 +2161,36 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
       <c r="D68" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C69" s="7"/>
     </row>
     <row r="70" ht="26" spans="1:7">
       <c r="A70" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C70" s="7"/>
       <c r="D70" s="14"/>
@@ -2188,20 +2200,20 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B71" s="14"/>
       <c r="C71" s="14"/>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D72" s="14"/>
       <c r="E72" s="14"/>
@@ -2210,11 +2222,11 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B73" s="14"/>
       <c r="C73" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D73" s="14"/>
       <c r="E73" s="14"/>
@@ -2223,12 +2235,12 @@
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D75" s="14"/>
       <c r="E75" s="14"/>
@@ -2237,17 +2249,17 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B76" s="14"/>
       <c r="C76" s="14"/>
       <c r="D76" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B77" s="7"/>
       <c r="C77" s="7"/>
@@ -2320,46 +2332,52 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="6"/>
+      <c r="B7" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="6"/>

--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -93,7 +93,7 @@
     <t>祥懿又是你、午餐（芹菜炒肉、土豆丝、秋葵、番茄酱）课间吃饭、画画、捏/咬/打人、炫耀、演讲、喵喵姐</t>
   </si>
   <si>
-    <t>萌、上课吃东西、作业没写说没带、宣泄、睡觉（低头/点头）</t>
+    <t>萌、上课吃东西、作业没写说没带、宣泄、睡觉（低头/点头）、带读（一，起）</t>
   </si>
   <si>
     <t>林钰颖</t>

--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -348,7 +348,7 @@
     <t>语3</t>
   </si>
   <si>
-    <t>微信窗口藏下面、C读“系”</t>
+    <t>微信窗口藏下面、C读“系”、我的天哪</t>
   </si>
   <si>
     <t>数1</t>
@@ -2021,7 +2021,7 @@
       <c r="F54" s="14"/>
       <c r="G54" s="14"/>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" ht="26" spans="1:4">
       <c r="A55" s="9" t="s">
         <v>105</v>
       </c>

--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -93,7 +93,7 @@
     <t>祥懿又是你、午餐（芹菜炒肉、土豆丝、秋葵、番茄酱）课间吃饭、画画、捏/咬/打人、炫耀、演讲、喵喵姐</t>
   </si>
   <si>
-    <t>萌、上课吃东西、作业没写说没带、宣泄、睡觉（低头/点头）、带读（一，起）</t>
+    <t>萌、上课吃东西、作业没写说没带、宣泄、睡觉（低头/点头）、带读（一，起）、水杯倒</t>
   </si>
   <si>
     <t>林钰颖</t>
@@ -129,16 +129,16 @@
     <t>陈婕</t>
   </si>
   <si>
+    <t>江允儿</t>
+  </si>
+  <si>
     <t>柠檬水</t>
   </si>
   <si>
-    <t>江允儿</t>
-  </si>
-  <si>
     <t>徐嘉明</t>
   </si>
   <si>
-    <t>物理学家、发明家</t>
+    <t>物理学家、发明家、列夫托尔斯泰</t>
   </si>
   <si>
     <t>俞昕辰</t>
@@ -207,7 +207,7 @@
     <t>推北师大、磨鞋、获奖时笑、菜被人吃、秀鼓包</t>
   </si>
   <si>
-    <t>朋友圈（模糊图片）、马克笔写字</t>
+    <t>朋友圈（模糊图片）、马克笔写字、挠痒动作</t>
   </si>
   <si>
     <t>林承钰</t>
@@ -315,7 +315,7 @@
     <t>李梦妍</t>
   </si>
   <si>
-    <t>狡猾、雕版印刷、抢东西、画粑粑、曾好、梳子/镜子/护手霜/增高鞋、梗（橙绿、盆地、六棱柱、考试成绩、大冒险</t>
+    <t>狡猾、雕版印刷、抢东西、画粑粑、曾好、梳子/镜子/护手霜/增高鞋、梗（橙绿、盆地、六棱柱、考试成绩）、大冒险、傻子吧</t>
   </si>
   <si>
     <t>曹世强</t>
@@ -348,7 +348,7 @@
     <t>语3</t>
   </si>
   <si>
-    <t>微信窗口藏下面、C读“系”、我的天哪</t>
+    <t>微信窗口藏下面、C读“系”、我的天哪、周末作业（周记、好段、读书笔记）</t>
   </si>
   <si>
     <t>数1</t>
@@ -1709,20 +1709,20 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:1">
       <c r="A15" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="10" t="s">
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="13" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="13" t="s">
+      <c r="C16" s="10" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" ht="26" spans="1:3">
       <c r="A17" s="13" t="s">
         <v>35</v>
       </c>
@@ -1970,7 +1970,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="50" ht="52" spans="1:3">
+    <row r="50" ht="65" spans="1:3">
       <c r="A50" s="13" t="s">
         <v>94</v>
       </c>
@@ -2021,7 +2021,7 @@
       <c r="F54" s="14"/>
       <c r="G54" s="14"/>
     </row>
-    <row r="55" ht="26" spans="1:4">
+    <row r="55" ht="39" spans="1:4">
       <c r="A55" s="9" t="s">
         <v>105</v>
       </c>

--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="161">
   <si>
     <t>姓名</t>
   </si>
@@ -93,7 +93,7 @@
     <t>祥懿又是你、午餐（芹菜炒肉、土豆丝、秋葵、番茄酱）课间吃饭、画画、捏/咬/打人、炫耀、演讲、喵喵姐</t>
   </si>
   <si>
-    <t>萌、上课吃东西、作业没写说没带、宣泄、睡觉（低头/点头）、带读（一，起）、水杯倒</t>
+    <t>萌、上课吃东西、作业没写说没带、宣泄、睡觉（低头/点头）、带读（一，起）、水杯倒、尼玛的、东西被陆梓豪偷吃</t>
   </si>
   <si>
     <t>林钰颖</t>
@@ -163,6 +163,9 @@
   </si>
   <si>
     <t>爆胎</t>
+  </si>
+  <si>
+    <t>踩桌子通行</t>
   </si>
   <si>
     <t>张桢烨</t>
@@ -1651,7 +1654,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" ht="52" spans="1:4">
+    <row r="7" ht="65" spans="1:4">
       <c r="A7" s="13" t="s">
         <v>18</v>
       </c>
@@ -1751,7 +1754,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" ht="39" spans="1:3">
+    <row r="21" ht="39" spans="1:4">
       <c r="A21" s="13" t="s">
         <v>42</v>
       </c>
@@ -1761,132 +1764,135 @@
       <c r="C21" s="10" t="s">
         <v>44</v>
       </c>
+      <c r="D21" s="10" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" ht="26" spans="1:2">
       <c r="A23" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" ht="39" spans="1:3">
       <c r="A24" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28" ht="91" spans="1:4">
       <c r="A28" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="37" ht="26" spans="1:4">
       <c r="A37" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C38" s="14"/>
       <c r="D38" s="14"/>
@@ -1896,110 +1902,110 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41" ht="26" spans="1:3">
       <c r="A41" s="13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="44" ht="26" spans="1:2">
       <c r="A44" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="50" ht="65" spans="1:3">
       <c r="A50" s="13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="52" ht="26" spans="1:3">
       <c r="A52" s="13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53" ht="26" spans="1:7">
       <c r="A53" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D53" s="14"/>
       <c r="E53" s="14"/>
@@ -2008,13 +2014,13 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D54" s="14"/>
       <c r="E54" s="14"/>
@@ -2023,41 +2029,41 @@
     </row>
     <row r="55" ht="39" spans="1:4">
       <c r="A55" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
       <c r="D55" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="56" ht="52" spans="1:3">
       <c r="A56" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C56" s="7"/>
     </row>
     <row r="57" ht="117" spans="1:4">
       <c r="A57" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C57" s="7"/>
       <c r="D57" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C58" s="14"/>
       <c r="D58" s="14"/>
@@ -2067,11 +2073,11 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B59" s="14"/>
       <c r="C59" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D59" s="14"/>
       <c r="E59" s="14"/>
@@ -2080,20 +2086,20 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B60" s="14"/>
       <c r="C60" s="14"/>
       <c r="D60" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C61" s="7"/>
       <c r="D61" s="14"/>
@@ -2103,20 +2109,20 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B62" s="14"/>
       <c r="C62" s="14"/>
     </row>
     <row r="63" ht="26" spans="1:7">
       <c r="A63" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D63" s="14"/>
       <c r="E63" s="14"/>
@@ -2125,20 +2131,20 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
       <c r="D64" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="65" ht="26" spans="1:7">
       <c r="A65" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C65" s="14"/>
       <c r="D65" s="14"/>
@@ -2148,11 +2154,11 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B66" s="14"/>
       <c r="C66" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D66" s="14"/>
       <c r="E66" s="14"/>
@@ -2161,36 +2167,36 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
       <c r="D68" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C69" s="7"/>
     </row>
     <row r="70" ht="26" spans="1:7">
       <c r="A70" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C70" s="7"/>
       <c r="D70" s="14"/>
@@ -2200,20 +2206,20 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B71" s="14"/>
       <c r="C71" s="14"/>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D72" s="14"/>
       <c r="E72" s="14"/>
@@ -2222,11 +2228,11 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B73" s="14"/>
       <c r="C73" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D73" s="14"/>
       <c r="E73" s="14"/>
@@ -2235,12 +2241,12 @@
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D75" s="14"/>
       <c r="E75" s="14"/>
@@ -2249,17 +2255,17 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B76" s="14"/>
       <c r="C76" s="14"/>
       <c r="D76" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B77" s="7"/>
       <c r="C77" s="7"/>
@@ -2332,51 +2338,51 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="6"/>
       <c r="B7" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8" spans="1:1">

--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="165">
   <si>
     <t>姓名</t>
   </si>
@@ -87,7 +87,7 @@
     <t>孔祥懿</t>
   </si>
   <si>
-    <t>济南</t>
+    <t>济南、2个包</t>
   </si>
   <si>
     <t>祥懿又是你、午餐（芹菜炒肉、土豆丝、秋葵、番茄酱）课间吃饭、画画、捏/咬/打人、炫耀、演讲、喵喵姐</t>
@@ -477,6 +477,12 @@
     <t>段长</t>
   </si>
   <si>
+    <t>集体</t>
+  </si>
+  <si>
+    <t>F5（画黑板报而认识，成员：孔、雨、允、诗、槿）</t>
+  </si>
+  <si>
     <t>教室</t>
   </si>
   <si>
@@ -492,6 +498,9 @@
     <t>环境</t>
   </si>
   <si>
+    <t>换桌子</t>
+  </si>
+  <si>
     <t>午餐</t>
   </si>
   <si>
@@ -507,10 +516,13 @@
     <t>水瓶、炸弹脚</t>
   </si>
   <si>
+    <t>梗</t>
+  </si>
+  <si>
     <t>金叵罗</t>
   </si>
   <si>
-    <t>睿昕咖啡</t>
+    <t>睿昕咖啡、谢谢爷爷</t>
   </si>
 </sst>
 </file>
@@ -692,7 +704,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -738,6 +750,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1075,7 +1093,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1099,16 +1117,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1117,92 +1135,92 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1250,6 +1268,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1581,7 +1602,7 @@
   <sheetPr>
     <tabColor theme="7" tint="0.8"/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="7.59090909090909" style="9" customWidth="1"/>
@@ -2269,6 +2290,14 @@
       </c>
       <c r="B77" s="7"/>
       <c r="C77" s="7"/>
+    </row>
+    <row r="78" ht="26" spans="1:2">
+      <c r="A78" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B78" s="10" t="s">
+        <v>150</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -2338,51 +2367,56 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="6" t="s">
-        <v>153</v>
+        <v>155</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="6" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="6" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="6"/>
+      <c r="A7" s="6" t="s">
+        <v>162</v>
+      </c>
       <c r="B7" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:1">

--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="学生、老师" sheetId="5" r:id="rId1"/>
     <sheet name="9班、四十中" sheetId="13" r:id="rId2"/>
+    <sheet name="佐证日常典型事例" sheetId="14" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="178">
   <si>
     <t>姓名</t>
   </si>
@@ -66,7 +67,7 @@
     <t>猴、郑致辰</t>
   </si>
   <si>
-    <t>带菜（给孔保管）</t>
+    <t>带菜（给孔保管）、小测降等级</t>
   </si>
   <si>
     <t>郭沁诗</t>
@@ -93,7 +94,7 @@
     <t>祥懿又是你、午餐（芹菜炒肉、土豆丝、秋葵、番茄酱）课间吃饭、画画、捏/咬/打人、炫耀、演讲、喵喵姐</t>
   </si>
   <si>
-    <t>萌、上课吃东西、作业没写说没带、宣泄、睡觉（低头/点头）、带读（一，起）、水杯倒、尼玛的、东西被陆梓豪偷吃</t>
+    <t>萌、上课吃东西、作业没写说没带、宣泄、睡觉（低头/点头）、带读（一，起）、水杯倒（不盖盖）、尼玛的、东西被陆梓豪偷吃、排队时讲话、我又……上了、我不行了……</t>
   </si>
   <si>
     <t>林钰颖</t>
@@ -210,7 +211,7 @@
     <t>推北师大、磨鞋、获奖时笑、菜被人吃、秀鼓包</t>
   </si>
   <si>
-    <t>朋友圈（模糊图片）、马克笔写字、挠痒动作</t>
+    <t>朋友圈（模糊图片、装）、马克笔写字、挠痒动作</t>
   </si>
   <si>
     <t>林承钰</t>
@@ -300,6 +301,9 @@
     <t>陆梓豪</t>
   </si>
   <si>
+    <t>中午拿矿泉水</t>
+  </si>
+  <si>
     <t>钱尚恩</t>
   </si>
   <si>
@@ -318,7 +322,7 @@
     <t>李梦妍</t>
   </si>
   <si>
-    <t>狡猾、雕版印刷、抢东西、画粑粑、曾好、梳子/镜子/护手霜/增高鞋、梗（橙绿、盆地、六棱柱、考试成绩）、大冒险、傻子吧</t>
+    <t>狡猾、雕版印刷、抢东西、画粑粑、曾好、梳子/镜子/护手霜/增高鞋、梗（橙绿、盆地、六棱柱、考试成绩、set bus come）、大冒险、傻子吧</t>
   </si>
   <si>
     <t>曹世强</t>
@@ -384,7 +388,7 @@
     <t>政3</t>
   </si>
   <si>
-    <t>啧+手势，对不对</t>
+    <t>啧+手势，对不对、重音</t>
   </si>
   <si>
     <t>史1</t>
@@ -486,13 +490,7 @@
     <t>教室</t>
   </si>
   <si>
-    <t>空调</t>
-  </si>
-  <si>
-    <t>校规</t>
-  </si>
-  <si>
-    <t>允许女生留长发</t>
+    <t>空调没冷气、允许女生留长发、活动课项目变少</t>
   </si>
   <si>
     <t>环境</t>
@@ -507,7 +505,7 @@
     <t>么么脆鸡排、密封条、虫卵</t>
   </si>
   <si>
-    <t>热门游戏</t>
+    <t>热门</t>
   </si>
   <si>
     <t>五子棋、笔</t>
@@ -523,6 +521,48 @@
   </si>
   <si>
     <t>睿昕咖啡、谢谢爷爷</t>
+  </si>
+  <si>
+    <t>日常</t>
+  </si>
+  <si>
+    <t>日期</t>
+  </si>
+  <si>
+    <t>事件</t>
+  </si>
+  <si>
+    <t>八上强制打印校本</t>
+  </si>
+  <si>
+    <t>八上10.14</t>
+  </si>
+  <si>
+    <t>没有校本——赶快去打印</t>
+  </si>
+  <si>
+    <t>“自愿”订校服</t>
+  </si>
+  <si>
+    <t>八上10.13</t>
+  </si>
+  <si>
+    <t>回执不同意——问家长，修改为同意</t>
+  </si>
+  <si>
+    <t>孔祥懿没写说没带</t>
+  </si>
+  <si>
+    <t>早读课抄物理作业，下午物理书没带，说：“作业夹在书里了”</t>
+  </si>
+  <si>
+    <t>男生和女生待遇</t>
+  </si>
+  <si>
+    <t>八上10.11</t>
+  </si>
+  <si>
+    <t>体锻跑操，①男生“还没跑完”女生“坚持住，时间还没到”②刘：男生讲话，女生安静休息；男生要不要跟女生跑③男生（3个班女生）留下跑3（4）圈</t>
   </si>
 </sst>
 </file>
@@ -535,10 +575,15 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="黑体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1072,204 +1117,225 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1605,698 +1671,701 @@
   <dimension ref="A1:G78"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="7.59090909090909" style="9" customWidth="1"/>
-    <col min="2" max="7" width="25.8727272727273" style="10" customWidth="1"/>
+    <col min="1" max="1" width="7.59090909090909" style="16" customWidth="1"/>
+    <col min="2" max="7" width="25.8727272727273" style="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="8" customFormat="1" spans="1:7">
-      <c r="A1" s="11" t="s">
+    <row r="1" s="15" customFormat="1" spans="1:7">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="19" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="17" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="13" t="s">
+    <row r="3" ht="26" spans="1:4">
+      <c r="A3" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="17" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="20" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="17" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="17" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" ht="65" spans="1:4">
-      <c r="A7" s="13" t="s">
+    <row r="7" ht="78" spans="1:4">
+      <c r="A7" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="17" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="20" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="20" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="17" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="20" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="20" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="17" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="17" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="20" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="17" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="17" ht="26" spans="1:3">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="17" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="20" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="20" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="20" ht="26" spans="1:3">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="17" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="21" ht="39" spans="1:4">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="17" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="20" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="23" ht="26" spans="1:2">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="17" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="24" ht="39" spans="1:3">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="17" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="20" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="20" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="17" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="28" ht="91" spans="1:4">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="17" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="20" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="13" t="s">
+      <c r="A30" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="17" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="20" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="13" t="s">
+      <c r="A32" s="20" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="13" t="s">
+      <c r="A33" s="20" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="13" t="s">
+      <c r="A34" s="20" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="13" t="s">
+      <c r="A35" s="20" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="13" t="s">
+      <c r="A36" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="B36" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="37" ht="26" spans="1:4">
-      <c r="A37" s="13" t="s">
+      <c r="A37" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="C37" s="10" t="s">
+      <c r="C37" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D37" s="10" t="s">
+      <c r="D37" s="17" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="13" t="s">
+      <c r="A38" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B38" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="13" t="s">
+      <c r="A39" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="C39" s="10" t="s">
+      <c r="C39" s="17" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="13" t="s">
+      <c r="A40" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="B40" s="10" t="s">
+      <c r="B40" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="C40" s="10" t="s">
+      <c r="C40" s="17" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="41" ht="26" spans="1:3">
-      <c r="A41" s="13" t="s">
+      <c r="A41" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="C41" s="10" t="s">
+      <c r="C41" s="17" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="13" t="s">
+      <c r="A42" s="20" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="13" t="s">
+      <c r="A43" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="B43" s="10" t="s">
+      <c r="B43" s="17" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="44" ht="26" spans="1:2">
-      <c r="A44" s="13" t="s">
+      <c r="A44" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B44" s="17" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="13" t="s">
+    <row r="45" spans="1:4">
+      <c r="A45" s="20" t="s">
         <v>89</v>
       </c>
+      <c r="D45" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="13" t="s">
-        <v>90</v>
+      <c r="A46" s="20" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="13" t="s">
-        <v>91</v>
+      <c r="A47" s="20" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="C48" s="10" t="s">
+      <c r="A48" s="20" t="s">
         <v>93</v>
       </c>
+      <c r="C48" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="13" t="s">
-        <v>94</v>
+      <c r="A49" s="20" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="50" ht="65" spans="1:3">
-      <c r="A50" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="C50" s="10" t="s">
+      <c r="A50" s="20" t="s">
         <v>96</v>
       </c>
+      <c r="C50" s="17" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="13" t="s">
-        <v>97</v>
+      <c r="A51" s="20" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="52" ht="26" spans="1:3">
-      <c r="A52" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="B52" s="10" t="s">
+      <c r="A52" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="C52" s="10" t="s">
+      <c r="B52" s="17" t="s">
         <v>100</v>
       </c>
+      <c r="C52" s="17" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="53" ht="26" spans="1:7">
-      <c r="A53" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="B53" s="10" t="s">
+      <c r="A53" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
+      <c r="B53" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="D53" s="21"/>
+      <c r="E53" s="21"/>
+      <c r="F53" s="21"/>
+      <c r="G53" s="21"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="B54" s="10" t="s">
+      <c r="A54" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="C54" s="10" t="s">
+      <c r="B54" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
+      <c r="C54" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="D54" s="21"/>
+      <c r="E54" s="21"/>
+      <c r="F54" s="21"/>
+      <c r="G54" s="21"/>
     </row>
     <row r="55" ht="39" spans="1:4">
-      <c r="A55" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="10" t="s">
+      <c r="A55" s="16" t="s">
         <v>107</v>
       </c>
+      <c r="B55" s="21"/>
+      <c r="C55" s="21"/>
+      <c r="D55" s="17" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="56" ht="52" spans="1:3">
-      <c r="A56" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="B56" s="7" t="s">
+      <c r="A56" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="C56" s="7"/>
+      <c r="B56" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="C56" s="14"/>
     </row>
     <row r="57" ht="117" spans="1:4">
-      <c r="A57" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="B57" s="7" t="s">
+      <c r="A57" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="C57" s="7"/>
-      <c r="D57" s="10" t="s">
+      <c r="B57" s="14" t="s">
         <v>112</v>
       </c>
+      <c r="C57" s="14"/>
+      <c r="D57" s="17" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="B58" s="10" t="s">
+      <c r="A58" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
+      <c r="B58" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="C58" s="21"/>
+      <c r="D58" s="21"/>
+      <c r="E58" s="21"/>
+      <c r="F58" s="21"/>
+      <c r="G58" s="21"/>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="B59" s="14"/>
-      <c r="C59" s="10" t="s">
+      <c r="A59" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
+      <c r="B59" s="21"/>
+      <c r="C59" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="D59" s="21"/>
+      <c r="E59" s="21"/>
+      <c r="F59" s="21"/>
+      <c r="G59" s="21"/>
     </row>
     <row r="60" spans="1:4">
-      <c r="A60" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="10" t="s">
+      <c r="A60" s="16" t="s">
         <v>118</v>
       </c>
+      <c r="B60" s="21"/>
+      <c r="C60" s="21"/>
+      <c r="D60" s="17" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="B61" s="7" t="s">
+      <c r="A61" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="C61" s="7"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
+      <c r="B61" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C61" s="14"/>
+      <c r="D61" s="21"/>
+      <c r="E61" s="21"/>
+      <c r="F61" s="21"/>
+      <c r="G61" s="21"/>
     </row>
     <row r="62" spans="1:3">
-      <c r="A62" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
+      <c r="A62" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="B62" s="21"/>
+      <c r="C62" s="21"/>
     </row>
     <row r="63" ht="26" spans="1:7">
-      <c r="A63" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="B63" s="7" t="s">
+      <c r="A63" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="C63" s="7" t="s">
+      <c r="B63" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
+      <c r="C63" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="D63" s="21"/>
+      <c r="E63" s="21"/>
+      <c r="F63" s="21"/>
+      <c r="G63" s="21"/>
     </row>
     <row r="64" spans="1:4">
-      <c r="A64" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="10" t="s">
+      <c r="A64" s="16" t="s">
         <v>126</v>
       </c>
+      <c r="B64" s="21"/>
+      <c r="C64" s="21"/>
+      <c r="D64" s="17" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="65" ht="26" spans="1:7">
-      <c r="A65" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="B65" s="15" t="s">
+      <c r="A65" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
+      <c r="B65" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="C65" s="21"/>
+      <c r="D65" s="21"/>
+      <c r="E65" s="21"/>
+      <c r="F65" s="21"/>
+      <c r="G65" s="21"/>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="B66" s="14"/>
-      <c r="C66" s="10" t="s">
+      <c r="A66" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
+      <c r="B66" s="21"/>
+      <c r="C66" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="D66" s="21"/>
+      <c r="E66" s="21"/>
+      <c r="F66" s="21"/>
+      <c r="G66" s="21"/>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
+      <c r="A67" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="B67" s="21"/>
+      <c r="C67" s="21"/>
     </row>
     <row r="68" spans="1:4">
-      <c r="A68" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="10" t="s">
+      <c r="A68" s="16" t="s">
         <v>133</v>
       </c>
+      <c r="B68" s="21"/>
+      <c r="C68" s="21"/>
+      <c r="D68" s="17" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="69" spans="1:3">
-      <c r="A69" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="B69" s="7" t="s">
+      <c r="A69" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="C69" s="7"/>
+      <c r="B69" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="C69" s="14"/>
     </row>
     <row r="70" ht="26" spans="1:7">
-      <c r="A70" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="B70" s="7" t="s">
+      <c r="A70" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
+      <c r="B70" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="C70" s="14"/>
+      <c r="D70" s="21"/>
+      <c r="E70" s="21"/>
+      <c r="F70" s="21"/>
+      <c r="G70" s="21"/>
     </row>
     <row r="71" spans="1:3">
-      <c r="A71" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="B71" s="14"/>
-      <c r="C71" s="14"/>
+      <c r="A71" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="B71" s="21"/>
+      <c r="C71" s="21"/>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="B72" s="10" t="s">
+      <c r="A72" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="C72" s="10" t="s">
+      <c r="B72" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
+      <c r="C72" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="D72" s="21"/>
+      <c r="E72" s="21"/>
+      <c r="F72" s="21"/>
+      <c r="G72" s="21"/>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="B73" s="14"/>
-      <c r="C73" s="10" t="s">
+      <c r="A73" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
+      <c r="B73" s="21"/>
+      <c r="C73" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="D73" s="21"/>
+      <c r="E73" s="21"/>
+      <c r="F73" s="21"/>
+      <c r="G73" s="21"/>
     </row>
     <row r="74" spans="1:1">
-      <c r="A74" s="9" t="s">
-        <v>144</v>
+      <c r="A74" s="16" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
-      <c r="G75" s="14"/>
+      <c r="A75" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D75" s="21"/>
+      <c r="E75" s="21"/>
+      <c r="F75" s="21"/>
+      <c r="G75" s="21"/>
     </row>
     <row r="76" spans="1:4">
-      <c r="A76" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="B76" s="14"/>
-      <c r="C76" s="14"/>
-      <c r="D76" s="10" t="s">
+      <c r="A76" s="16" t="s">
         <v>147</v>
       </c>
+      <c r="B76" s="21"/>
+      <c r="C76" s="21"/>
+      <c r="D76" s="17" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="77" spans="1:3">
-      <c r="A77" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="B77" s="7"/>
-      <c r="C77" s="7"/>
+      <c r="A77" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B77" s="14"/>
+      <c r="C77" s="14"/>
     </row>
     <row r="78" ht="26" spans="1:2">
-      <c r="A78" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="B78" s="10" t="s">
+      <c r="A78" s="23" t="s">
         <v>150</v>
+      </c>
+      <c r="B78" s="17" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -2336,235 +2405,305 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="6.64545454545455" style="1" customWidth="1"/>
-    <col min="2" max="7" width="16.4909090909091" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="8.72727272727273" style="3"/>
+    <col min="1" max="1" width="6.64545454545455" style="6" customWidth="1"/>
+    <col min="2" max="7" width="16.4909090909091" style="7" customWidth="1"/>
+    <col min="8" max="16384" width="8.72727272727273" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="4"/>
-      <c r="B1" s="5" t="s">
+      <c r="A1" s="9"/>
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="D2" s="2" t="s">
+    <row r="2" s="5" customFormat="1" ht="39" spans="1:7">
+      <c r="A2" s="11" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="6" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="13" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>155</v>
       </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="13"/>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="13"/>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="13"/>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="13"/>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="13"/>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="13"/>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="13"/>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="13"/>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="13"/>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="13"/>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="13"/>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="13"/>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="13"/>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="13"/>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="13"/>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="13"/>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="13"/>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="13"/>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="13"/>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="13"/>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="13"/>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="13"/>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="13"/>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="13"/>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="13"/>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="13"/>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="13"/>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="13"/>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="13"/>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="13"/>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="13"/>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="13"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="13"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="13"/>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="13"/>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="13"/>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="13"/>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="13"/>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="13"/>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="13"/>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="13"/>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="13"/>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="13"/>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="13"/>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="13"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="35.1818181818182" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.9090909090909" style="1" customWidth="1"/>
+    <col min="3" max="3" width="50.0909090909091" style="2" customWidth="1"/>
+    <col min="4" max="16384" width="8.72727272727273" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="4" ht="28" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>171</v>
+      </c>
       <c r="C4" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="6"/>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="6"/>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="6"/>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="6"/>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="6"/>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="6"/>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="6"/>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="6"/>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="6"/>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="6"/>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="6"/>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="6"/>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="6"/>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="6"/>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="6"/>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="6"/>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="6"/>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="6"/>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="6"/>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="6"/>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="6"/>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="6"/>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="6"/>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="6"/>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="6"/>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="6"/>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="6"/>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="6"/>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="6"/>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="6"/>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="6"/>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="6"/>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40" s="6"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="6"/>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="6"/>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="6"/>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" s="6"/>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="6"/>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="6"/>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" s="6"/>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="6"/>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" s="6"/>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="6"/>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="6"/>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" s="6"/>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="5" ht="42" spans="1:3">
+      <c r="A5" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>177</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -361,7 +361,7 @@
     <t>数1</t>
   </si>
   <si>
-    <t>讲评作业（折名字/3、4组过道）、课件（熊熊疑惑、喜羊羊修花圃）、今天纪律差、笔记本拿出来</t>
+    <t>讲评作业（折名字/3、4组过道）、课件（熊熊疑惑、喜羊羊修花圃）、今天纪律差、笔记本拿出来、作业只改正面</t>
   </si>
   <si>
     <t>英1</t>
@@ -388,7 +388,7 @@
     <t>政3</t>
   </si>
   <si>
-    <t>啧+手势，对不对、重音</t>
+    <t>啧+手势，对不对、重音、预习复习、透明水杯，拿学生水杯、嘛</t>
   </si>
   <si>
     <t>史1</t>
@@ -1265,7 +1265,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1275,12 +1275,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1307,9 +1301,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1671,700 +1662,700 @@
   <dimension ref="A1:G78"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="7.59090909090909" style="16" customWidth="1"/>
-    <col min="2" max="7" width="25.8727272727273" style="17" customWidth="1"/>
+    <col min="1" max="1" width="7.59090909090909" style="13" customWidth="1"/>
+    <col min="2" max="7" width="25.8727272727273" style="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="15" customFormat="1" spans="1:7">
-      <c r="A1" s="18" t="s">
+    <row r="1" s="12" customFormat="1" spans="1:7">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="16" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="14" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" ht="26" spans="1:4">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="17" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="14" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" ht="78" spans="1:4">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="14" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="17" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="17" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="14" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="17" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="17" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="14" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="14" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="17" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="14" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="17" ht="26" spans="1:3">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="14" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="17" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="17" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="20" ht="26" spans="1:3">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="14" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="21" ht="39" spans="1:4">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="D21" s="17" t="s">
+      <c r="D21" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="17" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="23" ht="26" spans="1:2">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="14" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="24" ht="39" spans="1:3">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="14" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="17" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="17" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="20" t="s">
+      <c r="A27" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="C27" s="14" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="28" ht="91" spans="1:4">
-      <c r="A28" s="20" t="s">
+      <c r="A28" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="B28" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D28" s="17" t="s">
+      <c r="D28" s="14" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="20" t="s">
+      <c r="A29" s="17" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="20" t="s">
+      <c r="A30" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="B30" s="17" t="s">
+      <c r="B30" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C30" s="17" t="s">
+      <c r="C30" s="14" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="20" t="s">
+      <c r="A31" s="17" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="20" t="s">
+      <c r="A32" s="17" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="20" t="s">
+      <c r="A33" s="17" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="20" t="s">
+      <c r="A34" s="17" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="20" t="s">
+      <c r="A35" s="17" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="20" t="s">
+      <c r="A36" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="17" t="s">
+      <c r="B36" s="14" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="37" ht="26" spans="1:4">
-      <c r="A37" s="20" t="s">
+      <c r="A37" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="C37" s="17" t="s">
+      <c r="C37" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="D37" s="17" t="s">
+      <c r="D37" s="14" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="20" t="s">
+      <c r="A38" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="B38" s="17" t="s">
+      <c r="B38" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="C38" s="21"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
-      <c r="G38" s="21"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="20" t="s">
+      <c r="A39" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="C39" s="17" t="s">
+      <c r="C39" s="14" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="20" t="s">
+      <c r="A40" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="B40" s="17" t="s">
+      <c r="B40" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="C40" s="17" t="s">
+      <c r="C40" s="14" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="41" ht="26" spans="1:3">
-      <c r="A41" s="20" t="s">
+      <c r="A41" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="C41" s="17" t="s">
+      <c r="C41" s="14" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="20" t="s">
+      <c r="A42" s="17" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="20" t="s">
+      <c r="A43" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="B43" s="17" t="s">
+      <c r="B43" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="44" ht="26" spans="1:2">
-      <c r="A44" s="20" t="s">
+      <c r="A44" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="B44" s="17" t="s">
+      <c r="B44" s="14" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="20" t="s">
+      <c r="A45" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="D45" s="17" t="s">
+      <c r="D45" s="14" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="20" t="s">
+      <c r="A46" s="17" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="20" t="s">
+      <c r="A47" s="17" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="20" t="s">
+      <c r="A48" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="C48" s="17" t="s">
+      <c r="C48" s="14" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="20" t="s">
+      <c r="A49" s="17" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="50" ht="65" spans="1:3">
-      <c r="A50" s="20" t="s">
+      <c r="A50" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="C50" s="17" t="s">
+      <c r="C50" s="14" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="20" t="s">
+      <c r="A51" s="17" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="52" ht="26" spans="1:3">
-      <c r="A52" s="20" t="s">
+      <c r="A52" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="B52" s="17" t="s">
+      <c r="B52" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="C52" s="17" t="s">
+      <c r="C52" s="14" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="53" ht="26" spans="1:7">
-      <c r="A53" s="16" t="s">
+      <c r="A53" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="B53" s="17" t="s">
+      <c r="B53" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="D53" s="21"/>
-      <c r="E53" s="21"/>
-      <c r="F53" s="21"/>
-      <c r="G53" s="21"/>
+      <c r="D53" s="18"/>
+      <c r="E53" s="18"/>
+      <c r="F53" s="18"/>
+      <c r="G53" s="18"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="16" t="s">
+      <c r="A54" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="B54" s="17" t="s">
+      <c r="B54" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="C54" s="17" t="s">
+      <c r="C54" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="D54" s="21"/>
-      <c r="E54" s="21"/>
-      <c r="F54" s="21"/>
-      <c r="G54" s="21"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="18"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="18"/>
     </row>
     <row r="55" ht="39" spans="1:4">
-      <c r="A55" s="16" t="s">
+      <c r="A55" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="B55" s="21"/>
-      <c r="C55" s="21"/>
-      <c r="D55" s="17" t="s">
+      <c r="B55" s="18"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="14" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="56" ht="52" spans="1:3">
-      <c r="A56" s="16" t="s">
+      <c r="A56" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="B56" s="14" t="s">
+      <c r="B56" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="C56" s="14"/>
+      <c r="C56" s="10"/>
     </row>
     <row r="57" ht="117" spans="1:4">
-      <c r="A57" s="16" t="s">
+      <c r="A57" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="B57" s="14" t="s">
+      <c r="B57" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="C57" s="14"/>
-      <c r="D57" s="17" t="s">
+      <c r="C57" s="10"/>
+      <c r="D57" s="14" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="16" t="s">
+      <c r="A58" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="B58" s="17" t="s">
+      <c r="B58" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="C58" s="21"/>
-      <c r="D58" s="21"/>
-      <c r="E58" s="21"/>
-      <c r="F58" s="21"/>
-      <c r="G58" s="21"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="18"/>
+      <c r="E58" s="18"/>
+      <c r="F58" s="18"/>
+      <c r="G58" s="18"/>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="16" t="s">
+      <c r="A59" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="B59" s="21"/>
-      <c r="C59" s="17" t="s">
+      <c r="B59" s="18"/>
+      <c r="C59" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="D59" s="21"/>
-      <c r="E59" s="21"/>
-      <c r="F59" s="21"/>
-      <c r="G59" s="21"/>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="A60" s="16" t="s">
+      <c r="D59" s="18"/>
+      <c r="E59" s="18"/>
+      <c r="F59" s="18"/>
+      <c r="G59" s="18"/>
+    </row>
+    <row r="60" ht="39" spans="1:4">
+      <c r="A60" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B60" s="21"/>
-      <c r="C60" s="21"/>
-      <c r="D60" s="17" t="s">
+      <c r="B60" s="18"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="14" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="16" t="s">
+      <c r="A61" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="B61" s="14" t="s">
+      <c r="B61" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="C61" s="14"/>
-      <c r="D61" s="21"/>
-      <c r="E61" s="21"/>
-      <c r="F61" s="21"/>
-      <c r="G61" s="21"/>
+      <c r="C61" s="10"/>
+      <c r="D61" s="18"/>
+      <c r="E61" s="18"/>
+      <c r="F61" s="18"/>
+      <c r="G61" s="18"/>
     </row>
     <row r="62" spans="1:3">
-      <c r="A62" s="16" t="s">
+      <c r="A62" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="B62" s="21"/>
-      <c r="C62" s="21"/>
+      <c r="B62" s="18"/>
+      <c r="C62" s="18"/>
     </row>
     <row r="63" ht="26" spans="1:7">
-      <c r="A63" s="16" t="s">
+      <c r="A63" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="B63" s="14" t="s">
+      <c r="B63" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="C63" s="14" t="s">
+      <c r="C63" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="D63" s="21"/>
-      <c r="E63" s="21"/>
-      <c r="F63" s="21"/>
-      <c r="G63" s="21"/>
+      <c r="D63" s="18"/>
+      <c r="E63" s="18"/>
+      <c r="F63" s="18"/>
+      <c r="G63" s="18"/>
     </row>
     <row r="64" spans="1:4">
-      <c r="A64" s="16" t="s">
+      <c r="A64" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="B64" s="21"/>
-      <c r="C64" s="21"/>
-      <c r="D64" s="17" t="s">
+      <c r="B64" s="18"/>
+      <c r="C64" s="18"/>
+      <c r="D64" s="14" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="65" ht="26" spans="1:7">
-      <c r="A65" s="16" t="s">
+      <c r="A65" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="B65" s="22" t="s">
+      <c r="B65" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="C65" s="21"/>
-      <c r="D65" s="21"/>
-      <c r="E65" s="21"/>
-      <c r="F65" s="21"/>
-      <c r="G65" s="21"/>
+      <c r="C65" s="18"/>
+      <c r="D65" s="18"/>
+      <c r="E65" s="18"/>
+      <c r="F65" s="18"/>
+      <c r="G65" s="18"/>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="16" t="s">
+      <c r="A66" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="B66" s="21"/>
-      <c r="C66" s="17" t="s">
+      <c r="B66" s="18"/>
+      <c r="C66" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="D66" s="21"/>
-      <c r="E66" s="21"/>
-      <c r="F66" s="21"/>
-      <c r="G66" s="21"/>
+      <c r="D66" s="18"/>
+      <c r="E66" s="18"/>
+      <c r="F66" s="18"/>
+      <c r="G66" s="18"/>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="16" t="s">
+      <c r="A67" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="B67" s="21"/>
-      <c r="C67" s="21"/>
+      <c r="B67" s="18"/>
+      <c r="C67" s="18"/>
     </row>
     <row r="68" spans="1:4">
-      <c r="A68" s="16" t="s">
+      <c r="A68" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="B68" s="21"/>
-      <c r="C68" s="21"/>
-      <c r="D68" s="17" t="s">
+      <c r="B68" s="18"/>
+      <c r="C68" s="18"/>
+      <c r="D68" s="14" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="69" spans="1:3">
-      <c r="A69" s="16" t="s">
+      <c r="A69" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="B69" s="14" t="s">
+      <c r="B69" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="C69" s="14"/>
+      <c r="C69" s="10"/>
     </row>
     <row r="70" ht="26" spans="1:7">
-      <c r="A70" s="16" t="s">
+      <c r="A70" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="B70" s="14" t="s">
+      <c r="B70" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="C70" s="14"/>
-      <c r="D70" s="21"/>
-      <c r="E70" s="21"/>
-      <c r="F70" s="21"/>
-      <c r="G70" s="21"/>
+      <c r="C70" s="10"/>
+      <c r="D70" s="18"/>
+      <c r="E70" s="18"/>
+      <c r="F70" s="18"/>
+      <c r="G70" s="18"/>
     </row>
     <row r="71" spans="1:3">
-      <c r="A71" s="16" t="s">
+      <c r="A71" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B71" s="21"/>
-      <c r="C71" s="21"/>
+      <c r="B71" s="18"/>
+      <c r="C71" s="18"/>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="16" t="s">
+      <c r="A72" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="B72" s="17" t="s">
+      <c r="B72" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="C72" s="17" t="s">
+      <c r="C72" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="D72" s="21"/>
-      <c r="E72" s="21"/>
-      <c r="F72" s="21"/>
-      <c r="G72" s="21"/>
+      <c r="D72" s="18"/>
+      <c r="E72" s="18"/>
+      <c r="F72" s="18"/>
+      <c r="G72" s="18"/>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="16" t="s">
+      <c r="A73" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="B73" s="21"/>
-      <c r="C73" s="17" t="s">
+      <c r="B73" s="18"/>
+      <c r="C73" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="D73" s="21"/>
-      <c r="E73" s="21"/>
-      <c r="F73" s="21"/>
-      <c r="G73" s="21"/>
+      <c r="D73" s="18"/>
+      <c r="E73" s="18"/>
+      <c r="F73" s="18"/>
+      <c r="G73" s="18"/>
     </row>
     <row r="74" spans="1:1">
-      <c r="A74" s="16" t="s">
+      <c r="A74" s="13" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="16" t="s">
+      <c r="A75" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="D75" s="21"/>
-      <c r="E75" s="21"/>
-      <c r="F75" s="21"/>
-      <c r="G75" s="21"/>
+      <c r="D75" s="18"/>
+      <c r="E75" s="18"/>
+      <c r="F75" s="18"/>
+      <c r="G75" s="18"/>
     </row>
     <row r="76" spans="1:4">
-      <c r="A76" s="16" t="s">
+      <c r="A76" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="B76" s="21"/>
-      <c r="C76" s="21"/>
-      <c r="D76" s="17" t="s">
+      <c r="B76" s="18"/>
+      <c r="C76" s="18"/>
+      <c r="D76" s="14" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="77" spans="1:3">
-      <c r="A77" s="16" t="s">
+      <c r="A77" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="B77" s="14"/>
-      <c r="C77" s="14"/>
+      <c r="B77" s="10"/>
+      <c r="C77" s="10"/>
     </row>
     <row r="78" ht="26" spans="1:2">
-      <c r="A78" s="23" t="s">
+      <c r="A78" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="B78" s="17" t="s">
+      <c r="B78" s="14" t="s">
         <v>151</v>
       </c>
     </row>
@@ -2408,229 +2399,229 @@
   <dimension ref="A1:G51"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="6.64545454545455" style="6" customWidth="1"/>
-    <col min="2" max="7" width="16.4909090909091" style="7" customWidth="1"/>
-    <col min="8" max="16384" width="8.72727272727273" style="8"/>
+    <col min="1" max="1" width="6.64545454545455" style="4" customWidth="1"/>
+    <col min="2" max="7" width="16.4909090909091" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="8.72727272727273" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="9"/>
-      <c r="B1" s="10" t="s">
+      <c r="A1" s="7"/>
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="5" customFormat="1" ht="39" spans="1:7">
-      <c r="A2" s="11" t="s">
+    <row r="2" s="3" customFormat="1" ht="39" spans="1:7">
+      <c r="A2" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="5" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="5" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="5" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="5" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="13"/>
+      <c r="A7" s="11"/>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="13"/>
+      <c r="A8" s="11"/>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="13"/>
+      <c r="A9" s="11"/>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="13"/>
+      <c r="A10" s="11"/>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="13"/>
+      <c r="A11" s="11"/>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="13"/>
+      <c r="A12" s="11"/>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="13"/>
+      <c r="A13" s="11"/>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="13"/>
+      <c r="A14" s="11"/>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="13"/>
+      <c r="A15" s="11"/>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="13"/>
+      <c r="A16" s="11"/>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="13"/>
+      <c r="A17" s="11"/>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="13"/>
+      <c r="A18" s="11"/>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="13"/>
+      <c r="A19" s="11"/>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="13"/>
+      <c r="A20" s="11"/>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="13"/>
+      <c r="A21" s="11"/>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="13"/>
+      <c r="A22" s="11"/>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="13"/>
+      <c r="A23" s="11"/>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="13"/>
+      <c r="A24" s="11"/>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="13"/>
+      <c r="A25" s="11"/>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="13"/>
+      <c r="A26" s="11"/>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="13"/>
+      <c r="A27" s="11"/>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="13"/>
+      <c r="A28" s="11"/>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="13"/>
+      <c r="A29" s="11"/>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="13"/>
+      <c r="A30" s="11"/>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="13"/>
+      <c r="A31" s="11"/>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="13"/>
+      <c r="A32" s="11"/>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="13"/>
+      <c r="A33" s="11"/>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="13"/>
+      <c r="A34" s="11"/>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="13"/>
+      <c r="A35" s="11"/>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="13"/>
+      <c r="A36" s="11"/>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="13"/>
+      <c r="A37" s="11"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
+      <c r="A38" s="11"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
+      <c r="A39" s="11"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="13"/>
+      <c r="A40" s="11"/>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="13"/>
+      <c r="A41" s="11"/>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="13"/>
+      <c r="A42" s="11"/>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="13"/>
+      <c r="A43" s="11"/>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="13"/>
+      <c r="A44" s="11"/>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="13"/>
+      <c r="A45" s="11"/>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="13"/>
+      <c r="A46" s="11"/>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="13"/>
+      <c r="A47" s="11"/>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="13"/>
+      <c r="A48" s="11"/>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="13"/>
+      <c r="A49" s="11"/>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="13"/>
+      <c r="A50" s="11"/>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="13"/>
+      <c r="A51" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2651,13 +2642,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>166</v>
       </c>
     </row>

--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -67,7 +67,7 @@
     <t>猴、郑致辰</t>
   </si>
   <si>
-    <t>带菜（给孔保管）、小测降等级</t>
+    <t>带菜（给孔保管）、小测降等级、测心电图时对薛阅晨说“在这里！”</t>
   </si>
   <si>
     <t>郭沁诗</t>
@@ -94,7 +94,7 @@
     <t>祥懿又是你、午餐（芹菜炒肉、土豆丝、秋葵、番茄酱）课间吃饭、画画、捏/咬/打人、炫耀、演讲、喵喵姐</t>
   </si>
   <si>
-    <t>萌、上课吃东西、作业没写说没带、宣泄、睡觉（低头/点头）、带读（一，起）、水杯倒（不盖盖）、尼玛的、东西被陆梓豪偷吃、排队时讲话、我又……上了、我不行了……</t>
+    <t>萌、上课吃东西、作业没写应对方式（没带法、证人法、偶然法、不会法、以为法、灭口法、自我安慰法）、宣泄、睡觉（低头/点头）、带读（一，起）、水杯倒（不盖盖）、尼玛的、东西被陆梓豪偷吃、排队时讲话、我又……上了、我不行了……</t>
   </si>
   <si>
     <t>林钰颖</t>
@@ -118,7 +118,7 @@
     <t>郑永泽</t>
   </si>
   <si>
-    <t>阮贞铭（眼光）</t>
+    <t>阮贞铭（眼光）、炸蛋脚（打人招数）</t>
   </si>
   <si>
     <t>郑致辰</t>
@@ -1700,7 +1700,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" ht="26" spans="1:4">
+    <row r="3" ht="39" spans="1:4">
       <c r="A3" s="17" t="s">
         <v>10</v>
       </c>
@@ -1732,7 +1732,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" ht="78" spans="1:4">
+    <row r="7" ht="117" spans="1:4">
       <c r="A7" s="17" t="s">
         <v>18</v>
       </c>
@@ -1774,7 +1774,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" ht="26" spans="1:4">
       <c r="A13" s="17" t="s">
         <v>28</v>
       </c>

--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="182">
   <si>
     <t>姓名</t>
   </si>
@@ -94,7 +94,7 @@
     <t>祥懿又是你、午餐（芹菜炒肉、土豆丝、秋葵、番茄酱）课间吃饭、画画、捏/咬/打人、炫耀、演讲、喵喵姐</t>
   </si>
   <si>
-    <t>萌、上课吃东西、作业没写应对方式（没带法、证人法、偶然法、不会法、以为法、灭口法、自我安慰法）、宣泄、睡觉（低头/点头）、带读（一，起）、水杯倒（不盖盖）、尼玛的、东西被陆梓豪偷吃、排队时讲话、我又……上了、我不行了……</t>
+    <t>萌、上课吃东西、作业没写应对方式（没带法、证人法、偶然法、不会法、以为法、灭口法、自我安慰法）、宣泄、睡觉（低头/点头）、带读（一，起）、水杯倒（不盖盖）、尼玛的、东西被陆梓豪偷吃、排队时讲话、我又……上了、我不行了……、自己做了……→谁做了……啊！</t>
   </si>
   <si>
     <t>林钰颖</t>
@@ -400,6 +400,9 @@
     <t>史2</t>
   </si>
   <si>
+    <t>历史屌丝（论述题“中国只有变得更NB”、“中国要完蛋了”）</t>
+  </si>
+  <si>
     <t>地1</t>
   </si>
   <si>
@@ -563,6 +566,15 @@
   </si>
   <si>
     <t>体锻跑操，①男生“还没跑完”女生“坚持住，时间还没到”②刘：男生讲话，女生安静休息；男生要不要跟女生跑③男生（3个班女生）留下跑3（4）圈</t>
+  </si>
+  <si>
+    <t>郑永泽·阮贞铭</t>
+  </si>
+  <si>
+    <t>八上10.16</t>
+  </si>
+  <si>
+    <t>活动课下课，外面人讨论阮贞铭和江乐萱，郑永泽比“嘘”、盯着阮贞铭并嘴角上扬</t>
   </si>
 </sst>
 </file>
@@ -1732,7 +1744,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" ht="117" spans="1:4">
+    <row r="7" ht="130" spans="1:4">
       <c r="A7" s="17" t="s">
         <v>18</v>
       </c>
@@ -2188,22 +2200,25 @@
       <c r="F61" s="18"/>
       <c r="G61" s="18"/>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" ht="39" spans="1:4">
       <c r="A62" s="13" t="s">
         <v>122</v>
       </c>
       <c r="B62" s="18"/>
       <c r="C62" s="18"/>
+      <c r="D62" s="14" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="63" ht="26" spans="1:7">
       <c r="A63" s="13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D63" s="18"/>
       <c r="E63" s="18"/>
@@ -2212,20 +2227,20 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B64" s="18"/>
       <c r="C64" s="18"/>
       <c r="D64" s="14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="65" ht="26" spans="1:7">
       <c r="A65" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C65" s="18"/>
       <c r="D65" s="18"/>
@@ -2235,11 +2250,11 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B66" s="18"/>
       <c r="C66" s="14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D66" s="18"/>
       <c r="E66" s="18"/>
@@ -2248,36 +2263,36 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B67" s="18"/>
       <c r="C67" s="18"/>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B68" s="18"/>
       <c r="C68" s="18"/>
       <c r="D68" s="14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C69" s="10"/>
     </row>
     <row r="70" ht="26" spans="1:7">
       <c r="A70" s="13" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C70" s="10"/>
       <c r="D70" s="18"/>
@@ -2287,20 +2302,20 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B71" s="18"/>
       <c r="C71" s="18"/>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="13" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B72" s="14" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D72" s="18"/>
       <c r="E72" s="18"/>
@@ -2309,11 +2324,11 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B73" s="18"/>
       <c r="C73" s="14" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D73" s="18"/>
       <c r="E73" s="18"/>
@@ -2322,12 +2337,12 @@
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D75" s="18"/>
       <c r="E75" s="18"/>
@@ -2336,27 +2351,27 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="13" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B76" s="18"/>
       <c r="C76" s="18"/>
       <c r="D76" s="14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B77" s="10"/>
       <c r="C77" s="10"/>
     </row>
     <row r="78" ht="26" spans="1:2">
       <c r="A78" s="20" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B78" s="14" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -2427,12 +2442,12 @@
     </row>
     <row r="2" s="3" customFormat="1" ht="39" spans="1:7">
       <c r="A2" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
       <c r="D2" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E2" s="10"/>
       <c r="F2" s="10"/>
@@ -2440,40 +2455,40 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:1">
@@ -2632,8 +2647,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="2"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="35.1818181818182" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.9090909090909" style="1" customWidth="1"/>
@@ -2643,57 +2658,68 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" ht="28" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" ht="42" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
+      </c>
+    </row>
+    <row r="6" ht="28" spans="1:3">
+      <c r="A6" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>

--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -94,7 +94,7 @@
     <t>祥懿又是你、午餐（芹菜炒肉、土豆丝、秋葵、番茄酱）课间吃饭、画画、捏/咬/打人、炫耀、演讲、喵喵姐</t>
   </si>
   <si>
-    <t>萌、上课吃东西、作业没写应对方式（没带法、证人法、偶然法、不会法、以为法、灭口法、自我安慰法）、宣泄、睡觉（低头/点头）、带读（一，起）、水杯倒（不盖盖）、尼玛的、东西被陆梓豪偷吃、排队时讲话、我又……上了、我不行了……、自己做了……→谁做了……啊！</t>
+    <t>萌、上课吃东西（早上水果，下午菜，下午高峰）（泡鸭爪/棒棒糖）、作业没写应对方式（没带法、证人法、偶然法、不会法、以为法、灭口法、自我安慰法）、宣泄、睡觉（低头/点头）、带读（一，起）、水杯倒（不盖盖）、尼玛的、东西被陆梓豪偷吃、排队时讲话、我又……上了、我不行了……、自己做了……→谁做了……啊！、告状、动作、英语小测翻书/笔记、隔班借作业抄</t>
   </si>
   <si>
     <t>林钰颖</t>
@@ -184,7 +184,7 @@
     <t>睡觉、趴/坐桌子、画画</t>
   </si>
   <si>
-    <t>咬手指、拉杆包、张桢烨、点空调时开窗、英语小测上画画/写“看不懂”</t>
+    <t>咬手指、拉杆包、张桢烨、点空调时开窗、英语小测上画画/写“看不懂”“不写交不了作业”、跑操走路/提裤子</t>
   </si>
   <si>
     <t>林梓颢</t>
@@ -322,7 +322,7 @@
     <t>李梦妍</t>
   </si>
   <si>
-    <t>狡猾、雕版印刷、抢东西、画粑粑、曾好、梳子/镜子/护手霜/增高鞋、梗（橙绿、盆地、六棱柱、考试成绩、set bus come）、大冒险、傻子吧</t>
+    <t>狡猾、雕版印刷、抢东西、画粑粑、曾好、梳子/镜子/护手霜/增高鞋、梗（橙绿、盆地、六棱柱、考试成绩、set bus come）、大冒险、傻子吧、我要吃这个</t>
   </si>
   <si>
     <t>曹世强</t>
@@ -415,7 +415,7 @@
     <t>地2</t>
   </si>
   <si>
-    <t>提纲、惩罚跳舞</t>
+    <t>提纲、惩罚跳舞、以前是以前</t>
   </si>
   <si>
     <t>生1</t>
@@ -1744,7 +1744,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" ht="130" spans="1:4">
+    <row r="7" ht="169" spans="1:4">
       <c r="A7" s="17" t="s">
         <v>18</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" ht="39" spans="1:3">
+    <row r="24" ht="52" spans="1:3">
       <c r="A24" s="17" t="s">
         <v>49</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="50" ht="65" spans="1:3">
+    <row r="50" ht="78" spans="1:3">
       <c r="A50" s="17" t="s">
         <v>96</v>
       </c>

--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -301,7 +301,7 @@
     <t>陆梓豪</t>
   </si>
   <si>
-    <t>中午拿矿泉水</t>
+    <t>中午拿2矿泉水</t>
   </si>
   <si>
     <t>钱尚恩</t>

--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -94,7 +94,7 @@
     <t>祥懿又是你、午餐（芹菜炒肉、土豆丝、秋葵、番茄酱）课间吃饭、画画、捏/咬/打人、炫耀、演讲、喵喵姐</t>
   </si>
   <si>
-    <t>萌、上课吃东西（早上水果，下午菜，下午高峰）（泡鸭爪/棒棒糖）、作业没写应对方式（没带法、证人法、偶然法、不会法、以为法、灭口法、自我安慰法）、宣泄、睡觉（低头/点头）、带读（一，起）、水杯倒（不盖盖）、尼玛的、东西被陆梓豪偷吃、排队时讲话、我又……上了、我不行了……、自己做了……→谁做了……啊！、告状、动作、英语小测翻书/笔记、隔班借作业抄</t>
+    <t>萌、上课吃东西（早上水果，下午菜，下午高峰）（泡鸭爪/棒棒糖/营养品（长高））、作业没写应对方式（没带法、证人法、偶然法、不会法、以为法、灭口法、自我安慰法）、宣泄、睡觉（低头/点头）、带读（一，起）、水杯倒（不盖盖）、尼玛的、东西被陆梓豪偷吃、排队时讲话、我又……上了、我不行了……、自己做了……→谁做了……啊！、告状、动作、英语小测翻书/笔记、隔班借作业抄</t>
   </si>
   <si>
     <t>林钰颖</t>
@@ -388,7 +388,7 @@
     <t>政3</t>
   </si>
   <si>
-    <t>啧+手势，对不对、重音、预习复习、透明水杯，拿学生水杯、嘛</t>
+    <t>啧+手势，对不对、重音、预习复习、透明水杯，拿学生水杯、嘛、欸欸欸</t>
   </si>
   <si>
     <t>史1</t>
@@ -400,7 +400,7 @@
     <t>史2</t>
   </si>
   <si>
-    <t>历史屌丝（论述题“中国只有变得更NB”、“中国要完蛋了”）</t>
+    <t>历史屌丝（论述题“中国只有变得更NB”、“中国要完蛋了”）我爱历史</t>
   </si>
   <si>
     <t>地1</t>
@@ -1744,7 +1744,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" ht="169" spans="1:4">
+    <row r="7" ht="182" spans="1:4">
       <c r="A7" s="17" t="s">
         <v>18</v>
       </c>

--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10480"/>
+    <workbookView windowWidth="20750" windowHeight="10480" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="学生、老师" sheetId="5" r:id="rId1"/>
@@ -94,7 +94,7 @@
     <t>祥懿又是你、午餐（芹菜炒肉、土豆丝、秋葵、番茄酱）课间吃饭、画画、捏/咬/打人、炫耀、演讲、喵喵姐</t>
   </si>
   <si>
-    <t>萌、上课吃东西（早上水果，下午菜，下午高峰）（泡鸭爪/棒棒糖/营养品（长高））、作业没写应对方式（没带法、证人法、偶然法、不会法、以为法、灭口法、自我安慰法）、宣泄、睡觉（低头/点头）、带读（一，起）、水杯倒（不盖盖）、尼玛的、东西被陆梓豪偷吃、排队时讲话、我又……上了、我不行了……、自己做了……→谁做了……啊！、告状、动作、英语小测翻书/笔记、隔班借作业抄</t>
+    <t>萌、上课吃东西（早上水果，下午菜，下午高峰）（泡鸭爪/棒棒糖/营养品（长高）/奥利奥）、作业没写应对方式（没带法、证人法、偶然法、不会法、以为法、灭口法、自我安慰法）、宣泄、睡觉（低头/点头）、带读（一，起）、水杯倒（不盖盖）、尼玛的、东西被陆梓豪偷吃、排队时讲话、我又……上了、我不行了……、自己做了……→谁做了……啊！、告状、动作、英语小测翻书/笔记、隔班借作业抄</t>
   </si>
   <si>
     <t>林钰颖</t>
@@ -355,7 +355,7 @@
     <t>语3</t>
   </si>
   <si>
-    <t>微信窗口藏下面、C读“系”、我的天哪、周末作业（周记、好段、读书笔记）</t>
+    <t>微信窗口藏下面、C读“系”、我的天哪、周末作业（周记、好段、读书笔记）、以行践言、崇拜</t>
   </si>
   <si>
     <t>数1</t>
@@ -415,7 +415,7 @@
     <t>地2</t>
   </si>
   <si>
-    <t>提纲、惩罚跳舞、以前是以前</t>
+    <t>提纲、惩罚跳舞、以前是以前、贴标</t>
   </si>
   <si>
     <t>生1</t>
@@ -436,7 +436,7 @@
     <t>物1</t>
   </si>
   <si>
-    <t>读“m”、写“解”</t>
+    <t>读“m”“l”“等于”、写“解”</t>
   </si>
   <si>
     <t>体1</t>
@@ -2120,7 +2120,7 @@
       <c r="F54" s="18"/>
       <c r="G54" s="18"/>
     </row>
-    <row r="55" ht="39" spans="1:4">
+    <row r="55" ht="52" spans="1:4">
       <c r="A55" s="13" t="s">
         <v>107</v>
       </c>
@@ -2225,7 +2225,7 @@
       <c r="F63" s="18"/>
       <c r="G63" s="18"/>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" ht="26" spans="1:4">
       <c r="A64" s="13" t="s">
         <v>127</v>
       </c>
@@ -2268,7 +2268,7 @@
       <c r="B67" s="18"/>
       <c r="C67" s="18"/>
     </row>
-    <row r="68" spans="1:4">
+    <row r="68" ht="26" spans="1:4">
       <c r="A68" s="13" t="s">
         <v>134</v>
       </c>

--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10480" activeTab="2"/>
+    <workbookView windowWidth="20750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="学生、老师" sheetId="5" r:id="rId1"/>
@@ -388,7 +388,7 @@
     <t>政3</t>
   </si>
   <si>
-    <t>啧+手势，对不对、重音、预习复习、透明水杯，拿学生水杯、嘛、欸欸欸</t>
+    <t>啧+手势，对不对、重音、预习复习、透明水杯，拿学生水杯、嘛、欸欸欸、复读机</t>
   </si>
   <si>
     <t>史1</t>

--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -94,7 +94,7 @@
     <t>祥懿又是你、午餐（芹菜炒肉、土豆丝、秋葵、番茄酱）课间吃饭、画画、捏/咬/打人、炫耀、演讲、喵喵姐</t>
   </si>
   <si>
-    <t>萌、上课吃东西（早上水果，下午菜，下午高峰）（泡鸭爪/棒棒糖/营养品（长高）/奥利奥）、作业没写应对方式（没带法、证人法、偶然法、不会法、以为法、灭口法、自我安慰法）、宣泄、睡觉（低头/点头）、带读（一，起）、水杯倒（不盖盖）、尼玛的、东西被陆梓豪偷吃、排队时讲话、我又……上了、我不行了……、自己做了……→谁做了……啊！、告状、动作、英语小测翻书/笔记、隔班借作业抄</t>
+    <t>萌、上课吃东西（早上水果，下午菜，下午高峰）（泡鸭爪/棒棒糖/营养品（长高）/奥利奥）、作业没写应对方式（没带法、证人法、偶然法、不会法、以为法、灭口法、自我安慰法）、宣泄、睡觉（低头/点头）、带读（一，起）、水杯倒（不盖盖）、尼玛的、东西被陆梓豪偷吃、排队时讲话、我又……上了、我不行了……、自己做了……→谁做了……啊！、告状、动作、英语小测翻书/笔记、隔班借作业抄、废啊</t>
   </si>
   <si>
     <t>林钰颖</t>
@@ -409,7 +409,7 @@
     <t>知识点（Z1）、拍照、“重男轻女”、打人、作业要求</t>
   </si>
   <si>
-    <t>抄知识点、做素养提升</t>
+    <t>抄知识点、做素养提升、在正确选项下画线</t>
   </si>
   <si>
     <t>地2</t>
@@ -436,7 +436,7 @@
     <t>物1</t>
   </si>
   <si>
-    <t>读“m”“l”“等于”、写“解”</t>
+    <t>读“m”“l”“等于”、写“解”、M来了</t>
   </si>
   <si>
     <t>体1</t>
@@ -1744,7 +1744,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" ht="182" spans="1:4">
+    <row r="7" ht="195" spans="1:4">
       <c r="A7" s="17" t="s">
         <v>18</v>
       </c>

--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -67,7 +67,7 @@
     <t>猴、郑致辰</t>
   </si>
   <si>
-    <t>带菜（给孔保管）、小测降等级、测心电图时对薛阅晨说“在这里！”</t>
+    <t>带菜（给孔保管）、小测降等级、测心电图时对薛阅晨说“在这里！”、小心点</t>
   </si>
   <si>
     <t>郭沁诗</t>
@@ -1701,7 +1701,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:7">
       <c r="A2" s="17" t="s">
         <v>7</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" ht="39" spans="1:4">
+    <row r="3" ht="39" spans="1:7">
       <c r="A3" s="17" t="s">
         <v>10</v>
       </c>
@@ -1723,12 +1723,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:7">
       <c r="A4" s="17" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:7">
       <c r="A5" s="17" t="s">
         <v>14</v>
       </c>
@@ -1736,7 +1736,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:7">
       <c r="A6" s="17" t="s">
         <v>16</v>
       </c>
@@ -1744,7 +1744,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" ht="195" spans="1:4">
+    <row r="7" ht="195" spans="1:7">
       <c r="A7" s="17" t="s">
         <v>18</v>
       </c>
@@ -1758,17 +1758,17 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:7">
       <c r="A8" s="17" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:7">
       <c r="A9" s="17" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:7">
       <c r="A10" s="17" t="s">
         <v>24</v>
       </c>
@@ -1776,17 +1776,17 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:7">
       <c r="A11" s="17" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:7">
       <c r="A12" s="17" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="13" ht="26" spans="1:4">
+    <row r="13" ht="26" spans="1:7">
       <c r="A13" s="17" t="s">
         <v>28</v>
       </c>
@@ -1794,7 +1794,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:7">
       <c r="A14" s="17" t="s">
         <v>30</v>
       </c>
@@ -1802,12 +1802,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:7">
       <c r="A15" s="17" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:7">
       <c r="A16" s="17" t="s">
         <v>33</v>
       </c>
@@ -1815,7 +1815,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" ht="26" spans="1:3">
+    <row r="17" ht="26" spans="1:4">
       <c r="A17" s="17" t="s">
         <v>35</v>
       </c>
@@ -1823,17 +1823,17 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:4">
       <c r="A18" s="17" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:4">
       <c r="A19" s="17" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="20" ht="26" spans="1:3">
+    <row r="20" ht="26" spans="1:4">
       <c r="A20" s="17" t="s">
         <v>39</v>
       </c>
@@ -1858,12 +1858,12 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:4">
       <c r="A22" s="17" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="23" ht="26" spans="1:2">
+    <row r="23" ht="26" spans="1:4">
       <c r="A23" s="17" t="s">
         <v>47</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" ht="52" spans="1:3">
+    <row r="24" ht="52" spans="1:4">
       <c r="A24" s="17" t="s">
         <v>49</v>
       </c>
@@ -1882,17 +1882,17 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:4">
       <c r="A25" s="17" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:4">
       <c r="A26" s="17" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:4">
       <c r="A27" s="17" t="s">
         <v>54</v>
       </c>
@@ -1917,12 +1917,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:4">
       <c r="A29" s="17" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:4">
       <c r="A30" s="17" t="s">
         <v>62</v>
       </c>
@@ -1933,32 +1933,32 @@
         <v>64</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:4">
       <c r="A31" s="17" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:4">
       <c r="A32" s="17" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:7">
       <c r="A33" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:7">
       <c r="A34" s="17" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:7">
       <c r="A35" s="17" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:7">
       <c r="A36" s="17" t="s">
         <v>70</v>
       </c>
@@ -1966,7 +1966,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" ht="26" spans="1:4">
+    <row r="37" ht="26" spans="1:7">
       <c r="A37" s="17" t="s">
         <v>72</v>
       </c>
@@ -1990,7 +1990,7 @@
       <c r="F38" s="18"/>
       <c r="G38" s="18"/>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:7">
       <c r="A39" s="17" t="s">
         <v>77</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:7">
       <c r="A40" s="17" t="s">
         <v>79</v>
       </c>
@@ -2009,7 +2009,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="41" ht="26" spans="1:3">
+    <row r="41" ht="26" spans="1:7">
       <c r="A41" s="17" t="s">
         <v>82</v>
       </c>
@@ -2017,12 +2017,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:7">
       <c r="A42" s="17" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:7">
       <c r="A43" s="17" t="s">
         <v>85</v>
       </c>
@@ -2030,7 +2030,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" ht="26" spans="1:2">
+    <row r="44" ht="26" spans="1:7">
       <c r="A44" s="17" t="s">
         <v>87</v>
       </c>
@@ -2038,7 +2038,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:7">
       <c r="A45" s="17" t="s">
         <v>89</v>
       </c>
@@ -2046,17 +2046,17 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:7">
       <c r="A46" s="17" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:7">
       <c r="A47" s="17" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:7">
       <c r="A48" s="17" t="s">
         <v>93</v>
       </c>
@@ -2064,12 +2064,12 @@
         <v>94</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:7">
       <c r="A49" s="17" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="50" ht="78" spans="1:3">
+    <row r="50" ht="78" spans="1:7">
       <c r="A50" s="17" t="s">
         <v>96</v>
       </c>
@@ -2077,12 +2077,12 @@
         <v>97</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
+    <row r="51" spans="1:7">
       <c r="A51" s="17" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="52" ht="26" spans="1:3">
+    <row r="52" ht="26" spans="1:7">
       <c r="A52" s="17" t="s">
         <v>99</v>
       </c>
@@ -2120,7 +2120,7 @@
       <c r="F54" s="18"/>
       <c r="G54" s="18"/>
     </row>
-    <row r="55" ht="52" spans="1:4">
+    <row r="55" ht="52" spans="1:7">
       <c r="A55" s="13" t="s">
         <v>107</v>
       </c>
@@ -2130,7 +2130,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="56" ht="52" spans="1:3">
+    <row r="56" ht="52" spans="1:7">
       <c r="A56" s="13" t="s">
         <v>109</v>
       </c>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="C56" s="10"/>
     </row>
-    <row r="57" ht="117" spans="1:4">
+    <row r="57" ht="117" spans="1:7">
       <c r="A57" s="13" t="s">
         <v>111</v>
       </c>
@@ -2177,7 +2177,7 @@
       <c r="F59" s="18"/>
       <c r="G59" s="18"/>
     </row>
-    <row r="60" ht="39" spans="1:4">
+    <row r="60" ht="39" spans="1:7">
       <c r="A60" s="13" t="s">
         <v>118</v>
       </c>
@@ -2200,7 +2200,7 @@
       <c r="F61" s="18"/>
       <c r="G61" s="18"/>
     </row>
-    <row r="62" ht="39" spans="1:4">
+    <row r="62" ht="39" spans="1:7">
       <c r="A62" s="13" t="s">
         <v>122</v>
       </c>
@@ -2225,7 +2225,7 @@
       <c r="F63" s="18"/>
       <c r="G63" s="18"/>
     </row>
-    <row r="64" ht="26" spans="1:4">
+    <row r="64" ht="26" spans="1:7">
       <c r="A64" s="13" t="s">
         <v>127</v>
       </c>
@@ -2261,14 +2261,14 @@
       <c r="F66" s="18"/>
       <c r="G66" s="18"/>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:7">
       <c r="A67" s="13" t="s">
         <v>133</v>
       </c>
       <c r="B67" s="18"/>
       <c r="C67" s="18"/>
     </row>
-    <row r="68" ht="26" spans="1:4">
+    <row r="68" ht="26" spans="1:7">
       <c r="A68" s="13" t="s">
         <v>134</v>
       </c>
@@ -2278,7 +2278,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:7">
       <c r="A69" s="13" t="s">
         <v>136</v>
       </c>
@@ -2300,7 +2300,7 @@
       <c r="F70" s="18"/>
       <c r="G70" s="18"/>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:7">
       <c r="A71" s="13" t="s">
         <v>140</v>
       </c>
@@ -2335,7 +2335,7 @@
       <c r="F73" s="18"/>
       <c r="G73" s="18"/>
     </row>
-    <row r="74" spans="1:1">
+    <row r="74" spans="1:7">
       <c r="A74" s="13" t="s">
         <v>146</v>
       </c>
@@ -2349,7 +2349,7 @@
       <c r="F75" s="18"/>
       <c r="G75" s="18"/>
     </row>
-    <row r="76" spans="1:4">
+    <row r="76" spans="1:7">
       <c r="A76" s="13" t="s">
         <v>148</v>
       </c>
@@ -2359,14 +2359,14 @@
         <v>149</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:7">
       <c r="A77" s="13" t="s">
         <v>150</v>
       </c>
       <c r="B77" s="10"/>
       <c r="C77" s="10"/>
     </row>
-    <row r="78" ht="26" spans="1:2">
+    <row r="78" ht="26" spans="1:7">
       <c r="A78" s="20" t="s">
         <v>151</v>
       </c>
@@ -2453,7 +2453,7 @@
       <c r="F2" s="10"/>
       <c r="G2" s="10"/>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:7">
       <c r="A3" s="11" t="s">
         <v>155</v>
       </c>
@@ -2461,7 +2461,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:7">
       <c r="A4" s="11" t="s">
         <v>157</v>
       </c>
@@ -2469,7 +2469,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:7">
       <c r="A5" s="11" t="s">
         <v>159</v>
       </c>
@@ -2480,7 +2480,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:7">
       <c r="A6" s="11" t="s">
         <v>162</v>
       </c>
@@ -2491,34 +2491,34 @@
         <v>164</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:7">
       <c r="A7" s="11"/>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:7">
       <c r="A8" s="11"/>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:7">
       <c r="A9" s="11"/>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:7">
       <c r="A10" s="11"/>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:7">
       <c r="A11" s="11"/>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:7">
       <c r="A12" s="11"/>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:7">
       <c r="A13" s="11"/>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:7">
       <c r="A14" s="11"/>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:7">
       <c r="A15" s="11"/>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:7">
       <c r="A16" s="11"/>
     </row>
     <row r="17" spans="1:1">
@@ -2569,19 +2569,19 @@
     <row r="32" spans="1:1">
       <c r="A32" s="11"/>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:7">
       <c r="A33" s="11"/>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:7">
       <c r="A34" s="11"/>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:7">
       <c r="A35" s="11"/>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:7">
       <c r="A36" s="11"/>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:7">
       <c r="A37" s="11"/>
     </row>
     <row r="38" spans="1:7">
@@ -2602,31 +2602,31 @@
       <c r="F39" s="10"/>
       <c r="G39" s="10"/>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:7">
       <c r="A40" s="11"/>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:7">
       <c r="A41" s="11"/>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:7">
       <c r="A42" s="11"/>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:7">
       <c r="A43" s="11"/>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:7">
       <c r="A44" s="11"/>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:7">
       <c r="A45" s="11"/>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:7">
       <c r="A46" s="11"/>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:7">
       <c r="A47" s="11"/>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:7">
       <c r="A48" s="11"/>
     </row>
     <row r="49" spans="1:1">

--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10480"/>
+    <workbookView windowWidth="20750" windowHeight="10480" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="学生、老师" sheetId="5" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="184">
   <si>
     <t>姓名</t>
   </si>
@@ -566,6 +566,12 @@
   </si>
   <si>
     <t>体锻跑操，①男生“还没跑完”女生“坚持住，时间还没到”②刘：男生讲话，女生安静休息；男生要不要跟女生跑③男生（3个班女生）留下跑3（4）圈</t>
+  </si>
+  <si>
+    <t>八上12.9</t>
+  </si>
+  <si>
+    <t>结束时女生已往棚子走约半圈，但偷懒直接掉头，被罚跑3圈。第一圈：提前掉头，导致混乱；第二圈：罚跑时唐家祺前面的学生越跑转弯越早；第三圈：罚跑时女生到棚子时走路。</t>
   </si>
   <si>
     <t>郑永泽·阮贞铭</t>
@@ -1003,7 +1009,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1021,6 +1027,32 @@
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -1150,7 +1182,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1162,34 +1194,34 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1277,7 +1309,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1286,6 +1318,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1674,703 +1712,703 @@
   <dimension ref="A1:G78"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="7.59090909090909" style="13" customWidth="1"/>
-    <col min="2" max="7" width="25.8727272727273" style="14" customWidth="1"/>
+    <col min="1" max="1" width="7.59090909090909" style="15" customWidth="1"/>
+    <col min="2" max="7" width="25.8727272727273" style="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="12" customFormat="1" spans="1:7">
-      <c r="A1" s="15" t="s">
+    <row r="1" s="14" customFormat="1" spans="1:7">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="18" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="16" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" ht="39" spans="1:7">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="16" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="19" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="16" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="16" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" ht="195" spans="1:7">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="16" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="19" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="19" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="16" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="19" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="19" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="13" ht="26" spans="1:7">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="16" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="19" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="16" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="17" ht="26" spans="1:4">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="16" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="19" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="20" ht="26" spans="1:4">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="16" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="21" ht="39" spans="1:4">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="16" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="19" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="23" ht="26" spans="1:4">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="16" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="24" ht="52" spans="1:4">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="16" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="19" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="19" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="16" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="28" ht="91" spans="1:4">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="C28" s="14" t="s">
+      <c r="C28" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="D28" s="16" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="19" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="B30" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="C30" s="14" t="s">
+      <c r="C30" s="16" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="19" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="19" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="17" t="s">
+      <c r="A33" s="19" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="17" t="s">
+      <c r="A34" s="19" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="17" t="s">
+      <c r="A35" s="19" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="17" t="s">
+      <c r="A36" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="B36" s="16" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="37" ht="26" spans="1:7">
-      <c r="A37" s="17" t="s">
+      <c r="A37" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C37" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="D37" s="14" t="s">
+      <c r="D37" s="16" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="17" t="s">
+      <c r="A38" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="B38" s="14" t="s">
+      <c r="B38" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="17" t="s">
+      <c r="A39" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C39" s="16" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="17" t="s">
+      <c r="A40" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="B40" s="14" t="s">
+      <c r="B40" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="C40" s="14" t="s">
+      <c r="C40" s="16" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="41" ht="26" spans="1:7">
-      <c r="A41" s="17" t="s">
+      <c r="A41" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="C41" s="14" t="s">
+      <c r="C41" s="16" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="17" t="s">
+      <c r="A42" s="19" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="17" t="s">
+      <c r="A43" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="B43" s="14" t="s">
+      <c r="B43" s="16" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="44" ht="26" spans="1:7">
-      <c r="A44" s="17" t="s">
+      <c r="A44" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="B44" s="14" t="s">
+      <c r="B44" s="16" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="17" t="s">
+      <c r="A45" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="D45" s="14" t="s">
+      <c r="D45" s="16" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="17" t="s">
+      <c r="A46" s="19" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="17" t="s">
+      <c r="A47" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="17" t="s">
+      <c r="A48" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="C48" s="14" t="s">
+      <c r="C48" s="16" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="17" t="s">
+      <c r="A49" s="19" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="50" ht="78" spans="1:7">
-      <c r="A50" s="17" t="s">
+      <c r="A50" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="C50" s="14" t="s">
+      <c r="C50" s="16" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="17" t="s">
+      <c r="A51" s="19" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="52" ht="26" spans="1:7">
-      <c r="A52" s="17" t="s">
+      <c r="A52" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="B52" s="14" t="s">
+      <c r="B52" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C52" s="14" t="s">
+      <c r="C52" s="16" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="53" ht="26" spans="1:7">
-      <c r="A53" s="13" t="s">
+      <c r="A53" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="B53" s="14" t="s">
+      <c r="B53" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="D53" s="18"/>
-      <c r="E53" s="18"/>
-      <c r="F53" s="18"/>
-      <c r="G53" s="18"/>
+      <c r="D53" s="20"/>
+      <c r="E53" s="20"/>
+      <c r="F53" s="20"/>
+      <c r="G53" s="20"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="13" t="s">
+      <c r="A54" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="B54" s="14" t="s">
+      <c r="B54" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="C54" s="14" t="s">
+      <c r="C54" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="D54" s="18"/>
-      <c r="E54" s="18"/>
-      <c r="F54" s="18"/>
-      <c r="G54" s="18"/>
+      <c r="D54" s="20"/>
+      <c r="E54" s="20"/>
+      <c r="F54" s="20"/>
+      <c r="G54" s="20"/>
     </row>
     <row r="55" ht="52" spans="1:7">
-      <c r="A55" s="13" t="s">
+      <c r="A55" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="B55" s="18"/>
-      <c r="C55" s="18"/>
-      <c r="D55" s="14" t="s">
+      <c r="B55" s="20"/>
+      <c r="C55" s="20"/>
+      <c r="D55" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="56" ht="52" spans="1:7">
-      <c r="A56" s="13" t="s">
+      <c r="A56" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="B56" s="10" t="s">
+      <c r="B56" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="C56" s="10"/>
+      <c r="C56" s="12"/>
     </row>
     <row r="57" ht="117" spans="1:7">
-      <c r="A57" s="13" t="s">
+      <c r="A57" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="B57" s="10" t="s">
+      <c r="B57" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="C57" s="10"/>
-      <c r="D57" s="14" t="s">
+      <c r="C57" s="12"/>
+      <c r="D57" s="16" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="13" t="s">
+      <c r="A58" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="B58" s="14" t="s">
+      <c r="B58" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="C58" s="18"/>
-      <c r="D58" s="18"/>
-      <c r="E58" s="18"/>
-      <c r="F58" s="18"/>
-      <c r="G58" s="18"/>
+      <c r="C58" s="20"/>
+      <c r="D58" s="20"/>
+      <c r="E58" s="20"/>
+      <c r="F58" s="20"/>
+      <c r="G58" s="20"/>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="13" t="s">
+      <c r="A59" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="B59" s="18"/>
-      <c r="C59" s="14" t="s">
+      <c r="B59" s="20"/>
+      <c r="C59" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="D59" s="18"/>
-      <c r="E59" s="18"/>
-      <c r="F59" s="18"/>
-      <c r="G59" s="18"/>
+      <c r="D59" s="20"/>
+      <c r="E59" s="20"/>
+      <c r="F59" s="20"/>
+      <c r="G59" s="20"/>
     </row>
     <row r="60" ht="39" spans="1:7">
-      <c r="A60" s="13" t="s">
+      <c r="A60" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="B60" s="18"/>
-      <c r="C60" s="18"/>
-      <c r="D60" s="14" t="s">
+      <c r="B60" s="20"/>
+      <c r="C60" s="20"/>
+      <c r="D60" s="16" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="13" t="s">
+      <c r="A61" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="B61" s="10" t="s">
+      <c r="B61" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="C61" s="10"/>
-      <c r="D61" s="18"/>
-      <c r="E61" s="18"/>
-      <c r="F61" s="18"/>
-      <c r="G61" s="18"/>
+      <c r="C61" s="12"/>
+      <c r="D61" s="20"/>
+      <c r="E61" s="20"/>
+      <c r="F61" s="20"/>
+      <c r="G61" s="20"/>
     </row>
     <row r="62" ht="39" spans="1:7">
-      <c r="A62" s="13" t="s">
+      <c r="A62" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="B62" s="18"/>
-      <c r="C62" s="18"/>
-      <c r="D62" s="14" t="s">
+      <c r="B62" s="20"/>
+      <c r="C62" s="20"/>
+      <c r="D62" s="16" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="63" ht="26" spans="1:7">
-      <c r="A63" s="13" t="s">
+      <c r="A63" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="B63" s="10" t="s">
+      <c r="B63" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="C63" s="10" t="s">
+      <c r="C63" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D63" s="18"/>
-      <c r="E63" s="18"/>
-      <c r="F63" s="18"/>
-      <c r="G63" s="18"/>
+      <c r="D63" s="20"/>
+      <c r="E63" s="20"/>
+      <c r="F63" s="20"/>
+      <c r="G63" s="20"/>
     </row>
     <row r="64" ht="26" spans="1:7">
-      <c r="A64" s="13" t="s">
+      <c r="A64" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="B64" s="18"/>
-      <c r="C64" s="18"/>
-      <c r="D64" s="14" t="s">
+      <c r="B64" s="20"/>
+      <c r="C64" s="20"/>
+      <c r="D64" s="16" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="65" ht="26" spans="1:7">
-      <c r="A65" s="13" t="s">
+      <c r="A65" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="B65" s="19" t="s">
+      <c r="B65" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="C65" s="18"/>
-      <c r="D65" s="18"/>
-      <c r="E65" s="18"/>
-      <c r="F65" s="18"/>
-      <c r="G65" s="18"/>
+      <c r="C65" s="20"/>
+      <c r="D65" s="20"/>
+      <c r="E65" s="20"/>
+      <c r="F65" s="20"/>
+      <c r="G65" s="20"/>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="13" t="s">
+      <c r="A66" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="B66" s="18"/>
-      <c r="C66" s="14" t="s">
+      <c r="B66" s="20"/>
+      <c r="C66" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="D66" s="18"/>
-      <c r="E66" s="18"/>
-      <c r="F66" s="18"/>
-      <c r="G66" s="18"/>
+      <c r="D66" s="20"/>
+      <c r="E66" s="20"/>
+      <c r="F66" s="20"/>
+      <c r="G66" s="20"/>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="13" t="s">
+      <c r="A67" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="B67" s="18"/>
-      <c r="C67" s="18"/>
+      <c r="B67" s="20"/>
+      <c r="C67" s="20"/>
     </row>
     <row r="68" ht="26" spans="1:7">
-      <c r="A68" s="13" t="s">
+      <c r="A68" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="B68" s="18"/>
-      <c r="C68" s="18"/>
-      <c r="D68" s="14" t="s">
+      <c r="B68" s="20"/>
+      <c r="C68" s="20"/>
+      <c r="D68" s="16" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="13" t="s">
+      <c r="A69" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="B69" s="10" t="s">
+      <c r="B69" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="C69" s="10"/>
+      <c r="C69" s="12"/>
     </row>
     <row r="70" ht="26" spans="1:7">
-      <c r="A70" s="13" t="s">
+      <c r="A70" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="B70" s="10" t="s">
+      <c r="B70" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="C70" s="10"/>
-      <c r="D70" s="18"/>
-      <c r="E70" s="18"/>
-      <c r="F70" s="18"/>
-      <c r="G70" s="18"/>
+      <c r="C70" s="12"/>
+      <c r="D70" s="20"/>
+      <c r="E70" s="20"/>
+      <c r="F70" s="20"/>
+      <c r="G70" s="20"/>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="13" t="s">
+      <c r="A71" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="B71" s="18"/>
-      <c r="C71" s="18"/>
+      <c r="B71" s="20"/>
+      <c r="C71" s="20"/>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="13" t="s">
+      <c r="A72" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="B72" s="14" t="s">
+      <c r="B72" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="C72" s="14" t="s">
+      <c r="C72" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="D72" s="18"/>
-      <c r="E72" s="18"/>
-      <c r="F72" s="18"/>
-      <c r="G72" s="18"/>
+      <c r="D72" s="20"/>
+      <c r="E72" s="20"/>
+      <c r="F72" s="20"/>
+      <c r="G72" s="20"/>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="13" t="s">
+      <c r="A73" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="B73" s="18"/>
-      <c r="C73" s="14" t="s">
+      <c r="B73" s="20"/>
+      <c r="C73" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="D73" s="18"/>
-      <c r="E73" s="18"/>
-      <c r="F73" s="18"/>
-      <c r="G73" s="18"/>
+      <c r="D73" s="20"/>
+      <c r="E73" s="20"/>
+      <c r="F73" s="20"/>
+      <c r="G73" s="20"/>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="13" t="s">
+      <c r="A74" s="15" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="13" t="s">
+      <c r="A75" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="D75" s="18"/>
-      <c r="E75" s="18"/>
-      <c r="F75" s="18"/>
-      <c r="G75" s="18"/>
+      <c r="D75" s="20"/>
+      <c r="E75" s="20"/>
+      <c r="F75" s="20"/>
+      <c r="G75" s="20"/>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="13" t="s">
+      <c r="A76" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="B76" s="18"/>
-      <c r="C76" s="18"/>
-      <c r="D76" s="14" t="s">
+      <c r="B76" s="20"/>
+      <c r="C76" s="20"/>
+      <c r="D76" s="16" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="13" t="s">
+      <c r="A77" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="B77" s="10"/>
-      <c r="C77" s="10"/>
+      <c r="B77" s="12"/>
+      <c r="C77" s="12"/>
     </row>
     <row r="78" ht="26" spans="1:7">
-      <c r="A78" s="20" t="s">
+      <c r="A78" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="B78" s="14" t="s">
+      <c r="B78" s="16" t="s">
         <v>152</v>
       </c>
     </row>
@@ -2414,229 +2452,229 @@
   <dimension ref="A1:G51"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="6.64545454545455" style="4" customWidth="1"/>
-    <col min="2" max="7" width="16.4909090909091" style="5" customWidth="1"/>
-    <col min="8" max="16384" width="8.72727272727273" style="6"/>
+    <col min="1" max="1" width="6.64545454545455" style="6" customWidth="1"/>
+    <col min="2" max="7" width="16.4909090909091" style="7" customWidth="1"/>
+    <col min="8" max="16384" width="8.72727272727273" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="7"/>
-      <c r="B1" s="8" t="s">
+      <c r="A1" s="9"/>
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="3" customFormat="1" ht="39" spans="1:7">
-      <c r="A2" s="9" t="s">
+    <row r="2" s="5" customFormat="1" ht="39" spans="1:7">
+      <c r="A2" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="7" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="7" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="7" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="7" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="11"/>
+      <c r="A7" s="13"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="11"/>
+      <c r="A8" s="13"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="11"/>
+      <c r="A9" s="13"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="11"/>
+      <c r="A10" s="13"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="11"/>
+      <c r="A11" s="13"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="11"/>
+      <c r="A12" s="13"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="11"/>
+      <c r="A13" s="13"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="11"/>
+      <c r="A14" s="13"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="11"/>
+      <c r="A15" s="13"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="11"/>
+      <c r="A16" s="13"/>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="11"/>
+      <c r="A17" s="13"/>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="11"/>
+      <c r="A18" s="13"/>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="11"/>
+      <c r="A19" s="13"/>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="11"/>
+      <c r="A20" s="13"/>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="11"/>
+      <c r="A21" s="13"/>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="11"/>
+      <c r="A22" s="13"/>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="11"/>
+      <c r="A23" s="13"/>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="11"/>
+      <c r="A24" s="13"/>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="11"/>
+      <c r="A25" s="13"/>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="11"/>
+      <c r="A26" s="13"/>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="11"/>
+      <c r="A27" s="13"/>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="11"/>
+      <c r="A28" s="13"/>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="11"/>
+      <c r="A29" s="13"/>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="11"/>
+      <c r="A30" s="13"/>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="11"/>
+      <c r="A31" s="13"/>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="11"/>
+      <c r="A32" s="13"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="11"/>
+      <c r="A33" s="13"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="11"/>
+      <c r="A34" s="13"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="11"/>
+      <c r="A35" s="13"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="11"/>
+      <c r="A36" s="13"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="11"/>
+      <c r="A37" s="13"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="11"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
+      <c r="A38" s="13"/>
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="11"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
+      <c r="A39" s="13"/>
+      <c r="B39" s="12"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="11"/>
+      <c r="A40" s="13"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="11"/>
+      <c r="A41" s="13"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="11"/>
+      <c r="A42" s="13"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="11"/>
+      <c r="A43" s="13"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="11"/>
+      <c r="A44" s="13"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="11"/>
+      <c r="A45" s="13"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="11"/>
+      <c r="A46" s="13"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="11"/>
+      <c r="A47" s="13"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="11"/>
+      <c r="A48" s="13"/>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="11"/>
+      <c r="A49" s="13"/>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="11"/>
+      <c r="A50" s="13"/>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="11"/>
+      <c r="A51" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2647,8 +2685,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="2"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="35.1818181818182" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.9090909090909" style="1" customWidth="1"/>
@@ -2701,7 +2739,7 @@
       </c>
     </row>
     <row r="5" ht="42" spans="1:3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>176</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -2711,18 +2749,30 @@
         <v>178</v>
       </c>
     </row>
-    <row r="6" ht="28" spans="1:3">
-      <c r="A6" s="1" t="s">
+    <row r="6" ht="56" spans="1:3">
+      <c r="A6" s="4"/>
+      <c r="B6" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C6" s="2" t="s">
+    </row>
+    <row r="7" ht="28" spans="1:3">
+      <c r="A7" s="1" t="s">
         <v>181</v>
       </c>
+      <c r="B7" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>183</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A5:A6"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10480" activeTab="2"/>
+    <workbookView windowWidth="20750" windowHeight="10480" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="学生、老师" sheetId="5" r:id="rId1"/>
     <sheet name="9班、四十中" sheetId="13" r:id="rId2"/>
     <sheet name="佐证日常典型事例" sheetId="14" r:id="rId3"/>
+    <sheet name="统计数据" sheetId="15" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="192">
   <si>
     <t>姓名</t>
   </si>
@@ -211,7 +212,7 @@
     <t>推北师大、磨鞋、获奖时笑、菜被人吃、秀鼓包</t>
   </si>
   <si>
-    <t>朋友圈（模糊图片、装）、马克笔写字、挠痒动作</t>
+    <t>朋友圈（模糊图片、装）、马克笔写字、挠痒动作、起立时（借口、拖延、不情愿、偷坐）</t>
   </si>
   <si>
     <t>林承钰</t>
@@ -361,7 +362,10 @@
     <t>数1</t>
   </si>
   <si>
-    <t>讲评作业（折名字/3、4组过道）、课件（熊熊疑惑、喜羊羊修花圃）、今天纪律差、笔记本拿出来、作业只改正面</t>
+    <t>讲评作业（折名字/3、4组过道）、课件（熊熊疑惑、喜羊羊修花圃）、今天纪律差、笔记本拿出来、作业只改正面、告诉原因</t>
+  </si>
+  <si>
+    <t>××写第×题、固定请人、站后面</t>
   </si>
   <si>
     <t>英1</t>
@@ -370,7 +374,10 @@
     <t>小测（CTMO）、作业（抄几默几、积累本、AB本、订正）、one by one、笔记（活页、不要换笔、一课一页）、课前带读、作文本/草稿本/小绿（粉、黄、红）/预习、抄作业本、手机管理、做题标记、羽毛球、一人一包、学习小组、巡课、3条红领巾、AI视频</t>
   </si>
   <si>
-    <t>请假13个工作日（作业减、早读乱）、投屏打字</t>
+    <t>跑操造句</t>
+  </si>
+  <si>
+    <t>请假13个工作日（作业减、早读乱、大脚）、投屏打字、收作业制度、男厕洗手、量化制度、监控、电脑控制</t>
   </si>
   <si>
     <t>政1</t>
@@ -388,7 +395,7 @@
     <t>政3</t>
   </si>
   <si>
-    <t>啧+手势，对不对、重音、预习复习、透明水杯，拿学生水杯、嘛、欸欸欸、复读机</t>
+    <t>啧+手势，对不对、重音、预习复习、透明水杯，拿学生水杯、嘛、欸欸欸、复读机、××什么？×——×。</t>
   </si>
   <si>
     <t>史1</t>
@@ -581,6 +588,24 @@
   </si>
   <si>
     <t>活动课下课，外面人讨论阮贞铭和江乐萱，郑永泽比“嘘”、盯着阮贞铭并嘴角上扬</t>
+  </si>
+  <si>
+    <t>数学请人</t>
+  </si>
+  <si>
+    <t>政治啧</t>
+  </si>
+  <si>
+    <t>2，5，6，7，17，28，29，31，39，42，44</t>
+  </si>
+  <si>
+    <t>2，6，13，22，26，30，38，42，44</t>
+  </si>
+  <si>
+    <t>2，5，6，10，11，22，27，38，42，44</t>
+  </si>
+  <si>
+    <t>6，22，30，42，44，48</t>
   </si>
 </sst>
 </file>
@@ -593,10 +618,15 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1009,7 +1039,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1042,6 +1072,17 @@
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -1161,168 +1202,192 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1331,52 +1396,52 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1712,704 +1777,709 @@
   <dimension ref="A1:G78"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="7.59090909090909" style="15" customWidth="1"/>
-    <col min="2" max="7" width="25.8727272727273" style="16" customWidth="1"/>
+    <col min="1" max="1" width="7.59090909090909" style="23" customWidth="1"/>
+    <col min="2" max="7" width="25.8727272727273" style="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="14" customFormat="1" spans="1:7">
-      <c r="A1" s="17" t="s">
+    <row r="1" s="22" customFormat="1" spans="1:7">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="26" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="24" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" ht="39" spans="1:7">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="24" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="27" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="24" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="24" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" ht="195" spans="1:7">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="24" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="27" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="27" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="24" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="27" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="27" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="13" ht="26" spans="1:7">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="24" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="24" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="27" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="24" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="17" ht="26" spans="1:4">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="24" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="27" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="27" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="20" ht="26" spans="1:4">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="24" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="21" ht="39" spans="1:4">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="24" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="27" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="23" ht="26" spans="1:4">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="24" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="24" ht="52" spans="1:4">
-      <c r="A24" s="19" t="s">
+      <c r="A24" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="24" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="19" t="s">
+      <c r="A25" s="27" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="19" t="s">
+      <c r="A26" s="27" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="19" t="s">
+      <c r="A27" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="24" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="28" ht="91" spans="1:4">
-      <c r="A28" s="19" t="s">
+      <c r="A28" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="D28" s="16" t="s">
+      <c r="D28" s="24" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="19" t="s">
+      <c r="A29" s="27" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="19" t="s">
+      <c r="A30" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="24" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="19" t="s">
+      <c r="A31" s="27" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="19" t="s">
+      <c r="A32" s="27" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="19" t="s">
+      <c r="A33" s="27" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="19" t="s">
+      <c r="A34" s="27" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="19" t="s">
+      <c r="A35" s="27" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="19" t="s">
+      <c r="A36" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="16" t="s">
+      <c r="B36" s="24" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="37" ht="26" spans="1:7">
-      <c r="A37" s="19" t="s">
+      <c r="A37" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="C37" s="16" t="s">
+      <c r="C37" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="D37" s="16" t="s">
+      <c r="D37" s="24" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="19" t="s">
+      <c r="A38" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="B38" s="16" t="s">
+      <c r="B38" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
+      <c r="C38" s="28"/>
+      <c r="D38" s="28"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
+      <c r="G38" s="28"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="19" t="s">
+      <c r="A39" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="C39" s="16" t="s">
+      <c r="C39" s="24" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="19" t="s">
+      <c r="A40" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="B40" s="16" t="s">
+      <c r="B40" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="C40" s="24" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="41" ht="26" spans="1:7">
-      <c r="A41" s="19" t="s">
+      <c r="A41" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="C41" s="16" t="s">
+      <c r="C41" s="24" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="19" t="s">
+      <c r="A42" s="27" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="19" t="s">
+      <c r="A43" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="B43" s="16" t="s">
+      <c r="B43" s="24" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="44" ht="26" spans="1:7">
-      <c r="A44" s="19" t="s">
+      <c r="A44" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="B44" s="16" t="s">
+      <c r="B44" s="24" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="19" t="s">
+      <c r="A45" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="D45" s="16" t="s">
+      <c r="D45" s="24" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="19" t="s">
+      <c r="A46" s="27" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="19" t="s">
+      <c r="A47" s="27" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="19" t="s">
+      <c r="A48" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="C48" s="16" t="s">
+      <c r="C48" s="24" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="19" t="s">
+      <c r="A49" s="27" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="50" ht="78" spans="1:7">
-      <c r="A50" s="19" t="s">
+      <c r="A50" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="C50" s="16" t="s">
+      <c r="C50" s="24" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="19" t="s">
+      <c r="A51" s="27" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="52" ht="26" spans="1:7">
-      <c r="A52" s="19" t="s">
+      <c r="A52" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="B52" s="16" t="s">
+      <c r="B52" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="C52" s="16" t="s">
+      <c r="C52" s="24" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="53" ht="26" spans="1:7">
-      <c r="A53" s="15" t="s">
+      <c r="A53" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="B53" s="16" t="s">
+      <c r="B53" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="D53" s="20"/>
-      <c r="E53" s="20"/>
-      <c r="F53" s="20"/>
-      <c r="G53" s="20"/>
+      <c r="D53" s="28"/>
+      <c r="E53" s="28"/>
+      <c r="F53" s="28"/>
+      <c r="G53" s="28"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="15" t="s">
+      <c r="A54" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="B54" s="16" t="s">
+      <c r="B54" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="C54" s="16" t="s">
+      <c r="C54" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
-      <c r="F54" s="20"/>
-      <c r="G54" s="20"/>
+      <c r="D54" s="28"/>
+      <c r="E54" s="28"/>
+      <c r="F54" s="28"/>
+      <c r="G54" s="28"/>
     </row>
     <row r="55" ht="52" spans="1:7">
-      <c r="A55" s="15" t="s">
+      <c r="A55" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="B55" s="20"/>
-      <c r="C55" s="20"/>
-      <c r="D55" s="16" t="s">
+      <c r="B55" s="28"/>
+      <c r="C55" s="28"/>
+      <c r="D55" s="24" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="56" ht="52" spans="1:7">
-      <c r="A56" s="15" t="s">
+    <row r="56" ht="65" spans="1:7">
+      <c r="A56" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="B56" s="12" t="s">
+      <c r="B56" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="C56" s="12"/>
+      <c r="C56" s="20"/>
+      <c r="D56" s="24" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="57" ht="117" spans="1:7">
-      <c r="A57" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="B57" s="12" t="s">
+      <c r="A57" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="C57" s="12"/>
-      <c r="D57" s="16" t="s">
+      <c r="B57" s="20" t="s">
         <v>113</v>
       </c>
+      <c r="C57" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="D57" s="24" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="B58" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="C58" s="20"/>
-      <c r="D58" s="20"/>
-      <c r="E58" s="20"/>
-      <c r="F58" s="20"/>
-      <c r="G58" s="20"/>
+      <c r="A58" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="B58" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="C58" s="28"/>
+      <c r="D58" s="28"/>
+      <c r="E58" s="28"/>
+      <c r="F58" s="28"/>
+      <c r="G58" s="28"/>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="B59" s="20"/>
-      <c r="C59" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="D59" s="20"/>
-      <c r="E59" s="20"/>
-      <c r="F59" s="20"/>
-      <c r="G59" s="20"/>
-    </row>
-    <row r="60" ht="39" spans="1:7">
-      <c r="A60" s="15" t="s">
+      <c r="A59" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="B60" s="20"/>
-      <c r="C60" s="20"/>
-      <c r="D60" s="16" t="s">
+      <c r="B59" s="28"/>
+      <c r="C59" s="24" t="s">
         <v>119</v>
       </c>
+      <c r="D59" s="28"/>
+      <c r="E59" s="28"/>
+      <c r="F59" s="28"/>
+      <c r="G59" s="28"/>
+    </row>
+    <row r="60" ht="52" spans="1:7">
+      <c r="A60" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="B60" s="28"/>
+      <c r="C60" s="28"/>
+      <c r="D60" s="24" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="B61" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="C61" s="12"/>
-      <c r="D61" s="20"/>
-      <c r="E61" s="20"/>
-      <c r="F61" s="20"/>
-      <c r="G61" s="20"/>
+      <c r="A61" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="B61" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="C61" s="20"/>
+      <c r="D61" s="28"/>
+      <c r="E61" s="28"/>
+      <c r="F61" s="28"/>
+      <c r="G61" s="28"/>
     </row>
     <row r="62" ht="39" spans="1:7">
-      <c r="A62" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="B62" s="20"/>
-      <c r="C62" s="20"/>
-      <c r="D62" s="16" t="s">
-        <v>123</v>
+      <c r="A62" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="B62" s="28"/>
+      <c r="C62" s="28"/>
+      <c r="D62" s="24" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="63" ht="26" spans="1:7">
-      <c r="A63" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="B63" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="C63" s="12" t="s">
+      <c r="A63" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="D63" s="20"/>
-      <c r="E63" s="20"/>
-      <c r="F63" s="20"/>
-      <c r="G63" s="20"/>
+      <c r="B63" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C63" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="D63" s="28"/>
+      <c r="E63" s="28"/>
+      <c r="F63" s="28"/>
+      <c r="G63" s="28"/>
     </row>
     <row r="64" ht="26" spans="1:7">
-      <c r="A64" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="B64" s="20"/>
-      <c r="C64" s="20"/>
-      <c r="D64" s="16" t="s">
-        <v>128</v>
+      <c r="A64" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="B64" s="28"/>
+      <c r="C64" s="28"/>
+      <c r="D64" s="24" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="65" ht="26" spans="1:7">
-      <c r="A65" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="B65" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="C65" s="20"/>
-      <c r="D65" s="20"/>
-      <c r="E65" s="20"/>
-      <c r="F65" s="20"/>
-      <c r="G65" s="20"/>
+      <c r="A65" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="B65" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="C65" s="28"/>
+      <c r="D65" s="28"/>
+      <c r="E65" s="28"/>
+      <c r="F65" s="28"/>
+      <c r="G65" s="28"/>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="B66" s="20"/>
-      <c r="C66" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="D66" s="20"/>
-      <c r="E66" s="20"/>
-      <c r="F66" s="20"/>
-      <c r="G66" s="20"/>
+      <c r="A66" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="B66" s="28"/>
+      <c r="C66" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="D66" s="28"/>
+      <c r="E66" s="28"/>
+      <c r="F66" s="28"/>
+      <c r="G66" s="28"/>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="B67" s="20"/>
-      <c r="C67" s="20"/>
+      <c r="A67" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="B67" s="28"/>
+      <c r="C67" s="28"/>
     </row>
     <row r="68" ht="26" spans="1:7">
-      <c r="A68" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="B68" s="20"/>
-      <c r="C68" s="20"/>
-      <c r="D68" s="16" t="s">
-        <v>135</v>
+      <c r="A68" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="B68" s="28"/>
+      <c r="C68" s="28"/>
+      <c r="D68" s="24" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="B69" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="C69" s="12"/>
+      <c r="A69" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="B69" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="C69" s="20"/>
     </row>
     <row r="70" ht="26" spans="1:7">
-      <c r="A70" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="B70" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="C70" s="12"/>
-      <c r="D70" s="20"/>
-      <c r="E70" s="20"/>
-      <c r="F70" s="20"/>
-      <c r="G70" s="20"/>
+      <c r="A70" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="B70" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="C70" s="20"/>
+      <c r="D70" s="28"/>
+      <c r="E70" s="28"/>
+      <c r="F70" s="28"/>
+      <c r="G70" s="28"/>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="B71" s="20"/>
-      <c r="C71" s="20"/>
+      <c r="A71" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="B71" s="28"/>
+      <c r="C71" s="28"/>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="B72" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="C72" s="16" t="s">
+      <c r="A72" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="D72" s="20"/>
-      <c r="E72" s="20"/>
-      <c r="F72" s="20"/>
-      <c r="G72" s="20"/>
+      <c r="B72" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="C72" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="D72" s="28"/>
+      <c r="E72" s="28"/>
+      <c r="F72" s="28"/>
+      <c r="G72" s="28"/>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="B73" s="20"/>
-      <c r="C73" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="D73" s="20"/>
-      <c r="E73" s="20"/>
-      <c r="F73" s="20"/>
-      <c r="G73" s="20"/>
+      <c r="A73" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="B73" s="28"/>
+      <c r="C73" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="D73" s="28"/>
+      <c r="E73" s="28"/>
+      <c r="F73" s="28"/>
+      <c r="G73" s="28"/>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="15" t="s">
-        <v>146</v>
+      <c r="A74" s="23" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="D75" s="20"/>
-      <c r="E75" s="20"/>
-      <c r="F75" s="20"/>
-      <c r="G75" s="20"/>
+      <c r="A75" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="D75" s="28"/>
+      <c r="E75" s="28"/>
+      <c r="F75" s="28"/>
+      <c r="G75" s="28"/>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="B76" s="20"/>
-      <c r="C76" s="20"/>
-      <c r="D76" s="16" t="s">
-        <v>149</v>
+      <c r="A76" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="B76" s="28"/>
+      <c r="C76" s="28"/>
+      <c r="D76" s="24" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="B77" s="12"/>
-      <c r="C77" s="12"/>
+      <c r="A77" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="B77" s="20"/>
+      <c r="C77" s="20"/>
     </row>
     <row r="78" ht="26" spans="1:7">
-      <c r="A78" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="B78" s="16" t="s">
-        <v>152</v>
+      <c r="A78" s="30" t="s">
+        <v>153</v>
+      </c>
+      <c r="B78" s="24" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -2452,229 +2522,229 @@
   <dimension ref="A1:G51"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="6.64545454545455" style="6" customWidth="1"/>
-    <col min="2" max="7" width="16.4909090909091" style="7" customWidth="1"/>
-    <col min="8" max="16384" width="8.72727272727273" style="8"/>
+    <col min="1" max="1" width="6.64545454545455" style="14" customWidth="1"/>
+    <col min="2" max="7" width="16.4909090909091" style="15" customWidth="1"/>
+    <col min="8" max="16384" width="8.72727272727273" style="16"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="9"/>
-      <c r="B1" s="10" t="s">
+      <c r="A1" s="17"/>
+      <c r="B1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="18" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="5" customFormat="1" ht="39" spans="1:7">
-      <c r="A2" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
+    <row r="2" s="13" customFormat="1" ht="39" spans="1:7">
+      <c r="A2" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>156</v>
+      <c r="A3" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>158</v>
+      <c r="A4" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="D5" s="7" t="s">
+      <c r="A5" s="21" t="s">
         <v>161</v>
       </c>
+      <c r="C5" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="D6" s="7" t="s">
+      <c r="A6" s="21" t="s">
         <v>164</v>
       </c>
+      <c r="B6" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="13"/>
+      <c r="A7" s="21"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="13"/>
+      <c r="A8" s="21"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="13"/>
+      <c r="A9" s="21"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="13"/>
+      <c r="A10" s="21"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="13"/>
+      <c r="A11" s="21"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="13"/>
+      <c r="A12" s="21"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="13"/>
+      <c r="A13" s="21"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="13"/>
+      <c r="A14" s="21"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="13"/>
+      <c r="A15" s="21"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="13"/>
+      <c r="A16" s="21"/>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="13"/>
+      <c r="A17" s="21"/>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="13"/>
+      <c r="A18" s="21"/>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="13"/>
+      <c r="A19" s="21"/>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="13"/>
+      <c r="A20" s="21"/>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="13"/>
+      <c r="A21" s="21"/>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="13"/>
+      <c r="A22" s="21"/>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="13"/>
+      <c r="A23" s="21"/>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="13"/>
+      <c r="A24" s="21"/>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="13"/>
+      <c r="A25" s="21"/>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="13"/>
+      <c r="A26" s="21"/>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="13"/>
+      <c r="A27" s="21"/>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="13"/>
+      <c r="A28" s="21"/>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="13"/>
+      <c r="A29" s="21"/>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="13"/>
+      <c r="A30" s="21"/>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="13"/>
+      <c r="A31" s="21"/>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="13"/>
+      <c r="A32" s="21"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="13"/>
+      <c r="A33" s="21"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="13"/>
+      <c r="A34" s="21"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="13"/>
+      <c r="A35" s="21"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="13"/>
+      <c r="A36" s="21"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="13"/>
+      <c r="A37" s="21"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="13"/>
-      <c r="B38" s="12"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="12"/>
+      <c r="A38" s="21"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="13"/>
-      <c r="B39" s="12"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="12"/>
+      <c r="A39" s="21"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="20"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="13"/>
+      <c r="A40" s="21"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="13"/>
+      <c r="A41" s="21"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="13"/>
+      <c r="A42" s="21"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="13"/>
+      <c r="A43" s="21"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="13"/>
+      <c r="A44" s="21"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="13"/>
+      <c r="A45" s="21"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="13"/>
+      <c r="A46" s="21"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="13"/>
+      <c r="A47" s="21"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="13"/>
+      <c r="A48" s="21"/>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="13"/>
+      <c r="A49" s="21"/>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="13"/>
+      <c r="A50" s="21"/>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="13"/>
+      <c r="A51" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2688,85 +2758,85 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="35.1818181818182" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.9090909090909" style="1" customWidth="1"/>
-    <col min="3" max="3" width="50.0909090909091" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="8.72727272727273" style="1"/>
+    <col min="1" max="1" width="35.1818181818182" style="9" customWidth="1"/>
+    <col min="2" max="2" width="16.9090909090909" style="9" customWidth="1"/>
+    <col min="3" max="3" width="50.0909090909091" style="10" customWidth="1"/>
+    <col min="4" max="16384" width="8.72727272727273" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="A1" s="9" t="s">
         <v>167</v>
       </c>
+      <c r="B1" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="A2" s="9" t="s">
         <v>170</v>
       </c>
+      <c r="B2" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="A3" s="9" t="s">
         <v>173</v>
       </c>
+      <c r="B3" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="4" ht="28" spans="1:3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>175</v>
+      <c r="C4" s="10" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="5" ht="42" spans="1:3">
-      <c r="A5" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="A5" s="11" t="s">
         <v>178</v>
       </c>
+      <c r="B5" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="6" ht="56" spans="1:3">
-      <c r="A6" s="4"/>
-      <c r="B6" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>180</v>
+      <c r="A6" s="12"/>
+      <c r="B6" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="7" ht="28" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="A7" s="9" t="s">
         <v>183</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -2776,4 +2846,182 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="9.18181818181818" style="1"/>
+    <col min="2" max="2" width="8.72727272727273" style="2"/>
+    <col min="3" max="3" width="41" style="2" customWidth="1"/>
+    <col min="4" max="16384" width="8.72727272727273" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="5">
+        <v>2025.1</v>
+      </c>
+      <c r="B2" s="6">
+        <v>11</v>
+      </c>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="7"/>
+      <c r="B3" s="6">
+        <v>15</v>
+      </c>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="7"/>
+      <c r="B4" s="6">
+        <v>17</v>
+      </c>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="7"/>
+      <c r="B5" s="6">
+        <v>22</v>
+      </c>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="7"/>
+      <c r="B6" s="6">
+        <v>24</v>
+      </c>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="7"/>
+      <c r="B7" s="6">
+        <v>29</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="8"/>
+      <c r="B8" s="6">
+        <v>31</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="5">
+        <v>2025.11</v>
+      </c>
+      <c r="B9" s="6">
+        <v>5</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="7"/>
+      <c r="B10" s="6">
+        <v>7</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="8"/>
+      <c r="B11" s="6">
+        <v>14</v>
+      </c>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="3">
+        <v>2025.12</v>
+      </c>
+      <c r="B12" s="6">
+        <v>5</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="D12" s="6"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="3"/>
+      <c r="B13" s="6">
+        <v>6</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="D13" s="6"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="3"/>
+      <c r="B14" s="6">
+        <v>9</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="D14" s="6"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="3"/>
+      <c r="B15" s="6">
+        <v>10</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D15" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:A8"/>
+    <mergeCell ref="A9:A11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10480" activeTab="3"/>
+    <workbookView windowWidth="20750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="学生、老师" sheetId="5" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="194">
   <si>
     <t>姓名</t>
   </si>
@@ -284,6 +284,9 @@
     <t>早读（劝学/磨刀霍霍向鑫洋）、生物30分、记笔记</t>
   </si>
   <si>
+    <t>孺子、反思（老了、相见时难别亦难，东风无力百花残、未来是你们，的但现在未必）（一旬老人）、哲学（旁观者：学地理要以旁观者视角、水循环：逆水行舟，退到极点就是进）</t>
+  </si>
+  <si>
     <t>游武毅</t>
   </si>
   <si>
@@ -606,6 +609,9 @@
   </si>
   <si>
     <t>6，22，30，42，44，48</t>
+  </si>
+  <si>
+    <t>38，42</t>
   </si>
 </sst>
 </file>
@@ -1350,7 +1356,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1368,9 +1374,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1777,709 +1780,712 @@
   <dimension ref="A1:G78"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="7.59090909090909" style="23" customWidth="1"/>
-    <col min="2" max="7" width="25.8727272727273" style="24" customWidth="1"/>
+    <col min="1" max="1" width="7.59090909090909" style="22" customWidth="1"/>
+    <col min="2" max="7" width="25.8727272727273" style="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="22" customFormat="1" spans="1:7">
-      <c r="A1" s="25" t="s">
+    <row r="1" s="21" customFormat="1" spans="1:7">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="G1" s="25" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="23" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" ht="39" spans="1:7">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="23" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="26" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="23" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="23" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" ht="195" spans="1:7">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="23" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="26" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="26" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="23" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="26" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="26" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="13" ht="26" spans="1:7">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="24" t="s">
+      <c r="D13" s="23" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="23" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="27" t="s">
+      <c r="A15" s="26" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="17" ht="26" spans="1:4">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="C17" s="23" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="26" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="26" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="20" ht="26" spans="1:4">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="24" t="s">
+      <c r="C20" s="23" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="21" ht="39" spans="1:4">
-      <c r="A21" s="27" t="s">
+      <c r="A21" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="24" t="s">
+      <c r="C21" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="D21" s="24" t="s">
+      <c r="D21" s="23" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="27" t="s">
+      <c r="A22" s="26" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="23" ht="26" spans="1:4">
-      <c r="A23" s="27" t="s">
+      <c r="A23" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="24" t="s">
+      <c r="B23" s="23" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="24" ht="52" spans="1:4">
-      <c r="A24" s="27" t="s">
+      <c r="A24" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="24" t="s">
+      <c r="B24" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="24" t="s">
+      <c r="C24" s="23" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="27" t="s">
+      <c r="A25" s="26" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="27" t="s">
+      <c r="A26" s="26" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="27" t="s">
+      <c r="A27" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="24" t="s">
+      <c r="B27" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="24" t="s">
+      <c r="C27" s="23" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="28" ht="91" spans="1:4">
-      <c r="A28" s="27" t="s">
+      <c r="A28" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="B28" s="24" t="s">
+      <c r="B28" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="C28" s="24" t="s">
+      <c r="C28" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="D28" s="24" t="s">
+      <c r="D28" s="23" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="27" t="s">
+      <c r="A29" s="26" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="27" t="s">
+      <c r="A30" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="B30" s="24" t="s">
+      <c r="B30" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="C30" s="24" t="s">
+      <c r="C30" s="23" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="27" t="s">
+      <c r="A31" s="26" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="27" t="s">
+      <c r="A32" s="26" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="27" t="s">
+      <c r="A33" s="26" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="27" t="s">
+      <c r="A34" s="26" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="27" t="s">
+      <c r="A35" s="26" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="27" t="s">
+      <c r="A36" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="24" t="s">
+      <c r="B36" s="23" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="37" ht="26" spans="1:7">
-      <c r="A37" s="27" t="s">
+      <c r="A37" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="C37" s="24" t="s">
+      <c r="C37" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="D37" s="24" t="s">
+      <c r="D37" s="23" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="27" t="s">
+      <c r="A38" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="B38" s="24" t="s">
+      <c r="B38" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="28"/>
+      <c r="C38" s="27"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="27"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="27" t="s">
+      <c r="A39" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="C39" s="24" t="s">
+      <c r="C39" s="23" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="27" t="s">
+      <c r="A40" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="B40" s="24" t="s">
+      <c r="B40" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="C40" s="24" t="s">
+      <c r="C40" s="23" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="41" ht="26" spans="1:7">
-      <c r="A41" s="27" t="s">
+    <row r="41" ht="91" spans="1:7">
+      <c r="A41" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="C41" s="24" t="s">
+      <c r="C41" s="23" t="s">
         <v>83</v>
       </c>
+      <c r="D41" s="23" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="27" t="s">
-        <v>84</v>
+      <c r="A42" s="26" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="27" t="s">
-        <v>85</v>
-      </c>
-      <c r="B43" s="24" t="s">
+      <c r="A43" s="26" t="s">
         <v>86</v>
       </c>
+      <c r="B43" s="23" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="44" ht="26" spans="1:7">
-      <c r="A44" s="27" t="s">
-        <v>87</v>
-      </c>
-      <c r="B44" s="24" t="s">
+      <c r="A44" s="26" t="s">
         <v>88</v>
       </c>
+      <c r="B44" s="23" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="27" t="s">
-        <v>89</v>
-      </c>
-      <c r="D45" s="24" t="s">
+      <c r="A45" s="26" t="s">
         <v>90</v>
       </c>
+      <c r="D45" s="23" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="27" t="s">
-        <v>91</v>
+      <c r="A46" s="26" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="27" t="s">
-        <v>92</v>
+      <c r="A47" s="26" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C48" s="24" t="s">
+      <c r="A48" s="26" t="s">
         <v>94</v>
       </c>
+      <c r="C48" s="23" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="27" t="s">
-        <v>95</v>
+      <c r="A49" s="26" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="50" ht="78" spans="1:7">
-      <c r="A50" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="C50" s="24" t="s">
+      <c r="A50" s="26" t="s">
         <v>97</v>
       </c>
+      <c r="C50" s="23" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="27" t="s">
-        <v>98</v>
+      <c r="A51" s="26" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="52" ht="26" spans="1:7">
-      <c r="A52" s="27" t="s">
-        <v>99</v>
-      </c>
-      <c r="B52" s="24" t="s">
+      <c r="A52" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="C52" s="24" t="s">
+      <c r="B52" s="23" t="s">
         <v>101</v>
       </c>
+      <c r="C52" s="23" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="53" ht="26" spans="1:7">
-      <c r="A53" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="B53" s="24" t="s">
+      <c r="A53" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="D53" s="28"/>
-      <c r="E53" s="28"/>
-      <c r="F53" s="28"/>
-      <c r="G53" s="28"/>
+      <c r="B53" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="D53" s="27"/>
+      <c r="E53" s="27"/>
+      <c r="F53" s="27"/>
+      <c r="G53" s="27"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="B54" s="24" t="s">
+      <c r="A54" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="C54" s="24" t="s">
+      <c r="B54" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="D54" s="28"/>
-      <c r="E54" s="28"/>
-      <c r="F54" s="28"/>
-      <c r="G54" s="28"/>
+      <c r="C54" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="D54" s="27"/>
+      <c r="E54" s="27"/>
+      <c r="F54" s="27"/>
+      <c r="G54" s="27"/>
     </row>
     <row r="55" ht="52" spans="1:7">
-      <c r="A55" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="B55" s="28"/>
-      <c r="C55" s="28"/>
-      <c r="D55" s="24" t="s">
+      <c r="A55" s="22" t="s">
         <v>108</v>
       </c>
+      <c r="B55" s="27"/>
+      <c r="C55" s="27"/>
+      <c r="D55" s="23" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="56" ht="65" spans="1:7">
-      <c r="A56" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="B56" s="20" t="s">
+      <c r="A56" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="C56" s="20"/>
-      <c r="D56" s="24" t="s">
+      <c r="B56" s="19" t="s">
         <v>111</v>
       </c>
+      <c r="C56" s="19"/>
+      <c r="D56" s="23" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="57" ht="117" spans="1:7">
-      <c r="A57" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="B57" s="20" t="s">
+      <c r="A57" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="C57" s="20" t="s">
+      <c r="B57" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="D57" s="24" t="s">
+      <c r="C57" s="19" t="s">
         <v>115</v>
       </c>
+      <c r="D57" s="23" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="B58" s="24" t="s">
+      <c r="A58" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="C58" s="28"/>
-      <c r="D58" s="28"/>
-      <c r="E58" s="28"/>
-      <c r="F58" s="28"/>
-      <c r="G58" s="28"/>
+      <c r="B58" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="C58" s="27"/>
+      <c r="D58" s="27"/>
+      <c r="E58" s="27"/>
+      <c r="F58" s="27"/>
+      <c r="G58" s="27"/>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="B59" s="28"/>
-      <c r="C59" s="24" t="s">
+      <c r="A59" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="D59" s="28"/>
-      <c r="E59" s="28"/>
-      <c r="F59" s="28"/>
-      <c r="G59" s="28"/>
+      <c r="B59" s="27"/>
+      <c r="C59" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="D59" s="27"/>
+      <c r="E59" s="27"/>
+      <c r="F59" s="27"/>
+      <c r="G59" s="27"/>
     </row>
     <row r="60" ht="52" spans="1:7">
-      <c r="A60" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="B60" s="28"/>
-      <c r="C60" s="28"/>
-      <c r="D60" s="24" t="s">
+      <c r="A60" s="22" t="s">
         <v>121</v>
       </c>
+      <c r="B60" s="27"/>
+      <c r="C60" s="27"/>
+      <c r="D60" s="23" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="23" t="s">
-        <v>122</v>
-      </c>
-      <c r="B61" s="20" t="s">
+      <c r="A61" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="C61" s="20"/>
-      <c r="D61" s="28"/>
-      <c r="E61" s="28"/>
-      <c r="F61" s="28"/>
-      <c r="G61" s="28"/>
+      <c r="B61" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="27"/>
+      <c r="E61" s="27"/>
+      <c r="F61" s="27"/>
+      <c r="G61" s="27"/>
     </row>
     <row r="62" ht="39" spans="1:7">
-      <c r="A62" s="23" t="s">
-        <v>124</v>
-      </c>
-      <c r="B62" s="28"/>
-      <c r="C62" s="28"/>
-      <c r="D62" s="24" t="s">
+      <c r="A62" s="22" t="s">
         <v>125</v>
       </c>
+      <c r="B62" s="27"/>
+      <c r="C62" s="27"/>
+      <c r="D62" s="23" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="63" ht="26" spans="1:7">
-      <c r="A63" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="B63" s="20" t="s">
+      <c r="A63" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="C63" s="20" t="s">
+      <c r="B63" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="D63" s="28"/>
-      <c r="E63" s="28"/>
-      <c r="F63" s="28"/>
-      <c r="G63" s="28"/>
+      <c r="C63" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="D63" s="27"/>
+      <c r="E63" s="27"/>
+      <c r="F63" s="27"/>
+      <c r="G63" s="27"/>
     </row>
     <row r="64" ht="26" spans="1:7">
-      <c r="A64" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="B64" s="28"/>
-      <c r="C64" s="28"/>
-      <c r="D64" s="24" t="s">
+      <c r="A64" s="22" t="s">
         <v>130</v>
       </c>
+      <c r="B64" s="27"/>
+      <c r="C64" s="27"/>
+      <c r="D64" s="23" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="65" ht="26" spans="1:7">
-      <c r="A65" s="23" t="s">
-        <v>131</v>
-      </c>
-      <c r="B65" s="29" t="s">
+      <c r="A65" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="C65" s="28"/>
-      <c r="D65" s="28"/>
-      <c r="E65" s="28"/>
-      <c r="F65" s="28"/>
-      <c r="G65" s="28"/>
+      <c r="B65" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="C65" s="27"/>
+      <c r="D65" s="27"/>
+      <c r="E65" s="27"/>
+      <c r="F65" s="27"/>
+      <c r="G65" s="27"/>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="B66" s="28"/>
-      <c r="C66" s="24" t="s">
+      <c r="A66" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="D66" s="28"/>
-      <c r="E66" s="28"/>
-      <c r="F66" s="28"/>
-      <c r="G66" s="28"/>
+      <c r="B66" s="27"/>
+      <c r="C66" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="D66" s="27"/>
+      <c r="E66" s="27"/>
+      <c r="F66" s="27"/>
+      <c r="G66" s="27"/>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="B67" s="28"/>
-      <c r="C67" s="28"/>
+      <c r="A67" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="B67" s="27"/>
+      <c r="C67" s="27"/>
     </row>
     <row r="68" ht="26" spans="1:7">
-      <c r="A68" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="B68" s="28"/>
-      <c r="C68" s="28"/>
-      <c r="D68" s="24" t="s">
+      <c r="A68" s="22" t="s">
         <v>137</v>
       </c>
+      <c r="B68" s="27"/>
+      <c r="C68" s="27"/>
+      <c r="D68" s="23" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="B69" s="20" t="s">
+      <c r="A69" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="C69" s="20"/>
+      <c r="B69" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="C69" s="19"/>
     </row>
     <row r="70" ht="26" spans="1:7">
-      <c r="A70" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="B70" s="20" t="s">
+      <c r="A70" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="C70" s="20"/>
-      <c r="D70" s="28"/>
-      <c r="E70" s="28"/>
-      <c r="F70" s="28"/>
-      <c r="G70" s="28"/>
+      <c r="B70" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="C70" s="19"/>
+      <c r="D70" s="27"/>
+      <c r="E70" s="27"/>
+      <c r="F70" s="27"/>
+      <c r="G70" s="27"/>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="23" t="s">
-        <v>142</v>
-      </c>
-      <c r="B71" s="28"/>
-      <c r="C71" s="28"/>
+      <c r="A71" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="B71" s="27"/>
+      <c r="C71" s="27"/>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="23" t="s">
-        <v>143</v>
-      </c>
-      <c r="B72" s="24" t="s">
+      <c r="A72" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="C72" s="24" t="s">
+      <c r="B72" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="D72" s="28"/>
-      <c r="E72" s="28"/>
-      <c r="F72" s="28"/>
-      <c r="G72" s="28"/>
+      <c r="C72" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="D72" s="27"/>
+      <c r="E72" s="27"/>
+      <c r="F72" s="27"/>
+      <c r="G72" s="27"/>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="B73" s="28"/>
-      <c r="C73" s="24" t="s">
+      <c r="A73" s="22" t="s">
         <v>147</v>
       </c>
-      <c r="D73" s="28"/>
-      <c r="E73" s="28"/>
-      <c r="F73" s="28"/>
-      <c r="G73" s="28"/>
+      <c r="B73" s="27"/>
+      <c r="C73" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="D73" s="27"/>
+      <c r="E73" s="27"/>
+      <c r="F73" s="27"/>
+      <c r="G73" s="27"/>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="23" t="s">
-        <v>148</v>
+      <c r="A74" s="22" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="D75" s="28"/>
-      <c r="E75" s="28"/>
-      <c r="F75" s="28"/>
-      <c r="G75" s="28"/>
+      <c r="A75" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="D75" s="27"/>
+      <c r="E75" s="27"/>
+      <c r="F75" s="27"/>
+      <c r="G75" s="27"/>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="23" t="s">
-        <v>150</v>
-      </c>
-      <c r="B76" s="28"/>
-      <c r="C76" s="28"/>
-      <c r="D76" s="24" t="s">
+      <c r="A76" s="22" t="s">
         <v>151</v>
       </c>
+      <c r="B76" s="27"/>
+      <c r="C76" s="27"/>
+      <c r="D76" s="23" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="B77" s="20"/>
-      <c r="C77" s="20"/>
+      <c r="A77" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="B77" s="19"/>
+      <c r="C77" s="19"/>
     </row>
     <row r="78" ht="26" spans="1:7">
-      <c r="A78" s="30" t="s">
-        <v>153</v>
-      </c>
-      <c r="B78" s="24" t="s">
+      <c r="A78" s="29" t="s">
         <v>154</v>
+      </c>
+      <c r="B78" s="23" t="s">
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -2522,229 +2528,229 @@
   <dimension ref="A1:G51"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="6.64545454545455" style="14" customWidth="1"/>
-    <col min="2" max="7" width="16.4909090909091" style="15" customWidth="1"/>
-    <col min="8" max="16384" width="8.72727272727273" style="16"/>
+    <col min="1" max="1" width="6.64545454545455" style="13" customWidth="1"/>
+    <col min="2" max="7" width="16.4909090909091" style="14" customWidth="1"/>
+    <col min="8" max="16384" width="8.72727272727273" style="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="17"/>
-      <c r="B1" s="18" t="s">
+      <c r="A1" s="16"/>
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="17" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="13" customFormat="1" ht="39" spans="1:7">
-      <c r="A2" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20" t="s">
+    <row r="2" s="12" customFormat="1" ht="39" spans="1:7">
+      <c r="A2" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="C3" s="15" t="s">
+      <c r="A3" s="20" t="s">
         <v>158</v>
       </c>
+      <c r="C3" s="14" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="B4" s="15" t="s">
+      <c r="A4" s="20" t="s">
         <v>160</v>
       </c>
+      <c r="B4" s="14" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="C5" s="15" t="s">
+      <c r="A5" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>163</v>
       </c>
+      <c r="D5" s="14" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="21" t="s">
-        <v>164</v>
-      </c>
-      <c r="B6" s="15" t="s">
+      <c r="A6" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="B6" s="14" t="s">
         <v>166</v>
       </c>
+      <c r="D6" s="14" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="21"/>
+      <c r="A7" s="20"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="21"/>
+      <c r="A8" s="20"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="21"/>
+      <c r="A9" s="20"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="21"/>
+      <c r="A10" s="20"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="21"/>
+      <c r="A11" s="20"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="21"/>
+      <c r="A12" s="20"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="21"/>
+      <c r="A13" s="20"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="21"/>
+      <c r="A14" s="20"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="21"/>
+      <c r="A15" s="20"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="21"/>
+      <c r="A16" s="20"/>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="21"/>
+      <c r="A17" s="20"/>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="21"/>
+      <c r="A18" s="20"/>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="21"/>
+      <c r="A19" s="20"/>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="21"/>
+      <c r="A20" s="20"/>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="21"/>
+      <c r="A21" s="20"/>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="21"/>
+      <c r="A22" s="20"/>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="21"/>
+      <c r="A23" s="20"/>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="21"/>
+      <c r="A24" s="20"/>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="21"/>
+      <c r="A25" s="20"/>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="21"/>
+      <c r="A26" s="20"/>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="21"/>
+      <c r="A27" s="20"/>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="21"/>
+      <c r="A28" s="20"/>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="21"/>
+      <c r="A29" s="20"/>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="21"/>
+      <c r="A30" s="20"/>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="21"/>
+      <c r="A31" s="20"/>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="21"/>
+      <c r="A32" s="20"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="21"/>
+      <c r="A33" s="20"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="21"/>
+      <c r="A34" s="20"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="21"/>
+      <c r="A35" s="20"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="21"/>
+      <c r="A36" s="20"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="21"/>
+      <c r="A37" s="20"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="21"/>
-      <c r="B38" s="20"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
+      <c r="A38" s="20"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="21"/>
-      <c r="B39" s="20"/>
-      <c r="C39" s="20"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="20"/>
-      <c r="G39" s="20"/>
+      <c r="A39" s="20"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="21"/>
+      <c r="A40" s="20"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="21"/>
+      <c r="A41" s="20"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="21"/>
+      <c r="A42" s="20"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="21"/>
+      <c r="A43" s="20"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="21"/>
+      <c r="A44" s="20"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="21"/>
+      <c r="A45" s="20"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="21"/>
+      <c r="A46" s="20"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="21"/>
+      <c r="A47" s="20"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="21"/>
+      <c r="A48" s="20"/>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="21"/>
+      <c r="A49" s="20"/>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="21"/>
+      <c r="A50" s="20"/>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="21"/>
+      <c r="A51" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2758,85 +2764,85 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="35.1818181818182" style="9" customWidth="1"/>
-    <col min="2" max="2" width="16.9090909090909" style="9" customWidth="1"/>
-    <col min="3" max="3" width="50.0909090909091" style="10" customWidth="1"/>
-    <col min="4" max="16384" width="8.72727272727273" style="9"/>
+    <col min="1" max="1" width="35.1818181818182" style="8" customWidth="1"/>
+    <col min="2" max="2" width="16.9090909090909" style="8" customWidth="1"/>
+    <col min="3" max="3" width="50.0909090909091" style="9" customWidth="1"/>
+    <col min="4" max="16384" width="8.72727272727273" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="B1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>169</v>
       </c>
+      <c r="C1" s="9" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="B2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="B2" s="8" t="s">
         <v>172</v>
       </c>
+      <c r="C2" s="9" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="B3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="B3" s="8" t="s">
         <v>175</v>
       </c>
+      <c r="C3" s="9" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="4" ht="28" spans="1:3">
-      <c r="A4" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="C4" s="10" t="s">
+      <c r="A4" s="8" t="s">
         <v>177</v>
       </c>
+      <c r="B4" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="5" ht="42" spans="1:3">
-      <c r="A5" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="B5" s="9" t="s">
+      <c r="A5" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="B5" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="C5" s="9" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="6" ht="56" spans="1:3">
-      <c r="A6" s="12"/>
-      <c r="B6" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="C6" s="10" t="s">
+      <c r="A6" s="11"/>
+      <c r="B6" s="8" t="s">
         <v>182</v>
       </c>
+      <c r="C6" s="9" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="7" ht="28" spans="1:3">
-      <c r="A7" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="B7" s="9" t="s">
+      <c r="A7" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="B7" s="8" t="s">
         <v>185</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -2851,7 +2857,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="9.18181818181818" style="1"/>
@@ -2864,81 +2870,81 @@
       <c r="A1" s="3"/>
       <c r="B1" s="4"/>
       <c r="C1" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="5">
         <v>2025.1</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="4">
         <v>11</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6">
+      <c r="C2" s="4"/>
+      <c r="D2" s="4">
         <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="7"/>
-      <c r="B3" s="6">
+      <c r="A3" s="6"/>
+      <c r="B3" s="4">
         <v>15</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6">
+      <c r="C3" s="4"/>
+      <c r="D3" s="4">
         <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="7"/>
-      <c r="B4" s="6">
+      <c r="A4" s="6"/>
+      <c r="B4" s="4">
         <v>17</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6">
+      <c r="C4" s="4"/>
+      <c r="D4" s="4">
         <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="7"/>
-      <c r="B5" s="6">
+      <c r="A5" s="6"/>
+      <c r="B5" s="4">
         <v>22</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6">
+      <c r="C5" s="4"/>
+      <c r="D5" s="4">
         <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="7"/>
-      <c r="B6" s="6">
+      <c r="A6" s="6"/>
+      <c r="B6" s="4">
         <v>24</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6">
+      <c r="C6" s="4"/>
+      <c r="D6" s="4">
         <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="7"/>
-      <c r="B7" s="6">
+      <c r="A7" s="6"/>
+      <c r="B7" s="4">
         <v>29</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6">
+      <c r="C7" s="4"/>
+      <c r="D7" s="4">
         <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="8"/>
-      <c r="B8" s="6">
+      <c r="A8" s="7"/>
+      <c r="B8" s="4">
         <v>31</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6">
+      <c r="C8" s="4"/>
+      <c r="D8" s="4">
         <v>89</v>
       </c>
     </row>
@@ -2946,31 +2952,31 @@
       <c r="A9" s="5">
         <v>2025.11</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="4">
         <v>5</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6">
+      <c r="C9" s="4"/>
+      <c r="D9" s="4">
         <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="7"/>
-      <c r="B10" s="6">
+      <c r="A10" s="6"/>
+      <c r="B10" s="4">
         <v>7</v>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6">
+      <c r="C10" s="4"/>
+      <c r="D10" s="4">
         <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="8"/>
-      <c r="B11" s="6">
+      <c r="A11" s="7"/>
+      <c r="B11" s="4">
         <v>14</v>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6">
+      <c r="C11" s="4"/>
+      <c r="D11" s="4">
         <v>63</v>
       </c>
     </row>
@@ -2978,43 +2984,51 @@
       <c r="A12" s="3">
         <v>2025.12</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="4">
         <v>5</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D12" s="6"/>
+        <v>189</v>
+      </c>
+      <c r="D12" s="4"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="3"/>
-      <c r="B13" s="6">
+      <c r="B13" s="4">
         <v>6</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="D13" s="6"/>
+        <v>190</v>
+      </c>
+      <c r="D13" s="4"/>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="3"/>
-      <c r="B14" s="6">
+      <c r="B14" s="4">
         <v>9</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="D14" s="6"/>
+        <v>191</v>
+      </c>
+      <c r="D14" s="4"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="3"/>
-      <c r="B15" s="6">
+      <c r="B15" s="4">
         <v>10</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="D15" s="6"/>
+        <v>192</v>
+      </c>
+      <c r="D15" s="4"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="B16" s="2">
+        <v>11</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>193</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -95,7 +95,7 @@
     <t>祥懿又是你、午餐（芹菜炒肉、土豆丝、秋葵、番茄酱）课间吃饭、画画、捏/咬/打人、炫耀、演讲、喵喵姐</t>
   </si>
   <si>
-    <t>萌、上课吃东西（早上水果，下午菜，下午高峰）（泡鸭爪/棒棒糖/营养品（长高）/奥利奥）、作业没写应对方式（没带法、证人法、偶然法、不会法、以为法、灭口法、自我安慰法）、宣泄、睡觉（低头/点头）、带读（一，起）、水杯倒（不盖盖）、尼玛的、东西被陆梓豪偷吃、排队时讲话、我又……上了、我不行了……、自己做了……→谁做了……啊！、告状、动作、英语小测翻书/笔记、隔班借作业抄、废啊</t>
+    <t>萌、上课吃东西（早上水果，下午菜，下午高峰）（泡鸭爪/棒棒糖/营养品（长高）/奥利奥）、作业没写应对方式（没带法、证人法、偶然法、不会法、以为法、灭口法、自我安慰法）、宣泄、睡觉（低头/点头）、带读（一，起）、水杯倒（不盖盖）、尼玛的、东西被陆梓豪偷吃、排队时讲话、我又……上了、我不行了……、自己做了……→谁做了……啊！、告状、动作、英语小测翻书/笔记、隔班借作业抄、废啊、（12.11）带仓鼠</t>
   </si>
   <si>
     <t>林钰颖</t>
@@ -380,7 +380,7 @@
     <t>跑操造句</t>
   </si>
   <si>
-    <t>请假13个工作日（作业减、早读乱、大脚）、投屏打字、收作业制度、男厕洗手、量化制度、监控、电脑控制</t>
+    <t>请假13个工作日（作业减、早读乱、大脚）、投屏打字、收作业制度、男厕洗手、量化制度、监控、电脑控制、周五末节读书</t>
   </si>
   <si>
     <t>政1</t>

--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="200">
   <si>
     <t>姓名</t>
   </si>
@@ -167,7 +167,7 @@
     <t>爆胎</t>
   </si>
   <si>
-    <t>踩桌子通行</t>
+    <t>踩桌子通行、对臭味敏感</t>
   </si>
   <si>
     <t>张桢烨</t>
@@ -284,7 +284,7 @@
     <t>早读（劝学/磨刀霍霍向鑫洋）、生物30分、记笔记</t>
   </si>
   <si>
-    <t>孺子、反思（老了、相见时难别亦难，东风无力百花残、未来是你们，的但现在未必）（一旬老人）、哲学（旁观者：学地理要以旁观者视角、水循环：逆水行舟，退到极点就是进）</t>
+    <t>孺子、反思（我也老了、相见时难别亦难，东风无力百花残、未来是你们，但现在未必、革命尚未成功）（一旬老人）、哲学（旁观者：学地理要以旁观者视角、水循环：逆水行舟，退到极点就是进）、装（问第几题有问题，体现自己做得快、费马点）、考进班级前10</t>
   </si>
   <si>
     <t>游武毅</t>
@@ -446,7 +446,7 @@
     <t>物1</t>
   </si>
   <si>
-    <t>读“m”“l”“等于”、写“解”、M来了</t>
+    <t>读“m”“l”“等于”、写“解”、M来了、给课代表买奶茶</t>
   </si>
   <si>
     <t>体1</t>
@@ -591,6 +591,24 @@
   </si>
   <si>
     <t>活动课下课，外面人讨论阮贞铭和江乐萱，郑永泽比“嘘”、盯着阮贞铭并嘴角上扬</t>
+  </si>
+  <si>
+    <t>洪鑫洋装</t>
+  </si>
+  <si>
+    <t>八上12.17</t>
+  </si>
+  <si>
+    <t>数：十字相乘是不是还没讲？洪：数学书上都有写。生：哇……卓：被你装到我都受不了了。</t>
+  </si>
+  <si>
+    <t>孔祥懿睡觉</t>
+  </si>
+  <si>
+    <t>八上12.16</t>
+  </si>
+  <si>
+    <t>物：头都快埋到地板上去了。</t>
   </si>
   <si>
     <t>数学请人</t>
@@ -2115,7 +2133,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="41" ht="91" spans="1:7">
+    <row r="41" ht="130" spans="1:7">
       <c r="A41" s="26" t="s">
         <v>82</v>
       </c>
@@ -2761,8 +2779,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="2"/>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="35.1818181818182" style="8" customWidth="1"/>
     <col min="2" max="2" width="16.9090909090909" style="8" customWidth="1"/>
@@ -2843,6 +2861,28 @@
       </c>
       <c r="C7" s="9" t="s">
         <v>186</v>
+      </c>
+    </row>
+    <row r="8" ht="28" spans="1:3">
+      <c r="A8" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -2870,10 +2910,10 @@
       <c r="A1" s="3"/>
       <c r="B1" s="4"/>
       <c r="C1" s="4" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2988,7 +3028,7 @@
         <v>5</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D12" s="4"/>
     </row>
@@ -2998,7 +3038,7 @@
         <v>6</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="D13" s="4"/>
     </row>
@@ -3008,7 +3048,7 @@
         <v>9</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D14" s="4"/>
     </row>
@@ -3018,7 +3058,7 @@
         <v>10</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="D15" s="4"/>
     </row>
@@ -3027,7 +3067,7 @@
         <v>11</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>

--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10480"/>
+    <workbookView windowWidth="20750" windowHeight="10030" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="学生、老师" sheetId="5" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="211">
   <si>
     <t>姓名</t>
   </si>
@@ -68,7 +68,7 @@
     <t>猴、郑致辰</t>
   </si>
   <si>
-    <t>带菜（给孔保管）、小测降等级、测心电图时对薛阅晨说“在这里！”、小心点</t>
+    <t>带菜（给孔保管）、小测降等级、测心电图时对薛阅晨说“在这里！”、小心点、尖叫</t>
   </si>
   <si>
     <t>郭沁诗</t>
@@ -119,7 +119,7 @@
     <t>郑永泽</t>
   </si>
   <si>
-    <t>阮贞铭（眼光）、炸蛋脚（打人招数）</t>
+    <t>阮贞铭（眼光）、炸蛋脚（打人招数）、美国有乔丹中国有永泽</t>
   </si>
   <si>
     <t>郑致辰</t>
@@ -146,9 +146,15 @@
     <t>俞昕辰</t>
   </si>
   <si>
+    <t>有病啊！</t>
+  </si>
+  <si>
     <t>李欢颜</t>
   </si>
   <si>
+    <t>跑操回班速度</t>
+  </si>
+  <si>
     <t>廖成羲</t>
   </si>
   <si>
@@ -167,7 +173,7 @@
     <t>爆胎</t>
   </si>
   <si>
-    <t>踩桌子通行、对臭味敏感</t>
+    <t>踩桌子通行、对臭味敏感、头痛/腰痛/骨折/受伤、伙食</t>
   </si>
   <si>
     <t>张桢烨</t>
@@ -269,6 +275,9 @@
     <t>嘴甜、郑永泽</t>
   </si>
   <si>
+    <t>受着呗、……的都是gay、我操！</t>
+  </si>
+  <si>
     <t>蔡华楷</t>
   </si>
   <si>
@@ -630,6 +639,30 @@
   </si>
   <si>
     <t>38，42</t>
+  </si>
+  <si>
+    <t>5，14，22，44，46</t>
+  </si>
+  <si>
+    <t>6，7，11，26，28，29，35，38，40，42，44，47</t>
+  </si>
+  <si>
+    <t>2，6，7，13，20，22，29，30，35，36，38，42，44</t>
+  </si>
+  <si>
+    <t>2，6，7，19，20，30，35，38，39，40，42，44</t>
+  </si>
+  <si>
+    <t>2，3，26，40，44</t>
+  </si>
+  <si>
+    <t>4，6，9，11，12，13，18，19，38，40，42，44</t>
+  </si>
+  <si>
+    <t>7，13，27，40，44，47</t>
+  </si>
+  <si>
+    <t>6，9，11，17，30，35，40，44，46</t>
   </si>
 </sst>
 </file>
@@ -642,15 +675,10 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1226,151 +1254,151 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1381,34 +1409,34 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1417,52 +1445,52 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1910,7 +1938,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" ht="26" spans="1:7">
+    <row r="13" ht="39" spans="1:7">
       <c r="A13" s="26" t="s">
         <v>28</v>
       </c>
@@ -1951,162 +1979,171 @@
       <c r="A18" s="26" t="s">
         <v>37</v>
       </c>
+      <c r="D18" s="23" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="26" t="s">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="20" ht="26" spans="1:4">
       <c r="A20" s="26" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" ht="39" spans="1:4">
       <c r="A21" s="26" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="26" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" ht="26" spans="1:4">
       <c r="A23" s="26" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" ht="52" spans="1:4">
       <c r="A24" s="26" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>51</v>
+        <v>53</v>
+      </c>
+      <c r="D24" s="23" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="26" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="26" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="26" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" ht="91" spans="1:4">
       <c r="A28" s="26" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="26" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="26" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="26" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="26" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="26" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="26" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="26" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="26" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37" ht="26" spans="1:7">
       <c r="A37" s="26" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D37" s="23" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="26" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C38" s="27"/>
       <c r="D38" s="27"/>
@@ -2114,118 +2151,121 @@
       <c r="F38" s="27"/>
       <c r="G38" s="27"/>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" ht="26" spans="1:7">
       <c r="A39" s="26" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>78</v>
+        <v>80</v>
+      </c>
+      <c r="D39" s="23" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="26" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C40" s="23" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" ht="130" spans="1:7">
       <c r="A41" s="26" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C41" s="23" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D41" s="23" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="26" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="26" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44" ht="26" spans="1:7">
       <c r="A44" s="26" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B44" s="23" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="26" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D45" s="23" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="26" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="26" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="26" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C48" s="23" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="26" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="50" ht="78" spans="1:7">
       <c r="A50" s="26" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C50" s="23" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="26" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="52" ht="26" spans="1:7">
       <c r="A52" s="26" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B52" s="23" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C52" s="23" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="53" ht="26" spans="1:7">
       <c r="A53" s="22" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B53" s="23" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D53" s="27"/>
       <c r="E53" s="27"/>
@@ -2234,13 +2274,13 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="22" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B54" s="23" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C54" s="23" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D54" s="27"/>
       <c r="E54" s="27"/>
@@ -2249,46 +2289,46 @@
     </row>
     <row r="55" ht="52" spans="1:7">
       <c r="A55" s="22" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B55" s="27"/>
       <c r="C55" s="27"/>
       <c r="D55" s="23" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="56" ht="65" spans="1:7">
       <c r="A56" s="22" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C56" s="19"/>
       <c r="D56" s="23" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="57" ht="117" spans="1:7">
       <c r="A57" s="22" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D57" s="23" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="22" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B58" s="23" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C58" s="27"/>
       <c r="D58" s="27"/>
@@ -2298,11 +2338,11 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="22" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B59" s="27"/>
       <c r="C59" s="23" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D59" s="27"/>
       <c r="E59" s="27"/>
@@ -2311,20 +2351,20 @@
     </row>
     <row r="60" ht="52" spans="1:7">
       <c r="A60" s="22" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B60" s="27"/>
       <c r="C60" s="27"/>
       <c r="D60" s="23" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="22" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C61" s="19"/>
       <c r="D61" s="27"/>
@@ -2334,23 +2374,23 @@
     </row>
     <row r="62" ht="39" spans="1:7">
       <c r="A62" s="22" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B62" s="27"/>
       <c r="C62" s="27"/>
       <c r="D62" s="23" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="63" ht="26" spans="1:7">
       <c r="A63" s="22" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D63" s="27"/>
       <c r="E63" s="27"/>
@@ -2359,20 +2399,20 @@
     </row>
     <row r="64" ht="26" spans="1:7">
       <c r="A64" s="22" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B64" s="27"/>
       <c r="C64" s="27"/>
       <c r="D64" s="23" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="65" ht="26" spans="1:7">
       <c r="A65" s="22" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B65" s="28" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C65" s="27"/>
       <c r="D65" s="27"/>
@@ -2382,11 +2422,11 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="22" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B66" s="27"/>
       <c r="C66" s="23" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D66" s="27"/>
       <c r="E66" s="27"/>
@@ -2395,36 +2435,36 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="22" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B67" s="27"/>
       <c r="C67" s="27"/>
     </row>
     <row r="68" ht="26" spans="1:7">
       <c r="A68" s="22" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B68" s="27"/>
       <c r="C68" s="27"/>
       <c r="D68" s="23" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="22" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B69" s="19" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C69" s="19"/>
     </row>
     <row r="70" ht="26" spans="1:7">
       <c r="A70" s="22" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B70" s="19" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C70" s="19"/>
       <c r="D70" s="27"/>
@@ -2434,20 +2474,20 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="22" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B71" s="27"/>
       <c r="C71" s="27"/>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="22" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B72" s="23" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C72" s="23" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D72" s="27"/>
       <c r="E72" s="27"/>
@@ -2456,11 +2496,11 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="22" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B73" s="27"/>
       <c r="C73" s="23" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D73" s="27"/>
       <c r="E73" s="27"/>
@@ -2469,12 +2509,12 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="22" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="22" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D75" s="27"/>
       <c r="E75" s="27"/>
@@ -2483,27 +2523,27 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="22" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B76" s="27"/>
       <c r="C76" s="27"/>
       <c r="D76" s="23" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="22" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B77" s="19"/>
       <c r="C77" s="19"/>
     </row>
     <row r="78" ht="26" spans="1:7">
       <c r="A78" s="29" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -2574,12 +2614,12 @@
     </row>
     <row r="2" s="12" customFormat="1" ht="39" spans="1:7">
       <c r="A2" s="18" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
       <c r="D2" s="19" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E2" s="19"/>
       <c r="F2" s="19"/>
@@ -2587,40 +2627,40 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="20" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="20" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="20" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2782,107 +2822,107 @@
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="35.1818181818182" style="8" customWidth="1"/>
-    <col min="2" max="2" width="16.9090909090909" style="8" customWidth="1"/>
+    <col min="1" max="1" width="35.1818181818182" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.9090909090909" style="3" customWidth="1"/>
     <col min="3" max="3" width="50.0909090909091" style="9" customWidth="1"/>
-    <col min="4" max="16384" width="8.72727272727273" style="8"/>
+    <col min="4" max="16384" width="8.72727272727273" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>169</v>
+      <c r="A1" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>172</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>172</v>
+      <c r="A2" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>175</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>175</v>
+      <c r="A3" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>178</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" ht="28" spans="1:3">
-      <c r="A4" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>175</v>
+      <c r="A4" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>178</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" ht="42" spans="1:3">
       <c r="A5" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>180</v>
+        <v>182</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>183</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" ht="56" spans="1:3">
       <c r="A6" s="11"/>
-      <c r="B6" s="8" t="s">
-        <v>182</v>
+      <c r="B6" s="3" t="s">
+        <v>185</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" ht="28" spans="1:3">
-      <c r="A7" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>185</v>
+      <c r="A7" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>188</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" ht="28" spans="1:3">
-      <c r="A8" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>188</v>
+      <c r="A8" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>191</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>191</v>
+      <c r="A9" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>194</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -2897,177 +2937,237 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="9.18181818181818" style="1"/>
-    <col min="2" max="2" width="8.72727272727273" style="2"/>
-    <col min="3" max="3" width="41" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="8.72727272727273" style="2"/>
+    <col min="2" max="2" width="3.54545454545455" style="2" customWidth="1"/>
+    <col min="3" max="3" width="56.8181818181818" style="3" customWidth="1"/>
+    <col min="4" max="16384" width="8.72727272727273" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="3"/>
       <c r="B1" s="4"/>
-      <c r="C1" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>194</v>
+      <c r="C1" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="5">
+      <c r="A2" s="6">
         <v>2025.1</v>
       </c>
       <c r="B2" s="4">
         <v>11</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4">
+      <c r="C2" s="5"/>
+      <c r="D2" s="5">
         <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="6"/>
+      <c r="A3" s="7"/>
       <c r="B3" s="4">
         <v>15</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4">
+      <c r="C3" s="5"/>
+      <c r="D3" s="5">
         <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="6"/>
+      <c r="A4" s="7"/>
       <c r="B4" s="4">
         <v>17</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4">
+      <c r="C4" s="5"/>
+      <c r="D4" s="5">
         <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="6"/>
+      <c r="A5" s="7"/>
       <c r="B5" s="4">
         <v>22</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4">
+      <c r="C5" s="5"/>
+      <c r="D5" s="5">
         <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="6"/>
+      <c r="A6" s="7"/>
       <c r="B6" s="4">
         <v>24</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4">
+      <c r="C6" s="5"/>
+      <c r="D6" s="5">
         <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="6"/>
+      <c r="A7" s="7"/>
       <c r="B7" s="4">
         <v>29</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4">
+      <c r="C7" s="5"/>
+      <c r="D7" s="5">
         <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="7"/>
+      <c r="A8" s="8"/>
       <c r="B8" s="4">
         <v>31</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4">
+      <c r="C8" s="5"/>
+      <c r="D8" s="5">
         <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="5">
+      <c r="A9" s="6">
         <v>2025.11</v>
       </c>
       <c r="B9" s="4">
         <v>5</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4">
+      <c r="C9" s="5"/>
+      <c r="D9" s="5">
         <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="6"/>
+      <c r="A10" s="7"/>
       <c r="B10" s="4">
         <v>7</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4">
+      <c r="C10" s="5"/>
+      <c r="D10" s="5">
         <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="7"/>
+      <c r="A11" s="8"/>
       <c r="B11" s="4">
         <v>14</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4">
+      <c r="C11" s="5"/>
+      <c r="D11" s="5">
         <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="3">
+      <c r="A12" s="1">
         <v>2025.12</v>
       </c>
       <c r="B12" s="4">
         <v>5</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="D12" s="4"/>
+      <c r="C12" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D12" s="5"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="3"/>
       <c r="B13" s="4">
         <v>6</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="D13" s="4"/>
+      <c r="C13" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="D13" s="5"/>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="3"/>
       <c r="B14" s="4">
         <v>9</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="D14" s="4"/>
+      <c r="C14" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="3"/>
       <c r="B15" s="4">
         <v>10</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="D15" s="4"/>
+      <c r="C15" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="D15" s="5"/>
     </row>
     <row r="16" spans="1:4">
       <c r="B16" s="2">
         <v>11</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>199</v>
+      <c r="C16" s="3" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="B17" s="2">
+        <v>12</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="B18" s="2">
+        <v>15</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="B19" s="2">
+        <v>16</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="B20" s="2">
+        <v>17</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="B21" s="2">
+        <v>18</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="B22" s="2">
+        <v>19</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3">
+      <c r="B23" s="2">
+        <v>22</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3">
+      <c r="B24" s="2">
+        <v>23</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>210</v>
       </c>
     </row>
   </sheetData>

--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10030" activeTab="3"/>
+    <workbookView windowWidth="20750" windowHeight="10030" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="学生、老师" sheetId="5" r:id="rId1"/>
     <sheet name="9班、四十中" sheetId="13" r:id="rId2"/>
     <sheet name="佐证日常典型事例" sheetId="14" r:id="rId3"/>
     <sheet name="统计数据" sheetId="15" r:id="rId4"/>
+    <sheet name="数学课请人" sheetId="16" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="213">
   <si>
     <t>姓名</t>
   </si>
@@ -95,7 +96,7 @@
     <t>祥懿又是你、午餐（芹菜炒肉、土豆丝、秋葵、番茄酱）课间吃饭、画画、捏/咬/打人、炫耀、演讲、喵喵姐</t>
   </si>
   <si>
-    <t>萌、上课吃东西（早上水果，下午菜，下午高峰）（泡鸭爪/棒棒糖/营养品（长高）/奥利奥）、作业没写应对方式（没带法、证人法、偶然法、不会法、以为法、灭口法、自我安慰法）、宣泄、睡觉（低头/点头）、带读（一，起）、水杯倒（不盖盖）、尼玛的、东西被陆梓豪偷吃、排队时讲话、我又……上了、我不行了……、自己做了……→谁做了……啊！、告状、动作、英语小测翻书/笔记、隔班借作业抄、废啊、（12.11）带仓鼠</t>
+    <t>萌、上课吃东西（早上水果，下午菜，下午高峰）（泡鸭爪/棒棒糖/营养品（长高）/奥利奥）、作业没写应对方式（没带法、证人法、偶然法、不会法、以为法、灭口法、自我安慰法）、宣泄、睡觉（低头/点头）、带读（一，起）、水杯倒（不盖盖）、尼玛的、东西被陆梓豪偷吃、排队时讲话、我又……上了、我不行了……、自己做了……→谁做了……啊！、告状、动作、英语小测翻书/笔记、隔班借作业抄、废啊、（12.11）带仓鼠、OC（龙烛玥）</t>
   </si>
   <si>
     <t>林钰颖</t>
@@ -293,7 +294,7 @@
     <t>早读（劝学/磨刀霍霍向鑫洋）、生物30分、记笔记</t>
   </si>
   <si>
-    <t>孺子、反思（我也老了、相见时难别亦难，东风无力百花残、未来是你们，但现在未必、革命尚未成功）（一旬老人）、哲学（旁观者：学地理要以旁观者视角、水循环：逆水行舟，退到极点就是进）、装（问第几题有问题，体现自己做得快、费马点）、考进班级前10</t>
+    <t>孺子、反思（我也老了、相见时难别亦难，东风无力百花残、未来是你们，但现在未必、革命尚未成功）（一旬老人）、哲学（旁观者：学地理要以旁观者视角、水循环：逆水行舟，退到极点就是进）、装（问第几题有问题，体现自己做得快、费马点）、考进班级前10、种地（初二第三次月考、打赌八上期末物理自己和郑永泽考的低者种地）、因错题争论、嫂子（47）</t>
   </si>
   <si>
     <t>游武毅</t>
@@ -377,7 +378,7 @@
     <t>讲评作业（折名字/3、4组过道）、课件（熊熊疑惑、喜羊羊修花圃）、今天纪律差、笔记本拿出来、作业只改正面、告诉原因</t>
   </si>
   <si>
-    <t>××写第×题、固定请人、站后面</t>
+    <t>××写第×题、固定请人、站后面、每次考试后总结</t>
   </si>
   <si>
     <t>英1</t>
@@ -533,7 +534,7 @@
     <t>五子棋、笔</t>
   </si>
   <si>
-    <t>水瓶、炸弹脚</t>
+    <t>水瓶、炸弹脚、折星</t>
   </si>
   <si>
     <t>梗</t>
@@ -543,6 +544,12 @@
   </si>
   <si>
     <t>睿昕咖啡、谢谢爷爷</t>
+  </si>
+  <si>
+    <t>关系</t>
+  </si>
+  <si>
+    <t>2-13，40-15，36-17</t>
   </si>
   <si>
     <t>日常</t>
@@ -858,6 +865,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -943,12 +956,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1275,7 +1282,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1299,16 +1306,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1317,16 +1324,16 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1402,13 +1409,19 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1416,9 +1429,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1442,55 +1452,55 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1826,723 +1836,723 @@
   <dimension ref="A1:G78"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="7.59090909090909" style="22" customWidth="1"/>
-    <col min="2" max="7" width="25.8727272727273" style="23" customWidth="1"/>
+    <col min="1" max="1" width="7.59090909090909" style="23" customWidth="1"/>
+    <col min="2" max="7" width="25.8727272727273" style="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="21" customFormat="1" spans="1:7">
-      <c r="A1" s="24" t="s">
+    <row r="1" s="22" customFormat="1" spans="1:7">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="G1" s="26" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="24" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" ht="39" spans="1:7">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="24" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="27" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="24" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="24" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" ht="195" spans="1:7">
-      <c r="A7" s="26" t="s">
+    <row r="7" ht="208" spans="1:7">
+      <c r="A7" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="24" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="27" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="27" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="26" t="s">
+      <c r="A10" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="24" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="27" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="27" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="13" ht="39" spans="1:7">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="23" t="s">
+      <c r="D13" s="24" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="24" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="26" t="s">
+      <c r="A15" s="27" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="24" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="17" ht="26" spans="1:4">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="23" t="s">
+      <c r="C17" s="24" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="23" t="s">
+      <c r="D18" s="24" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="26" t="s">
+      <c r="A19" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="23" t="s">
+      <c r="D19" s="24" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="20" ht="26" spans="1:4">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="23" t="s">
+      <c r="B20" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="24" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="21" ht="39" spans="1:4">
-      <c r="A21" s="26" t="s">
+      <c r="A21" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="23" t="s">
+      <c r="B21" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C21" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="D21" s="23" t="s">
+      <c r="D21" s="24" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="26" t="s">
+      <c r="A22" s="27" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="23" ht="26" spans="1:4">
-      <c r="A23" s="26" t="s">
+      <c r="A23" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="23" t="s">
+      <c r="B23" s="24" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="24" ht="52" spans="1:4">
-      <c r="A24" s="26" t="s">
+      <c r="A24" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="C24" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="D24" s="23" t="s">
+      <c r="D24" s="24" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="27" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="27" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="26" t="s">
+      <c r="A27" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="B27" s="23" t="s">
+      <c r="B27" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="23" t="s">
+      <c r="C27" s="24" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="28" ht="91" spans="1:4">
-      <c r="A28" s="26" t="s">
+      <c r="A28" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="B28" s="23" t="s">
+      <c r="B28" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="C28" s="23" t="s">
+      <c r="C28" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="D28" s="23" t="s">
+      <c r="D28" s="24" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="26" t="s">
+      <c r="A29" s="27" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="26" t="s">
+      <c r="A30" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="B30" s="23" t="s">
+      <c r="B30" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="C30" s="23" t="s">
+      <c r="C30" s="24" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="26" t="s">
+      <c r="A31" s="27" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="26" t="s">
+      <c r="A32" s="27" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="26" t="s">
+      <c r="A33" s="27" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="26" t="s">
+      <c r="A34" s="27" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="26" t="s">
+      <c r="A35" s="27" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="26" t="s">
+      <c r="A36" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="B36" s="23" t="s">
+      <c r="B36" s="24" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="37" ht="26" spans="1:7">
-      <c r="A37" s="26" t="s">
+      <c r="A37" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="C37" s="23" t="s">
+      <c r="C37" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="D37" s="23" t="s">
+      <c r="D37" s="24" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="26" t="s">
+      <c r="A38" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="B38" s="23" t="s">
+      <c r="B38" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="C38" s="27"/>
-      <c r="D38" s="27"/>
-      <c r="E38" s="27"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
+      <c r="C38" s="28"/>
+      <c r="D38" s="28"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
+      <c r="G38" s="28"/>
     </row>
     <row r="39" ht="26" spans="1:7">
-      <c r="A39" s="26" t="s">
+      <c r="A39" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="C39" s="23" t="s">
+      <c r="C39" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="D39" s="23" t="s">
+      <c r="D39" s="24" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="26" t="s">
+      <c r="A40" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="B40" s="23" t="s">
+      <c r="B40" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="C40" s="23" t="s">
+      <c r="C40" s="24" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="41" ht="130" spans="1:7">
-      <c r="A41" s="26" t="s">
+    <row r="41" ht="169" spans="1:7">
+      <c r="A41" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="C41" s="23" t="s">
+      <c r="C41" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="D41" s="23" t="s">
+      <c r="D41" s="24" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="26" t="s">
+      <c r="A42" s="27" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="26" t="s">
+      <c r="A43" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="B43" s="23" t="s">
+      <c r="B43" s="24" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="44" ht="26" spans="1:7">
-      <c r="A44" s="26" t="s">
+      <c r="A44" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="B44" s="23" t="s">
+      <c r="B44" s="24" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="26" t="s">
+      <c r="A45" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="D45" s="23" t="s">
+      <c r="D45" s="24" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="26" t="s">
+      <c r="A46" s="27" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="26" t="s">
+      <c r="A47" s="27" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="26" t="s">
+      <c r="A48" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="C48" s="23" t="s">
+      <c r="C48" s="24" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="26" t="s">
+      <c r="A49" s="27" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="50" ht="78" spans="1:7">
-      <c r="A50" s="26" t="s">
+      <c r="A50" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="C50" s="23" t="s">
+      <c r="C50" s="24" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="26" t="s">
+      <c r="A51" s="27" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="52" ht="26" spans="1:7">
-      <c r="A52" s="26" t="s">
+      <c r="A52" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="B52" s="23" t="s">
+      <c r="B52" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="C52" s="23" t="s">
+      <c r="C52" s="24" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="53" ht="26" spans="1:7">
-      <c r="A53" s="22" t="s">
+      <c r="A53" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="B53" s="23" t="s">
+      <c r="B53" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="D53" s="27"/>
-      <c r="E53" s="27"/>
-      <c r="F53" s="27"/>
-      <c r="G53" s="27"/>
+      <c r="D53" s="28"/>
+      <c r="E53" s="28"/>
+      <c r="F53" s="28"/>
+      <c r="G53" s="28"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="22" t="s">
+      <c r="A54" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="B54" s="23" t="s">
+      <c r="B54" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="C54" s="23" t="s">
+      <c r="C54" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="D54" s="27"/>
-      <c r="E54" s="27"/>
-      <c r="F54" s="27"/>
-      <c r="G54" s="27"/>
+      <c r="D54" s="28"/>
+      <c r="E54" s="28"/>
+      <c r="F54" s="28"/>
+      <c r="G54" s="28"/>
     </row>
     <row r="55" ht="52" spans="1:7">
-      <c r="A55" s="22" t="s">
+      <c r="A55" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="B55" s="27"/>
-      <c r="C55" s="27"/>
-      <c r="D55" s="23" t="s">
+      <c r="B55" s="28"/>
+      <c r="C55" s="28"/>
+      <c r="D55" s="24" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="56" ht="65" spans="1:7">
-      <c r="A56" s="22" t="s">
+      <c r="A56" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="B56" s="19" t="s">
+      <c r="B56" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="C56" s="19"/>
-      <c r="D56" s="23" t="s">
+      <c r="C56" s="20"/>
+      <c r="D56" s="24" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="57" ht="117" spans="1:7">
-      <c r="A57" s="22" t="s">
+      <c r="A57" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="B57" s="19" t="s">
+      <c r="B57" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="C57" s="19" t="s">
+      <c r="C57" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D57" s="23" t="s">
+      <c r="D57" s="24" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="22" t="s">
+      <c r="A58" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="B58" s="23" t="s">
+      <c r="B58" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="C58" s="27"/>
-      <c r="D58" s="27"/>
-      <c r="E58" s="27"/>
-      <c r="F58" s="27"/>
-      <c r="G58" s="27"/>
+      <c r="C58" s="28"/>
+      <c r="D58" s="28"/>
+      <c r="E58" s="28"/>
+      <c r="F58" s="28"/>
+      <c r="G58" s="28"/>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="22" t="s">
+      <c r="A59" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="B59" s="27"/>
-      <c r="C59" s="23" t="s">
+      <c r="B59" s="28"/>
+      <c r="C59" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="D59" s="27"/>
-      <c r="E59" s="27"/>
-      <c r="F59" s="27"/>
-      <c r="G59" s="27"/>
+      <c r="D59" s="28"/>
+      <c r="E59" s="28"/>
+      <c r="F59" s="28"/>
+      <c r="G59" s="28"/>
     </row>
     <row r="60" ht="52" spans="1:7">
-      <c r="A60" s="22" t="s">
+      <c r="A60" s="23" t="s">
         <v>124</v>
       </c>
-      <c r="B60" s="27"/>
-      <c r="C60" s="27"/>
-      <c r="D60" s="23" t="s">
+      <c r="B60" s="28"/>
+      <c r="C60" s="28"/>
+      <c r="D60" s="24" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="22" t="s">
+      <c r="A61" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="B61" s="19" t="s">
+      <c r="B61" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="C61" s="19"/>
-      <c r="D61" s="27"/>
-      <c r="E61" s="27"/>
-      <c r="F61" s="27"/>
-      <c r="G61" s="27"/>
+      <c r="C61" s="20"/>
+      <c r="D61" s="28"/>
+      <c r="E61" s="28"/>
+      <c r="F61" s="28"/>
+      <c r="G61" s="28"/>
     </row>
     <row r="62" ht="39" spans="1:7">
-      <c r="A62" s="22" t="s">
+      <c r="A62" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="B62" s="27"/>
-      <c r="C62" s="27"/>
-      <c r="D62" s="23" t="s">
+      <c r="B62" s="28"/>
+      <c r="C62" s="28"/>
+      <c r="D62" s="24" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="63" ht="26" spans="1:7">
-      <c r="A63" s="22" t="s">
+      <c r="A63" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="B63" s="19" t="s">
+      <c r="B63" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="C63" s="19" t="s">
+      <c r="C63" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="D63" s="27"/>
-      <c r="E63" s="27"/>
-      <c r="F63" s="27"/>
-      <c r="G63" s="27"/>
+      <c r="D63" s="28"/>
+      <c r="E63" s="28"/>
+      <c r="F63" s="28"/>
+      <c r="G63" s="28"/>
     </row>
     <row r="64" ht="26" spans="1:7">
-      <c r="A64" s="22" t="s">
+      <c r="A64" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="B64" s="27"/>
-      <c r="C64" s="27"/>
-      <c r="D64" s="23" t="s">
+      <c r="B64" s="28"/>
+      <c r="C64" s="28"/>
+      <c r="D64" s="24" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="65" ht="26" spans="1:7">
-      <c r="A65" s="22" t="s">
+      <c r="A65" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="B65" s="28" t="s">
+      <c r="B65" s="29" t="s">
         <v>136</v>
       </c>
-      <c r="C65" s="27"/>
-      <c r="D65" s="27"/>
-      <c r="E65" s="27"/>
-      <c r="F65" s="27"/>
-      <c r="G65" s="27"/>
+      <c r="C65" s="28"/>
+      <c r="D65" s="28"/>
+      <c r="E65" s="28"/>
+      <c r="F65" s="28"/>
+      <c r="G65" s="28"/>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="22" t="s">
+      <c r="A66" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="B66" s="27"/>
-      <c r="C66" s="23" t="s">
+      <c r="B66" s="28"/>
+      <c r="C66" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="D66" s="27"/>
-      <c r="E66" s="27"/>
-      <c r="F66" s="27"/>
-      <c r="G66" s="27"/>
+      <c r="D66" s="28"/>
+      <c r="E66" s="28"/>
+      <c r="F66" s="28"/>
+      <c r="G66" s="28"/>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="22" t="s">
+      <c r="A67" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="B67" s="27"/>
-      <c r="C67" s="27"/>
+      <c r="B67" s="28"/>
+      <c r="C67" s="28"/>
     </row>
     <row r="68" ht="26" spans="1:7">
-      <c r="A68" s="22" t="s">
+      <c r="A68" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="B68" s="27"/>
-      <c r="C68" s="27"/>
-      <c r="D68" s="23" t="s">
+      <c r="B68" s="28"/>
+      <c r="C68" s="28"/>
+      <c r="D68" s="24" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="22" t="s">
+      <c r="A69" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="B69" s="19" t="s">
+      <c r="B69" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="C69" s="19"/>
+      <c r="C69" s="20"/>
     </row>
     <row r="70" ht="26" spans="1:7">
-      <c r="A70" s="22" t="s">
+      <c r="A70" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="B70" s="19" t="s">
+      <c r="B70" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="C70" s="19"/>
-      <c r="D70" s="27"/>
-      <c r="E70" s="27"/>
-      <c r="F70" s="27"/>
-      <c r="G70" s="27"/>
+      <c r="C70" s="20"/>
+      <c r="D70" s="28"/>
+      <c r="E70" s="28"/>
+      <c r="F70" s="28"/>
+      <c r="G70" s="28"/>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="22" t="s">
+      <c r="A71" s="23" t="s">
         <v>146</v>
       </c>
-      <c r="B71" s="27"/>
-      <c r="C71" s="27"/>
+      <c r="B71" s="28"/>
+      <c r="C71" s="28"/>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="22" t="s">
+      <c r="A72" s="23" t="s">
         <v>147</v>
       </c>
-      <c r="B72" s="23" t="s">
+      <c r="B72" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="C72" s="23" t="s">
+      <c r="C72" s="24" t="s">
         <v>149</v>
       </c>
-      <c r="D72" s="27"/>
-      <c r="E72" s="27"/>
-      <c r="F72" s="27"/>
-      <c r="G72" s="27"/>
+      <c r="D72" s="28"/>
+      <c r="E72" s="28"/>
+      <c r="F72" s="28"/>
+      <c r="G72" s="28"/>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="22" t="s">
+      <c r="A73" s="23" t="s">
         <v>150</v>
       </c>
-      <c r="B73" s="27"/>
-      <c r="C73" s="23" t="s">
+      <c r="B73" s="28"/>
+      <c r="C73" s="24" t="s">
         <v>151</v>
       </c>
-      <c r="D73" s="27"/>
-      <c r="E73" s="27"/>
-      <c r="F73" s="27"/>
-      <c r="G73" s="27"/>
+      <c r="D73" s="28"/>
+      <c r="E73" s="28"/>
+      <c r="F73" s="28"/>
+      <c r="G73" s="28"/>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="22" t="s">
+      <c r="A74" s="23" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="22" t="s">
+      <c r="A75" s="23" t="s">
         <v>153</v>
       </c>
-      <c r="D75" s="27"/>
-      <c r="E75" s="27"/>
-      <c r="F75" s="27"/>
-      <c r="G75" s="27"/>
+      <c r="D75" s="28"/>
+      <c r="E75" s="28"/>
+      <c r="F75" s="28"/>
+      <c r="G75" s="28"/>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="22" t="s">
+      <c r="A76" s="23" t="s">
         <v>154</v>
       </c>
-      <c r="B76" s="27"/>
-      <c r="C76" s="27"/>
-      <c r="D76" s="23" t="s">
+      <c r="B76" s="28"/>
+      <c r="C76" s="28"/>
+      <c r="D76" s="24" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="22" t="s">
+      <c r="A77" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="B77" s="19"/>
-      <c r="C77" s="19"/>
+      <c r="B77" s="20"/>
+      <c r="C77" s="20"/>
     </row>
     <row r="78" ht="26" spans="1:7">
-      <c r="A78" s="29" t="s">
+      <c r="A78" s="30" t="s">
         <v>157</v>
       </c>
-      <c r="B78" s="23" t="s">
+      <c r="B78" s="24" t="s">
         <v>158</v>
       </c>
     </row>
@@ -2586,229 +2596,234 @@
   <dimension ref="A1:G51"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="6.64545454545455" style="13" customWidth="1"/>
-    <col min="2" max="7" width="16.4909090909091" style="14" customWidth="1"/>
-    <col min="8" max="16384" width="8.72727272727273" style="15"/>
+    <col min="1" max="1" width="6.64545454545455" style="14" customWidth="1"/>
+    <col min="2" max="7" width="16.4909090909091" style="15" customWidth="1"/>
+    <col min="8" max="16384" width="8.72727272727273" style="16"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="16"/>
-      <c r="B1" s="17" t="s">
+      <c r="A1" s="17"/>
+      <c r="B1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="18" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="12" customFormat="1" ht="39" spans="1:7">
-      <c r="A2" s="18" t="s">
+    <row r="2" s="13" customFormat="1" ht="39" spans="1:7">
+      <c r="A2" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19" t="s">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="15" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="21" t="s">
         <v>163</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="15" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="21" t="s">
         <v>165</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="15" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="15" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="20"/>
+      <c r="A7" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="20"/>
+      <c r="A8" s="21"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="20"/>
+      <c r="A9" s="21"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="20"/>
+      <c r="A10" s="21"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="20"/>
+      <c r="A11" s="21"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="20"/>
+      <c r="A12" s="21"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="20"/>
+      <c r="A13" s="21"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="20"/>
+      <c r="A14" s="21"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="20"/>
+      <c r="A15" s="21"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="20"/>
+      <c r="A16" s="21"/>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="20"/>
+      <c r="A17" s="21"/>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="20"/>
+      <c r="A18" s="21"/>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="20"/>
+      <c r="A19" s="21"/>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="20"/>
+      <c r="A20" s="21"/>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="20"/>
+      <c r="A21" s="21"/>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="20"/>
+      <c r="A22" s="21"/>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="20"/>
+      <c r="A23" s="21"/>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="20"/>
+      <c r="A24" s="21"/>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="20"/>
+      <c r="A25" s="21"/>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="20"/>
+      <c r="A26" s="21"/>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="20"/>
+      <c r="A27" s="21"/>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="20"/>
+      <c r="A28" s="21"/>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="20"/>
+      <c r="A29" s="21"/>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="20"/>
+      <c r="A30" s="21"/>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="20"/>
+      <c r="A31" s="21"/>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="20"/>
+      <c r="A32" s="21"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="20"/>
+      <c r="A33" s="21"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="20"/>
+      <c r="A34" s="21"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="20"/>
+      <c r="A35" s="21"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="20"/>
+      <c r="A36" s="21"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="20"/>
+      <c r="A37" s="21"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="20"/>
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
+      <c r="A38" s="21"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="20"/>
-      <c r="B39" s="19"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
+      <c r="A39" s="21"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="20"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="20"/>
+      <c r="A40" s="21"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="20"/>
+      <c r="A41" s="21"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="20"/>
+      <c r="A42" s="21"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="20"/>
+      <c r="A43" s="21"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="20"/>
+      <c r="A44" s="21"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="20"/>
+      <c r="A45" s="21"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="20"/>
+      <c r="A46" s="21"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="20"/>
+      <c r="A47" s="21"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="20"/>
+      <c r="A48" s="21"/>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="20"/>
+      <c r="A49" s="21"/>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="20"/>
+      <c r="A50" s="21"/>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="20"/>
+      <c r="A51" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2822,107 +2837,107 @@
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="35.1818181818182" style="3" customWidth="1"/>
-    <col min="2" max="2" width="16.9090909090909" style="3" customWidth="1"/>
-    <col min="3" max="3" width="50.0909090909091" style="9" customWidth="1"/>
-    <col min="4" max="16384" width="8.72727272727273" style="3"/>
+    <col min="1" max="1" width="35.1818181818182" style="5" customWidth="1"/>
+    <col min="2" max="2" width="16.9090909090909" style="5" customWidth="1"/>
+    <col min="3" max="3" width="50.0909090909091" style="10" customWidth="1"/>
+    <col min="4" max="16384" width="8.72727272727273" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="C1" s="9" t="s">
+      <c r="A1" s="5" t="s">
         <v>173</v>
       </c>
+      <c r="B1" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="C2" s="9" t="s">
+      <c r="A2" s="5" t="s">
         <v>176</v>
       </c>
+      <c r="B2" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C3" s="9" t="s">
+      <c r="A3" s="5" t="s">
         <v>179</v>
       </c>
+      <c r="B3" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="4" ht="28" spans="1:3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>181</v>
+      <c r="C4" s="10" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="5" ht="42" spans="1:3">
-      <c r="A5" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="C5" s="9" t="s">
+      <c r="A5" s="11" t="s">
         <v>184</v>
       </c>
+      <c r="B5" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="6" ht="56" spans="1:3">
-      <c r="A6" s="11"/>
-      <c r="B6" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>186</v>
+      <c r="A6" s="12"/>
+      <c r="B6" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="7" ht="28" spans="1:3">
-      <c r="A7" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C7" s="9" t="s">
+      <c r="A7" s="5" t="s">
         <v>189</v>
       </c>
+      <c r="B7" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="8" ht="28" spans="1:3">
-      <c r="A8" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="C8" s="9" t="s">
+      <c r="A8" s="5" t="s">
         <v>192</v>
       </c>
+      <c r="B8" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="C9" s="9" t="s">
+      <c r="A9" s="5" t="s">
         <v>195</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -2937,237 +2952,241 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="9.18181818181818" style="1"/>
-    <col min="2" max="2" width="3.54545454545455" style="2" customWidth="1"/>
-    <col min="3" max="3" width="56.8181818181818" style="3" customWidth="1"/>
-    <col min="4" max="16384" width="8.72727272727273" style="3"/>
+    <col min="1" max="1" width="9.18181818181818" style="3"/>
+    <col min="2" max="2" width="3.54545454545455" style="4" customWidth="1"/>
+    <col min="3" max="3" width="56.8181818181818" style="5" customWidth="1"/>
+    <col min="4" max="16384" width="8.72727272727273" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="B1" s="4"/>
-      <c r="C1" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>197</v>
+      <c r="C1" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="6">
+      <c r="A2" s="7">
         <v>2025.1</v>
       </c>
       <c r="B2" s="4">
         <v>11</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5">
+      <c r="C2" s="6"/>
+      <c r="D2" s="6">
         <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="7"/>
+      <c r="A3" s="8"/>
       <c r="B3" s="4">
         <v>15</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5">
+      <c r="C3" s="6"/>
+      <c r="D3" s="6">
         <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="7"/>
+      <c r="A4" s="8"/>
       <c r="B4" s="4">
         <v>17</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5">
+      <c r="C4" s="6"/>
+      <c r="D4" s="6">
         <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="7"/>
+      <c r="A5" s="8"/>
       <c r="B5" s="4">
         <v>22</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5">
+      <c r="C5" s="6"/>
+      <c r="D5" s="6">
         <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="7"/>
+      <c r="A6" s="8"/>
       <c r="B6" s="4">
         <v>24</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5">
+      <c r="C6" s="6"/>
+      <c r="D6" s="6">
         <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="7"/>
+      <c r="A7" s="8"/>
       <c r="B7" s="4">
         <v>29</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5">
+      <c r="C7" s="6"/>
+      <c r="D7" s="6">
         <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="8"/>
+      <c r="A8" s="9"/>
       <c r="B8" s="4">
         <v>31</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5">
+      <c r="C8" s="6"/>
+      <c r="D8" s="6">
         <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="6">
+      <c r="A9" s="7">
         <v>2025.11</v>
       </c>
       <c r="B9" s="4">
         <v>5</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5">
+      <c r="C9" s="6"/>
+      <c r="D9" s="6">
         <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="7"/>
+      <c r="A10" s="8"/>
       <c r="B10" s="4">
         <v>7</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5">
+      <c r="C10" s="6"/>
+      <c r="D10" s="6">
         <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="8"/>
+      <c r="A11" s="9"/>
       <c r="B11" s="4">
         <v>14</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5">
+      <c r="C11" s="6"/>
+      <c r="D11" s="6">
         <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="1">
+      <c r="A12" s="3">
         <v>2025.12</v>
       </c>
       <c r="B12" s="4">
         <v>5</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="D12" s="5"/>
+      <c r="C12" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="D12" s="6"/>
     </row>
     <row r="13" spans="1:4">
       <c r="B13" s="4">
         <v>6</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="D13" s="5"/>
+      <c r="C13" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D13" s="6"/>
     </row>
     <row r="14" spans="1:4">
       <c r="B14" s="4">
         <v>9</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="D14" s="5"/>
+      <c r="C14" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="D14" s="6"/>
     </row>
     <row r="15" spans="1:4">
       <c r="B15" s="4">
         <v>10</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D15" s="5"/>
+      <c r="C15" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="D15" s="6"/>
     </row>
     <row r="16" spans="1:4">
-      <c r="B16" s="2">
+      <c r="B16" s="4">
         <v>11</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>202</v>
+      <c r="C16" s="5" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="17" spans="2:3">
-      <c r="B17" s="2">
+      <c r="B17" s="4">
         <v>12</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>203</v>
+      <c r="C17" s="5" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="18" spans="2:3">
-      <c r="B18" s="2">
+      <c r="B18" s="4">
         <v>15</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>204</v>
+      <c r="C18" s="5" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="19" spans="2:3">
-      <c r="B19" s="2">
+      <c r="B19" s="4">
         <v>16</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>205</v>
+      <c r="C19" s="5" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="20" spans="2:3">
-      <c r="B20" s="2">
+      <c r="B20" s="4">
         <v>17</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>206</v>
+      <c r="C20" s="5" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="21" spans="2:3">
-      <c r="B21" s="2">
+      <c r="B21" s="4">
         <v>18</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>207</v>
+      <c r="C21" s="5" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="22" spans="2:3">
-      <c r="B22" s="2">
+      <c r="B22" s="4">
         <v>19</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>208</v>
+      <c r="C22" s="5" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="23" spans="2:3">
-      <c r="B23" s="2">
+      <c r="B23" s="4">
         <v>22</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>209</v>
+      <c r="C23" s="5" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="24" spans="2:3">
-      <c r="B24" s="2">
+      <c r="B24" s="4">
         <v>23</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>210</v>
+      <c r="C24" s="5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3">
+      <c r="B25" s="4">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -3178,4 +3197,1034 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:O52"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="4.07272727272727" customWidth="1"/>
+    <col min="2" max="15" width="5.14545454545455" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1">
+        <v>10</v>
+      </c>
+      <c r="F1" s="1">
+        <v>11</v>
+      </c>
+      <c r="G1" s="1">
+        <v>12</v>
+      </c>
+      <c r="H1" s="1">
+        <v>15</v>
+      </c>
+      <c r="I1" s="1">
+        <v>16</v>
+      </c>
+      <c r="J1" s="1">
+        <v>17</v>
+      </c>
+      <c r="K1" s="1">
+        <v>18</v>
+      </c>
+      <c r="L1" s="1">
+        <v>19</v>
+      </c>
+      <c r="M1" s="1">
+        <v>22</v>
+      </c>
+      <c r="N1" s="1">
+        <v>23</v>
+      </c>
+      <c r="O1" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:15">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+    </row>
+    <row r="3" ht="28" customHeight="1" spans="1:15">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:15">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+    </row>
+    <row r="5" ht="28" customHeight="1" spans="1:15">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+    </row>
+    <row r="6" ht="28" customHeight="1" spans="1:15">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+    </row>
+    <row r="7" ht="28" customHeight="1" spans="1:15">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="1"/>
+    </row>
+    <row r="8" ht="28" customHeight="1" spans="1:15">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+    </row>
+    <row r="9" ht="28" customHeight="1" spans="1:15">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:15">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="1"/>
+    </row>
+    <row r="11" ht="28" customHeight="1" spans="1:15">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+    </row>
+    <row r="12" ht="28" customHeight="1" spans="1:15">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="1"/>
+    </row>
+    <row r="13" ht="28" customHeight="1" spans="1:15">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+    </row>
+    <row r="14" ht="28" customHeight="1" spans="1:15">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+    </row>
+    <row r="15" ht="28" customHeight="1" spans="1:15">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+    </row>
+    <row r="16" ht="28" customHeight="1" spans="1:15">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+    </row>
+    <row r="17" ht="28" customHeight="1" spans="1:15">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+    </row>
+    <row r="18" ht="28" customHeight="1" spans="1:15">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="1"/>
+    </row>
+    <row r="19" ht="28" customHeight="1" spans="1:15">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+    </row>
+    <row r="20" ht="28" customHeight="1" spans="1:15">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+    </row>
+    <row r="21" ht="28" customHeight="1" spans="1:15">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+    </row>
+    <row r="22" ht="28" customHeight="1" spans="1:15">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+    </row>
+    <row r="23" ht="28" customHeight="1" spans="1:15">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+    </row>
+    <row r="24" ht="28" customHeight="1" spans="1:15">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+    </row>
+    <row r="25" ht="28" customHeight="1" spans="1:15">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+    </row>
+    <row r="26" ht="28" customHeight="1" spans="1:15">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+    </row>
+    <row r="27" ht="28" customHeight="1" spans="1:15">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+    </row>
+    <row r="28" ht="28" customHeight="1" spans="1:15">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+    </row>
+    <row r="29" ht="28" customHeight="1" spans="1:15">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+    </row>
+    <row r="30" ht="28" customHeight="1" spans="1:15">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+    </row>
+    <row r="31" ht="28" customHeight="1" spans="1:15">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="1"/>
+    </row>
+    <row r="32" ht="28" customHeight="1" spans="1:15">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+    </row>
+    <row r="33" ht="28" customHeight="1" spans="1:15">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+    </row>
+    <row r="34" ht="28" customHeight="1" spans="1:15">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+    </row>
+    <row r="35" ht="28" customHeight="1" spans="1:15">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+    </row>
+    <row r="36" ht="28" customHeight="1" spans="1:15">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+    </row>
+    <row r="37" ht="28" customHeight="1" spans="1:15">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
+    </row>
+    <row r="38" ht="28" customHeight="1" spans="1:15">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
+    </row>
+    <row r="39" ht="28" customHeight="1" spans="1:15">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
+    </row>
+    <row r="40" ht="28" customHeight="1" spans="1:15">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
+    </row>
+    <row r="41" ht="28" customHeight="1" spans="1:15">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
+    </row>
+    <row r="42" ht="28" customHeight="1" spans="1:15">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="O42" s="1"/>
+    </row>
+    <row r="43" ht="28" customHeight="1" spans="1:15">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+      <c r="O43" s="1"/>
+    </row>
+    <row r="44" ht="28" customHeight="1" spans="1:15">
+      <c r="A44" s="1">
+        <v>43</v>
+      </c>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="O44" s="1"/>
+    </row>
+    <row r="45" ht="28" customHeight="1" spans="1:15">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
+    </row>
+    <row r="46" ht="28" customHeight="1" spans="1:15">
+      <c r="A46" s="1">
+        <v>45</v>
+      </c>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
+      <c r="O46" s="1"/>
+    </row>
+    <row r="47" ht="28" customHeight="1" spans="1:15">
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+      <c r="O47" s="1"/>
+    </row>
+    <row r="48" ht="28" customHeight="1" spans="1:15">
+      <c r="A48" s="1">
+        <v>47</v>
+      </c>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1"/>
+      <c r="O48" s="1"/>
+    </row>
+    <row r="49" ht="28" customHeight="1" spans="1:15">
+      <c r="A49" s="1">
+        <v>48</v>
+      </c>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1"/>
+      <c r="O49" s="1"/>
+    </row>
+    <row r="50" ht="28" customHeight="1" spans="1:15">
+      <c r="A50" s="1">
+        <v>49</v>
+      </c>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1"/>
+      <c r="O50" s="1"/>
+    </row>
+    <row r="51" ht="28" customHeight="1" spans="1:15">
+      <c r="A51" s="1">
+        <v>50</v>
+      </c>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1"/>
+    </row>
+    <row r="52" ht="28" customHeight="1" spans="1:15">
+      <c r="A52" s="1">
+        <v>51</v>
+      </c>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
+      <c r="M52" s="1"/>
+      <c r="N52" s="1"/>
+      <c r="O52" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10030" activeTab="4"/>
+    <workbookView windowWidth="20750" windowHeight="10480" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="学生、老师" sheetId="5" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="207">
   <si>
     <t>姓名</t>
   </si>
@@ -96,7 +96,7 @@
     <t>祥懿又是你、午餐（芹菜炒肉、土豆丝、秋葵、番茄酱）课间吃饭、画画、捏/咬/打人、炫耀、演讲、喵喵姐</t>
   </si>
   <si>
-    <t>萌、上课吃东西（早上水果，下午菜，下午高峰）（泡鸭爪/棒棒糖/营养品（长高）/奥利奥）、作业没写应对方式（没带法、证人法、偶然法、不会法、以为法、灭口法、自我安慰法）、宣泄、睡觉（低头/点头）、带读（一，起）、水杯倒（不盖盖）、尼玛的、东西被陆梓豪偷吃、排队时讲话、我又……上了、我不行了……、自己做了……→谁做了……啊！、告状、动作、英语小测翻书/笔记、隔班借作业抄、废啊、（12.11）带仓鼠、OC（龙烛玥）</t>
+    <t>萌、上课吃东西（早上水果，下午菜，下午高峰）（泡鸭爪/棒棒糖/营养品（长高）/奥利奥）、作业没写应对方式（没带法、证人法、偶然法、不会法、以为法、灭口法、自我安慰法）、宣泄、睡觉（低头/点头）、带读（一，起）、水杯倒（不盖盖）、尼玛的、东西被陆梓豪偷吃、排队时讲话、我又……上了、我不行了……、自己做了……→谁做了……啊！、告状、动作、英语小测翻书/笔记、隔班借作业抄、废啊、（12.11）带仓鼠、OC（龙烛玥）、在干嘛啊</t>
   </si>
   <si>
     <t>林钰颖</t>
@@ -174,7 +174,7 @@
     <t>爆胎</t>
   </si>
   <si>
-    <t>踩桌子通行、对臭味敏感、头痛/腰痛/骨折/受伤、伙食</t>
+    <t>踩桌子通行、对臭味敏感、头痛/腰痛/骨折/受伤、伙食、林奕扬来校吐槽/分享</t>
   </si>
   <si>
     <t>张桢烨</t>
@@ -552,6 +552,9 @@
     <t>2-13，40-15，36-17</t>
   </si>
   <si>
+    <t>零食饮料、背书、吃早餐</t>
+  </si>
+  <si>
     <t>日常</t>
   </si>
   <si>
@@ -627,49 +630,28 @@
     <t>物：头都快埋到地板上去了。</t>
   </si>
   <si>
-    <t>数学请人</t>
+    <t>江允儿装</t>
+  </si>
+  <si>
+    <t>八上12.26</t>
+  </si>
+  <si>
+    <t>小测A-，“我都没背”</t>
+  </si>
+  <si>
+    <t>政治首个视频</t>
+  </si>
+  <si>
+    <t>八上12.18</t>
   </si>
   <si>
     <t>政治啧</t>
   </si>
   <si>
-    <t>2，5，6，7，17，28，29，31，39，42，44</t>
-  </si>
-  <si>
-    <t>2，6，13，22，26，30，38，42，44</t>
-  </si>
-  <si>
-    <t>2，5，6，10，11，22，27，38，42，44</t>
-  </si>
-  <si>
-    <t>6，22，30，42，44，48</t>
-  </si>
-  <si>
-    <t>38，42</t>
-  </si>
-  <si>
-    <t>5，14，22，44，46</t>
-  </si>
-  <si>
-    <t>6，7，11，26，28，29，35，38，40，42，44，47</t>
-  </si>
-  <si>
-    <t>2，6，7，13，20，22，29，30，35，36，38，42，44</t>
-  </si>
-  <si>
-    <t>2，6，7，19，20，30，35，38，39，40，42，44</t>
-  </si>
-  <si>
-    <t>2，3，26，40，44</t>
-  </si>
-  <si>
-    <t>4，6，9，11，12，13，18，19，38，40，42，44</t>
-  </si>
-  <si>
-    <t>7，13，27，40，44，47</t>
-  </si>
-  <si>
-    <t>6，9，11，17，30，35，40，44，46</t>
+    <t>敲讲台</t>
+  </si>
+  <si>
+    <t>12月</t>
   </si>
 </sst>
 </file>
@@ -856,7 +838,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -865,7 +847,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.05"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -979,12 +979,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -998,12 +992,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1282,7 +1270,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1306,16 +1294,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1324,102 +1312,116 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1449,58 +1451,61 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1836,723 +1841,723 @@
   <dimension ref="A1:G78"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="7.59090909090909" style="23" customWidth="1"/>
-    <col min="2" max="7" width="25.8727272727273" style="24" customWidth="1"/>
+    <col min="1" max="1" width="7.59090909090909" style="28" customWidth="1"/>
+    <col min="2" max="7" width="25.8727272727273" style="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="22" customFormat="1" spans="1:7">
-      <c r="A1" s="25" t="s">
+    <row r="1" s="27" customFormat="1" spans="1:7">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="G1" s="31" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="29" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" ht="39" spans="1:7">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="29" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="32" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="29" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="29" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" ht="208" spans="1:7">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="29" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="32" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="32" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="29" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="32" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="32" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="13" ht="39" spans="1:7">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="24" t="s">
+      <c r="D13" s="29" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="29" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="27" t="s">
+      <c r="A15" s="32" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="29" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="17" ht="26" spans="1:4">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="C17" s="29" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="24" t="s">
+      <c r="D18" s="29" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="24" t="s">
+      <c r="D19" s="29" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="20" ht="26" spans="1:4">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="24" t="s">
+      <c r="C20" s="29" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="21" ht="39" spans="1:4">
-      <c r="A21" s="27" t="s">
+      <c r="A21" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="24" t="s">
+      <c r="C21" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="D21" s="24" t="s">
+      <c r="D21" s="29" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="27" t="s">
+      <c r="A22" s="32" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="23" ht="26" spans="1:4">
-      <c r="A23" s="27" t="s">
+      <c r="A23" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="24" t="s">
+      <c r="B23" s="29" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="24" ht="52" spans="1:4">
-      <c r="A24" s="27" t="s">
+      <c r="A24" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="B24" s="24" t="s">
+      <c r="B24" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="24" t="s">
+      <c r="C24" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="D24" s="24" t="s">
+      <c r="D24" s="29" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="27" t="s">
+      <c r="A25" s="32" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="27" t="s">
+      <c r="A26" s="32" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="27" t="s">
+      <c r="A27" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="B27" s="24" t="s">
+      <c r="B27" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="24" t="s">
+      <c r="C27" s="29" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="28" ht="91" spans="1:4">
-      <c r="A28" s="27" t="s">
+      <c r="A28" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="B28" s="24" t="s">
+      <c r="B28" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="C28" s="24" t="s">
+      <c r="C28" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="D28" s="24" t="s">
+      <c r="D28" s="29" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="27" t="s">
+      <c r="A29" s="32" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="27" t="s">
+      <c r="A30" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="B30" s="24" t="s">
+      <c r="B30" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="C30" s="24" t="s">
+      <c r="C30" s="29" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="27" t="s">
+      <c r="A31" s="32" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="27" t="s">
+      <c r="A32" s="32" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="27" t="s">
+      <c r="A33" s="32" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="27" t="s">
+      <c r="A34" s="32" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="27" t="s">
+      <c r="A35" s="32" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="27" t="s">
+      <c r="A36" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="B36" s="24" t="s">
+      <c r="B36" s="29" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="37" ht="26" spans="1:7">
-      <c r="A37" s="27" t="s">
+      <c r="A37" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="C37" s="24" t="s">
+      <c r="C37" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="D37" s="24" t="s">
+      <c r="D37" s="29" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="27" t="s">
+      <c r="A38" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="B38" s="24" t="s">
+      <c r="B38" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="28"/>
+      <c r="C38" s="33"/>
+      <c r="D38" s="33"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="33"/>
+      <c r="G38" s="33"/>
     </row>
     <row r="39" ht="26" spans="1:7">
-      <c r="A39" s="27" t="s">
+      <c r="A39" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="C39" s="24" t="s">
+      <c r="C39" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="D39" s="24" t="s">
+      <c r="D39" s="29" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="27" t="s">
+      <c r="A40" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="B40" s="24" t="s">
+      <c r="B40" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="C40" s="24" t="s">
+      <c r="C40" s="29" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="41" ht="169" spans="1:7">
-      <c r="A41" s="27" t="s">
+      <c r="A41" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="C41" s="24" t="s">
+      <c r="C41" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="D41" s="24" t="s">
+      <c r="D41" s="29" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="27" t="s">
+      <c r="A42" s="32" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="27" t="s">
+      <c r="A43" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="B43" s="24" t="s">
+      <c r="B43" s="29" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="44" ht="26" spans="1:7">
-      <c r="A44" s="27" t="s">
+      <c r="A44" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="B44" s="24" t="s">
+      <c r="B44" s="29" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="27" t="s">
+      <c r="A45" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="D45" s="24" t="s">
+      <c r="D45" s="29" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="27" t="s">
+      <c r="A46" s="32" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="27" t="s">
+      <c r="A47" s="32" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="27" t="s">
+      <c r="A48" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="C48" s="24" t="s">
+      <c r="C48" s="29" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="27" t="s">
+      <c r="A49" s="32" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="50" ht="78" spans="1:7">
-      <c r="A50" s="27" t="s">
+      <c r="A50" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="C50" s="24" t="s">
+      <c r="C50" s="29" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="27" t="s">
+      <c r="A51" s="32" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="52" ht="26" spans="1:7">
-      <c r="A52" s="27" t="s">
+      <c r="A52" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="B52" s="24" t="s">
+      <c r="B52" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="C52" s="24" t="s">
+      <c r="C52" s="29" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="53" ht="26" spans="1:7">
-      <c r="A53" s="23" t="s">
+      <c r="A53" s="28" t="s">
         <v>106</v>
       </c>
-      <c r="B53" s="24" t="s">
+      <c r="B53" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="D53" s="28"/>
-      <c r="E53" s="28"/>
-      <c r="F53" s="28"/>
-      <c r="G53" s="28"/>
+      <c r="D53" s="33"/>
+      <c r="E53" s="33"/>
+      <c r="F53" s="33"/>
+      <c r="G53" s="33"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="23" t="s">
+      <c r="A54" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="B54" s="24" t="s">
+      <c r="B54" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="C54" s="24" t="s">
+      <c r="C54" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="D54" s="28"/>
-      <c r="E54" s="28"/>
-      <c r="F54" s="28"/>
-      <c r="G54" s="28"/>
+      <c r="D54" s="33"/>
+      <c r="E54" s="33"/>
+      <c r="F54" s="33"/>
+      <c r="G54" s="33"/>
     </row>
     <row r="55" ht="52" spans="1:7">
-      <c r="A55" s="23" t="s">
+      <c r="A55" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="B55" s="28"/>
-      <c r="C55" s="28"/>
-      <c r="D55" s="24" t="s">
+      <c r="B55" s="33"/>
+      <c r="C55" s="33"/>
+      <c r="D55" s="29" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="56" ht="65" spans="1:7">
-      <c r="A56" s="23" t="s">
+      <c r="A56" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="B56" s="20" t="s">
+      <c r="B56" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="C56" s="20"/>
-      <c r="D56" s="24" t="s">
+      <c r="C56" s="25"/>
+      <c r="D56" s="29" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="57" ht="117" spans="1:7">
-      <c r="A57" s="23" t="s">
+      <c r="A57" s="28" t="s">
         <v>116</v>
       </c>
-      <c r="B57" s="20" t="s">
+      <c r="B57" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="C57" s="20" t="s">
+      <c r="C57" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="D57" s="24" t="s">
+      <c r="D57" s="29" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="23" t="s">
+      <c r="A58" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="B58" s="24" t="s">
+      <c r="B58" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="C58" s="28"/>
-      <c r="D58" s="28"/>
-      <c r="E58" s="28"/>
-      <c r="F58" s="28"/>
-      <c r="G58" s="28"/>
+      <c r="C58" s="33"/>
+      <c r="D58" s="33"/>
+      <c r="E58" s="33"/>
+      <c r="F58" s="33"/>
+      <c r="G58" s="33"/>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="23" t="s">
+      <c r="A59" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="B59" s="28"/>
-      <c r="C59" s="24" t="s">
+      <c r="B59" s="33"/>
+      <c r="C59" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="D59" s="28"/>
-      <c r="E59" s="28"/>
-      <c r="F59" s="28"/>
-      <c r="G59" s="28"/>
+      <c r="D59" s="33"/>
+      <c r="E59" s="33"/>
+      <c r="F59" s="33"/>
+      <c r="G59" s="33"/>
     </row>
     <row r="60" ht="52" spans="1:7">
-      <c r="A60" s="23" t="s">
+      <c r="A60" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="B60" s="28"/>
-      <c r="C60" s="28"/>
-      <c r="D60" s="24" t="s">
+      <c r="B60" s="33"/>
+      <c r="C60" s="33"/>
+      <c r="D60" s="29" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="23" t="s">
+      <c r="A61" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="B61" s="20" t="s">
+      <c r="B61" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="C61" s="20"/>
-      <c r="D61" s="28"/>
-      <c r="E61" s="28"/>
-      <c r="F61" s="28"/>
-      <c r="G61" s="28"/>
+      <c r="C61" s="25"/>
+      <c r="D61" s="33"/>
+      <c r="E61" s="33"/>
+      <c r="F61" s="33"/>
+      <c r="G61" s="33"/>
     </row>
     <row r="62" ht="39" spans="1:7">
-      <c r="A62" s="23" t="s">
+      <c r="A62" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="B62" s="28"/>
-      <c r="C62" s="28"/>
-      <c r="D62" s="24" t="s">
+      <c r="B62" s="33"/>
+      <c r="C62" s="33"/>
+      <c r="D62" s="29" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="63" ht="26" spans="1:7">
-      <c r="A63" s="23" t="s">
+      <c r="A63" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="B63" s="20" t="s">
+      <c r="B63" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="C63" s="20" t="s">
+      <c r="C63" s="25" t="s">
         <v>132</v>
       </c>
-      <c r="D63" s="28"/>
-      <c r="E63" s="28"/>
-      <c r="F63" s="28"/>
-      <c r="G63" s="28"/>
+      <c r="D63" s="33"/>
+      <c r="E63" s="33"/>
+      <c r="F63" s="33"/>
+      <c r="G63" s="33"/>
     </row>
     <row r="64" ht="26" spans="1:7">
-      <c r="A64" s="23" t="s">
+      <c r="A64" s="28" t="s">
         <v>133</v>
       </c>
-      <c r="B64" s="28"/>
-      <c r="C64" s="28"/>
-      <c r="D64" s="24" t="s">
+      <c r="B64" s="33"/>
+      <c r="C64" s="33"/>
+      <c r="D64" s="29" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="65" ht="26" spans="1:7">
-      <c r="A65" s="23" t="s">
+      <c r="A65" s="28" t="s">
         <v>135</v>
       </c>
-      <c r="B65" s="29" t="s">
+      <c r="B65" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="C65" s="28"/>
-      <c r="D65" s="28"/>
-      <c r="E65" s="28"/>
-      <c r="F65" s="28"/>
-      <c r="G65" s="28"/>
+      <c r="C65" s="33"/>
+      <c r="D65" s="33"/>
+      <c r="E65" s="33"/>
+      <c r="F65" s="33"/>
+      <c r="G65" s="33"/>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="23" t="s">
+      <c r="A66" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="B66" s="28"/>
-      <c r="C66" s="24" t="s">
+      <c r="B66" s="33"/>
+      <c r="C66" s="29" t="s">
         <v>138</v>
       </c>
-      <c r="D66" s="28"/>
-      <c r="E66" s="28"/>
-      <c r="F66" s="28"/>
-      <c r="G66" s="28"/>
+      <c r="D66" s="33"/>
+      <c r="E66" s="33"/>
+      <c r="F66" s="33"/>
+      <c r="G66" s="33"/>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="23" t="s">
+      <c r="A67" s="28" t="s">
         <v>139</v>
       </c>
-      <c r="B67" s="28"/>
-      <c r="C67" s="28"/>
+      <c r="B67" s="33"/>
+      <c r="C67" s="33"/>
     </row>
     <row r="68" ht="26" spans="1:7">
-      <c r="A68" s="23" t="s">
+      <c r="A68" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="B68" s="28"/>
-      <c r="C68" s="28"/>
-      <c r="D68" s="24" t="s">
+      <c r="B68" s="33"/>
+      <c r="C68" s="33"/>
+      <c r="D68" s="29" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="23" t="s">
+      <c r="A69" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="B69" s="20" t="s">
+      <c r="B69" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="C69" s="20"/>
+      <c r="C69" s="25"/>
     </row>
     <row r="70" ht="26" spans="1:7">
-      <c r="A70" s="23" t="s">
+      <c r="A70" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="B70" s="20" t="s">
+      <c r="B70" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="C70" s="20"/>
-      <c r="D70" s="28"/>
-      <c r="E70" s="28"/>
-      <c r="F70" s="28"/>
-      <c r="G70" s="28"/>
+      <c r="C70" s="25"/>
+      <c r="D70" s="33"/>
+      <c r="E70" s="33"/>
+      <c r="F70" s="33"/>
+      <c r="G70" s="33"/>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="23" t="s">
+      <c r="A71" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="B71" s="28"/>
-      <c r="C71" s="28"/>
+      <c r="B71" s="33"/>
+      <c r="C71" s="33"/>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="23" t="s">
+      <c r="A72" s="28" t="s">
         <v>147</v>
       </c>
-      <c r="B72" s="24" t="s">
+      <c r="B72" s="29" t="s">
         <v>148</v>
       </c>
-      <c r="C72" s="24" t="s">
+      <c r="C72" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="D72" s="28"/>
-      <c r="E72" s="28"/>
-      <c r="F72" s="28"/>
-      <c r="G72" s="28"/>
+      <c r="D72" s="33"/>
+      <c r="E72" s="33"/>
+      <c r="F72" s="33"/>
+      <c r="G72" s="33"/>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="23" t="s">
+      <c r="A73" s="28" t="s">
         <v>150</v>
       </c>
-      <c r="B73" s="28"/>
-      <c r="C73" s="24" t="s">
+      <c r="B73" s="33"/>
+      <c r="C73" s="29" t="s">
         <v>151</v>
       </c>
-      <c r="D73" s="28"/>
-      <c r="E73" s="28"/>
-      <c r="F73" s="28"/>
-      <c r="G73" s="28"/>
+      <c r="D73" s="33"/>
+      <c r="E73" s="33"/>
+      <c r="F73" s="33"/>
+      <c r="G73" s="33"/>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="23" t="s">
+      <c r="A74" s="28" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="23" t="s">
+      <c r="A75" s="28" t="s">
         <v>153</v>
       </c>
-      <c r="D75" s="28"/>
-      <c r="E75" s="28"/>
-      <c r="F75" s="28"/>
-      <c r="G75" s="28"/>
+      <c r="D75" s="33"/>
+      <c r="E75" s="33"/>
+      <c r="F75" s="33"/>
+      <c r="G75" s="33"/>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="23" t="s">
+      <c r="A76" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="B76" s="28"/>
-      <c r="C76" s="28"/>
-      <c r="D76" s="24" t="s">
+      <c r="B76" s="33"/>
+      <c r="C76" s="33"/>
+      <c r="D76" s="29" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="23" t="s">
+      <c r="A77" s="28" t="s">
         <v>156</v>
       </c>
-      <c r="B77" s="20"/>
-      <c r="C77" s="20"/>
+      <c r="B77" s="25"/>
+      <c r="C77" s="25"/>
     </row>
     <row r="78" ht="26" spans="1:7">
-      <c r="A78" s="30" t="s">
+      <c r="A78" s="35" t="s">
         <v>157</v>
       </c>
-      <c r="B78" s="24" t="s">
+      <c r="B78" s="29" t="s">
         <v>158</v>
       </c>
     </row>
@@ -2596,234 +2601,237 @@
   <dimension ref="A1:G51"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="6.64545454545455" style="14" customWidth="1"/>
-    <col min="2" max="7" width="16.4909090909091" style="15" customWidth="1"/>
-    <col min="8" max="16384" width="8.72727272727273" style="16"/>
+    <col min="1" max="1" width="6.64545454545455" style="19" customWidth="1"/>
+    <col min="2" max="7" width="16.4909090909091" style="20" customWidth="1"/>
+    <col min="8" max="16384" width="8.72727272727273" style="21"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="17"/>
-      <c r="B1" s="18" t="s">
+      <c r="A1" s="22"/>
+      <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="23" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="13" customFormat="1" ht="39" spans="1:7">
-      <c r="A2" s="19" t="s">
+    <row r="2" s="18" customFormat="1" ht="39" spans="1:7">
+      <c r="A2" s="24" t="s">
         <v>159</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20" t="s">
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25" t="s">
         <v>160</v>
       </c>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="26" t="s">
         <v>161</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="20" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="26" t="s">
         <v>163</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="20" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="26" t="s">
         <v>165</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="20" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="20" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="26" t="s">
         <v>171</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="20" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="21"/>
+      <c r="A8" s="26"/>
+      <c r="D8" s="20" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="21"/>
+      <c r="A9" s="26"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="21"/>
+      <c r="A10" s="26"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="21"/>
+      <c r="A11" s="26"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="21"/>
+      <c r="A12" s="26"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="21"/>
+      <c r="A13" s="26"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="21"/>
+      <c r="A14" s="26"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="21"/>
+      <c r="A15" s="26"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="21"/>
+      <c r="A16" s="26"/>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="21"/>
+      <c r="A17" s="26"/>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="21"/>
+      <c r="A18" s="26"/>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="21"/>
+      <c r="A19" s="26"/>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="21"/>
+      <c r="A20" s="26"/>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="21"/>
+      <c r="A21" s="26"/>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="21"/>
+      <c r="A22" s="26"/>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="21"/>
+      <c r="A23" s="26"/>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="21"/>
+      <c r="A24" s="26"/>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="21"/>
+      <c r="A25" s="26"/>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="21"/>
+      <c r="A26" s="26"/>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="21"/>
+      <c r="A27" s="26"/>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="21"/>
+      <c r="A28" s="26"/>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="21"/>
+      <c r="A29" s="26"/>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="21"/>
+      <c r="A30" s="26"/>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="21"/>
+      <c r="A31" s="26"/>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="21"/>
+      <c r="A32" s="26"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="21"/>
+      <c r="A33" s="26"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="21"/>
+      <c r="A34" s="26"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="21"/>
+      <c r="A35" s="26"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="21"/>
+      <c r="A36" s="26"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="21"/>
+      <c r="A37" s="26"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="21"/>
-      <c r="B38" s="20"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
+      <c r="A38" s="26"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="25"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="21"/>
-      <c r="B39" s="20"/>
-      <c r="C39" s="20"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="20"/>
-      <c r="G39" s="20"/>
+      <c r="A39" s="26"/>
+      <c r="B39" s="25"/>
+      <c r="C39" s="25"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="21"/>
+      <c r="A40" s="26"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="21"/>
+      <c r="A41" s="26"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="21"/>
+      <c r="A42" s="26"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="21"/>
+      <c r="A43" s="26"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="21"/>
+      <c r="A44" s="26"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="21"/>
+      <c r="A45" s="26"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="21"/>
+      <c r="A46" s="26"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="21"/>
+      <c r="A47" s="26"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="21"/>
+      <c r="A48" s="26"/>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="21"/>
+      <c r="A49" s="26"/>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="21"/>
+      <c r="A50" s="26"/>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="21"/>
+      <c r="A51" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2834,110 +2842,132 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="35.1818181818182" style="5" customWidth="1"/>
-    <col min="2" max="2" width="16.9090909090909" style="5" customWidth="1"/>
-    <col min="3" max="3" width="50.0909090909091" style="10" customWidth="1"/>
-    <col min="4" max="16384" width="8.72727272727273" style="5"/>
+    <col min="1" max="1" width="35.1818181818182" style="9" customWidth="1"/>
+    <col min="2" max="2" width="16.9090909090909" style="9" customWidth="1"/>
+    <col min="3" max="3" width="50.0909090909091" style="14" customWidth="1"/>
+    <col min="4" max="16384" width="8.72727272727273" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="B1" s="5" t="s">
+      <c r="A1" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>175</v>
       </c>
+      <c r="C1" s="14" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="B2" s="5" t="s">
+      <c r="A2" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="B2" s="9" t="s">
         <v>178</v>
       </c>
+      <c r="C2" s="14" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="A3" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="B3" s="9" t="s">
         <v>181</v>
       </c>
+      <c r="C3" s="14" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="4" ht="28" spans="1:3">
-      <c r="A4" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="C4" s="10" t="s">
+      <c r="A4" s="9" t="s">
         <v>183</v>
       </c>
+      <c r="B4" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="5" ht="42" spans="1:3">
-      <c r="A5" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="B5" s="9" t="s">
         <v>186</v>
       </c>
+      <c r="C5" s="14" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="6" ht="56" spans="1:3">
-      <c r="A6" s="12"/>
-      <c r="B6" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="C6" s="10" t="s">
+      <c r="A6" s="16"/>
+      <c r="B6" s="9" t="s">
         <v>188</v>
       </c>
+      <c r="C6" s="14" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="7" ht="28" spans="1:3">
-      <c r="A7" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="B7" s="5" t="s">
+      <c r="A7" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="B7" s="9" t="s">
         <v>191</v>
       </c>
+      <c r="C7" s="14" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="8" ht="28" spans="1:3">
-      <c r="A8" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="B8" s="5" t="s">
+      <c r="A8" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="B8" s="9" t="s">
         <v>194</v>
       </c>
+      <c r="C8" s="14" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="B9" s="5" t="s">
+      <c r="A9" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="B9" s="9" t="s">
         <v>197</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C11" s="17">
+        <v>0.440972222222222</v>
       </c>
     </row>
   </sheetData>
@@ -2952,124 +2982,113 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="9.18181818181818" style="3"/>
-    <col min="2" max="2" width="3.54545454545455" style="4" customWidth="1"/>
-    <col min="3" max="3" width="56.8181818181818" style="5" customWidth="1"/>
-    <col min="4" max="16384" width="8.72727272727273" style="5"/>
+    <col min="2" max="2" width="3.54545454545455" style="8" customWidth="1"/>
+    <col min="3" max="16384" width="8.72727272727273" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="C1" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>199</v>
+      <c r="C1" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="7">
+      <c r="A2" s="11">
         <v>2025.1</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="8">
         <v>11</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6">
+      <c r="C2" s="10">
         <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="8"/>
-      <c r="B3" s="4">
+      <c r="A3" s="12"/>
+      <c r="B3" s="8">
         <v>15</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6">
+      <c r="C3" s="10">
         <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="8"/>
-      <c r="B4" s="4">
+      <c r="A4" s="12"/>
+      <c r="B4" s="8">
         <v>17</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6">
+      <c r="C4" s="10">
         <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="8"/>
-      <c r="B5" s="4">
+      <c r="A5" s="12"/>
+      <c r="B5" s="8">
         <v>22</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6">
+      <c r="C5" s="10">
         <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="8"/>
-      <c r="B6" s="4">
+      <c r="A6" s="12"/>
+      <c r="B6" s="8">
         <v>24</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6">
+      <c r="C6" s="10">
         <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="8"/>
-      <c r="B7" s="4">
+      <c r="A7" s="12"/>
+      <c r="B7" s="8">
         <v>29</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6">
+      <c r="C7" s="10">
         <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="9"/>
-      <c r="B8" s="4">
+      <c r="A8" s="13"/>
+      <c r="B8" s="8">
         <v>31</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6">
+      <c r="C8" s="10">
         <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="7">
+      <c r="A9" s="11">
         <v>2025.11</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="8">
         <v>5</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6">
+      <c r="C9" s="10">
         <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="8"/>
-      <c r="B10" s="4">
+      <c r="A10" s="12"/>
+      <c r="B10" s="8">
         <v>7</v>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6">
+      <c r="C10" s="10">
         <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="9"/>
-      <c r="B11" s="4">
+      <c r="A11" s="13"/>
+      <c r="B11" s="8">
         <v>14</v>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6">
+      <c r="C11" s="10">
         <v>63</v>
       </c>
     </row>
@@ -3077,117 +3096,24 @@
       <c r="A12" s="3">
         <v>2025.12</v>
       </c>
-      <c r="B12" s="4">
-        <v>5</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="D12" s="6"/>
+      <c r="B12" s="8">
+        <v>26</v>
+      </c>
+      <c r="C12" s="10">
+        <v>225</v>
+      </c>
+      <c r="D12" s="9">
+        <v>74</v>
+      </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="B13" s="4">
-        <v>6</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="D13" s="6"/>
+      <c r="C13" s="10"/>
     </row>
     <row r="14" spans="1:4">
-      <c r="B14" s="4">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="D14" s="6"/>
+      <c r="C14" s="10"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="B15" s="4">
-        <v>10</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="D15" s="6"/>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="B16" s="4">
-        <v>11</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3">
-      <c r="B17" s="4">
-        <v>12</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3">
-      <c r="B18" s="4">
-        <v>15</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3">
-      <c r="B19" s="4">
-        <v>16</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3">
-      <c r="B20" s="4">
-        <v>17</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3">
-      <c r="B21" s="4">
-        <v>18</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3">
-      <c r="B22" s="4">
-        <v>19</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3">
-      <c r="B23" s="4">
-        <v>22</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3">
-      <c r="B24" s="4">
-        <v>23</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3">
-      <c r="B25" s="4">
-        <v>25</v>
-      </c>
+      <c r="C15" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3202,1026 +3128,1082 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O52"/>
+  <dimension ref="A1:P52"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="4.07272727272727" customWidth="1"/>
-    <col min="2" max="15" width="5.14545454545455" customWidth="1"/>
+    <col min="2" max="16" width="5.14545454545455" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1">
+    <row r="1" s="1" customFormat="1" spans="1:16">
+      <c r="A1" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B1" s="2">
         <v>5</v>
       </c>
-      <c r="C1" s="1">
+      <c r="C1" s="2">
         <v>6</v>
       </c>
-      <c r="D1" s="1">
+      <c r="D1" s="2">
         <v>9</v>
       </c>
-      <c r="E1" s="1">
+      <c r="E1" s="2">
         <v>10</v>
       </c>
-      <c r="F1" s="1">
+      <c r="F1" s="2">
         <v>11</v>
       </c>
-      <c r="G1" s="1">
+      <c r="G1" s="2">
         <v>12</v>
       </c>
-      <c r="H1" s="1">
+      <c r="H1" s="2">
         <v>15</v>
       </c>
-      <c r="I1" s="1">
+      <c r="I1" s="2">
         <v>16</v>
       </c>
-      <c r="J1" s="1">
+      <c r="J1" s="2">
         <v>17</v>
       </c>
-      <c r="K1" s="1">
+      <c r="K1" s="2">
         <v>18</v>
       </c>
-      <c r="L1" s="1">
+      <c r="L1" s="2">
         <v>19</v>
       </c>
-      <c r="M1" s="1">
+      <c r="M1" s="2">
         <v>22</v>
       </c>
-      <c r="N1" s="1">
+      <c r="N1" s="2">
         <v>23</v>
       </c>
-      <c r="O1" s="1">
+      <c r="O1" s="2">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" ht="28" customHeight="1" spans="1:15">
-      <c r="A2" s="1">
+      <c r="P1" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:16">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:15">
-      <c r="A3" s="1">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+    </row>
+    <row r="3" customHeight="1" spans="1:16">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-    </row>
-    <row r="4" ht="28" customHeight="1" spans="1:15">
-      <c r="A4" s="1">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+    </row>
+    <row r="4" customHeight="1" spans="1:16">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:15">
-      <c r="A5" s="1">
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+    </row>
+    <row r="5" customHeight="1" spans="1:16">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-    </row>
-    <row r="6" ht="28" customHeight="1" spans="1:15">
-      <c r="A6" s="1">
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+    </row>
+    <row r="6" customHeight="1" spans="1:16">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-    </row>
-    <row r="7" ht="28" customHeight="1" spans="1:15">
-      <c r="A7" s="1">
+      <c r="B6" s="4"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+    </row>
+    <row r="7" customHeight="1" spans="1:16">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="1"/>
-    </row>
-    <row r="8" ht="28" customHeight="1" spans="1:15">
-      <c r="A8" s="1">
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="4"/>
+    </row>
+    <row r="8" customHeight="1" spans="1:16">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-    </row>
-    <row r="9" ht="28" customHeight="1" spans="1:15">
-      <c r="A9" s="1">
+      <c r="B8" s="4"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" customHeight="1" spans="1:16">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-    </row>
-    <row r="10" ht="28" customHeight="1" spans="1:15">
-      <c r="A10" s="1">
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:16">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="1"/>
-    </row>
-    <row r="11" ht="28" customHeight="1" spans="1:15">
-      <c r="A11" s="1">
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" customHeight="1" spans="1:16">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-    </row>
-    <row r="12" ht="28" customHeight="1" spans="1:15">
-      <c r="A12" s="1">
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" customHeight="1" spans="1:16">
+      <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="1"/>
-    </row>
-    <row r="13" ht="28" customHeight="1" spans="1:15">
-      <c r="A13" s="1">
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" customHeight="1" spans="1:16">
+      <c r="A13" s="3">
         <v>12</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-    </row>
-    <row r="14" ht="28" customHeight="1" spans="1:15">
-      <c r="A14" s="1">
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:16">
+      <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-    </row>
-    <row r="15" ht="28" customHeight="1" spans="1:15">
-      <c r="A15" s="1">
+      <c r="B14" s="3"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:16">
+      <c r="A15" s="3">
         <v>14</v>
       </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-    </row>
-    <row r="16" ht="28" customHeight="1" spans="1:15">
-      <c r="A16" s="1">
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:16">
+      <c r="A16" s="3">
         <v>15</v>
       </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-    </row>
-    <row r="17" ht="28" customHeight="1" spans="1:15">
-      <c r="A17" s="1">
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" customHeight="1" spans="1:16">
+      <c r="A17" s="3">
         <v>16</v>
       </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-    </row>
-    <row r="18" ht="28" customHeight="1" spans="1:15">
-      <c r="A18" s="1">
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" customHeight="1" spans="1:16">
+      <c r="A18" s="3">
         <v>17</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="1"/>
-    </row>
-    <row r="19" ht="28" customHeight="1" spans="1:15">
-      <c r="A19" s="1">
+      <c r="B18" s="4"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" customHeight="1" spans="1:16">
+      <c r="A19" s="3">
         <v>18</v>
       </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-    </row>
-    <row r="20" ht="28" customHeight="1" spans="1:15">
-      <c r="A20" s="1">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" customHeight="1" spans="1:16">
+      <c r="A20" s="3">
         <v>19</v>
       </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-    </row>
-    <row r="21" ht="28" customHeight="1" spans="1:15">
-      <c r="A21" s="1">
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" customHeight="1" spans="1:16">
+      <c r="A21" s="3">
         <v>20</v>
       </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-    </row>
-    <row r="22" ht="28" customHeight="1" spans="1:15">
-      <c r="A22" s="1">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:16">
+      <c r="A22" s="3">
         <v>21</v>
       </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-    </row>
-    <row r="23" ht="28" customHeight="1" spans="1:15">
-      <c r="A23" s="1">
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" customHeight="1" spans="1:16">
+      <c r="A23" s="3">
         <v>22</v>
       </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-    </row>
-    <row r="24" ht="28" customHeight="1" spans="1:15">
-      <c r="A24" s="1">
+      <c r="B23" s="3"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:16">
+      <c r="A24" s="3">
         <v>23</v>
       </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-    </row>
-    <row r="25" ht="28" customHeight="1" spans="1:15">
-      <c r="A25" s="1">
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" customHeight="1" spans="1:16">
+      <c r="A25" s="3">
         <v>24</v>
       </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-    </row>
-    <row r="26" ht="28" customHeight="1" spans="1:15">
-      <c r="A26" s="1">
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" customHeight="1" spans="1:16">
+      <c r="A26" s="3">
         <v>25</v>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-    </row>
-    <row r="27" ht="28" customHeight="1" spans="1:15">
-      <c r="A27" s="1">
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" customHeight="1" spans="1:16">
+      <c r="A27" s="3">
         <v>26</v>
       </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-    </row>
-    <row r="28" ht="28" customHeight="1" spans="1:15">
-      <c r="A28" s="1">
+      <c r="B27" s="3"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" customHeight="1" spans="1:16">
+      <c r="A28" s="3">
         <v>27</v>
       </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="2"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-    </row>
-    <row r="29" ht="28" customHeight="1" spans="1:15">
-      <c r="A29" s="1">
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="4"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" customHeight="1" spans="1:16">
+      <c r="A29" s="3">
         <v>28</v>
       </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-    </row>
-    <row r="30" ht="28" customHeight="1" spans="1:15">
-      <c r="A30" s="1">
+      <c r="B29" s="4"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" customHeight="1" spans="1:16">
+      <c r="A30" s="3">
         <v>29</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-    </row>
-    <row r="31" ht="28" customHeight="1" spans="1:15">
-      <c r="A31" s="1">
+      <c r="B30" s="4"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:16">
+      <c r="A31" s="3">
         <v>30</v>
       </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="2"/>
-      <c r="O31" s="1"/>
-    </row>
-    <row r="32" ht="28" customHeight="1" spans="1:15">
-      <c r="A32" s="1">
+      <c r="B31" s="3"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="4"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:16">
+      <c r="A32" s="3">
         <v>31</v>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-    </row>
-    <row r="33" ht="28" customHeight="1" spans="1:15">
-      <c r="A33" s="1">
+      <c r="B32" s="4"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" customHeight="1" spans="1:16">
+      <c r="A33" s="3">
         <v>32</v>
       </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
-    </row>
-    <row r="34" ht="28" customHeight="1" spans="1:15">
-      <c r="A34" s="1">
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3"/>
+      <c r="O33" s="3"/>
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" customHeight="1" spans="1:16">
+      <c r="A34" s="3">
         <v>33</v>
       </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
-    </row>
-    <row r="35" ht="28" customHeight="1" spans="1:15">
-      <c r="A35" s="1">
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3"/>
+      <c r="O34" s="3"/>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" customHeight="1" spans="1:16">
+      <c r="A35" s="3">
         <v>34</v>
       </c>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-    </row>
-    <row r="36" ht="28" customHeight="1" spans="1:15">
-      <c r="A36" s="1">
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
+      <c r="N35" s="3"/>
+      <c r="O35" s="3"/>
+      <c r="P35" s="3"/>
+    </row>
+    <row r="36" customHeight="1" spans="1:16">
+      <c r="A36" s="3">
         <v>35</v>
       </c>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
-    </row>
-    <row r="37" ht="28" customHeight="1" spans="1:15">
-      <c r="A37" s="1">
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="4"/>
+      <c r="O36" s="3"/>
+      <c r="P36" s="3"/>
+    </row>
+    <row r="37" customHeight="1" spans="1:16">
+      <c r="A37" s="3">
         <v>36</v>
       </c>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
-    </row>
-    <row r="38" ht="28" customHeight="1" spans="1:15">
-      <c r="A38" s="1">
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="3"/>
+      <c r="O37" s="3"/>
+      <c r="P37" s="3"/>
+    </row>
+    <row r="38" customHeight="1" spans="1:16">
+      <c r="A38" s="3">
         <v>37</v>
       </c>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-    </row>
-    <row r="39" ht="28" customHeight="1" spans="1:15">
-      <c r="A39" s="1">
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+      <c r="O38" s="3"/>
+      <c r="P38" s="3"/>
+    </row>
+    <row r="39" customHeight="1" spans="1:16">
+      <c r="A39" s="3">
         <v>38</v>
       </c>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
-    </row>
-    <row r="40" ht="28" customHeight="1" spans="1:15">
-      <c r="A40" s="1">
+      <c r="B39" s="3"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="3"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" customHeight="1" spans="1:16">
+      <c r="A40" s="3">
         <v>39</v>
       </c>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
-      <c r="O40" s="1"/>
-    </row>
-    <row r="41" ht="28" customHeight="1" spans="1:15">
-      <c r="A41" s="1">
+      <c r="B40" s="4"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="3"/>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" customHeight="1" spans="1:16">
+      <c r="A41" s="3">
         <v>40</v>
       </c>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
-    </row>
-    <row r="42" ht="28" customHeight="1" spans="1:15">
-      <c r="A42" s="1">
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4"/>
+      <c r="N41" s="4"/>
+      <c r="O41" s="3"/>
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" customHeight="1" spans="1:16">
+      <c r="A42" s="3">
         <v>41</v>
       </c>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
-      <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
-    </row>
-    <row r="43" ht="28" customHeight="1" spans="1:15">
-      <c r="A43" s="1">
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3"/>
+      <c r="M42" s="3"/>
+      <c r="N42" s="3"/>
+      <c r="O42" s="3"/>
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" customHeight="1" spans="1:16">
+      <c r="A43" s="3">
         <v>42</v>
       </c>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-      <c r="O43" s="1"/>
-    </row>
-    <row r="44" ht="28" customHeight="1" spans="1:15">
-      <c r="A44" s="1">
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="3"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="3"/>
+      <c r="N43" s="3"/>
+      <c r="O43" s="3"/>
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" customHeight="1" spans="1:16">
+      <c r="A44" s="3">
         <v>43</v>
       </c>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
-    </row>
-    <row r="45" ht="28" customHeight="1" spans="1:15">
-      <c r="A45" s="1">
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3"/>
+      <c r="M44" s="3"/>
+      <c r="N44" s="3"/>
+      <c r="O44" s="3"/>
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" customHeight="1" spans="1:16">
+      <c r="A45" s="3">
         <v>44</v>
       </c>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="1"/>
-      <c r="N45" s="1"/>
-      <c r="O45" s="1"/>
-    </row>
-    <row r="46" ht="28" customHeight="1" spans="1:15">
-      <c r="A46" s="1">
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="7"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="3"/>
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" customHeight="1" spans="1:16">
+      <c r="A46" s="3">
         <v>45</v>
       </c>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
-      <c r="N46" s="1"/>
-      <c r="O46" s="1"/>
-    </row>
-    <row r="47" ht="28" customHeight="1" spans="1:15">
-      <c r="A47" s="1">
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3"/>
+      <c r="L46" s="3"/>
+      <c r="M46" s="3"/>
+      <c r="N46" s="3"/>
+      <c r="O46" s="3"/>
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" customHeight="1" spans="1:16">
+      <c r="A47" s="3">
         <v>46</v>
       </c>
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
-      <c r="M47" s="1"/>
-      <c r="N47" s="1"/>
-      <c r="O47" s="1"/>
-    </row>
-    <row r="48" ht="28" customHeight="1" spans="1:15">
-      <c r="A48" s="1">
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="3"/>
+      <c r="L47" s="3"/>
+      <c r="M47" s="3"/>
+      <c r="N47" s="4"/>
+      <c r="O47" s="3"/>
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" customHeight="1" spans="1:16">
+      <c r="A48" s="3">
         <v>47</v>
       </c>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
-      <c r="N48" s="1"/>
-      <c r="O48" s="1"/>
-    </row>
-    <row r="49" ht="28" customHeight="1" spans="1:15">
-      <c r="A49" s="1">
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3"/>
+      <c r="L48" s="3"/>
+      <c r="M48" s="4"/>
+      <c r="N48" s="3"/>
+      <c r="O48" s="3"/>
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" customHeight="1" spans="1:16">
+      <c r="A49" s="3">
         <v>48</v>
       </c>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-      <c r="K49" s="1"/>
-      <c r="L49" s="1"/>
-      <c r="M49" s="1"/>
-      <c r="N49" s="1"/>
-      <c r="O49" s="1"/>
-    </row>
-    <row r="50" ht="28" customHeight="1" spans="1:15">
-      <c r="A50" s="1">
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="3"/>
+      <c r="L49" s="3"/>
+      <c r="M49" s="3"/>
+      <c r="N49" s="3"/>
+      <c r="O49" s="3"/>
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" customHeight="1" spans="1:16">
+      <c r="A50" s="3">
         <v>49</v>
       </c>
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="1"/>
-      <c r="M50" s="1"/>
-      <c r="N50" s="1"/>
-      <c r="O50" s="1"/>
-    </row>
-    <row r="51" ht="28" customHeight="1" spans="1:15">
-      <c r="A51" s="1">
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="3"/>
+      <c r="J50" s="3"/>
+      <c r="K50" s="3"/>
+      <c r="L50" s="3"/>
+      <c r="M50" s="3"/>
+      <c r="N50" s="3"/>
+      <c r="O50" s="3"/>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" customHeight="1" spans="1:16">
+      <c r="A51" s="3">
         <v>50</v>
       </c>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
-      <c r="L51" s="1"/>
-      <c r="M51" s="1"/>
-      <c r="N51" s="1"/>
-      <c r="O51" s="1"/>
-    </row>
-    <row r="52" ht="28" customHeight="1" spans="1:15">
-      <c r="A52" s="1">
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
+      <c r="I51" s="3"/>
+      <c r="J51" s="3"/>
+      <c r="K51" s="3"/>
+      <c r="L51" s="3"/>
+      <c r="M51" s="3"/>
+      <c r="N51" s="3"/>
+      <c r="O51" s="3"/>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" customHeight="1" spans="1:16">
+      <c r="A52" s="3">
         <v>51</v>
       </c>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="1"/>
-      <c r="M52" s="1"/>
-      <c r="N52" s="1"/>
-      <c r="O52" s="1"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="3"/>
+      <c r="I52" s="3"/>
+      <c r="J52" s="3"/>
+      <c r="K52" s="3"/>
+      <c r="L52" s="3"/>
+      <c r="M52" s="3"/>
+      <c r="N52" s="3"/>
+      <c r="O52" s="3"/>
+      <c r="P52" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10480" activeTab="1"/>
+    <workbookView windowWidth="20750" windowHeight="10480" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="学生、老师" sheetId="5" r:id="rId1"/>
@@ -30,8 +30,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="213">
   <si>
     <t>姓名</t>
   </si>
@@ -294,7 +316,7 @@
     <t>早读（劝学/磨刀霍霍向鑫洋）、生物30分、记笔记</t>
   </si>
   <si>
-    <t>孺子、反思（我也老了、相见时难别亦难，东风无力百花残、未来是你们，但现在未必、革命尚未成功）（一旬老人）、哲学（旁观者：学地理要以旁观者视角、水循环：逆水行舟，退到极点就是进）、装（问第几题有问题，体现自己做得快、费马点）、考进班级前10、种地（初二第三次月考、打赌八上期末物理自己和郑永泽考的低者种地）、因错题争论、嫂子（47）</t>
+    <t>孺子、反思（我也老了、相见时难别亦难，东风无力百花残、未来是你们，但现在未必、革命尚未成功）（一旬老人）、哲学（旁观者：学地理要以旁观者视角、水循环：逆水行舟，退到极点就是进）、装（问第几题有问题，体现自己做得快、费马点）、考进班级前10、种地（初二第三次月考、打赌八上期末物理自己和郑永泽考的低者种地）、因错题争论、嫂子（47）、三江口</t>
   </si>
   <si>
     <t>游武毅</t>
@@ -375,10 +397,10 @@
     <t>数1</t>
   </si>
   <si>
-    <t>讲评作业（折名字/3、4组过道）、课件（熊熊疑惑、喜羊羊修花圃）、今天纪律差、笔记本拿出来、作业只改正面、告诉原因</t>
-  </si>
-  <si>
-    <t>××写第×题、固定请人、站后面、每次考试后总结</t>
+    <t>讲评作业（折名字/3、4组过道）、课件（熊熊疑惑、喜羊羊修花圃）、今天纪律差、笔记本拿出来、作业只改正面、告诉原因、同意举手</t>
+  </si>
+  <si>
+    <t>××写第×题、固定请人、站后面、每次考试后总结、同意→弘毅</t>
   </si>
   <si>
     <t>英1</t>
@@ -390,7 +412,7 @@
     <t>跑操造句</t>
   </si>
   <si>
-    <t>请假13个工作日（作业减、早读乱、大脚）、投屏打字、收作业制度、男厕洗手、量化制度、监控、电脑控制、周五末节读书</t>
+    <t>请假13个工作日（作业减、早读乱、大脚）、投屏打字、收作业制度、男厕洗手、量化制度、监控、电脑控制、周五末节读书、干嘛嘞/清楚没/理解没理解</t>
   </si>
   <si>
     <t>政1</t>
@@ -645,6 +667,12 @@
     <t>八上12.18</t>
   </si>
   <si>
+    <t>八上12.29</t>
+  </si>
+  <si>
+    <t>和46号上台写英语句，多次探头看，刘老师让唐家祺改正后同步改正</t>
+  </si>
+  <si>
     <t>政治啧</t>
   </si>
   <si>
@@ -652,22 +680,40 @@
   </si>
   <si>
     <t>12月</t>
+  </si>
+  <si>
+    <t>被请次数</t>
+  </si>
+  <si>
+    <t>被请节数</t>
+  </si>
+  <si>
+    <t>最高连击</t>
+  </si>
+  <si>
+    <t>单节被请概率</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
@@ -838,7 +884,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="42">
+  <fills count="44">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -848,6 +894,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.05"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1086,7 +1144,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -1101,6 +1159,19 @@
       <right style="thin">
         <color auto="1"/>
       </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -1249,115 +1320,109 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1366,10 +1431,10 @@
     <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1378,10 +1443,10 @@
     <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1390,14 +1455,20 @@
     <xf numFmtId="0" fontId="22" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1405,107 +1476,143 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1841,723 +1948,723 @@
   <dimension ref="A1:G78"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="7.59090909090909" style="28" customWidth="1"/>
-    <col min="2" max="7" width="25.8727272727273" style="29" customWidth="1"/>
+    <col min="1" max="1" width="7.59090909090909" style="39" customWidth="1"/>
+    <col min="2" max="7" width="25.8727272727273" style="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="27" customFormat="1" spans="1:7">
-      <c r="A1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="31" t="s">
+    <row r="1" s="38" customFormat="1" spans="1:7">
+      <c r="A1" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="42" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="40" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" ht="39" spans="1:7">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="40" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="43" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="32" t="s">
+      <c r="A5" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="40" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" s="40" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" ht="208" spans="1:7">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="29" t="s">
+      <c r="D7" s="40" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="32" t="s">
+      <c r="A8" s="43" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="43" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="40" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="32" t="s">
+      <c r="A11" s="43" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="32" t="s">
+      <c r="A12" s="43" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="13" ht="39" spans="1:7">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="29" t="s">
+      <c r="D13" s="40" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="32" t="s">
+      <c r="A14" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="40" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="32" t="s">
+      <c r="A16" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" s="40" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="17" ht="26" spans="1:4">
-      <c r="A17" s="32" t="s">
+      <c r="A17" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" s="40" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="32" t="s">
+      <c r="A18" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="29" t="s">
+      <c r="D18" s="40" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="32" t="s">
+      <c r="A19" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="29" t="s">
+      <c r="D19" s="40" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="20" ht="26" spans="1:4">
-      <c r="A20" s="32" t="s">
+      <c r="A20" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="29" t="s">
+      <c r="B20" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="C20" s="40" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="21" ht="39" spans="1:4">
-      <c r="A21" s="32" t="s">
+      <c r="A21" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="29" t="s">
+      <c r="B21" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="D21" s="29" t="s">
+      <c r="D21" s="40" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="32" t="s">
+      <c r="A22" s="43" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="23" ht="26" spans="1:4">
-      <c r="A23" s="32" t="s">
+      <c r="A23" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="29" t="s">
+      <c r="B23" s="40" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="24" ht="52" spans="1:4">
-      <c r="A24" s="32" t="s">
+      <c r="A24" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="B24" s="29" t="s">
+      <c r="B24" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="D24" s="29" t="s">
+      <c r="D24" s="40" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="32" t="s">
+      <c r="A25" s="43" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="32" t="s">
+      <c r="A26" s="43" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="32" t="s">
+      <c r="A27" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="B27" s="29" t="s">
+      <c r="B27" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C27" s="40" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="28" ht="91" spans="1:4">
-      <c r="A28" s="32" t="s">
+      <c r="A28" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="B28" s="29" t="s">
+      <c r="B28" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="D28" s="29" t="s">
+      <c r="D28" s="40" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="32" t="s">
+      <c r="A29" s="43" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="32" t="s">
+      <c r="A30" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="B30" s="29" t="s">
+      <c r="B30" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="C30" s="29" t="s">
+      <c r="C30" s="40" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="32" t="s">
+      <c r="A31" s="43" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="32" t="s">
+      <c r="A32" s="43" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="32" t="s">
+      <c r="A33" s="43" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="32" t="s">
+      <c r="A34" s="43" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="32" t="s">
+      <c r="A35" s="43" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="32" t="s">
+      <c r="A36" s="43" t="s">
         <v>72</v>
       </c>
-      <c r="B36" s="29" t="s">
+      <c r="B36" s="40" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="37" ht="26" spans="1:7">
-      <c r="A37" s="32" t="s">
+      <c r="A37" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="C37" s="29" t="s">
+      <c r="C37" s="40" t="s">
         <v>75</v>
       </c>
-      <c r="D37" s="29" t="s">
+      <c r="D37" s="40" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="32" t="s">
+      <c r="A38" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="B38" s="29" t="s">
+      <c r="B38" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="C38" s="33"/>
-      <c r="D38" s="33"/>
-      <c r="E38" s="33"/>
-      <c r="F38" s="33"/>
-      <c r="G38" s="33"/>
+      <c r="C38" s="44"/>
+      <c r="D38" s="44"/>
+      <c r="E38" s="44"/>
+      <c r="F38" s="44"/>
+      <c r="G38" s="44"/>
     </row>
     <row r="39" ht="26" spans="1:7">
-      <c r="A39" s="32" t="s">
+      <c r="A39" s="43" t="s">
         <v>79</v>
       </c>
-      <c r="C39" s="29" t="s">
+      <c r="C39" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="D39" s="29" t="s">
+      <c r="D39" s="40" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="32" t="s">
+      <c r="A40" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="B40" s="29" t="s">
+      <c r="B40" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="C40" s="29" t="s">
+      <c r="C40" s="40" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="41" ht="169" spans="1:7">
-      <c r="A41" s="32" t="s">
+      <c r="A41" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="C41" s="29" t="s">
+      <c r="C41" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="D41" s="29" t="s">
+      <c r="D41" s="40" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="32" t="s">
+      <c r="A42" s="43" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="32" t="s">
+      <c r="A43" s="43" t="s">
         <v>89</v>
       </c>
-      <c r="B43" s="29" t="s">
+      <c r="B43" s="40" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="44" ht="26" spans="1:7">
-      <c r="A44" s="32" t="s">
+      <c r="A44" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="B44" s="29" t="s">
+      <c r="B44" s="40" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="32" t="s">
+      <c r="A45" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="D45" s="29" t="s">
+      <c r="D45" s="40" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="32" t="s">
+      <c r="A46" s="43" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="32" t="s">
+      <c r="A47" s="43" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="32" t="s">
+      <c r="A48" s="43" t="s">
         <v>97</v>
       </c>
-      <c r="C48" s="29" t="s">
+      <c r="C48" s="40" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="32" t="s">
+      <c r="A49" s="43" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="50" ht="78" spans="1:7">
-      <c r="A50" s="32" t="s">
+      <c r="A50" s="43" t="s">
         <v>100</v>
       </c>
-      <c r="C50" s="29" t="s">
+      <c r="C50" s="40" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="32" t="s">
+      <c r="A51" s="43" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="52" ht="26" spans="1:7">
-      <c r="A52" s="32" t="s">
+      <c r="A52" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="B52" s="29" t="s">
+      <c r="B52" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="C52" s="29" t="s">
+      <c r="C52" s="40" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="53" ht="26" spans="1:7">
-      <c r="A53" s="28" t="s">
+      <c r="A53" s="39" t="s">
         <v>106</v>
       </c>
-      <c r="B53" s="29" t="s">
+      <c r="B53" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="D53" s="33"/>
-      <c r="E53" s="33"/>
-      <c r="F53" s="33"/>
-      <c r="G53" s="33"/>
+      <c r="D53" s="44"/>
+      <c r="E53" s="44"/>
+      <c r="F53" s="44"/>
+      <c r="G53" s="44"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="28" t="s">
+      <c r="A54" s="39" t="s">
         <v>108</v>
       </c>
-      <c r="B54" s="29" t="s">
+      <c r="B54" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="C54" s="29" t="s">
+      <c r="C54" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="D54" s="33"/>
-      <c r="E54" s="33"/>
-      <c r="F54" s="33"/>
-      <c r="G54" s="33"/>
+      <c r="D54" s="44"/>
+      <c r="E54" s="44"/>
+      <c r="F54" s="44"/>
+      <c r="G54" s="44"/>
     </row>
     <row r="55" ht="52" spans="1:7">
-      <c r="A55" s="28" t="s">
+      <c r="A55" s="39" t="s">
         <v>111</v>
       </c>
-      <c r="B55" s="33"/>
-      <c r="C55" s="33"/>
-      <c r="D55" s="29" t="s">
+      <c r="B55" s="44"/>
+      <c r="C55" s="44"/>
+      <c r="D55" s="40" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="56" ht="65" spans="1:7">
-      <c r="A56" s="28" t="s">
+      <c r="A56" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="B56" s="25" t="s">
+      <c r="B56" s="36" t="s">
         <v>114</v>
       </c>
-      <c r="C56" s="25"/>
-      <c r="D56" s="29" t="s">
+      <c r="C56" s="36"/>
+      <c r="D56" s="40" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="57" ht="117" spans="1:7">
-      <c r="A57" s="28" t="s">
+      <c r="A57" s="39" t="s">
         <v>116</v>
       </c>
-      <c r="B57" s="25" t="s">
+      <c r="B57" s="36" t="s">
         <v>117</v>
       </c>
-      <c r="C57" s="25" t="s">
+      <c r="C57" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="D57" s="29" t="s">
+      <c r="D57" s="40" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="28" t="s">
+      <c r="A58" s="39" t="s">
         <v>120</v>
       </c>
-      <c r="B58" s="29" t="s">
+      <c r="B58" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="C58" s="33"/>
-      <c r="D58" s="33"/>
-      <c r="E58" s="33"/>
-      <c r="F58" s="33"/>
-      <c r="G58" s="33"/>
+      <c r="C58" s="44"/>
+      <c r="D58" s="44"/>
+      <c r="E58" s="44"/>
+      <c r="F58" s="44"/>
+      <c r="G58" s="44"/>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="28" t="s">
+      <c r="A59" s="39" t="s">
         <v>122</v>
       </c>
-      <c r="B59" s="33"/>
-      <c r="C59" s="29" t="s">
+      <c r="B59" s="44"/>
+      <c r="C59" s="40" t="s">
         <v>123</v>
       </c>
-      <c r="D59" s="33"/>
-      <c r="E59" s="33"/>
-      <c r="F59" s="33"/>
-      <c r="G59" s="33"/>
+      <c r="D59" s="44"/>
+      <c r="E59" s="44"/>
+      <c r="F59" s="44"/>
+      <c r="G59" s="44"/>
     </row>
     <row r="60" ht="52" spans="1:7">
-      <c r="A60" s="28" t="s">
+      <c r="A60" s="39" t="s">
         <v>124</v>
       </c>
-      <c r="B60" s="33"/>
-      <c r="C60" s="33"/>
-      <c r="D60" s="29" t="s">
+      <c r="B60" s="44"/>
+      <c r="C60" s="44"/>
+      <c r="D60" s="40" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="28" t="s">
+      <c r="A61" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="B61" s="25" t="s">
+      <c r="B61" s="36" t="s">
         <v>127</v>
       </c>
-      <c r="C61" s="25"/>
-      <c r="D61" s="33"/>
-      <c r="E61" s="33"/>
-      <c r="F61" s="33"/>
-      <c r="G61" s="33"/>
+      <c r="C61" s="36"/>
+      <c r="D61" s="44"/>
+      <c r="E61" s="44"/>
+      <c r="F61" s="44"/>
+      <c r="G61" s="44"/>
     </row>
     <row r="62" ht="39" spans="1:7">
-      <c r="A62" s="28" t="s">
+      <c r="A62" s="39" t="s">
         <v>128</v>
       </c>
-      <c r="B62" s="33"/>
-      <c r="C62" s="33"/>
-      <c r="D62" s="29" t="s">
+      <c r="B62" s="44"/>
+      <c r="C62" s="44"/>
+      <c r="D62" s="40" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="63" ht="26" spans="1:7">
-      <c r="A63" s="28" t="s">
+      <c r="A63" s="39" t="s">
         <v>130</v>
       </c>
-      <c r="B63" s="25" t="s">
+      <c r="B63" s="36" t="s">
         <v>131</v>
       </c>
-      <c r="C63" s="25" t="s">
+      <c r="C63" s="36" t="s">
         <v>132</v>
       </c>
-      <c r="D63" s="33"/>
-      <c r="E63" s="33"/>
-      <c r="F63" s="33"/>
-      <c r="G63" s="33"/>
+      <c r="D63" s="44"/>
+      <c r="E63" s="44"/>
+      <c r="F63" s="44"/>
+      <c r="G63" s="44"/>
     </row>
     <row r="64" ht="26" spans="1:7">
-      <c r="A64" s="28" t="s">
+      <c r="A64" s="39" t="s">
         <v>133</v>
       </c>
-      <c r="B64" s="33"/>
-      <c r="C64" s="33"/>
-      <c r="D64" s="29" t="s">
+      <c r="B64" s="44"/>
+      <c r="C64" s="44"/>
+      <c r="D64" s="40" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="65" ht="26" spans="1:7">
-      <c r="A65" s="28" t="s">
+      <c r="A65" s="39" t="s">
         <v>135</v>
       </c>
-      <c r="B65" s="34" t="s">
+      <c r="B65" s="45" t="s">
         <v>136</v>
       </c>
-      <c r="C65" s="33"/>
-      <c r="D65" s="33"/>
-      <c r="E65" s="33"/>
-      <c r="F65" s="33"/>
-      <c r="G65" s="33"/>
+      <c r="C65" s="44"/>
+      <c r="D65" s="44"/>
+      <c r="E65" s="44"/>
+      <c r="F65" s="44"/>
+      <c r="G65" s="44"/>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="28" t="s">
+      <c r="A66" s="39" t="s">
         <v>137</v>
       </c>
-      <c r="B66" s="33"/>
-      <c r="C66" s="29" t="s">
+      <c r="B66" s="44"/>
+      <c r="C66" s="40" t="s">
         <v>138</v>
       </c>
-      <c r="D66" s="33"/>
-      <c r="E66" s="33"/>
-      <c r="F66" s="33"/>
-      <c r="G66" s="33"/>
+      <c r="D66" s="44"/>
+      <c r="E66" s="44"/>
+      <c r="F66" s="44"/>
+      <c r="G66" s="44"/>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="28" t="s">
+      <c r="A67" s="39" t="s">
         <v>139</v>
       </c>
-      <c r="B67" s="33"/>
-      <c r="C67" s="33"/>
+      <c r="B67" s="44"/>
+      <c r="C67" s="44"/>
     </row>
     <row r="68" ht="26" spans="1:7">
-      <c r="A68" s="28" t="s">
+      <c r="A68" s="39" t="s">
         <v>140</v>
       </c>
-      <c r="B68" s="33"/>
-      <c r="C68" s="33"/>
-      <c r="D68" s="29" t="s">
+      <c r="B68" s="44"/>
+      <c r="C68" s="44"/>
+      <c r="D68" s="40" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="28" t="s">
+      <c r="A69" s="39" t="s">
         <v>142</v>
       </c>
-      <c r="B69" s="25" t="s">
+      <c r="B69" s="36" t="s">
         <v>143</v>
       </c>
-      <c r="C69" s="25"/>
+      <c r="C69" s="36"/>
     </row>
     <row r="70" ht="26" spans="1:7">
-      <c r="A70" s="28" t="s">
+      <c r="A70" s="39" t="s">
         <v>144</v>
       </c>
-      <c r="B70" s="25" t="s">
+      <c r="B70" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="C70" s="25"/>
-      <c r="D70" s="33"/>
-      <c r="E70" s="33"/>
-      <c r="F70" s="33"/>
-      <c r="G70" s="33"/>
+      <c r="C70" s="36"/>
+      <c r="D70" s="44"/>
+      <c r="E70" s="44"/>
+      <c r="F70" s="44"/>
+      <c r="G70" s="44"/>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="28" t="s">
+      <c r="A71" s="39" t="s">
         <v>146</v>
       </c>
-      <c r="B71" s="33"/>
-      <c r="C71" s="33"/>
+      <c r="B71" s="44"/>
+      <c r="C71" s="44"/>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="28" t="s">
+      <c r="A72" s="39" t="s">
         <v>147</v>
       </c>
-      <c r="B72" s="29" t="s">
+      <c r="B72" s="40" t="s">
         <v>148</v>
       </c>
-      <c r="C72" s="29" t="s">
+      <c r="C72" s="40" t="s">
         <v>149</v>
       </c>
-      <c r="D72" s="33"/>
-      <c r="E72" s="33"/>
-      <c r="F72" s="33"/>
-      <c r="G72" s="33"/>
+      <c r="D72" s="44"/>
+      <c r="E72" s="44"/>
+      <c r="F72" s="44"/>
+      <c r="G72" s="44"/>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="28" t="s">
+      <c r="A73" s="39" t="s">
         <v>150</v>
       </c>
-      <c r="B73" s="33"/>
-      <c r="C73" s="29" t="s">
+      <c r="B73" s="44"/>
+      <c r="C73" s="40" t="s">
         <v>151</v>
       </c>
-      <c r="D73" s="33"/>
-      <c r="E73" s="33"/>
-      <c r="F73" s="33"/>
-      <c r="G73" s="33"/>
+      <c r="D73" s="44"/>
+      <c r="E73" s="44"/>
+      <c r="F73" s="44"/>
+      <c r="G73" s="44"/>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="28" t="s">
+      <c r="A74" s="39" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="28" t="s">
+      <c r="A75" s="39" t="s">
         <v>153</v>
       </c>
-      <c r="D75" s="33"/>
-      <c r="E75" s="33"/>
-      <c r="F75" s="33"/>
-      <c r="G75" s="33"/>
+      <c r="D75" s="44"/>
+      <c r="E75" s="44"/>
+      <c r="F75" s="44"/>
+      <c r="G75" s="44"/>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="28" t="s">
+      <c r="A76" s="39" t="s">
         <v>154</v>
       </c>
-      <c r="B76" s="33"/>
-      <c r="C76" s="33"/>
-      <c r="D76" s="29" t="s">
+      <c r="B76" s="44"/>
+      <c r="C76" s="44"/>
+      <c r="D76" s="40" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="28" t="s">
+      <c r="A77" s="39" t="s">
         <v>156</v>
       </c>
-      <c r="B77" s="25"/>
-      <c r="C77" s="25"/>
+      <c r="B77" s="36"/>
+      <c r="C77" s="36"/>
     </row>
     <row r="78" ht="26" spans="1:7">
-      <c r="A78" s="35" t="s">
+      <c r="A78" s="46" t="s">
         <v>157</v>
       </c>
-      <c r="B78" s="29" t="s">
+      <c r="B78" s="40" t="s">
         <v>158</v>
       </c>
     </row>
@@ -2601,237 +2708,237 @@
   <dimension ref="A1:G51"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="6.64545454545455" style="19" customWidth="1"/>
-    <col min="2" max="7" width="16.4909090909091" style="20" customWidth="1"/>
-    <col min="8" max="16384" width="8.72727272727273" style="21"/>
+    <col min="1" max="1" width="6.64545454545455" style="30" customWidth="1"/>
+    <col min="2" max="7" width="16.4909090909091" style="31" customWidth="1"/>
+    <col min="8" max="16384" width="8.72727272727273" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="22"/>
-      <c r="B1" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="23" t="s">
+      <c r="A1" s="33"/>
+      <c r="B1" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="E1" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="23" t="s">
+      <c r="G1" s="34" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="18" customFormat="1" ht="39" spans="1:7">
-      <c r="A2" s="24" t="s">
+    <row r="2" s="29" customFormat="1" ht="39" spans="1:7">
+      <c r="A2" s="35" t="s">
         <v>159</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25" t="s">
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36" t="s">
         <v>160</v>
       </c>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="37" t="s">
         <v>161</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="31" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="37" t="s">
         <v>163</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="31" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="37" t="s">
         <v>165</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="31" t="s">
         <v>166</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="31" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="37" t="s">
         <v>168</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="31" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="37" t="s">
         <v>171</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="31" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="26"/>
-      <c r="D8" s="20" t="s">
+      <c r="A8" s="37"/>
+      <c r="D8" s="31" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="26"/>
+      <c r="A9" s="37"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="26"/>
+      <c r="A10" s="37"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="26"/>
+      <c r="A11" s="37"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="26"/>
+      <c r="A12" s="37"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="26"/>
+      <c r="A13" s="37"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="26"/>
+      <c r="A14" s="37"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="26"/>
+      <c r="A15" s="37"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="26"/>
+      <c r="A16" s="37"/>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="26"/>
+      <c r="A17" s="37"/>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="26"/>
+      <c r="A18" s="37"/>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="26"/>
+      <c r="A19" s="37"/>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="26"/>
+      <c r="A20" s="37"/>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="26"/>
+      <c r="A21" s="37"/>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="26"/>
+      <c r="A22" s="37"/>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="26"/>
+      <c r="A23" s="37"/>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="26"/>
+      <c r="A24" s="37"/>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="26"/>
+      <c r="A25" s="37"/>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="26"/>
+      <c r="A26" s="37"/>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="26"/>
+      <c r="A27" s="37"/>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="26"/>
+      <c r="A28" s="37"/>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="26"/>
+      <c r="A29" s="37"/>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="26"/>
+      <c r="A30" s="37"/>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="26"/>
+      <c r="A31" s="37"/>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="26"/>
+      <c r="A32" s="37"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="26"/>
+      <c r="A33" s="37"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="26"/>
+      <c r="A34" s="37"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="26"/>
+      <c r="A35" s="37"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="26"/>
+      <c r="A36" s="37"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="26"/>
+      <c r="A37" s="37"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="26"/>
-      <c r="B38" s="25"/>
-      <c r="C38" s="25"/>
-      <c r="D38" s="25"/>
-      <c r="E38" s="25"/>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
+      <c r="A38" s="37"/>
+      <c r="B38" s="36"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="36"/>
+      <c r="F38" s="36"/>
+      <c r="G38" s="36"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="26"/>
-      <c r="B39" s="25"/>
-      <c r="C39" s="25"/>
-      <c r="D39" s="25"/>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
+      <c r="A39" s="37"/>
+      <c r="B39" s="36"/>
+      <c r="C39" s="36"/>
+      <c r="D39" s="36"/>
+      <c r="E39" s="36"/>
+      <c r="F39" s="36"/>
+      <c r="G39" s="36"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="26"/>
+      <c r="A40" s="37"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="26"/>
+      <c r="A41" s="37"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="26"/>
+      <c r="A42" s="37"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="26"/>
+      <c r="A43" s="37"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="26"/>
+      <c r="A44" s="37"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="26"/>
+      <c r="A45" s="37"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="26"/>
+      <c r="A46" s="37"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="26"/>
+      <c r="A47" s="37"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="26"/>
+      <c r="A48" s="37"/>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="26"/>
+      <c r="A49" s="37"/>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="26"/>
+      <c r="A50" s="37"/>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="26"/>
+      <c r="A51" s="37"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2842,132 +2949,143 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="35.1818181818182" style="9" customWidth="1"/>
-    <col min="2" max="2" width="16.9090909090909" style="9" customWidth="1"/>
-    <col min="3" max="3" width="50.0909090909091" style="14" customWidth="1"/>
-    <col min="4" max="16384" width="8.72727272727273" style="9"/>
+    <col min="1" max="1" width="35.1818181818182" style="20" customWidth="1"/>
+    <col min="2" max="2" width="16.9090909090909" style="20" customWidth="1"/>
+    <col min="3" max="3" width="50.0909090909091" style="25" customWidth="1"/>
+    <col min="4" max="16384" width="8.72727272727273" style="20"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="20" t="s">
         <v>174</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="25" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="25" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="25" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="4" ht="28" spans="1:3">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="25" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="5" ht="42" spans="1:3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="26" t="s">
         <v>185</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="25" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="6" ht="56" spans="1:3">
-      <c r="A6" s="16"/>
-      <c r="B6" s="9" t="s">
+      <c r="A6" s="27"/>
+      <c r="B6" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="25" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="7" ht="28" spans="1:3">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="20" t="s">
         <v>190</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="25" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="8" ht="28" spans="1:3">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="25" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="20" t="s">
         <v>197</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="25" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="20" t="s">
         <v>199</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="25" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="28">
         <v>0.440972222222222</v>
+      </c>
+    </row>
+    <row r="12" ht="28" spans="1:3">
+      <c r="A12" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -2985,135 +3103,135 @@
   <dimension ref="A1:D15"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="9.18181818181818" style="3"/>
-    <col min="2" max="2" width="3.54545454545455" style="8" customWidth="1"/>
-    <col min="3" max="16384" width="8.72727272727273" style="9"/>
+    <col min="1" max="1" width="9.18181818181818" style="7"/>
+    <col min="2" max="2" width="3.54545454545455" style="19" customWidth="1"/>
+    <col min="3" max="16384" width="8.72727272727273" style="20"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="C1" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>205</v>
+      <c r="C1" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="11">
+      <c r="A2" s="22">
         <v>2025.1</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="19">
         <v>11</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="21">
         <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="12"/>
-      <c r="B3" s="8">
+      <c r="A3" s="23"/>
+      <c r="B3" s="19">
         <v>15</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="21">
         <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="12"/>
-      <c r="B4" s="8">
+      <c r="A4" s="23"/>
+      <c r="B4" s="19">
         <v>17</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="21">
         <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="12"/>
-      <c r="B5" s="8">
+      <c r="A5" s="23"/>
+      <c r="B5" s="19">
         <v>22</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="21">
         <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="12"/>
-      <c r="B6" s="8">
+      <c r="A6" s="23"/>
+      <c r="B6" s="19">
         <v>24</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="21">
         <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="12"/>
-      <c r="B7" s="8">
+      <c r="A7" s="23"/>
+      <c r="B7" s="19">
         <v>29</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="21">
         <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="13"/>
-      <c r="B8" s="8">
+      <c r="A8" s="24"/>
+      <c r="B8" s="19">
         <v>31</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="21">
         <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="11">
+      <c r="A9" s="22">
         <v>2025.11</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="19">
         <v>5</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="21">
         <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="12"/>
-      <c r="B10" s="8">
+      <c r="A10" s="23"/>
+      <c r="B10" s="19">
         <v>7</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="21">
         <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="13"/>
-      <c r="B11" s="8">
+      <c r="A11" s="24"/>
+      <c r="B11" s="19">
         <v>14</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="21">
         <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="3">
+      <c r="A12" s="7">
         <v>2025.12</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="19">
         <v>26</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="21">
         <v>225</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="20">
         <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="C13" s="10"/>
+      <c r="C13" s="21"/>
     </row>
     <row r="14" spans="1:4">
-      <c r="C14" s="10"/>
+      <c r="C14" s="21"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="C15" s="10"/>
+      <c r="C15" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3128,1082 +3246,2324 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P52"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
+  <dimension ref="A1:W52"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="4.07272727272727" customWidth="1"/>
-    <col min="2" max="16" width="5.14545454545455" customWidth="1"/>
+    <col min="2" max="18" width="5.14545454545455" customWidth="1"/>
+    <col min="19" max="19" width="5.14545454545455" customWidth="1"/>
+    <col min="20" max="20" width="8.72727272727273" style="2"/>
+    <col min="21" max="22" width="8.72727272727273" style="3"/>
+    <col min="23" max="23" width="12.8181818181818" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:16">
-      <c r="A1" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="B1" s="2">
+    <row r="1" s="1" customFormat="1" ht="14" spans="1:23">
+      <c r="A1" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B1" s="4">
         <v>5</v>
       </c>
-      <c r="C1" s="2">
+      <c r="C1" s="4">
         <v>6</v>
       </c>
-      <c r="D1" s="2">
+      <c r="D1" s="4">
         <v>9</v>
       </c>
-      <c r="E1" s="2">
+      <c r="E1" s="4">
         <v>10</v>
       </c>
-      <c r="F1" s="2">
+      <c r="F1" s="4">
         <v>11</v>
       </c>
-      <c r="G1" s="2">
+      <c r="G1" s="4">
         <v>12</v>
       </c>
-      <c r="H1" s="2">
+      <c r="H1" s="4">
         <v>15</v>
       </c>
-      <c r="I1" s="2">
+      <c r="I1" s="4">
         <v>16</v>
       </c>
-      <c r="J1" s="2">
+      <c r="J1" s="4">
         <v>17</v>
       </c>
-      <c r="K1" s="2">
+      <c r="K1" s="4">
         <v>18</v>
       </c>
-      <c r="L1" s="2">
+      <c r="L1" s="4">
         <v>19</v>
       </c>
-      <c r="M1" s="2">
+      <c r="M1" s="4">
         <v>22</v>
       </c>
-      <c r="N1" s="2">
+      <c r="N1" s="4">
         <v>23</v>
       </c>
-      <c r="O1" s="2">
+      <c r="O1" s="4">
         <v>25</v>
       </c>
-      <c r="P1" s="2">
+      <c r="P1" s="4">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" customHeight="1" spans="1:16">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-    </row>
-    <row r="3" customHeight="1" spans="1:16">
-      <c r="A3" s="3">
+      <c r="Q1" s="4">
+        <v>29</v>
+      </c>
+      <c r="R1" s="4"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="U1" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="V1" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="W1" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="2" ht="14" customHeight="1" spans="1:23">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="2">
+        <f>SUM(B2:S2)</f>
+        <v>0</v>
+      </c>
+      <c r="U2" s="3" cm="1">
+        <f t="array" ref="U2">SUMPRODUCT(--(B2:S2=INT(B2:S2)),--(B2:S2&gt;0))</f>
+        <v>0</v>
+      </c>
+      <c r="V2" s="3" cm="1">
+        <f t="array" ref="V2">MAX(FREQUENCY(IF((B2:S2=INT(B2:S2))*(B2:S2&gt;0),COLUMN(B2:S2)),IF((B2:S2&lt;&gt;INT(B2:S2))+(B2:S2&lt;=0),COLUMN(B2:S2))))</f>
+        <v>0</v>
+      </c>
+      <c r="W2" s="10" t="str" cm="1">
+        <f t="array" ref="W2">TEXT(SUMPRODUCT(--(B2:S2=INT(B2:S2)),--(B2:S2&gt;0))/18*100%,0%)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" ht="14" customHeight="1" spans="1:23">
+      <c r="A3" s="7">
         <v>2</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-    </row>
-    <row r="4" customHeight="1" spans="1:16">
-      <c r="A4" s="3">
+      <c r="B3" s="11">
+        <v>1</v>
+      </c>
+      <c r="C3" s="11">
+        <v>1</v>
+      </c>
+      <c r="D3" s="11">
+        <v>1</v>
+      </c>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="11">
+        <v>1</v>
+      </c>
+      <c r="J3" s="11">
+        <v>1</v>
+      </c>
+      <c r="K3" s="11">
+        <v>1</v>
+      </c>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="11">
+        <v>1</v>
+      </c>
+      <c r="R3" s="12"/>
+      <c r="S3" s="13"/>
+      <c r="T3" s="2">
+        <f>SUM(B3:S3)</f>
+        <v>7</v>
+      </c>
+      <c r="U3" s="3" cm="1">
+        <f t="array" ref="U3">SUMPRODUCT(--(B3:S3=INT(B3:S3)),--(B3:S3&gt;0))</f>
+        <v>7</v>
+      </c>
+      <c r="V3" s="3" cm="1">
+        <f t="array" ref="V3">MAX(FREQUENCY(IF((B3:S3=INT(B3:S3))*(B3:S3&gt;0),COLUMN(B3:S3)),IF((B3:S3&lt;&gt;INT(B3:S3))+(B3:S3&lt;=0),COLUMN(B3:S3))))</f>
         <v>3</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-    </row>
-    <row r="5" customHeight="1" spans="1:16">
-      <c r="A5" s="3">
+      <c r="W3" s="14" cm="1">
+        <f t="array" ref="W3">SUMPRODUCT(--(B3:S3=INT(B3:S3)),--(B3:S3&gt;0))/18*100%</f>
+        <v>0.388888888888889</v>
+      </c>
+    </row>
+    <row r="4" ht="14" customHeight="1" spans="1:23">
+      <c r="A4" s="7">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="11">
+        <v>1</v>
+      </c>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="8"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="2">
+        <f t="shared" ref="T4:T35" si="0">SUM(B4:S4)</f>
+        <v>1</v>
+      </c>
+      <c r="U4" s="3" cm="1">
+        <f t="array" ref="U4">SUMPRODUCT(--(B4:S4=INT(B4:S4)),--(B4:S4&gt;0))</f>
+        <v>1</v>
+      </c>
+      <c r="V4" s="3" cm="1">
+        <f t="array" ref="V4">MAX(FREQUENCY(IF((B4:S4=INT(B4:S4))*(B4:S4&gt;0),COLUMN(B4:S4)),IF((B4:S4&lt;&gt;INT(B4:S4))+(B4:S4&lt;=0),COLUMN(B4:S4))))</f>
+        <v>1</v>
+      </c>
+      <c r="W4" s="10" t="str" cm="1">
+        <f t="array" ref="W4">TEXT(SUMPRODUCT(--(B4:S4=INT(B4:S4)),--(B4:S4&gt;0))/18*100%,0%)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" ht="14" customHeight="1" spans="1:23">
+      <c r="A5" s="7">
         <v>4</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-    </row>
-    <row r="6" customHeight="1" spans="1:16">
-      <c r="A6" s="3">
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="11">
+        <v>1</v>
+      </c>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="11">
+        <v>1</v>
+      </c>
+      <c r="R5" s="12"/>
+      <c r="S5" s="13"/>
+      <c r="T5" s="2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U5" s="3" cm="1">
+        <f t="array" ref="U5">SUMPRODUCT(--(B5:S5=INT(B5:S5)),--(B5:S5&gt;0))</f>
+        <v>2</v>
+      </c>
+      <c r="V5" s="3" cm="1">
+        <f t="array" ref="V5">MAX(FREQUENCY(IF((B5:S5=INT(B5:S5))*(B5:S5&gt;0),COLUMN(B5:S5)),IF((B5:S5&lt;&gt;INT(B5:S5))+(B5:S5&lt;=0),COLUMN(B5:S5))))</f>
+        <v>1</v>
+      </c>
+      <c r="W5" s="14" cm="1">
+        <f t="array" ref="W5">SUMPRODUCT(--(B5:S5=INT(B5:S5)),--(B5:S5&gt;0))/18*100%</f>
+        <v>0.111111111111111</v>
+      </c>
+    </row>
+    <row r="6" ht="14" customHeight="1" spans="1:23">
+      <c r="A6" s="7">
         <v>5</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-    </row>
-    <row r="7" customHeight="1" spans="1:16">
-      <c r="A7" s="3">
+      <c r="B6" s="11">
+        <v>1</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="15">
+        <v>2</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="11">
+        <v>1</v>
+      </c>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="8"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="2">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="U6" s="3" cm="1">
+        <f t="array" ref="U6">SUMPRODUCT(--(B6:S6=INT(B6:S6)),--(B6:S6&gt;0))</f>
+        <v>3</v>
+      </c>
+      <c r="V6" s="3" cm="1">
+        <f t="array" ref="V6">MAX(FREQUENCY(IF((B6:S6=INT(B6:S6))*(B6:S6&gt;0),COLUMN(B6:S6)),IF((B6:S6&lt;&gt;INT(B6:S6))+(B6:S6&lt;=0),COLUMN(B6:S6))))</f>
+        <v>1</v>
+      </c>
+      <c r="W6" s="10" t="str" cm="1">
+        <f t="array" ref="W6">TEXT(SUMPRODUCT(--(B6:S6=INT(B6:S6)),--(B6:S6&gt;0))/18*100%,0%)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="14" customHeight="1" spans="1:23">
+      <c r="A7" s="7">
         <v>6</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="4"/>
-    </row>
-    <row r="8" customHeight="1" spans="1:16">
-      <c r="A8" s="3">
+      <c r="B7" s="11">
+        <v>1</v>
+      </c>
+      <c r="C7" s="11">
+        <v>1</v>
+      </c>
+      <c r="D7" s="11">
+        <v>1</v>
+      </c>
+      <c r="E7" s="11">
+        <v>1</v>
+      </c>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="11">
+        <v>1</v>
+      </c>
+      <c r="I7" s="11">
+        <v>1</v>
+      </c>
+      <c r="J7" s="11">
+        <v>1</v>
+      </c>
+      <c r="K7" s="7"/>
+      <c r="L7" s="11">
+        <v>1</v>
+      </c>
+      <c r="M7" s="7"/>
+      <c r="N7" s="11">
+        <v>1</v>
+      </c>
+      <c r="O7" s="7"/>
+      <c r="P7" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="11">
+        <v>1</v>
+      </c>
+      <c r="R7" s="12"/>
+      <c r="S7" s="13"/>
+      <c r="T7" s="2">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="U7" s="3" cm="1">
+        <f t="array" ref="U7">SUMPRODUCT(--(B7:S7=INT(B7:S7)),--(B7:S7&gt;0))</f>
+        <v>11</v>
+      </c>
+      <c r="V7" s="3" cm="1">
+        <f t="array" ref="V7">MAX(FREQUENCY(IF((B7:S7=INT(B7:S7))*(B7:S7&gt;0),COLUMN(B7:S7)),IF((B7:S7&lt;&gt;INT(B7:S7))+(B7:S7&lt;=0),COLUMN(B7:S7))))</f>
+        <v>4</v>
+      </c>
+      <c r="W7" s="14" cm="1">
+        <f t="array" ref="W7">SUMPRODUCT(--(B7:S7=INT(B7:S7)),--(B7:S7&gt;0))/18*100%</f>
+        <v>0.611111111111111</v>
+      </c>
+    </row>
+    <row r="8" ht="14" customHeight="1" spans="1:23">
+      <c r="A8" s="7">
         <v>7</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" customHeight="1" spans="1:16">
-      <c r="A9" s="3">
+      <c r="B8" s="11">
+        <v>1</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="11">
+        <v>1</v>
+      </c>
+      <c r="I8" s="11">
+        <v>1</v>
+      </c>
+      <c r="J8" s="11">
+        <v>1</v>
+      </c>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="11">
+        <v>1</v>
+      </c>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="2">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U8" s="3" cm="1">
+        <f t="array" ref="U8">SUMPRODUCT(--(B8:S8=INT(B8:S8)),--(B8:S8&gt;0))</f>
+        <v>5</v>
+      </c>
+      <c r="V8" s="3" cm="1">
+        <f t="array" ref="V8">MAX(FREQUENCY(IF((B8:S8=INT(B8:S8))*(B8:S8&gt;0),COLUMN(B8:S8)),IF((B8:S8&lt;&gt;INT(B8:S8))+(B8:S8&lt;=0),COLUMN(B8:S8))))</f>
+        <v>3</v>
+      </c>
+      <c r="W8" s="10" t="str" cm="1">
+        <f t="array" ref="W8">TEXT(SUMPRODUCT(--(B8:S8=INT(B8:S8)),--(B8:S8&gt;0))/18*100%,0%)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="14" customHeight="1" spans="1:23">
+      <c r="A9" s="7">
         <v>8</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" customHeight="1" spans="1:16">
-      <c r="A10" s="3">
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="9"/>
+      <c r="T9" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="3" cm="1">
+        <f t="array" ref="U9">SUMPRODUCT(--(B9:S9=INT(B9:S9)),--(B9:S9&gt;0))</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" cm="1">
+        <f t="array" ref="V9">MAX(FREQUENCY(IF((B9:S9=INT(B9:S9))*(B9:S9&gt;0),COLUMN(B9:S9)),IF((B9:S9&lt;&gt;INT(B9:S9))+(B9:S9&lt;=0),COLUMN(B9:S9))))</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="14" cm="1">
+        <f t="array" ref="W9">SUMPRODUCT(--(B9:S9=INT(B9:S9)),--(B9:S9&gt;0))/18*100%</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="14" customHeight="1" spans="1:23">
+      <c r="A10" s="7">
         <v>9</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" customHeight="1" spans="1:16">
-      <c r="A11" s="3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="11">
+        <v>1</v>
+      </c>
+      <c r="M10" s="7"/>
+      <c r="N10" s="11">
+        <v>1</v>
+      </c>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="11">
+        <v>1</v>
+      </c>
+      <c r="R10" s="12"/>
+      <c r="S10" s="13"/>
+      <c r="T10" s="2">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="U10" s="3" cm="1">
+        <f t="array" ref="U10">SUMPRODUCT(--(B10:S10=INT(B10:S10)),--(B10:S10&gt;0))</f>
+        <v>3</v>
+      </c>
+      <c r="V10" s="3" cm="1">
+        <f t="array" ref="V10">MAX(FREQUENCY(IF((B10:S10=INT(B10:S10))*(B10:S10&gt;0),COLUMN(B10:S10)),IF((B10:S10&lt;&gt;INT(B10:S10))+(B10:S10&lt;=0),COLUMN(B10:S10))))</f>
+        <v>1</v>
+      </c>
+      <c r="W10" s="10" t="str" cm="1">
+        <f t="array" ref="W10">TEXT(SUMPRODUCT(--(B10:S10=INT(B10:S10)),--(B10:S10&gt;0))/18*100%,0%)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="14" customHeight="1" spans="1:23">
+      <c r="A11" s="7">
         <v>10</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-    </row>
-    <row r="12" customHeight="1" spans="1:16">
-      <c r="A12" s="3">
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="11">
+        <v>1</v>
+      </c>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="8"/>
+      <c r="S11" s="9"/>
+      <c r="T11" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U11" s="3" cm="1">
+        <f t="array" ref="U11">SUMPRODUCT(--(B11:S11=INT(B11:S11)),--(B11:S11&gt;0))</f>
+        <v>1</v>
+      </c>
+      <c r="V11" s="3" cm="1">
+        <f t="array" ref="V11">MAX(FREQUENCY(IF((B11:S11=INT(B11:S11))*(B11:S11&gt;0),COLUMN(B11:S11)),IF((B11:S11&lt;&gt;INT(B11:S11))+(B11:S11&lt;=0),COLUMN(B11:S11))))</f>
+        <v>1</v>
+      </c>
+      <c r="W11" s="14" cm="1">
+        <f t="array" ref="W11">SUMPRODUCT(--(B11:S11=INT(B11:S11)),--(B11:S11&gt;0))/18*100%</f>
+        <v>0.0555555555555556</v>
+      </c>
+    </row>
+    <row r="12" ht="14" customHeight="1" spans="1:23">
+      <c r="A12" s="7">
         <v>11</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" customHeight="1" spans="1:16">
-      <c r="A13" s="3">
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="11">
+        <v>1</v>
+      </c>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="11">
+        <v>1</v>
+      </c>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="11">
+        <v>1</v>
+      </c>
+      <c r="M12" s="7"/>
+      <c r="N12" s="11">
+        <v>1</v>
+      </c>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="11">
+        <v>1</v>
+      </c>
+      <c r="R12" s="12"/>
+      <c r="S12" s="13"/>
+      <c r="T12" s="2">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U12" s="3" cm="1">
+        <f t="array" ref="U12">SUMPRODUCT(--(B12:S12=INT(B12:S12)),--(B12:S12&gt;0))</f>
+        <v>5</v>
+      </c>
+      <c r="V12" s="3" cm="1">
+        <f t="array" ref="V12">MAX(FREQUENCY(IF((B12:S12=INT(B12:S12))*(B12:S12&gt;0),COLUMN(B12:S12)),IF((B12:S12&lt;&gt;INT(B12:S12))+(B12:S12&lt;=0),COLUMN(B12:S12))))</f>
+        <v>1</v>
+      </c>
+      <c r="W12" s="10" t="str" cm="1">
+        <f t="array" ref="W12">TEXT(SUMPRODUCT(--(B12:S12=INT(B12:S12)),--(B12:S12&gt;0))/18*100%,0%)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="14" customHeight="1" spans="1:23">
+      <c r="A13" s="7">
         <v>12</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" customHeight="1" spans="1:16">
-      <c r="A14" s="3">
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="11">
+        <v>1</v>
+      </c>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="8"/>
+      <c r="S13" s="9"/>
+      <c r="T13" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U13" s="3" cm="1">
+        <f t="array" ref="U13">SUMPRODUCT(--(B13:S13=INT(B13:S13)),--(B13:S13&gt;0))</f>
+        <v>1</v>
+      </c>
+      <c r="V13" s="3" cm="1">
+        <f t="array" ref="V13">MAX(FREQUENCY(IF((B13:S13=INT(B13:S13))*(B13:S13&gt;0),COLUMN(B13:S13)),IF((B13:S13&lt;&gt;INT(B13:S13))+(B13:S13&lt;=0),COLUMN(B13:S13))))</f>
+        <v>1</v>
+      </c>
+      <c r="W13" s="14" cm="1">
+        <f t="array" ref="W13">SUMPRODUCT(--(B13:S13=INT(B13:S13)),--(B13:S13&gt;0))/18*100%</f>
+        <v>0.0555555555555556</v>
+      </c>
+    </row>
+    <row r="14" ht="14" customHeight="1" spans="1:23">
+      <c r="A14" s="7">
         <v>13</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" customHeight="1" spans="1:16">
-      <c r="A15" s="3">
+      <c r="B14" s="7"/>
+      <c r="C14" s="11">
+        <v>1</v>
+      </c>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="11">
+        <v>1</v>
+      </c>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="11">
+        <v>1</v>
+      </c>
+      <c r="M14" s="11">
+        <v>1</v>
+      </c>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="11">
+        <v>1</v>
+      </c>
+      <c r="R14" s="12"/>
+      <c r="S14" s="13"/>
+      <c r="T14" s="2">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U14" s="3" cm="1">
+        <f t="array" ref="U14">SUMPRODUCT(--(B14:S14=INT(B14:S14)),--(B14:S14&gt;0))</f>
+        <v>5</v>
+      </c>
+      <c r="V14" s="3" cm="1">
+        <f t="array" ref="V14">MAX(FREQUENCY(IF((B14:S14=INT(B14:S14))*(B14:S14&gt;0),COLUMN(B14:S14)),IF((B14:S14&lt;&gt;INT(B14:S14))+(B14:S14&lt;=0),COLUMN(B14:S14))))</f>
+        <v>2</v>
+      </c>
+      <c r="W14" s="10" t="str" cm="1">
+        <f t="array" ref="W14">TEXT(SUMPRODUCT(--(B14:S14=INT(B14:S14)),--(B14:S14&gt;0))/18*100%,0%)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="14" customHeight="1" spans="1:23">
+      <c r="A15" s="7">
         <v>14</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" customHeight="1" spans="1:16">
-      <c r="A16" s="3">
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="11">
+        <v>1</v>
+      </c>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="8"/>
+      <c r="S15" s="9"/>
+      <c r="T15" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U15" s="3" cm="1">
+        <f t="array" ref="U15">SUMPRODUCT(--(B15:S15=INT(B15:S15)),--(B15:S15&gt;0))</f>
+        <v>1</v>
+      </c>
+      <c r="V15" s="3" cm="1">
+        <f t="array" ref="V15">MAX(FREQUENCY(IF((B15:S15=INT(B15:S15))*(B15:S15&gt;0),COLUMN(B15:S15)),IF((B15:S15&lt;&gt;INT(B15:S15))+(B15:S15&lt;=0),COLUMN(B15:S15))))</f>
+        <v>1</v>
+      </c>
+      <c r="W15" s="14" cm="1">
+        <f t="array" ref="W15">SUMPRODUCT(--(B15:S15=INT(B15:S15)),--(B15:S15&gt;0))/18*100%</f>
+        <v>0.0555555555555556</v>
+      </c>
+    </row>
+    <row r="16" ht="14" customHeight="1" spans="1:23">
+      <c r="A16" s="7">
         <v>15</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-    </row>
-    <row r="17" customHeight="1" spans="1:16">
-      <c r="A17" s="3">
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="8"/>
+      <c r="S16" s="9"/>
+      <c r="T16" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="3" cm="1">
+        <f t="array" ref="U16">SUMPRODUCT(--(B16:S16=INT(B16:S16)),--(B16:S16&gt;0))</f>
+        <v>0</v>
+      </c>
+      <c r="V16" s="3" cm="1">
+        <f t="array" ref="V16">MAX(FREQUENCY(IF((B16:S16=INT(B16:S16))*(B16:S16&gt;0),COLUMN(B16:S16)),IF((B16:S16&lt;&gt;INT(B16:S16))+(B16:S16&lt;=0),COLUMN(B16:S16))))</f>
+        <v>0</v>
+      </c>
+      <c r="W16" s="10" t="str" cm="1">
+        <f t="array" ref="W16">TEXT(SUMPRODUCT(--(B16:S16=INT(B16:S16)),--(B16:S16&gt;0))/18*100%,0%)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="14" customHeight="1" spans="1:23">
+      <c r="A17" s="7">
         <v>16</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" customHeight="1" spans="1:16">
-      <c r="A18" s="3">
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="8"/>
+      <c r="S17" s="9"/>
+      <c r="T17" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="3" cm="1">
+        <f t="array" ref="U17">SUMPRODUCT(--(B17:S17=INT(B17:S17)),--(B17:S17&gt;0))</f>
+        <v>0</v>
+      </c>
+      <c r="V17" s="3" cm="1">
+        <f t="array" ref="V17">MAX(FREQUENCY(IF((B17:S17=INT(B17:S17))*(B17:S17&gt;0),COLUMN(B17:S17)),IF((B17:S17&lt;&gt;INT(B17:S17))+(B17:S17&lt;=0),COLUMN(B17:S17))))</f>
+        <v>0</v>
+      </c>
+      <c r="W17" s="14" cm="1">
+        <f t="array" ref="W17">SUMPRODUCT(--(B17:S17=INT(B17:S17)),--(B17:S17&gt;0))/18*100%</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="14" customHeight="1" spans="1:23">
+      <c r="A18" s="7">
         <v>17</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="4"/>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" customHeight="1" spans="1:16">
-      <c r="A19" s="3">
+      <c r="B18" s="11">
+        <v>1</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="11">
+        <v>1</v>
+      </c>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="8"/>
+      <c r="S18" s="9"/>
+      <c r="T18" s="2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U18" s="3" cm="1">
+        <f t="array" ref="U18">SUMPRODUCT(--(B18:S18=INT(B18:S18)),--(B18:S18&gt;0))</f>
+        <v>2</v>
+      </c>
+      <c r="V18" s="3" cm="1">
+        <f t="array" ref="V18">MAX(FREQUENCY(IF((B18:S18=INT(B18:S18))*(B18:S18&gt;0),COLUMN(B18:S18)),IF((B18:S18&lt;&gt;INT(B18:S18))+(B18:S18&lt;=0),COLUMN(B18:S18))))</f>
+        <v>1</v>
+      </c>
+      <c r="W18" s="10" t="str" cm="1">
+        <f t="array" ref="W18">TEXT(SUMPRODUCT(--(B18:S18=INT(B18:S18)),--(B18:S18&gt;0))/18*100%,0%)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="14" customHeight="1" spans="1:23">
+      <c r="A19" s="7">
         <v>18</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
-    </row>
-    <row r="20" customHeight="1" spans="1:16">
-      <c r="A20" s="3">
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="11">
+        <v>1</v>
+      </c>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="8"/>
+      <c r="S19" s="9"/>
+      <c r="T19" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U19" s="3" cm="1">
+        <f t="array" ref="U19">SUMPRODUCT(--(B19:S19=INT(B19:S19)),--(B19:S19&gt;0))</f>
+        <v>1</v>
+      </c>
+      <c r="V19" s="3" cm="1">
+        <f t="array" ref="V19">MAX(FREQUENCY(IF((B19:S19=INT(B19:S19))*(B19:S19&gt;0),COLUMN(B19:S19)),IF((B19:S19&lt;&gt;INT(B19:S19))+(B19:S19&lt;=0),COLUMN(B19:S19))))</f>
+        <v>1</v>
+      </c>
+      <c r="W19" s="14" cm="1">
+        <f t="array" ref="W19">SUMPRODUCT(--(B19:S19=INT(B19:S19)),--(B19:S19&gt;0))/18*100%</f>
+        <v>0.0555555555555556</v>
+      </c>
+    </row>
+    <row r="20" ht="14" customHeight="1" spans="1:23">
+      <c r="A20" s="7">
         <v>19</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="4"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" customHeight="1" spans="1:16">
-      <c r="A21" s="3">
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="11">
+        <v>1</v>
+      </c>
+      <c r="K20" s="7"/>
+      <c r="L20" s="11">
+        <v>1</v>
+      </c>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
+      <c r="O20" s="7"/>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="7"/>
+      <c r="R20" s="8"/>
+      <c r="S20" s="9"/>
+      <c r="T20" s="2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U20" s="3" cm="1">
+        <f t="array" ref="U20">SUMPRODUCT(--(B20:S20=INT(B20:S20)),--(B20:S20&gt;0))</f>
+        <v>2</v>
+      </c>
+      <c r="V20" s="3" cm="1">
+        <f t="array" ref="V20">MAX(FREQUENCY(IF((B20:S20=INT(B20:S20))*(B20:S20&gt;0),COLUMN(B20:S20)),IF((B20:S20&lt;&gt;INT(B20:S20))+(B20:S20&lt;=0),COLUMN(B20:S20))))</f>
+        <v>1</v>
+      </c>
+      <c r="W20" s="10" t="str" cm="1">
+        <f t="array" ref="W20">TEXT(SUMPRODUCT(--(B20:S20=INT(B20:S20)),--(B20:S20&gt;0))/18*100%,0%)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="14" customHeight="1" spans="1:23">
+      <c r="A21" s="7">
         <v>20</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" customHeight="1" spans="1:16">
-      <c r="A22" s="3">
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="11">
+        <v>1</v>
+      </c>
+      <c r="J21" s="11">
+        <v>1</v>
+      </c>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
+      <c r="O21" s="7"/>
+      <c r="P21" s="7"/>
+      <c r="Q21" s="11">
+        <v>1</v>
+      </c>
+      <c r="R21" s="12"/>
+      <c r="S21" s="13"/>
+      <c r="T21" s="2">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="U21" s="3" cm="1">
+        <f t="array" ref="U21">SUMPRODUCT(--(B21:S21=INT(B21:S21)),--(B21:S21&gt;0))</f>
+        <v>3</v>
+      </c>
+      <c r="V21" s="3" cm="1">
+        <f t="array" ref="V21">MAX(FREQUENCY(IF((B21:S21=INT(B21:S21))*(B21:S21&gt;0),COLUMN(B21:S21)),IF((B21:S21&lt;&gt;INT(B21:S21))+(B21:S21&lt;=0),COLUMN(B21:S21))))</f>
+        <v>2</v>
+      </c>
+      <c r="W21" s="14" cm="1">
+        <f t="array" ref="W21">SUMPRODUCT(--(B21:S21=INT(B21:S21)),--(B21:S21&gt;0))/18*100%</f>
+        <v>0.166666666666667</v>
+      </c>
+    </row>
+    <row r="22" ht="14" customHeight="1" spans="1:23">
+      <c r="A22" s="7">
         <v>21</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="3"/>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" customHeight="1" spans="1:16">
-      <c r="A23" s="3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
+      <c r="O22" s="7"/>
+      <c r="P22" s="7"/>
+      <c r="Q22" s="7"/>
+      <c r="R22" s="8"/>
+      <c r="S22" s="9"/>
+      <c r="T22" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="3" cm="1">
+        <f t="array" ref="U22">SUMPRODUCT(--(B22:S22=INT(B22:S22)),--(B22:S22&gt;0))</f>
+        <v>0</v>
+      </c>
+      <c r="V22" s="3" cm="1">
+        <f t="array" ref="V22">MAX(FREQUENCY(IF((B22:S22=INT(B22:S22))*(B22:S22&gt;0),COLUMN(B22:S22)),IF((B22:S22&lt;&gt;INT(B22:S22))+(B22:S22&lt;=0),COLUMN(B22:S22))))</f>
+        <v>0</v>
+      </c>
+      <c r="W22" s="10" t="str" cm="1">
+        <f t="array" ref="W22">TEXT(SUMPRODUCT(--(B22:S22=INT(B22:S22)),--(B22:S22&gt;0))/18*100%,0%)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="14" customHeight="1" spans="1:23">
+      <c r="A23" s="7">
         <v>22</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="3"/>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" customHeight="1" spans="1:16">
-      <c r="A24" s="3">
+      <c r="B23" s="7"/>
+      <c r="C23" s="11">
+        <v>1</v>
+      </c>
+      <c r="D23" s="11">
+        <v>1</v>
+      </c>
+      <c r="E23" s="11">
+        <v>1</v>
+      </c>
+      <c r="F23" s="7"/>
+      <c r="G23" s="11">
+        <v>1</v>
+      </c>
+      <c r="H23" s="7"/>
+      <c r="I23" s="11">
+        <v>1</v>
+      </c>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
+      <c r="O23" s="7"/>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="7"/>
+      <c r="R23" s="8"/>
+      <c r="S23" s="9"/>
+      <c r="T23" s="2">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U23" s="3" cm="1">
+        <f t="array" ref="U23">SUMPRODUCT(--(B23:S23=INT(B23:S23)),--(B23:S23&gt;0))</f>
+        <v>5</v>
+      </c>
+      <c r="V23" s="3" cm="1">
+        <f t="array" ref="V23">MAX(FREQUENCY(IF((B23:S23=INT(B23:S23))*(B23:S23&gt;0),COLUMN(B23:S23)),IF((B23:S23&lt;&gt;INT(B23:S23))+(B23:S23&lt;=0),COLUMN(B23:S23))))</f>
+        <v>3</v>
+      </c>
+      <c r="W23" s="14" cm="1">
+        <f t="array" ref="W23">SUMPRODUCT(--(B23:S23=INT(B23:S23)),--(B23:S23&gt;0))/18*100%</f>
+        <v>0.277777777777778</v>
+      </c>
+    </row>
+    <row r="24" ht="14" customHeight="1" spans="1:23">
+      <c r="A24" s="7">
         <v>23</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" customHeight="1" spans="1:16">
-      <c r="A25" s="3">
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
+      <c r="O24" s="7"/>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="7"/>
+      <c r="R24" s="8"/>
+      <c r="S24" s="9"/>
+      <c r="T24" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="3" cm="1">
+        <f t="array" ref="U24">SUMPRODUCT(--(B24:S24=INT(B24:S24)),--(B24:S24&gt;0))</f>
+        <v>0</v>
+      </c>
+      <c r="V24" s="3" cm="1">
+        <f t="array" ref="V24">MAX(FREQUENCY(IF((B24:S24=INT(B24:S24))*(B24:S24&gt;0),COLUMN(B24:S24)),IF((B24:S24&lt;&gt;INT(B24:S24))+(B24:S24&lt;=0),COLUMN(B24:S24))))</f>
+        <v>0</v>
+      </c>
+      <c r="W24" s="10" t="str" cm="1">
+        <f t="array" ref="W24">TEXT(SUMPRODUCT(--(B24:S24=INT(B24:S24)),--(B24:S24&gt;0))/18*100%,0%)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="14" customHeight="1" spans="1:23">
+      <c r="A25" s="7">
         <v>24</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" customHeight="1" spans="1:16">
-      <c r="A26" s="3">
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
+      <c r="O25" s="7"/>
+      <c r="P25" s="7"/>
+      <c r="Q25" s="7"/>
+      <c r="R25" s="8"/>
+      <c r="S25" s="9"/>
+      <c r="T25" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="3" cm="1">
+        <f t="array" ref="U25">SUMPRODUCT(--(B25:S25=INT(B25:S25)),--(B25:S25&gt;0))</f>
+        <v>0</v>
+      </c>
+      <c r="V25" s="3" cm="1">
+        <f t="array" ref="V25">MAX(FREQUENCY(IF((B25:S25=INT(B25:S25))*(B25:S25&gt;0),COLUMN(B25:S25)),IF((B25:S25&lt;&gt;INT(B25:S25))+(B25:S25&lt;=0),COLUMN(B25:S25))))</f>
+        <v>0</v>
+      </c>
+      <c r="W25" s="14" cm="1">
+        <f t="array" ref="W25">SUMPRODUCT(--(B25:S25=INT(B25:S25)),--(B25:S25&gt;0))/18*100%</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="14" customHeight="1" spans="1:23">
+      <c r="A26" s="7">
         <v>25</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" customHeight="1" spans="1:16">
-      <c r="A27" s="3">
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="7"/>
+      <c r="O26" s="7"/>
+      <c r="P26" s="7"/>
+      <c r="Q26" s="7"/>
+      <c r="R26" s="8"/>
+      <c r="S26" s="9"/>
+      <c r="T26" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="3" cm="1">
+        <f t="array" ref="U26">SUMPRODUCT(--(B26:S26=INT(B26:S26)),--(B26:S26&gt;0))</f>
+        <v>0</v>
+      </c>
+      <c r="V26" s="3" cm="1">
+        <f t="array" ref="V26">MAX(FREQUENCY(IF((B26:S26=INT(B26:S26))*(B26:S26&gt;0),COLUMN(B26:S26)),IF((B26:S26&lt;&gt;INT(B26:S26))+(B26:S26&lt;=0),COLUMN(B26:S26))))</f>
+        <v>0</v>
+      </c>
+      <c r="W26" s="10" t="str" cm="1">
+        <f t="array" ref="W26">TEXT(SUMPRODUCT(--(B26:S26=INT(B26:S26)),--(B26:S26&gt;0))/18*100%,0%)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="14" customHeight="1" spans="1:23">
+      <c r="A27" s="7">
         <v>26</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
-      <c r="O27" s="3"/>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" customHeight="1" spans="1:16">
-      <c r="A28" s="3">
+      <c r="B27" s="7"/>
+      <c r="C27" s="11">
+        <v>1</v>
+      </c>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="11">
+        <v>1</v>
+      </c>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="11">
+        <v>1</v>
+      </c>
+      <c r="L27" s="7"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="7"/>
+      <c r="O27" s="7"/>
+      <c r="P27" s="7"/>
+      <c r="Q27" s="11">
+        <v>1</v>
+      </c>
+      <c r="R27" s="12"/>
+      <c r="S27" s="13"/>
+      <c r="T27" s="2">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="U27" s="3" cm="1">
+        <f t="array" ref="U27">SUMPRODUCT(--(B27:S27=INT(B27:S27)),--(B27:S27&gt;0))</f>
+        <v>4</v>
+      </c>
+      <c r="V27" s="3" cm="1">
+        <f t="array" ref="V27">MAX(FREQUENCY(IF((B27:S27=INT(B27:S27))*(B27:S27&gt;0),COLUMN(B27:S27)),IF((B27:S27&lt;&gt;INT(B27:S27))+(B27:S27&lt;=0),COLUMN(B27:S27))))</f>
+        <v>1</v>
+      </c>
+      <c r="W27" s="14" cm="1">
+        <f t="array" ref="W27">SUMPRODUCT(--(B27:S27=INT(B27:S27)),--(B27:S27&gt;0))/18*100%</f>
+        <v>0.222222222222222</v>
+      </c>
+    </row>
+    <row r="28" ht="14" customHeight="1" spans="1:23">
+      <c r="A28" s="7">
         <v>27</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="3"/>
-      <c r="O28" s="3"/>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" customHeight="1" spans="1:16">
-      <c r="A29" s="3">
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="11">
+        <v>1</v>
+      </c>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
+      <c r="L28" s="7"/>
+      <c r="M28" s="11">
+        <v>1</v>
+      </c>
+      <c r="N28" s="7"/>
+      <c r="O28" s="7"/>
+      <c r="P28" s="7"/>
+      <c r="Q28" s="7"/>
+      <c r="R28" s="8"/>
+      <c r="S28" s="9"/>
+      <c r="T28" s="2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U28" s="3" cm="1">
+        <f t="array" ref="U28">SUMPRODUCT(--(B28:S28=INT(B28:S28)),--(B28:S28&gt;0))</f>
+        <v>2</v>
+      </c>
+      <c r="V28" s="3" cm="1">
+        <f t="array" ref="V28">MAX(FREQUENCY(IF((B28:S28=INT(B28:S28))*(B28:S28&gt;0),COLUMN(B28:S28)),IF((B28:S28&lt;&gt;INT(B28:S28))+(B28:S28&lt;=0),COLUMN(B28:S28))))</f>
+        <v>1</v>
+      </c>
+      <c r="W28" s="10" t="str" cm="1">
+        <f t="array" ref="W28">TEXT(SUMPRODUCT(--(B28:S28=INT(B28:S28)),--(B28:S28&gt;0))/18*100%,0%)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="14" customHeight="1" spans="1:23">
+      <c r="A29" s="7">
         <v>28</v>
       </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="3"/>
-      <c r="O29" s="3"/>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" customHeight="1" spans="1:16">
-      <c r="A30" s="3">
+      <c r="B29" s="11">
+        <v>1</v>
+      </c>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="11">
+        <v>1</v>
+      </c>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="7"/>
+      <c r="O29" s="7"/>
+      <c r="P29" s="7"/>
+      <c r="Q29" s="7"/>
+      <c r="R29" s="8"/>
+      <c r="S29" s="9"/>
+      <c r="T29" s="2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U29" s="3" cm="1">
+        <f t="array" ref="U29">SUMPRODUCT(--(B29:S29=INT(B29:S29)),--(B29:S29&gt;0))</f>
+        <v>2</v>
+      </c>
+      <c r="V29" s="3" cm="1">
+        <f t="array" ref="V29">MAX(FREQUENCY(IF((B29:S29=INT(B29:S29))*(B29:S29&gt;0),COLUMN(B29:S29)),IF((B29:S29&lt;&gt;INT(B29:S29))+(B29:S29&lt;=0),COLUMN(B29:S29))))</f>
+        <v>1</v>
+      </c>
+      <c r="W29" s="14" cm="1">
+        <f t="array" ref="W29">SUMPRODUCT(--(B29:S29=INT(B29:S29)),--(B29:S29&gt;0))/18*100%</f>
+        <v>0.111111111111111</v>
+      </c>
+    </row>
+    <row r="30" ht="14" customHeight="1" spans="1:23">
+      <c r="A30" s="7">
         <v>29</v>
       </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
-      <c r="N30" s="3"/>
-      <c r="O30" s="3"/>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" customHeight="1" spans="1:16">
-      <c r="A31" s="3">
+      <c r="B30" s="11">
+        <v>1</v>
+      </c>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="11">
+        <v>1</v>
+      </c>
+      <c r="I30" s="15">
+        <v>2</v>
+      </c>
+      <c r="J30" s="7"/>
+      <c r="K30" s="7"/>
+      <c r="L30" s="7"/>
+      <c r="M30" s="7"/>
+      <c r="N30" s="7"/>
+      <c r="O30" s="7"/>
+      <c r="P30" s="7"/>
+      <c r="Q30" s="11">
+        <v>1</v>
+      </c>
+      <c r="R30" s="12"/>
+      <c r="S30" s="13"/>
+      <c r="T30" s="2">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U30" s="3" cm="1">
+        <f t="array" ref="U30">SUMPRODUCT(--(B30:S30=INT(B30:S30)),--(B30:S30&gt;0))</f>
+        <v>4</v>
+      </c>
+      <c r="V30" s="3" cm="1">
+        <f t="array" ref="V30">MAX(FREQUENCY(IF((B30:S30=INT(B30:S30))*(B30:S30&gt;0),COLUMN(B30:S30)),IF((B30:S30&lt;&gt;INT(B30:S30))+(B30:S30&lt;=0),COLUMN(B30:S30))))</f>
+        <v>2</v>
+      </c>
+      <c r="W30" s="10" t="str" cm="1">
+        <f t="array" ref="W30">TEXT(SUMPRODUCT(--(B30:S30=INT(B30:S30)),--(B30:S30&gt;0))/18*100%,0%)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="14" customHeight="1" spans="1:23">
+      <c r="A31" s="7">
         <v>30</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
-      <c r="N31" s="4"/>
-      <c r="O31" s="3"/>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:16">
-      <c r="A32" s="3">
+      <c r="B31" s="7"/>
+      <c r="C31" s="11">
+        <v>1</v>
+      </c>
+      <c r="D31" s="7"/>
+      <c r="E31" s="11">
+        <v>1</v>
+      </c>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="15">
+        <v>2</v>
+      </c>
+      <c r="J31" s="11">
+        <v>1</v>
+      </c>
+      <c r="K31" s="7"/>
+      <c r="L31" s="7"/>
+      <c r="M31" s="7"/>
+      <c r="N31" s="11">
+        <v>1</v>
+      </c>
+      <c r="O31" s="7"/>
+      <c r="P31" s="7"/>
+      <c r="Q31" s="7"/>
+      <c r="R31" s="8"/>
+      <c r="S31" s="9"/>
+      <c r="T31" s="2">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="U31" s="3" cm="1">
+        <f t="array" ref="U31">SUMPRODUCT(--(B31:S31=INT(B31:S31)),--(B31:S31&gt;0))</f>
+        <v>5</v>
+      </c>
+      <c r="V31" s="3" cm="1">
+        <f t="array" ref="V31">MAX(FREQUENCY(IF((B31:S31=INT(B31:S31))*(B31:S31&gt;0),COLUMN(B31:S31)),IF((B31:S31&lt;&gt;INT(B31:S31))+(B31:S31&lt;=0),COLUMN(B31:S31))))</f>
+        <v>2</v>
+      </c>
+      <c r="W31" s="14" cm="1">
+        <f t="array" ref="W31">SUMPRODUCT(--(B31:S31=INT(B31:S31)),--(B31:S31&gt;0))/18*100%</f>
+        <v>0.277777777777778</v>
+      </c>
+    </row>
+    <row r="32" ht="14" customHeight="1" spans="1:23">
+      <c r="A32" s="7">
         <v>31</v>
       </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
-      <c r="M32" s="3"/>
-      <c r="N32" s="3"/>
-      <c r="O32" s="3"/>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" customHeight="1" spans="1:16">
-      <c r="A33" s="3">
+      <c r="B32" s="11">
+        <v>1</v>
+      </c>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="7"/>
+      <c r="K32" s="7"/>
+      <c r="L32" s="7"/>
+      <c r="M32" s="7"/>
+      <c r="N32" s="7"/>
+      <c r="O32" s="7"/>
+      <c r="P32" s="7"/>
+      <c r="Q32" s="7"/>
+      <c r="R32" s="8"/>
+      <c r="S32" s="9"/>
+      <c r="T32" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U32" s="3" cm="1">
+        <f t="array" ref="U32">SUMPRODUCT(--(B32:S32=INT(B32:S32)),--(B32:S32&gt;0))</f>
+        <v>1</v>
+      </c>
+      <c r="V32" s="3" cm="1">
+        <f t="array" ref="V32">MAX(FREQUENCY(IF((B32:S32=INT(B32:S32))*(B32:S32&gt;0),COLUMN(B32:S32)),IF((B32:S32&lt;&gt;INT(B32:S32))+(B32:S32&lt;=0),COLUMN(B32:S32))))</f>
+        <v>1</v>
+      </c>
+      <c r="W32" s="10" t="str" cm="1">
+        <f t="array" ref="W32">TEXT(SUMPRODUCT(--(B32:S32=INT(B32:S32)),--(B32:S32&gt;0))/18*100%,0%)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="14" customHeight="1" spans="1:23">
+      <c r="A33" s="7">
         <v>32</v>
       </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
-      <c r="K33" s="3"/>
-      <c r="L33" s="3"/>
-      <c r="M33" s="3"/>
-      <c r="N33" s="3"/>
-      <c r="O33" s="3"/>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" customHeight="1" spans="1:16">
-      <c r="A34" s="3">
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
+      <c r="L33" s="7"/>
+      <c r="M33" s="7"/>
+      <c r="N33" s="7"/>
+      <c r="O33" s="7"/>
+      <c r="P33" s="7"/>
+      <c r="Q33" s="7"/>
+      <c r="R33" s="8"/>
+      <c r="S33" s="9"/>
+      <c r="T33" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="3" cm="1">
+        <f t="array" ref="U33">SUMPRODUCT(--(B33:S33=INT(B33:S33)),--(B33:S33&gt;0))</f>
+        <v>0</v>
+      </c>
+      <c r="V33" s="3" cm="1">
+        <f t="array" ref="V33">MAX(FREQUENCY(IF((B33:S33=INT(B33:S33))*(B33:S33&gt;0),COLUMN(B33:S33)),IF((B33:S33&lt;&gt;INT(B33:S33))+(B33:S33&lt;=0),COLUMN(B33:S33))))</f>
+        <v>0</v>
+      </c>
+      <c r="W33" s="14" cm="1">
+        <f t="array" ref="W33">SUMPRODUCT(--(B33:S33=INT(B33:S33)),--(B33:S33&gt;0))/18*100%</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="14" customHeight="1" spans="1:23">
+      <c r="A34" s="7">
         <v>33</v>
       </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3"/>
-      <c r="N34" s="3"/>
-      <c r="O34" s="3"/>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" customHeight="1" spans="1:16">
-      <c r="A35" s="3">
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="7"/>
+      <c r="K34" s="7"/>
+      <c r="L34" s="7"/>
+      <c r="M34" s="7"/>
+      <c r="N34" s="7"/>
+      <c r="O34" s="7"/>
+      <c r="P34" s="7"/>
+      <c r="Q34" s="7"/>
+      <c r="R34" s="8"/>
+      <c r="S34" s="9"/>
+      <c r="T34" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U34" s="3" cm="1">
+        <f t="array" ref="U34">SUMPRODUCT(--(B34:S34=INT(B34:S34)),--(B34:S34&gt;0))</f>
+        <v>0</v>
+      </c>
+      <c r="V34" s="3" cm="1">
+        <f t="array" ref="V34">MAX(FREQUENCY(IF((B34:S34=INT(B34:S34))*(B34:S34&gt;0),COLUMN(B34:S34)),IF((B34:S34&lt;&gt;INT(B34:S34))+(B34:S34&lt;=0),COLUMN(B34:S34))))</f>
+        <v>0</v>
+      </c>
+      <c r="W34" s="10" t="str" cm="1">
+        <f t="array" ref="W34">TEXT(SUMPRODUCT(--(B34:S34=INT(B34:S34)),--(B34:S34&gt;0))/18*100%,0%)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" ht="14" customHeight="1" spans="1:23">
+      <c r="A35" s="7">
         <v>34</v>
       </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3"/>
-      <c r="M35" s="3"/>
-      <c r="N35" s="3"/>
-      <c r="O35" s="3"/>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="36" customHeight="1" spans="1:16">
-      <c r="A36" s="3">
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="7"/>
+      <c r="K35" s="7"/>
+      <c r="L35" s="7"/>
+      <c r="M35" s="7"/>
+      <c r="N35" s="7"/>
+      <c r="O35" s="7"/>
+      <c r="P35" s="7"/>
+      <c r="Q35" s="7"/>
+      <c r="R35" s="8"/>
+      <c r="S35" s="9"/>
+      <c r="T35" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="3" cm="1">
+        <f t="array" ref="U35">SUMPRODUCT(--(B35:S35=INT(B35:S35)),--(B35:S35&gt;0))</f>
+        <v>0</v>
+      </c>
+      <c r="V35" s="3" cm="1">
+        <f t="array" ref="V35">MAX(FREQUENCY(IF((B35:S35=INT(B35:S35))*(B35:S35&gt;0),COLUMN(B35:S35)),IF((B35:S35&lt;&gt;INT(B35:S35))+(B35:S35&lt;=0),COLUMN(B35:S35))))</f>
+        <v>0</v>
+      </c>
+      <c r="W35" s="14" cm="1">
+        <f t="array" ref="W35">SUMPRODUCT(--(B35:S35=INT(B35:S35)),--(B35:S35&gt;0))/18*100%</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="14" customHeight="1" spans="1:23">
+      <c r="A36" s="7">
         <v>35</v>
       </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3"/>
-      <c r="M36" s="3"/>
-      <c r="N36" s="4"/>
-      <c r="O36" s="3"/>
-      <c r="P36" s="3"/>
-    </row>
-    <row r="37" customHeight="1" spans="1:16">
-      <c r="A37" s="3">
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
+      <c r="H36" s="11">
+        <v>1</v>
+      </c>
+      <c r="I36" s="11">
+        <v>1</v>
+      </c>
+      <c r="J36" s="11">
+        <v>1</v>
+      </c>
+      <c r="K36" s="7"/>
+      <c r="L36" s="7"/>
+      <c r="M36" s="7"/>
+      <c r="N36" s="11">
+        <v>1</v>
+      </c>
+      <c r="O36" s="7"/>
+      <c r="P36" s="7"/>
+      <c r="Q36" s="7"/>
+      <c r="R36" s="8"/>
+      <c r="S36" s="9"/>
+      <c r="T36" s="2">
+        <f t="shared" ref="T36:T52" si="1">SUM(B36:S36)</f>
+        <v>4</v>
+      </c>
+      <c r="U36" s="3" cm="1">
+        <f t="array" ref="U36">SUMPRODUCT(--(B36:S36=INT(B36:S36)),--(B36:S36&gt;0))</f>
+        <v>4</v>
+      </c>
+      <c r="V36" s="3" cm="1">
+        <f t="array" ref="V36">MAX(FREQUENCY(IF((B36:S36=INT(B36:S36))*(B36:S36&gt;0),COLUMN(B36:S36)),IF((B36:S36&lt;&gt;INT(B36:S36))+(B36:S36&lt;=0),COLUMN(B36:S36))))</f>
+        <v>3</v>
+      </c>
+      <c r="W36" s="10" t="str" cm="1">
+        <f t="array" ref="W36">TEXT(SUMPRODUCT(--(B36:S36=INT(B36:S36)),--(B36:S36&gt;0))/18*100%,0%)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" ht="14" customHeight="1" spans="1:23">
+      <c r="A37" s="7">
         <v>36</v>
       </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="3"/>
-      <c r="K37" s="3"/>
-      <c r="L37" s="3"/>
-      <c r="M37" s="3"/>
-      <c r="N37" s="3"/>
-      <c r="O37" s="3"/>
-      <c r="P37" s="3"/>
-    </row>
-    <row r="38" customHeight="1" spans="1:16">
-      <c r="A38" s="3">
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="15">
+        <v>2</v>
+      </c>
+      <c r="J37" s="7"/>
+      <c r="K37" s="7"/>
+      <c r="L37" s="7"/>
+      <c r="M37" s="7"/>
+      <c r="N37" s="7"/>
+      <c r="O37" s="7"/>
+      <c r="P37" s="7"/>
+      <c r="Q37" s="7"/>
+      <c r="R37" s="8"/>
+      <c r="S37" s="9"/>
+      <c r="T37" s="2">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="U37" s="3" cm="1">
+        <f t="array" ref="U37">SUMPRODUCT(--(B37:S37=INT(B37:S37)),--(B37:S37&gt;0))</f>
+        <v>1</v>
+      </c>
+      <c r="V37" s="3" cm="1">
+        <f t="array" ref="V37">MAX(FREQUENCY(IF((B37:S37=INT(B37:S37))*(B37:S37&gt;0),COLUMN(B37:S37)),IF((B37:S37&lt;&gt;INT(B37:S37))+(B37:S37&lt;=0),COLUMN(B37:S37))))</f>
+        <v>1</v>
+      </c>
+      <c r="W37" s="14" cm="1">
+        <f t="array" ref="W37">SUMPRODUCT(--(B37:S37=INT(B37:S37)),--(B37:S37&gt;0))/18*100%</f>
+        <v>0.0555555555555556</v>
+      </c>
+    </row>
+    <row r="38" ht="14" customHeight="1" spans="1:23">
+      <c r="A38" s="7">
         <v>37</v>
       </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
-      <c r="J38" s="3"/>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3"/>
-      <c r="M38" s="3"/>
-      <c r="N38" s="3"/>
-      <c r="O38" s="3"/>
-      <c r="P38" s="3"/>
-    </row>
-    <row r="39" customHeight="1" spans="1:16">
-      <c r="A39" s="3">
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="7"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="7"/>
+      <c r="M38" s="7"/>
+      <c r="N38" s="7"/>
+      <c r="O38" s="7"/>
+      <c r="P38" s="7"/>
+      <c r="Q38" s="7"/>
+      <c r="R38" s="8"/>
+      <c r="S38" s="9"/>
+      <c r="T38" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="3" cm="1">
+        <f t="array" ref="U38">SUMPRODUCT(--(B38:S38=INT(B38:S38)),--(B38:S38&gt;0))</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="3" cm="1">
+        <f t="array" ref="V38">MAX(FREQUENCY(IF((B38:S38=INT(B38:S38))*(B38:S38&gt;0),COLUMN(B38:S38)),IF((B38:S38&lt;&gt;INT(B38:S38))+(B38:S38&lt;=0),COLUMN(B38:S38))))</f>
+        <v>0</v>
+      </c>
+      <c r="W38" s="10" t="str" cm="1">
+        <f t="array" ref="W38">TEXT(SUMPRODUCT(--(B38:S38=INT(B38:S38)),--(B38:S38&gt;0))/18*100%,0%)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="14" customHeight="1" spans="1:23">
+      <c r="A39" s="7">
         <v>38</v>
       </c>
-      <c r="B39" s="3"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="5"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="4"/>
-      <c r="M39" s="3"/>
-      <c r="N39" s="3"/>
-      <c r="O39" s="3"/>
-      <c r="P39" s="3"/>
-    </row>
-    <row r="40" customHeight="1" spans="1:16">
-      <c r="A40" s="3">
+      <c r="B39" s="7"/>
+      <c r="C39" s="11">
+        <v>1</v>
+      </c>
+      <c r="D39" s="11">
+        <v>1</v>
+      </c>
+      <c r="E39" s="7"/>
+      <c r="F39" s="11">
+        <v>1</v>
+      </c>
+      <c r="G39" s="7"/>
+      <c r="H39" s="11">
+        <v>1</v>
+      </c>
+      <c r="I39" s="11">
+        <v>1</v>
+      </c>
+      <c r="J39" s="15">
+        <v>2</v>
+      </c>
+      <c r="K39" s="7"/>
+      <c r="L39" s="11">
+        <v>1</v>
+      </c>
+      <c r="M39" s="7"/>
+      <c r="N39" s="7"/>
+      <c r="O39" s="7"/>
+      <c r="P39" s="7"/>
+      <c r="Q39" s="11">
+        <v>1</v>
+      </c>
+      <c r="R39" s="12"/>
+      <c r="S39" s="13"/>
+      <c r="T39" s="2">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="U39" s="3" cm="1">
+        <f t="array" ref="U39">SUMPRODUCT(--(B39:S39=INT(B39:S39)),--(B39:S39&gt;0))</f>
+        <v>8</v>
+      </c>
+      <c r="V39" s="3" cm="1">
+        <f t="array" ref="V39">MAX(FREQUENCY(IF((B39:S39=INT(B39:S39))*(B39:S39&gt;0),COLUMN(B39:S39)),IF((B39:S39&lt;&gt;INT(B39:S39))+(B39:S39&lt;=0),COLUMN(B39:S39))))</f>
+        <v>3</v>
+      </c>
+      <c r="W39" s="14" cm="1">
+        <f t="array" ref="W39">SUMPRODUCT(--(B39:S39=INT(B39:S39)),--(B39:S39&gt;0))/18*100%</f>
+        <v>0.444444444444444</v>
+      </c>
+    </row>
+    <row r="40" ht="14" customHeight="1" spans="1:23">
+      <c r="A40" s="7">
         <v>39</v>
       </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="3"/>
-      <c r="L40" s="3"/>
-      <c r="M40" s="3"/>
-      <c r="N40" s="3"/>
-      <c r="O40" s="3"/>
-      <c r="P40" s="3"/>
-    </row>
-    <row r="41" customHeight="1" spans="1:16">
-      <c r="A41" s="3">
+      <c r="B40" s="11">
+        <v>1</v>
+      </c>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="7"/>
+      <c r="J40" s="11">
+        <v>1</v>
+      </c>
+      <c r="K40" s="7"/>
+      <c r="L40" s="7"/>
+      <c r="M40" s="7"/>
+      <c r="N40" s="7"/>
+      <c r="O40" s="7"/>
+      <c r="P40" s="7"/>
+      <c r="Q40" s="11">
+        <v>1</v>
+      </c>
+      <c r="R40" s="12"/>
+      <c r="S40" s="13"/>
+      <c r="T40" s="2">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="U40" s="3" cm="1">
+        <f t="array" ref="U40">SUMPRODUCT(--(B40:S40=INT(B40:S40)),--(B40:S40&gt;0))</f>
+        <v>3</v>
+      </c>
+      <c r="V40" s="3" cm="1">
+        <f t="array" ref="V40">MAX(FREQUENCY(IF((B40:S40=INT(B40:S40))*(B40:S40&gt;0),COLUMN(B40:S40)),IF((B40:S40&lt;&gt;INT(B40:S40))+(B40:S40&lt;=0),COLUMN(B40:S40))))</f>
+        <v>1</v>
+      </c>
+      <c r="W40" s="10" t="str" cm="1">
+        <f t="array" ref="W40">TEXT(SUMPRODUCT(--(B40:S40=INT(B40:S40)),--(B40:S40&gt;0))/18*100%,0%)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" ht="14" customHeight="1" spans="1:23">
+      <c r="A41" s="7">
         <v>40</v>
       </c>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="3"/>
-      <c r="J41" s="4"/>
-      <c r="K41" s="4"/>
-      <c r="L41" s="4"/>
-      <c r="M41" s="4"/>
-      <c r="N41" s="4"/>
-      <c r="O41" s="3"/>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" customHeight="1" spans="1:16">
-      <c r="A42" s="3">
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="11">
+        <v>1</v>
+      </c>
+      <c r="I41" s="7"/>
+      <c r="J41" s="11">
+        <v>1</v>
+      </c>
+      <c r="K41" s="11">
+        <v>1</v>
+      </c>
+      <c r="L41" s="11">
+        <v>1</v>
+      </c>
+      <c r="M41" s="11">
+        <v>1</v>
+      </c>
+      <c r="N41" s="11">
+        <v>1</v>
+      </c>
+      <c r="O41" s="7"/>
+      <c r="P41" s="7"/>
+      <c r="Q41" s="11">
+        <v>1</v>
+      </c>
+      <c r="R41" s="12"/>
+      <c r="S41" s="13"/>
+      <c r="T41" s="2">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="U41" s="3" cm="1">
+        <f t="array" ref="U41">SUMPRODUCT(--(B41:S41=INT(B41:S41)),--(B41:S41&gt;0))</f>
+        <v>7</v>
+      </c>
+      <c r="V41" s="3" cm="1">
+        <f t="array" ref="V41">MAX(FREQUENCY(IF((B41:S41=INT(B41:S41))*(B41:S41&gt;0),COLUMN(B41:S41)),IF((B41:S41&lt;&gt;INT(B41:S41))+(B41:S41&lt;=0),COLUMN(B41:S41))))</f>
+        <v>5</v>
+      </c>
+      <c r="W41" s="14" cm="1">
+        <f t="array" ref="W41">SUMPRODUCT(--(B41:S41=INT(B41:S41)),--(B41:S41&gt;0))/18*100%</f>
+        <v>0.388888888888889</v>
+      </c>
+    </row>
+    <row r="42" ht="14" customHeight="1" spans="1:23">
+      <c r="A42" s="7">
         <v>41</v>
       </c>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3"/>
-      <c r="M42" s="3"/>
-      <c r="N42" s="3"/>
-      <c r="O42" s="3"/>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" customHeight="1" spans="1:16">
-      <c r="A43" s="3">
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="7"/>
+      <c r="J42" s="7"/>
+      <c r="K42" s="7"/>
+      <c r="L42" s="7"/>
+      <c r="M42" s="7"/>
+      <c r="N42" s="7"/>
+      <c r="O42" s="7"/>
+      <c r="P42" s="7"/>
+      <c r="Q42" s="7"/>
+      <c r="R42" s="8"/>
+      <c r="S42" s="9"/>
+      <c r="T42" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U42" s="3" cm="1">
+        <f t="array" ref="U42">SUMPRODUCT(--(B42:S42=INT(B42:S42)),--(B42:S42&gt;0))</f>
+        <v>0</v>
+      </c>
+      <c r="V42" s="3" cm="1">
+        <f t="array" ref="V42">MAX(FREQUENCY(IF((B42:S42=INT(B42:S42))*(B42:S42&gt;0),COLUMN(B42:S42)),IF((B42:S42&lt;&gt;INT(B42:S42))+(B42:S42&lt;=0),COLUMN(B42:S42))))</f>
+        <v>0</v>
+      </c>
+      <c r="W42" s="10" t="str" cm="1">
+        <f t="array" ref="W42">TEXT(SUMPRODUCT(--(B42:S42=INT(B42:S42)),--(B42:S42&gt;0))/18*100%,0%)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" ht="14" customHeight="1" spans="1:23">
+      <c r="A43" s="7">
         <v>42</v>
       </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
-      <c r="K43" s="3"/>
-      <c r="L43" s="4"/>
-      <c r="M43" s="3"/>
-      <c r="N43" s="3"/>
-      <c r="O43" s="3"/>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" customHeight="1" spans="1:16">
-      <c r="A44" s="3">
+      <c r="B43" s="11">
+        <v>1</v>
+      </c>
+      <c r="C43" s="11">
+        <v>1</v>
+      </c>
+      <c r="D43" s="15">
+        <v>2</v>
+      </c>
+      <c r="E43" s="11">
+        <v>1</v>
+      </c>
+      <c r="F43" s="11">
+        <v>1</v>
+      </c>
+      <c r="G43" s="7"/>
+      <c r="H43" s="11">
+        <v>1</v>
+      </c>
+      <c r="I43" s="11">
+        <v>1</v>
+      </c>
+      <c r="J43" s="11">
+        <v>1</v>
+      </c>
+      <c r="K43" s="7"/>
+      <c r="L43" s="11">
+        <v>1</v>
+      </c>
+      <c r="M43" s="7"/>
+      <c r="N43" s="7"/>
+      <c r="O43" s="7"/>
+      <c r="P43" s="7"/>
+      <c r="Q43" s="7"/>
+      <c r="R43" s="8"/>
+      <c r="S43" s="9"/>
+      <c r="T43" s="2">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="U43" s="3" cm="1">
+        <f t="array" ref="U43">SUMPRODUCT(--(B43:S43=INT(B43:S43)),--(B43:S43&gt;0))</f>
+        <v>9</v>
+      </c>
+      <c r="V43" s="3" cm="1">
+        <f t="array" ref="V43">MAX(FREQUENCY(IF((B43:S43=INT(B43:S43))*(B43:S43&gt;0),COLUMN(B43:S43)),IF((B43:S43&lt;&gt;INT(B43:S43))+(B43:S43&lt;=0),COLUMN(B43:S43))))</f>
+        <v>5</v>
+      </c>
+      <c r="W43" s="14" cm="1">
+        <f t="array" ref="W43">SUMPRODUCT(--(B43:S43=INT(B43:S43)),--(B43:S43&gt;0))/18*100%</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="44" ht="14" customHeight="1" spans="1:23">
+      <c r="A44" s="7">
         <v>43</v>
       </c>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
-      <c r="J44" s="3"/>
-      <c r="K44" s="3"/>
-      <c r="L44" s="3"/>
-      <c r="M44" s="3"/>
-      <c r="N44" s="3"/>
-      <c r="O44" s="3"/>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" customHeight="1" spans="1:16">
-      <c r="A45" s="3">
+      <c r="B44" s="7"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="7"/>
+      <c r="H44" s="7"/>
+      <c r="I44" s="7"/>
+      <c r="J44" s="7"/>
+      <c r="K44" s="7"/>
+      <c r="L44" s="7"/>
+      <c r="M44" s="7"/>
+      <c r="N44" s="7"/>
+      <c r="O44" s="7"/>
+      <c r="P44" s="7"/>
+      <c r="Q44" s="7"/>
+      <c r="R44" s="8"/>
+      <c r="S44" s="9"/>
+      <c r="T44" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U44" s="3" cm="1">
+        <f t="array" ref="U44">SUMPRODUCT(--(B44:S44=INT(B44:S44)),--(B44:S44&gt;0))</f>
+        <v>0</v>
+      </c>
+      <c r="V44" s="3" cm="1">
+        <f t="array" ref="V44">MAX(FREQUENCY(IF((B44:S44=INT(B44:S44))*(B44:S44&gt;0),COLUMN(B44:S44)),IF((B44:S44&lt;&gt;INT(B44:S44))+(B44:S44&lt;=0),COLUMN(B44:S44))))</f>
+        <v>0</v>
+      </c>
+      <c r="W44" s="10" t="str" cm="1">
+        <f t="array" ref="W44">TEXT(SUMPRODUCT(--(B44:S44=INT(B44:S44)),--(B44:S44&gt;0))/18*100%,0%)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" ht="14" customHeight="1" spans="1:23">
+      <c r="A45" s="7">
         <v>44</v>
       </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="7"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="4"/>
-      <c r="J45" s="5"/>
-      <c r="K45" s="5"/>
-      <c r="L45" s="4"/>
-      <c r="M45" s="5"/>
-      <c r="N45" s="5"/>
-      <c r="O45" s="3"/>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" customHeight="1" spans="1:16">
-      <c r="A46" s="3">
+      <c r="B45" s="11">
+        <v>1</v>
+      </c>
+      <c r="C45" s="11">
+        <v>1</v>
+      </c>
+      <c r="D45" s="11">
+        <v>1</v>
+      </c>
+      <c r="E45" s="11">
+        <v>1</v>
+      </c>
+      <c r="F45" s="7"/>
+      <c r="G45" s="17">
+        <v>3</v>
+      </c>
+      <c r="H45" s="11">
+        <v>1</v>
+      </c>
+      <c r="I45" s="11">
+        <v>1</v>
+      </c>
+      <c r="J45" s="15">
+        <v>2</v>
+      </c>
+      <c r="K45" s="15">
+        <v>2</v>
+      </c>
+      <c r="L45" s="11">
+        <v>1</v>
+      </c>
+      <c r="M45" s="15">
+        <v>2</v>
+      </c>
+      <c r="N45" s="15">
+        <v>2</v>
+      </c>
+      <c r="O45" s="7"/>
+      <c r="P45" s="7"/>
+      <c r="Q45" s="7"/>
+      <c r="R45" s="8"/>
+      <c r="S45" s="9"/>
+      <c r="T45" s="2">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="U45" s="3" cm="1">
+        <f t="array" ref="U45">SUMPRODUCT(--(B45:S45=INT(B45:S45)),--(B45:S45&gt;0))</f>
+        <v>12</v>
+      </c>
+      <c r="V45" s="3" cm="1">
+        <f t="array" ref="V45">MAX(FREQUENCY(IF((B45:S45=INT(B45:S45))*(B45:S45&gt;0),COLUMN(B45:S45)),IF((B45:S45&lt;&gt;INT(B45:S45))+(B45:S45&lt;=0),COLUMN(B45:S45))))</f>
+        <v>8</v>
+      </c>
+      <c r="W45" s="14" cm="1">
+        <f t="array" ref="W45">SUMPRODUCT(--(B45:S45=INT(B45:S45)),--(B45:S45&gt;0))/18*100%</f>
+        <v>0.666666666666667</v>
+      </c>
+    </row>
+    <row r="46" ht="14" customHeight="1" spans="1:23">
+      <c r="A46" s="7">
         <v>45</v>
       </c>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
-      <c r="J46" s="3"/>
-      <c r="K46" s="3"/>
-      <c r="L46" s="3"/>
-      <c r="M46" s="3"/>
-      <c r="N46" s="3"/>
-      <c r="O46" s="3"/>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" customHeight="1" spans="1:16">
-      <c r="A47" s="3">
+      <c r="B46" s="7"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="7"/>
+      <c r="H46" s="7"/>
+      <c r="I46" s="7"/>
+      <c r="J46" s="7"/>
+      <c r="K46" s="7"/>
+      <c r="L46" s="7"/>
+      <c r="M46" s="7"/>
+      <c r="N46" s="7"/>
+      <c r="O46" s="7"/>
+      <c r="P46" s="7"/>
+      <c r="Q46" s="7"/>
+      <c r="R46" s="8"/>
+      <c r="S46" s="9"/>
+      <c r="T46" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="3" cm="1">
+        <f t="array" ref="U46">SUMPRODUCT(--(B46:S46=INT(B46:S46)),--(B46:S46&gt;0))</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="3" cm="1">
+        <f t="array" ref="V46">MAX(FREQUENCY(IF((B46:S46=INT(B46:S46))*(B46:S46&gt;0),COLUMN(B46:S46)),IF((B46:S46&lt;&gt;INT(B46:S46))+(B46:S46&lt;=0),COLUMN(B46:S46))))</f>
+        <v>0</v>
+      </c>
+      <c r="W46" s="10" t="str" cm="1">
+        <f t="array" ref="W46">TEXT(SUMPRODUCT(--(B46:S46=INT(B46:S46)),--(B46:S46&gt;0))/18*100%,0%)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" ht="14" customHeight="1" spans="1:23">
+      <c r="A47" s="7">
         <v>46</v>
       </c>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
-      <c r="L47" s="3"/>
-      <c r="M47" s="3"/>
-      <c r="N47" s="4"/>
-      <c r="O47" s="3"/>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" customHeight="1" spans="1:16">
-      <c r="A48" s="3">
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="11">
+        <v>1</v>
+      </c>
+      <c r="H47" s="7"/>
+      <c r="I47" s="7"/>
+      <c r="J47" s="7"/>
+      <c r="K47" s="7"/>
+      <c r="L47" s="7"/>
+      <c r="M47" s="7"/>
+      <c r="N47" s="11">
+        <v>1</v>
+      </c>
+      <c r="O47" s="7"/>
+      <c r="P47" s="7"/>
+      <c r="Q47" s="11">
+        <v>1</v>
+      </c>
+      <c r="R47" s="12"/>
+      <c r="S47" s="13"/>
+      <c r="T47" s="2">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="U47" s="3" cm="1">
+        <f t="array" ref="U47">SUMPRODUCT(--(B47:S47=INT(B47:S47)),--(B47:S47&gt;0))</f>
+        <v>3</v>
+      </c>
+      <c r="V47" s="3" cm="1">
+        <f t="array" ref="V47">MAX(FREQUENCY(IF((B47:S47=INT(B47:S47))*(B47:S47&gt;0),COLUMN(B47:S47)),IF((B47:S47&lt;&gt;INT(B47:S47))+(B47:S47&lt;=0),COLUMN(B47:S47))))</f>
+        <v>1</v>
+      </c>
+      <c r="W47" s="14" cm="1">
+        <f t="array" ref="W47">SUMPRODUCT(--(B47:S47=INT(B47:S47)),--(B47:S47&gt;0))/18*100%</f>
+        <v>0.166666666666667</v>
+      </c>
+    </row>
+    <row r="48" ht="14" customHeight="1" spans="1:23">
+      <c r="A48" s="7">
         <v>47</v>
       </c>
-      <c r="B48" s="3"/>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="3"/>
-      <c r="J48" s="3"/>
-      <c r="K48" s="3"/>
-      <c r="L48" s="3"/>
-      <c r="M48" s="4"/>
-      <c r="N48" s="3"/>
-      <c r="O48" s="3"/>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" customHeight="1" spans="1:16">
-      <c r="A49" s="3">
+      <c r="B48" s="7"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="11">
+        <v>1</v>
+      </c>
+      <c r="I48" s="7"/>
+      <c r="J48" s="7"/>
+      <c r="K48" s="7"/>
+      <c r="L48" s="7"/>
+      <c r="M48" s="11">
+        <v>1</v>
+      </c>
+      <c r="N48" s="7"/>
+      <c r="O48" s="7"/>
+      <c r="P48" s="7"/>
+      <c r="Q48" s="7"/>
+      <c r="R48" s="8"/>
+      <c r="S48" s="9"/>
+      <c r="T48" s="2">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="U48" s="3" cm="1">
+        <f t="array" ref="U48">SUMPRODUCT(--(B48:S48=INT(B48:S48)),--(B48:S48&gt;0))</f>
+        <v>2</v>
+      </c>
+      <c r="V48" s="3" cm="1">
+        <f t="array" ref="V48">MAX(FREQUENCY(IF((B48:S48=INT(B48:S48))*(B48:S48&gt;0),COLUMN(B48:S48)),IF((B48:S48&lt;&gt;INT(B48:S48))+(B48:S48&lt;=0),COLUMN(B48:S48))))</f>
+        <v>1</v>
+      </c>
+      <c r="W48" s="10" t="str" cm="1">
+        <f t="array" ref="W48">TEXT(SUMPRODUCT(--(B48:S48=INT(B48:S48)),--(B48:S48&gt;0))/18*100%,0%)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" ht="14" customHeight="1" spans="1:23">
+      <c r="A49" s="7">
         <v>48</v>
       </c>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
-      <c r="J49" s="3"/>
-      <c r="K49" s="3"/>
-      <c r="L49" s="3"/>
-      <c r="M49" s="3"/>
-      <c r="N49" s="3"/>
-      <c r="O49" s="3"/>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" customHeight="1" spans="1:16">
-      <c r="A50" s="3">
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="11">
+        <v>1</v>
+      </c>
+      <c r="F49" s="7"/>
+      <c r="G49" s="7"/>
+      <c r="H49" s="7"/>
+      <c r="I49" s="7"/>
+      <c r="J49" s="7"/>
+      <c r="K49" s="7"/>
+      <c r="L49" s="7"/>
+      <c r="M49" s="7"/>
+      <c r="N49" s="7"/>
+      <c r="O49" s="7"/>
+      <c r="P49" s="7"/>
+      <c r="Q49" s="7"/>
+      <c r="R49" s="7"/>
+      <c r="S49" s="18"/>
+      <c r="T49" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="U49" s="3" cm="1">
+        <f t="array" ref="U49">SUMPRODUCT(--(B49:S49=INT(B49:S49)),--(B49:S49&gt;0))</f>
+        <v>1</v>
+      </c>
+      <c r="V49" s="3" cm="1">
+        <f t="array" ref="V49">MAX(FREQUENCY(IF((B49:S49=INT(B49:S49))*(B49:S49&gt;0),COLUMN(B49:S49)),IF((B49:S49&lt;&gt;INT(B49:S49))+(B49:S49&lt;=0),COLUMN(B49:S49))))</f>
+        <v>1</v>
+      </c>
+      <c r="W49" s="14" cm="1">
+        <f t="array" ref="W49">SUMPRODUCT(--(B49:S49=INT(B49:S49)),--(B49:S49&gt;0))/18*100%</f>
+        <v>0.0555555555555556</v>
+      </c>
+    </row>
+    <row r="50" ht="14" customHeight="1" spans="1:23">
+      <c r="A50" s="7">
         <v>49</v>
       </c>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
-      <c r="J50" s="3"/>
-      <c r="K50" s="3"/>
-      <c r="L50" s="3"/>
-      <c r="M50" s="3"/>
-      <c r="N50" s="3"/>
-      <c r="O50" s="3"/>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" customHeight="1" spans="1:16">
-      <c r="A51" s="3">
+      <c r="B50" s="7"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="7"/>
+      <c r="G50" s="7"/>
+      <c r="H50" s="7"/>
+      <c r="I50" s="7"/>
+      <c r="J50" s="7"/>
+      <c r="K50" s="7"/>
+      <c r="L50" s="7"/>
+      <c r="M50" s="7"/>
+      <c r="N50" s="7"/>
+      <c r="O50" s="7"/>
+      <c r="P50" s="7"/>
+      <c r="Q50" s="7"/>
+      <c r="R50" s="7"/>
+      <c r="S50" s="18"/>
+      <c r="T50" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="3" cm="1">
+        <f t="array" ref="U50">SUMPRODUCT(--(B50:S50=INT(B50:S50)),--(B50:S50&gt;0))</f>
+        <v>0</v>
+      </c>
+      <c r="V50" s="3" cm="1">
+        <f t="array" ref="V50">MAX(FREQUENCY(IF((B50:S50=INT(B50:S50))*(B50:S50&gt;0),COLUMN(B50:S50)),IF((B50:S50&lt;&gt;INT(B50:S50))+(B50:S50&lt;=0),COLUMN(B50:S50))))</f>
+        <v>0</v>
+      </c>
+      <c r="W50" s="10" t="str" cm="1">
+        <f t="array" ref="W50">TEXT(SUMPRODUCT(--(B50:S50=INT(B50:S50)),--(B50:S50&gt;0))/18*100%,0%)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" ht="14" customHeight="1" spans="1:23">
+      <c r="A51" s="7">
         <v>50</v>
       </c>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
-      <c r="J51" s="3"/>
-      <c r="K51" s="3"/>
-      <c r="L51" s="3"/>
-      <c r="M51" s="3"/>
-      <c r="N51" s="3"/>
-      <c r="O51" s="3"/>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" customHeight="1" spans="1:16">
-      <c r="A52" s="3">
+      <c r="B51" s="7"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="7"/>
+      <c r="H51" s="7"/>
+      <c r="I51" s="7"/>
+      <c r="J51" s="7"/>
+      <c r="K51" s="7"/>
+      <c r="L51" s="7"/>
+      <c r="M51" s="7"/>
+      <c r="N51" s="7"/>
+      <c r="O51" s="7"/>
+      <c r="P51" s="7"/>
+      <c r="Q51" s="7"/>
+      <c r="R51" s="7"/>
+      <c r="S51" s="18"/>
+      <c r="T51" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="3" cm="1">
+        <f t="array" ref="U51">SUMPRODUCT(--(B51:S51=INT(B51:S51)),--(B51:S51&gt;0))</f>
+        <v>0</v>
+      </c>
+      <c r="V51" s="3" cm="1">
+        <f t="array" ref="V51">MAX(FREQUENCY(IF((B51:S51=INT(B51:S51))*(B51:S51&gt;0),COLUMN(B51:S51)),IF((B51:S51&lt;&gt;INT(B51:S51))+(B51:S51&lt;=0),COLUMN(B51:S51))))</f>
+        <v>0</v>
+      </c>
+      <c r="W51" s="14" cm="1">
+        <f t="array" ref="W51">SUMPRODUCT(--(B51:S51=INT(B51:S51)),--(B51:S51&gt;0))/18*100%</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" ht="14" customHeight="1" spans="1:23">
+      <c r="A52" s="7">
         <v>51</v>
       </c>
-      <c r="B52" s="3"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3"/>
-      <c r="H52" s="3"/>
-      <c r="I52" s="3"/>
-      <c r="J52" s="3"/>
-      <c r="K52" s="3"/>
-      <c r="L52" s="3"/>
-      <c r="M52" s="3"/>
-      <c r="N52" s="3"/>
-      <c r="O52" s="3"/>
-      <c r="P52" s="3"/>
+      <c r="B52" s="7"/>
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="7"/>
+      <c r="G52" s="7"/>
+      <c r="H52" s="7"/>
+      <c r="I52" s="7"/>
+      <c r="J52" s="7"/>
+      <c r="K52" s="7"/>
+      <c r="L52" s="7"/>
+      <c r="M52" s="7"/>
+      <c r="N52" s="7"/>
+      <c r="O52" s="7"/>
+      <c r="P52" s="7"/>
+      <c r="Q52" s="7"/>
+      <c r="R52" s="7"/>
+      <c r="S52" s="18"/>
+      <c r="T52" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="3" cm="1">
+        <f t="array" ref="U52">SUMPRODUCT(--(B52:S52=INT(B52:S52)),--(B52:S52&gt;0))</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="3" cm="1">
+        <f t="array" ref="V52">MAX(FREQUENCY(IF((B52:S52=INT(B52:S52))*(B52:S52&gt;0),COLUMN(B52:S52)),IF((B52:S52&lt;&gt;INT(B52:S52))+(B52:S52&lt;=0),COLUMN(B52:S52))))</f>
+        <v>0</v>
+      </c>
+      <c r="W52" s="10" t="str" cm="1">
+        <f t="array" ref="W52">TEXT(SUMPRODUCT(--(B52:S52=INT(B52:S52)),--(B52:S52&gt;0))/18*100%,0%)</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="222">
   <si>
     <t>姓名</t>
   </si>
@@ -103,6 +103,9 @@
     <t>骂人、没错</t>
   </si>
   <si>
+    <t>贝多芬</t>
+  </si>
+  <si>
     <t>江雨晴</t>
   </si>
   <si>
@@ -310,13 +313,16 @@
     <t>讨饭</t>
   </si>
   <si>
+    <t>不靠谱、晴蔡</t>
+  </si>
+  <si>
     <t>洪鑫洋</t>
   </si>
   <si>
     <t>早读（劝学/磨刀霍霍向鑫洋）、生物30分、记笔记</t>
   </si>
   <si>
-    <t>孺子、反思（我也老了、相见时难别亦难，东风无力百花残、未来是你们，但现在未必、革命尚未成功）（一旬老人）、哲学（旁观者：学地理要以旁观者视角、水循环：逆水行舟，退到极点就是进）、装（问第几题有问题，体现自己做得快、费马点）、考进班级前10、种地（初二第三次月考、打赌八上期末物理自己和郑永泽考的低者种地）、因错题争论、嫂子（47）、三江口</t>
+    <t>孺子、反思（我也老了、相见时难别亦难，东风无力百花残、未来是你们，但现在未必、革命尚未成功）（一旬老人）、哲学（旁观者：学地理要以旁观者视角、水循环：逆水行舟，退到极点就是进）、装（问第几题有问题，体现自己做得快、费马点）、考进班级前10、种地（初二第三次月考、打赌八上期末物理自己和郑永泽考的低者种地）、因错题争论、嫂子（47）、三江口（小宝）、问问题（秦岭山顶的人）</t>
   </si>
   <si>
     <t>游武毅</t>
@@ -673,6 +679,18 @@
     <t>和46号上台写英语句，多次探头看，刘老师让唐家祺改正后同步改正</t>
   </si>
   <si>
+    <t>八上12.30</t>
+  </si>
+  <si>
+    <t>迟到，多人提醒不站</t>
+  </si>
+  <si>
+    <t>手机管理</t>
+  </si>
+  <si>
+    <t>崔母将崔玩手机事情告诉刘老师，手机被收，次日谈话</t>
+  </si>
+  <si>
     <t>政治啧</t>
   </si>
   <si>
@@ -691,7 +709,16 @@
     <t>最高连击</t>
   </si>
   <si>
-    <t>单节被请概率</t>
+    <t>被请概率</t>
+  </si>
+  <si>
+    <t>次数排名</t>
+  </si>
+  <si>
+    <t>节数排名</t>
+  </si>
+  <si>
+    <t>连击排名</t>
   </si>
 </sst>
 </file>
@@ -905,7 +932,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.8"/>
+        <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -948,18 +987,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1392,7 +1419,7 @@
     <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1404,7 +1431,7 @@
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1416,7 +1443,7 @@
     <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1483,6 +1510,9 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1491,10 +1521,14 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1507,27 +1541,15 @@
     <xf numFmtId="176" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1561,55 +1583,61 @@
     <xf numFmtId="20" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2009,263 +2037,266 @@
       <c r="C5" s="40" t="s">
         <v>15</v>
       </c>
+      <c r="D5" s="40" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="43" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="40" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" ht="208" spans="1:7">
       <c r="A7" s="43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="40" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7" s="40" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="43" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="43" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="43" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="43" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="43" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" ht="39" spans="1:7">
       <c r="A13" s="43" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D13" s="40" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="43" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="43" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="43" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C16" s="40" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" ht="26" spans="1:4">
       <c r="A17" s="43" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C17" s="40" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="43" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D18" s="40" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="43" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D19" s="40" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" ht="26" spans="1:4">
       <c r="A20" s="43" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B20" s="40" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C20" s="40" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" ht="39" spans="1:4">
       <c r="A21" s="43" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B21" s="40" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C21" s="40" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D21" s="40" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="43" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" ht="26" spans="1:4">
       <c r="A23" s="43" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B23" s="40" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" ht="52" spans="1:4">
       <c r="A24" s="43" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B24" s="40" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C24" s="40" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D24" s="40" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="43" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="43" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="43" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B27" s="40" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C27" s="40" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" ht="91" spans="1:4">
       <c r="A28" s="43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B28" s="40" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C28" s="40" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D28" s="40" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="43" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="43" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B30" s="40" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C30" s="40" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="43" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="43" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="43" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="43" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="43" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="43" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B36" s="40" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37" ht="26" spans="1:7">
       <c r="A37" s="43" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C37" s="40" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D37" s="40" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="43" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B38" s="40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C38" s="44"/>
       <c r="D38" s="44"/>
@@ -2275,119 +2306,122 @@
     </row>
     <row r="39" ht="26" spans="1:7">
       <c r="A39" s="43" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C39" s="40" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D39" s="40" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="43" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B40" s="40" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C40" s="40" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="41" ht="169" spans="1:7">
+        <v>85</v>
+      </c>
+      <c r="D40" s="40" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="41" ht="195" spans="1:7">
       <c r="A41" s="43" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C41" s="40" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D41" s="40" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="43" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="43" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B43" s="40" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="44" ht="26" spans="1:7">
       <c r="A44" s="43" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B44" s="40" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="43" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D45" s="40" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="43" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="43" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="43" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C48" s="40" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="43" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="50" ht="78" spans="1:7">
       <c r="A50" s="43" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C50" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="43" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="52" ht="26" spans="1:7">
       <c r="A52" s="43" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B52" s="40" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C52" s="40" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="53" ht="26" spans="1:7">
       <c r="A53" s="39" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B53" s="40" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D53" s="44"/>
       <c r="E53" s="44"/>
@@ -2396,13 +2430,13 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="39" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B54" s="40" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C54" s="40" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D54" s="44"/>
       <c r="E54" s="44"/>
@@ -2411,46 +2445,46 @@
     </row>
     <row r="55" ht="52" spans="1:7">
       <c r="A55" s="39" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B55" s="44"/>
       <c r="C55" s="44"/>
       <c r="D55" s="40" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="56" ht="65" spans="1:7">
       <c r="A56" s="39" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B56" s="36" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C56" s="36"/>
       <c r="D56" s="40" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="57" ht="117" spans="1:7">
       <c r="A57" s="39" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C57" s="36" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D57" s="40" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="39" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B58" s="40" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C58" s="44"/>
       <c r="D58" s="44"/>
@@ -2460,11 +2494,11 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="39" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B59" s="44"/>
       <c r="C59" s="40" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D59" s="44"/>
       <c r="E59" s="44"/>
@@ -2473,20 +2507,20 @@
     </row>
     <row r="60" ht="52" spans="1:7">
       <c r="A60" s="39" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B60" s="44"/>
       <c r="C60" s="44"/>
       <c r="D60" s="40" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="39" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B61" s="36" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C61" s="36"/>
       <c r="D61" s="44"/>
@@ -2496,23 +2530,23 @@
     </row>
     <row r="62" ht="39" spans="1:7">
       <c r="A62" s="39" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B62" s="44"/>
       <c r="C62" s="44"/>
       <c r="D62" s="40" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="63" ht="26" spans="1:7">
       <c r="A63" s="39" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B63" s="36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C63" s="36" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D63" s="44"/>
       <c r="E63" s="44"/>
@@ -2521,20 +2555,20 @@
     </row>
     <row r="64" ht="26" spans="1:7">
       <c r="A64" s="39" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B64" s="44"/>
       <c r="C64" s="44"/>
       <c r="D64" s="40" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="65" ht="26" spans="1:7">
       <c r="A65" s="39" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B65" s="45" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C65" s="44"/>
       <c r="D65" s="44"/>
@@ -2544,11 +2578,11 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="39" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B66" s="44"/>
       <c r="C66" s="40" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D66" s="44"/>
       <c r="E66" s="44"/>
@@ -2557,36 +2591,36 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="39" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B67" s="44"/>
       <c r="C67" s="44"/>
     </row>
     <row r="68" ht="26" spans="1:7">
       <c r="A68" s="39" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B68" s="44"/>
       <c r="C68" s="44"/>
       <c r="D68" s="40" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="39" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B69" s="36" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C69" s="36"/>
     </row>
     <row r="70" ht="26" spans="1:7">
       <c r="A70" s="39" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B70" s="36" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C70" s="36"/>
       <c r="D70" s="44"/>
@@ -2596,20 +2630,20 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="39" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B71" s="44"/>
       <c r="C71" s="44"/>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="39" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B72" s="40" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C72" s="40" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D72" s="44"/>
       <c r="E72" s="44"/>
@@ -2618,11 +2652,11 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="39" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B73" s="44"/>
       <c r="C73" s="40" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D73" s="44"/>
       <c r="E73" s="44"/>
@@ -2631,12 +2665,12 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="39" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="39" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D75" s="44"/>
       <c r="E75" s="44"/>
@@ -2645,27 +2679,27 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="39" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B76" s="44"/>
       <c r="C76" s="44"/>
       <c r="D76" s="40" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="39" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B77" s="36"/>
       <c r="C77" s="36"/>
     </row>
     <row r="78" ht="26" spans="1:7">
       <c r="A78" s="46" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B78" s="40" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -2736,12 +2770,12 @@
     </row>
     <row r="2" s="29" customFormat="1" ht="39" spans="1:7">
       <c r="A2" s="35" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
       <c r="D2" s="36" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E2" s="36"/>
       <c r="F2" s="36"/>
@@ -2749,54 +2783,54 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="37" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="37" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="37" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="37" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="37" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="37"/>
       <c r="D8" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2949,148 +2983,169 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="35.1818181818182" style="20" customWidth="1"/>
-    <col min="2" max="2" width="16.9090909090909" style="20" customWidth="1"/>
-    <col min="3" max="3" width="50.0909090909091" style="25" customWidth="1"/>
-    <col min="4" max="16384" width="8.72727272727273" style="20"/>
+    <col min="1" max="1" width="35.1818181818182" style="18" customWidth="1"/>
+    <col min="2" max="2" width="16.9090909090909" style="18" customWidth="1"/>
+    <col min="3" max="3" width="50.0909090909091" style="23" customWidth="1"/>
+    <col min="4" max="16384" width="8.72727272727273" style="18"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="20" t="s">
-        <v>174</v>
-      </c>
-      <c r="B1" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="C1" s="25" t="s">
+      <c r="A1" s="18" t="s">
         <v>176</v>
       </c>
+      <c r="B1" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="20" t="s">
-        <v>177</v>
-      </c>
-      <c r="B2" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="C2" s="25" t="s">
+      <c r="A2" s="18" t="s">
         <v>179</v>
       </c>
+      <c r="B2" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="20" t="s">
-        <v>180</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>181</v>
-      </c>
-      <c r="C3" s="25" t="s">
+      <c r="A3" s="18" t="s">
         <v>182</v>
       </c>
+      <c r="B3" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="4" ht="28" spans="1:3">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="B4" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="B4" s="20" t="s">
-        <v>181</v>
-      </c>
-      <c r="C4" s="25" t="s">
-        <v>184</v>
+      <c r="C4" s="23" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="5" ht="42" spans="1:3">
-      <c r="A5" s="26" t="s">
-        <v>185</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="C5" s="25" t="s">
+      <c r="A5" s="24" t="s">
         <v>187</v>
       </c>
+      <c r="B5" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="6" ht="56" spans="1:3">
-      <c r="A6" s="27"/>
-      <c r="B6" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="C6" s="25" t="s">
-        <v>189</v>
+      <c r="A6" s="25"/>
+      <c r="B6" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="7" ht="28" spans="1:3">
-      <c r="A7" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="C7" s="25" t="s">
+      <c r="A7" s="18" t="s">
         <v>192</v>
       </c>
+      <c r="B7" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="8" ht="28" spans="1:3">
-      <c r="A8" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="C8" s="25" t="s">
+      <c r="A8" s="18" t="s">
         <v>195</v>
       </c>
+      <c r="B8" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="20" t="s">
-        <v>196</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="C9" s="25" t="s">
+      <c r="A9" s="18" t="s">
         <v>198</v>
       </c>
+      <c r="B9" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>200</v>
-      </c>
-      <c r="C10" s="25" t="s">
+      <c r="A10" s="18" t="s">
         <v>201</v>
       </c>
+      <c r="B10" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="20" t="s">
-        <v>202</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>203</v>
-      </c>
-      <c r="C11" s="28">
+      <c r="A11" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="C11" s="26">
         <v>0.440972222222222</v>
       </c>
     </row>
     <row r="12" ht="28" spans="1:3">
-      <c r="A12" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>204</v>
-      </c>
-      <c r="C12" s="25" t="s">
-        <v>205</v>
+      <c r="A12" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="28"/>
+      <c r="B13" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>211</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A12:A13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -3103,135 +3158,135 @@
   <dimension ref="A1:D15"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="9.18181818181818" style="7"/>
-    <col min="2" max="2" width="3.54545454545455" style="19" customWidth="1"/>
-    <col min="3" max="16384" width="8.72727272727273" style="20"/>
+    <col min="1" max="1" width="9.18181818181818" style="9"/>
+    <col min="2" max="2" width="3.54545454545455" style="17" customWidth="1"/>
+    <col min="3" max="16384" width="8.72727272727273" style="18"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="C1" s="21" t="s">
-        <v>206</v>
-      </c>
-      <c r="D1" s="20" t="s">
-        <v>207</v>
+      <c r="C1" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="22">
+      <c r="A2" s="20">
         <v>2025.1</v>
       </c>
-      <c r="B2" s="19">
+      <c r="B2" s="17">
         <v>11</v>
       </c>
-      <c r="C2" s="21">
+      <c r="C2" s="19">
         <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="23"/>
-      <c r="B3" s="19">
+      <c r="A3" s="21"/>
+      <c r="B3" s="17">
         <v>15</v>
       </c>
-      <c r="C3" s="21">
+      <c r="C3" s="19">
         <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="23"/>
-      <c r="B4" s="19">
+      <c r="A4" s="21"/>
+      <c r="B4" s="17">
         <v>17</v>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="19">
         <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="23"/>
-      <c r="B5" s="19">
+      <c r="A5" s="21"/>
+      <c r="B5" s="17">
         <v>22</v>
       </c>
-      <c r="C5" s="21">
+      <c r="C5" s="19">
         <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="23"/>
-      <c r="B6" s="19">
+      <c r="A6" s="21"/>
+      <c r="B6" s="17">
         <v>24</v>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="19">
         <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="23"/>
-      <c r="B7" s="19">
+      <c r="A7" s="21"/>
+      <c r="B7" s="17">
         <v>29</v>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="19">
         <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="24"/>
-      <c r="B8" s="19">
+      <c r="A8" s="22"/>
+      <c r="B8" s="17">
         <v>31</v>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="19">
         <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="22">
+      <c r="A9" s="20">
         <v>2025.11</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="17">
         <v>5</v>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="19">
         <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="23"/>
-      <c r="B10" s="19">
+      <c r="A10" s="21"/>
+      <c r="B10" s="17">
         <v>7</v>
       </c>
-      <c r="C10" s="21">
+      <c r="C10" s="19">
         <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="24"/>
-      <c r="B11" s="19">
+      <c r="A11" s="22"/>
+      <c r="B11" s="17">
         <v>14</v>
       </c>
-      <c r="C11" s="21">
+      <c r="C11" s="19">
         <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="7">
+      <c r="A12" s="9">
         <v>2025.12</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="17">
         <v>26</v>
       </c>
-      <c r="C12" s="21">
+      <c r="C12" s="19">
         <v>225</v>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="18">
         <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="C13" s="21"/>
+      <c r="C13" s="19"/>
     </row>
     <row r="14" spans="1:4">
-      <c r="C14" s="21"/>
+      <c r="C14" s="19"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="C15" s="21"/>
+      <c r="C15" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3246,106 +3301,119 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W52"/>
+  <dimension ref="A1:Z52"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="4.07272727272727" customWidth="1"/>
-    <col min="2" max="18" width="5.14545454545455" customWidth="1"/>
-    <col min="19" max="19" width="5.14545454545455" customWidth="1"/>
+    <col min="2" max="19" width="5.14545454545455" customWidth="1"/>
     <col min="20" max="20" width="8.72727272727273" style="2"/>
     <col min="21" max="22" width="8.72727272727273" style="3"/>
-    <col min="23" max="23" width="12.8181818181818" style="3"/>
+    <col min="23" max="23" width="8.53636363636364" style="3" customWidth="1"/>
+    <col min="24" max="26" width="8.72727272727273" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="14" spans="1:23">
-      <c r="A1" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="B1" s="4">
+    <row r="1" s="1" customFormat="1" ht="14" spans="1:26">
+      <c r="A1" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1" s="5">
         <v>5</v>
       </c>
-      <c r="C1" s="4">
+      <c r="C1" s="5">
         <v>6</v>
       </c>
-      <c r="D1" s="4">
+      <c r="D1" s="5">
         <v>9</v>
       </c>
-      <c r="E1" s="4">
+      <c r="E1" s="5">
         <v>10</v>
       </c>
-      <c r="F1" s="4">
+      <c r="F1" s="5">
         <v>11</v>
       </c>
-      <c r="G1" s="4">
+      <c r="G1" s="5">
         <v>12</v>
       </c>
-      <c r="H1" s="4">
+      <c r="H1" s="5">
         <v>15</v>
       </c>
-      <c r="I1" s="4">
+      <c r="I1" s="5">
         <v>16</v>
       </c>
-      <c r="J1" s="4">
+      <c r="J1" s="5">
         <v>17</v>
       </c>
-      <c r="K1" s="4">
+      <c r="K1" s="5">
         <v>18</v>
       </c>
-      <c r="L1" s="4">
+      <c r="L1" s="5">
         <v>19</v>
       </c>
-      <c r="M1" s="4">
+      <c r="M1" s="5">
         <v>22</v>
       </c>
-      <c r="N1" s="4">
+      <c r="N1" s="5">
         <v>23</v>
       </c>
-      <c r="O1" s="4">
+      <c r="O1" s="5">
         <v>25</v>
       </c>
-      <c r="P1" s="4">
+      <c r="P1" s="5">
         <v>26</v>
       </c>
-      <c r="Q1" s="4">
+      <c r="Q1" s="5">
         <v>29</v>
       </c>
-      <c r="R1" s="4"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="U1" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="V1" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="W1" s="6" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="2" ht="14" customHeight="1" spans="1:23">
-      <c r="A2" s="7">
-        <v>1</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="8"/>
-      <c r="S2" s="9"/>
+      <c r="R1" s="5">
+        <v>30</v>
+      </c>
+      <c r="S1" s="6">
+        <v>31</v>
+      </c>
+      <c r="T1" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="U1" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="V1" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="W1" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="X1" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="Y1" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="Z1" s="8" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="2" ht="14" customHeight="1" spans="1:26">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="11"/>
       <c r="T2" s="2">
         <f>SUM(B2:S2)</f>
         <v>0</v>
@@ -3358,47 +3426,59 @@
         <f t="array" ref="V2">MAX(FREQUENCY(IF((B2:S2=INT(B2:S2))*(B2:S2&gt;0),COLUMN(B2:S2)),IF((B2:S2&lt;&gt;INT(B2:S2))+(B2:S2&lt;=0),COLUMN(B2:S2))))</f>
         <v>0</v>
       </c>
-      <c r="W2" s="10" t="str" cm="1">
-        <f t="array" ref="W2">TEXT(SUMPRODUCT(--(B2:S2=INT(B2:S2)),--(B2:S2&gt;0))/18*100%,0%)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" ht="14" customHeight="1" spans="1:23">
-      <c r="A3" s="7">
+      <c r="W2" s="12" cm="1">
+        <f t="array" ref="W2">SUMPRODUCT(--(B2:S2=INT(B2:S2)),--(B2:S2&gt;0))/18*100%</f>
+        <v>0</v>
+      </c>
+      <c r="X2" s="4">
+        <f>RANK(T2,T$2:T$52,0)</f>
+        <v>35</v>
+      </c>
+      <c r="Y2" s="4">
+        <f>RANK(U2,U$2:U$52,0)</f>
+        <v>35</v>
+      </c>
+      <c r="Z2" s="4">
+        <f>RANK(V2,V$2:V$52,0)</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" ht="14" customHeight="1" spans="1:26">
+      <c r="A3" s="9">
         <v>2</v>
       </c>
-      <c r="B3" s="11">
-        <v>1</v>
-      </c>
-      <c r="C3" s="11">
-        <v>1</v>
-      </c>
-      <c r="D3" s="11">
-        <v>1</v>
-      </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="11">
-        <v>1</v>
-      </c>
-      <c r="J3" s="11">
-        <v>1</v>
-      </c>
-      <c r="K3" s="11">
-        <v>1</v>
-      </c>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="11">
-        <v>1</v>
-      </c>
-      <c r="R3" s="12"/>
-      <c r="S3" s="13"/>
+      <c r="B3" s="13">
+        <v>1</v>
+      </c>
+      <c r="C3" s="13">
+        <v>1</v>
+      </c>
+      <c r="D3" s="13">
+        <v>1</v>
+      </c>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="13">
+        <v>1</v>
+      </c>
+      <c r="J3" s="13">
+        <v>1</v>
+      </c>
+      <c r="K3" s="13">
+        <v>1</v>
+      </c>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="13">
+        <v>1</v>
+      </c>
+      <c r="R3" s="10"/>
+      <c r="S3" s="11"/>
       <c r="T3" s="2">
         <f>SUM(B3:S3)</f>
         <v>7</v>
@@ -3411,37 +3491,49 @@
         <f t="array" ref="V3">MAX(FREQUENCY(IF((B3:S3=INT(B3:S3))*(B3:S3&gt;0),COLUMN(B3:S3)),IF((B3:S3&lt;&gt;INT(B3:S3))+(B3:S3&lt;=0),COLUMN(B3:S3))))</f>
         <v>3</v>
       </c>
-      <c r="W3" s="14" cm="1">
+      <c r="W3" s="12" cm="1">
         <f t="array" ref="W3">SUMPRODUCT(--(B3:S3=INT(B3:S3)),--(B3:S3&gt;0))/18*100%</f>
         <v>0.388888888888889</v>
       </c>
-    </row>
-    <row r="4" ht="14" customHeight="1" spans="1:23">
-      <c r="A4" s="7">
+      <c r="X3" s="4">
+        <f t="shared" ref="X3:X34" si="0">RANK(T3,T$2:T$52,0)</f>
+        <v>6</v>
+      </c>
+      <c r="Y3" s="4">
+        <f t="shared" ref="Y3:Y34" si="1">RANK(U3,U$2:U$52,0)</f>
+        <v>6</v>
+      </c>
+      <c r="Z3" s="4">
+        <f t="shared" ref="Z3:Z34" si="2">RANK(V3,V$2:V$52,0)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" ht="14" customHeight="1" spans="1:26">
+      <c r="A4" s="9">
         <v>3</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="11">
-        <v>1</v>
-      </c>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="8"/>
-      <c r="S4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="13">
+        <v>1</v>
+      </c>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="11"/>
       <c r="T4" s="2">
-        <f t="shared" ref="T4:T35" si="0">SUM(B4:S4)</f>
+        <f t="shared" ref="T4:T35" si="3">SUM(B4:S4)</f>
         <v>1</v>
       </c>
       <c r="U4" s="3" cm="1">
@@ -3452,39 +3544,51 @@
         <f t="array" ref="V4">MAX(FREQUENCY(IF((B4:S4=INT(B4:S4))*(B4:S4&gt;0),COLUMN(B4:S4)),IF((B4:S4&lt;&gt;INT(B4:S4))+(B4:S4&lt;=0),COLUMN(B4:S4))))</f>
         <v>1</v>
       </c>
-      <c r="W4" s="10" t="str" cm="1">
-        <f t="array" ref="W4">TEXT(SUMPRODUCT(--(B4:S4=INT(B4:S4)),--(B4:S4&gt;0))/18*100%,0%)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" ht="14" customHeight="1" spans="1:23">
-      <c r="A5" s="7">
+      <c r="W4" s="12" cm="1">
+        <f t="array" ref="W4">SUMPRODUCT(--(B4:S4=INT(B4:S4)),--(B4:S4&gt;0))/18*100%</f>
+        <v>0.0555555555555556</v>
+      </c>
+      <c r="X4" s="4">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="Y4" s="4">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="Z4" s="4">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" ht="14" customHeight="1" spans="1:26">
+      <c r="A5" s="9">
         <v>4</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="11">
-        <v>1</v>
-      </c>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="11">
-        <v>1</v>
-      </c>
-      <c r="R5" s="12"/>
-      <c r="S5" s="13"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="13">
+        <v>1</v>
+      </c>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="13">
+        <v>1</v>
+      </c>
+      <c r="R5" s="10"/>
+      <c r="S5" s="11"/>
       <c r="T5" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="U5" s="3" cm="1">
@@ -3495,41 +3599,53 @@
         <f t="array" ref="V5">MAX(FREQUENCY(IF((B5:S5=INT(B5:S5))*(B5:S5&gt;0),COLUMN(B5:S5)),IF((B5:S5&lt;&gt;INT(B5:S5))+(B5:S5&lt;=0),COLUMN(B5:S5))))</f>
         <v>1</v>
       </c>
-      <c r="W5" s="14" cm="1">
+      <c r="W5" s="12" cm="1">
         <f t="array" ref="W5">SUMPRODUCT(--(B5:S5=INT(B5:S5)),--(B5:S5&gt;0))/18*100%</f>
         <v>0.111111111111111</v>
       </c>
-    </row>
-    <row r="6" ht="14" customHeight="1" spans="1:23">
-      <c r="A6" s="7">
+      <c r="X5" s="4">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="Y5" s="4">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="Z5" s="4">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" ht="14" customHeight="1" spans="1:26">
+      <c r="A6" s="9">
         <v>5</v>
       </c>
-      <c r="B6" s="11">
-        <v>1</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="15">
+      <c r="B6" s="13">
+        <v>1</v>
+      </c>
+      <c r="C6" s="9"/>
+      <c r="D6" s="14">
         <v>2</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="11">
-        <v>1</v>
-      </c>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="13">
+        <v>1</v>
+      </c>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="10"/>
+      <c r="S6" s="11"/>
       <c r="T6" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="U6" s="3" cm="1">
@@ -3540,145 +3656,185 @@
         <f t="array" ref="V6">MAX(FREQUENCY(IF((B6:S6=INT(B6:S6))*(B6:S6&gt;0),COLUMN(B6:S6)),IF((B6:S6&lt;&gt;INT(B6:S6))+(B6:S6&lt;=0),COLUMN(B6:S6))))</f>
         <v>1</v>
       </c>
-      <c r="W6" s="10" t="str" cm="1">
-        <f t="array" ref="W6">TEXT(SUMPRODUCT(--(B6:S6=INT(B6:S6)),--(B6:S6&gt;0))/18*100%,0%)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="14" customHeight="1" spans="1:23">
-      <c r="A7" s="7">
+      <c r="W6" s="12" cm="1">
+        <f t="array" ref="W6">SUMPRODUCT(--(B6:S6=INT(B6:S6)),--(B6:S6&gt;0))/18*100%</f>
+        <v>0.166666666666667</v>
+      </c>
+      <c r="X6" s="4">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="Y6" s="4">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="Z6" s="4">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" ht="14" customHeight="1" spans="1:26">
+      <c r="A7" s="9">
         <v>6</v>
       </c>
-      <c r="B7" s="11">
-        <v>1</v>
-      </c>
-      <c r="C7" s="11">
-        <v>1</v>
-      </c>
-      <c r="D7" s="11">
-        <v>1</v>
-      </c>
-      <c r="E7" s="11">
-        <v>1</v>
-      </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="11">
-        <v>1</v>
-      </c>
-      <c r="I7" s="11">
-        <v>1</v>
-      </c>
-      <c r="J7" s="11">
-        <v>1</v>
-      </c>
-      <c r="K7" s="7"/>
-      <c r="L7" s="11">
-        <v>1</v>
-      </c>
-      <c r="M7" s="7"/>
-      <c r="N7" s="11">
-        <v>1</v>
-      </c>
-      <c r="O7" s="7"/>
-      <c r="P7" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="11">
-        <v>1</v>
-      </c>
-      <c r="R7" s="12"/>
-      <c r="S7" s="13"/>
+      <c r="B7" s="13">
+        <v>1</v>
+      </c>
+      <c r="C7" s="13">
+        <v>1</v>
+      </c>
+      <c r="D7" s="13">
+        <v>1</v>
+      </c>
+      <c r="E7" s="13">
+        <v>1</v>
+      </c>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="13">
+        <v>1</v>
+      </c>
+      <c r="I7" s="13">
+        <v>1</v>
+      </c>
+      <c r="J7" s="13">
+        <v>1</v>
+      </c>
+      <c r="K7" s="9"/>
+      <c r="L7" s="13">
+        <v>1</v>
+      </c>
+      <c r="M7" s="9"/>
+      <c r="N7" s="13">
+        <v>1</v>
+      </c>
+      <c r="O7" s="9"/>
+      <c r="P7" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="13">
+        <v>1</v>
+      </c>
+      <c r="R7" s="13">
+        <v>1</v>
+      </c>
+      <c r="S7" s="11"/>
       <c r="T7" s="2">
-        <f t="shared" si="0"/>
-        <v>11</v>
+        <f t="shared" si="3"/>
+        <v>12</v>
       </c>
       <c r="U7" s="3" cm="1">
         <f t="array" ref="U7">SUMPRODUCT(--(B7:S7=INT(B7:S7)),--(B7:S7&gt;0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V7" s="3" cm="1">
         <f t="array" ref="V7">MAX(FREQUENCY(IF((B7:S7=INT(B7:S7))*(B7:S7&gt;0),COLUMN(B7:S7)),IF((B7:S7&lt;&gt;INT(B7:S7))+(B7:S7&lt;=0),COLUMN(B7:S7))))</f>
         <v>4</v>
       </c>
-      <c r="W7" s="14" cm="1">
+      <c r="W7" s="12" cm="1">
         <f t="array" ref="W7">SUMPRODUCT(--(B7:S7=INT(B7:S7)),--(B7:S7&gt;0))/18*100%</f>
-        <v>0.611111111111111</v>
-      </c>
-    </row>
-    <row r="8" ht="14" customHeight="1" spans="1:23">
-      <c r="A8" s="7">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="X7" s="4">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Y7" s="4">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="Z7" s="4">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" ht="14" customHeight="1" spans="1:26">
+      <c r="A8" s="9">
         <v>7</v>
       </c>
-      <c r="B8" s="11">
-        <v>1</v>
-      </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="11">
-        <v>1</v>
-      </c>
-      <c r="I8" s="11">
-        <v>1</v>
-      </c>
-      <c r="J8" s="11">
-        <v>1</v>
-      </c>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="11">
-        <v>1</v>
-      </c>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7"/>
-      <c r="R8" s="8"/>
-      <c r="S8" s="9"/>
+      <c r="B8" s="13">
+        <v>1</v>
+      </c>
+      <c r="C8" s="9"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="13">
+        <v>1</v>
+      </c>
+      <c r="I8" s="13">
+        <v>1</v>
+      </c>
+      <c r="J8" s="13">
+        <v>1</v>
+      </c>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="13">
+        <v>1</v>
+      </c>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="13">
+        <v>1</v>
+      </c>
+      <c r="S8" s="11"/>
       <c r="T8" s="2">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>6</v>
       </c>
       <c r="U8" s="3" cm="1">
         <f t="array" ref="U8">SUMPRODUCT(--(B8:S8=INT(B8:S8)),--(B8:S8&gt;0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V8" s="3" cm="1">
         <f t="array" ref="V8">MAX(FREQUENCY(IF((B8:S8=INT(B8:S8))*(B8:S8&gt;0),COLUMN(B8:S8)),IF((B8:S8&lt;&gt;INT(B8:S8))+(B8:S8&lt;=0),COLUMN(B8:S8))))</f>
         <v>3</v>
       </c>
-      <c r="W8" s="10" t="str" cm="1">
-        <f t="array" ref="W8">TEXT(SUMPRODUCT(--(B8:S8=INT(B8:S8)),--(B8:S8&gt;0))/18*100%,0%)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="14" customHeight="1" spans="1:23">
-      <c r="A9" s="7">
+      <c r="W8" s="12" cm="1">
+        <f t="array" ref="W8">SUMPRODUCT(--(B8:S8=INT(B8:S8)),--(B8:S8&gt;0))/18*100%</f>
+        <v>0.333333333333333</v>
+      </c>
+      <c r="X8" s="4">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="8"/>
-      <c r="S9" s="9"/>
+      <c r="Y8" s="4">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="Z8" s="4">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" ht="14" customHeight="1" spans="1:26">
+      <c r="A9" s="9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="10"/>
+      <c r="S9" s="11"/>
       <c r="T9" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U9" s="3" cm="1">
@@ -3689,41 +3845,53 @@
         <f t="array" ref="V9">MAX(FREQUENCY(IF((B9:S9=INT(B9:S9))*(B9:S9&gt;0),COLUMN(B9:S9)),IF((B9:S9&lt;&gt;INT(B9:S9))+(B9:S9&lt;=0),COLUMN(B9:S9))))</f>
         <v>0</v>
       </c>
-      <c r="W9" s="14" cm="1">
+      <c r="W9" s="12" cm="1">
         <f t="array" ref="W9">SUMPRODUCT(--(B9:S9=INT(B9:S9)),--(B9:S9&gt;0))/18*100%</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="10" ht="14" customHeight="1" spans="1:23">
-      <c r="A10" s="7">
+      <c r="X9" s="4">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="Y9" s="4">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="Z9" s="4">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" ht="14" customHeight="1" spans="1:26">
+      <c r="A10" s="9">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="11">
-        <v>1</v>
-      </c>
-      <c r="M10" s="7"/>
-      <c r="N10" s="11">
-        <v>1</v>
-      </c>
-      <c r="O10" s="7"/>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="11">
-        <v>1</v>
-      </c>
-      <c r="R10" s="12"/>
-      <c r="S10" s="13"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="13">
+        <v>1</v>
+      </c>
+      <c r="M10" s="9"/>
+      <c r="N10" s="13">
+        <v>1</v>
+      </c>
+      <c r="O10" s="9"/>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="13">
+        <v>1</v>
+      </c>
+      <c r="R10" s="10"/>
+      <c r="S10" s="11"/>
       <c r="T10" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="U10" s="3" cm="1">
@@ -3734,37 +3902,49 @@
         <f t="array" ref="V10">MAX(FREQUENCY(IF((B10:S10=INT(B10:S10))*(B10:S10&gt;0),COLUMN(B10:S10)),IF((B10:S10&lt;&gt;INT(B10:S10))+(B10:S10&lt;=0),COLUMN(B10:S10))))</f>
         <v>1</v>
       </c>
-      <c r="W10" s="10" t="str" cm="1">
-        <f t="array" ref="W10">TEXT(SUMPRODUCT(--(B10:S10=INT(B10:S10)),--(B10:S10&gt;0))/18*100%,0%)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="14" customHeight="1" spans="1:23">
-      <c r="A11" s="7">
+      <c r="W10" s="12" cm="1">
+        <f t="array" ref="W10">SUMPRODUCT(--(B10:S10=INT(B10:S10)),--(B10:S10&gt;0))/18*100%</f>
+        <v>0.166666666666667</v>
+      </c>
+      <c r="X10" s="4">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="Y10" s="4">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="Z10" s="4">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" ht="14" customHeight="1" spans="1:26">
+      <c r="A11" s="9">
         <v>10</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="11">
-        <v>1</v>
-      </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="7"/>
-      <c r="R11" s="8"/>
-      <c r="S11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="13">
+        <v>1</v>
+      </c>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="9"/>
+      <c r="R11" s="10"/>
+      <c r="S11" s="11"/>
       <c r="T11" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="U11" s="3" cm="1">
@@ -3775,45 +3955,57 @@
         <f t="array" ref="V11">MAX(FREQUENCY(IF((B11:S11=INT(B11:S11))*(B11:S11&gt;0),COLUMN(B11:S11)),IF((B11:S11&lt;&gt;INT(B11:S11))+(B11:S11&lt;=0),COLUMN(B11:S11))))</f>
         <v>1</v>
       </c>
-      <c r="W11" s="14" cm="1">
+      <c r="W11" s="12" cm="1">
         <f t="array" ref="W11">SUMPRODUCT(--(B11:S11=INT(B11:S11)),--(B11:S11&gt;0))/18*100%</f>
         <v>0.0555555555555556</v>
       </c>
-    </row>
-    <row r="12" ht="14" customHeight="1" spans="1:23">
-      <c r="A12" s="7">
+      <c r="X11" s="4">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="Y11" s="4">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="Z11" s="4">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" ht="14" customHeight="1" spans="1:26">
+      <c r="A12" s="9">
         <v>11</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="11">
-        <v>1</v>
-      </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="11">
-        <v>1</v>
-      </c>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="11">
-        <v>1</v>
-      </c>
-      <c r="M12" s="7"/>
-      <c r="N12" s="11">
-        <v>1</v>
-      </c>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="11">
-        <v>1</v>
-      </c>
-      <c r="R12" s="12"/>
-      <c r="S12" s="13"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="13">
+        <v>1</v>
+      </c>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="13">
+        <v>1</v>
+      </c>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="13">
+        <v>1</v>
+      </c>
+      <c r="M12" s="9"/>
+      <c r="N12" s="13">
+        <v>1</v>
+      </c>
+      <c r="O12" s="9"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="13">
+        <v>1</v>
+      </c>
+      <c r="R12" s="10"/>
+      <c r="S12" s="11"/>
       <c r="T12" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="U12" s="3" cm="1">
@@ -3824,37 +4016,49 @@
         <f t="array" ref="V12">MAX(FREQUENCY(IF((B12:S12=INT(B12:S12))*(B12:S12&gt;0),COLUMN(B12:S12)),IF((B12:S12&lt;&gt;INT(B12:S12))+(B12:S12&lt;=0),COLUMN(B12:S12))))</f>
         <v>1</v>
       </c>
-      <c r="W12" s="10" t="str" cm="1">
-        <f t="array" ref="W12">TEXT(SUMPRODUCT(--(B12:S12=INT(B12:S12)),--(B12:S12&gt;0))/18*100%,0%)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="14" customHeight="1" spans="1:23">
-      <c r="A13" s="7">
+      <c r="W12" s="12" cm="1">
+        <f t="array" ref="W12">SUMPRODUCT(--(B12:S12=INT(B12:S12)),--(B12:S12&gt;0))/18*100%</f>
+        <v>0.277777777777778</v>
+      </c>
+      <c r="X12" s="4">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="Y12" s="4">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="Z12" s="4">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" ht="14" customHeight="1" spans="1:26">
+      <c r="A13" s="9">
         <v>12</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="11">
-        <v>1</v>
-      </c>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="7"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="13">
+        <v>1</v>
+      </c>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="9"/>
+      <c r="R13" s="10"/>
+      <c r="S13" s="11"/>
       <c r="T13" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="U13" s="3" cm="1">
@@ -3865,45 +4069,57 @@
         <f t="array" ref="V13">MAX(FREQUENCY(IF((B13:S13=INT(B13:S13))*(B13:S13&gt;0),COLUMN(B13:S13)),IF((B13:S13&lt;&gt;INT(B13:S13))+(B13:S13&lt;=0),COLUMN(B13:S13))))</f>
         <v>1</v>
       </c>
-      <c r="W13" s="14" cm="1">
+      <c r="W13" s="12" cm="1">
         <f t="array" ref="W13">SUMPRODUCT(--(B13:S13=INT(B13:S13)),--(B13:S13&gt;0))/18*100%</f>
         <v>0.0555555555555556</v>
       </c>
-    </row>
-    <row r="14" ht="14" customHeight="1" spans="1:23">
-      <c r="A14" s="7">
+      <c r="X13" s="4">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="Y13" s="4">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="Z13" s="4">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" ht="14" customHeight="1" spans="1:26">
+      <c r="A14" s="9">
         <v>13</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="11">
-        <v>1</v>
-      </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="11">
-        <v>1</v>
-      </c>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="11">
-        <v>1</v>
-      </c>
-      <c r="M14" s="11">
-        <v>1</v>
-      </c>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="7"/>
-      <c r="Q14" s="11">
-        <v>1</v>
-      </c>
-      <c r="R14" s="12"/>
-      <c r="S14" s="13"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="13">
+        <v>1</v>
+      </c>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="13">
+        <v>1</v>
+      </c>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="13">
+        <v>1</v>
+      </c>
+      <c r="M14" s="13">
+        <v>1</v>
+      </c>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="9"/>
+      <c r="Q14" s="13">
+        <v>1</v>
+      </c>
+      <c r="R14" s="10"/>
+      <c r="S14" s="11"/>
       <c r="T14" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="U14" s="3" cm="1">
@@ -3914,37 +4130,49 @@
         <f t="array" ref="V14">MAX(FREQUENCY(IF((B14:S14=INT(B14:S14))*(B14:S14&gt;0),COLUMN(B14:S14)),IF((B14:S14&lt;&gt;INT(B14:S14))+(B14:S14&lt;=0),COLUMN(B14:S14))))</f>
         <v>2</v>
       </c>
-      <c r="W14" s="10" t="str" cm="1">
-        <f t="array" ref="W14">TEXT(SUMPRODUCT(--(B14:S14=INT(B14:S14)),--(B14:S14&gt;0))/18*100%,0%)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="14" customHeight="1" spans="1:23">
-      <c r="A15" s="7">
+      <c r="W14" s="12" cm="1">
+        <f t="array" ref="W14">SUMPRODUCT(--(B14:S14=INT(B14:S14)),--(B14:S14&gt;0))/18*100%</f>
+        <v>0.277777777777778</v>
+      </c>
+      <c r="X14" s="4">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="Y14" s="4">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="Z14" s="4">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" ht="14" customHeight="1" spans="1:26">
+      <c r="A15" s="9">
         <v>14</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="11">
-        <v>1</v>
-      </c>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
-      <c r="R15" s="8"/>
-      <c r="S15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="13">
+        <v>1</v>
+      </c>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="9"/>
+      <c r="R15" s="10"/>
+      <c r="S15" s="11"/>
       <c r="T15" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="U15" s="3" cm="1">
@@ -3955,74 +4183,100 @@
         <f t="array" ref="V15">MAX(FREQUENCY(IF((B15:S15=INT(B15:S15))*(B15:S15&gt;0),COLUMN(B15:S15)),IF((B15:S15&lt;&gt;INT(B15:S15))+(B15:S15&lt;=0),COLUMN(B15:S15))))</f>
         <v>1</v>
       </c>
-      <c r="W15" s="14" cm="1">
+      <c r="W15" s="12" cm="1">
         <f t="array" ref="W15">SUMPRODUCT(--(B15:S15=INT(B15:S15)),--(B15:S15&gt;0))/18*100%</f>
         <v>0.0555555555555556</v>
       </c>
-    </row>
-    <row r="16" ht="14" customHeight="1" spans="1:23">
-      <c r="A16" s="7">
+      <c r="X15" s="4">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="Y15" s="4">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="Z15" s="4">
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="7"/>
-      <c r="R16" s="8"/>
-      <c r="S16" s="9"/>
+    </row>
+    <row r="16" ht="14" customHeight="1" spans="1:26">
+      <c r="A16" s="9">
+        <v>15</v>
+      </c>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="9"/>
+      <c r="R16" s="13">
+        <v>1</v>
+      </c>
+      <c r="S16" s="11"/>
       <c r="T16" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="U16" s="3" cm="1">
         <f t="array" ref="U16">SUMPRODUCT(--(B16:S16=INT(B16:S16)),--(B16:S16&gt;0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="3" cm="1">
         <f t="array" ref="V16">MAX(FREQUENCY(IF((B16:S16=INT(B16:S16))*(B16:S16&gt;0),COLUMN(B16:S16)),IF((B16:S16&lt;&gt;INT(B16:S16))+(B16:S16&lt;=0),COLUMN(B16:S16))))</f>
-        <v>0</v>
-      </c>
-      <c r="W16" s="10" t="str" cm="1">
-        <f t="array" ref="W16">TEXT(SUMPRODUCT(--(B16:S16=INT(B16:S16)),--(B16:S16&gt;0))/18*100%,0%)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" ht="14" customHeight="1" spans="1:23">
-      <c r="A17" s="7">
+        <v>1</v>
+      </c>
+      <c r="W16" s="12" cm="1">
+        <f t="array" ref="W16">SUMPRODUCT(--(B16:S16=INT(B16:S16)),--(B16:S16&gt;0))/18*100%</f>
+        <v>0.0555555555555556</v>
+      </c>
+      <c r="X16" s="4">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="Y16" s="4">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="Z16" s="4">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" ht="14" customHeight="1" spans="1:26">
+      <c r="A17" s="9">
         <v>16</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="7"/>
-      <c r="R17" s="8"/>
-      <c r="S17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="9"/>
+      <c r="R17" s="10"/>
+      <c r="S17" s="11"/>
       <c r="T17" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U17" s="3" cm="1">
@@ -4033,39 +4287,51 @@
         <f t="array" ref="V17">MAX(FREQUENCY(IF((B17:S17=INT(B17:S17))*(B17:S17&gt;0),COLUMN(B17:S17)),IF((B17:S17&lt;&gt;INT(B17:S17))+(B17:S17&lt;=0),COLUMN(B17:S17))))</f>
         <v>0</v>
       </c>
-      <c r="W17" s="14" cm="1">
+      <c r="W17" s="12" cm="1">
         <f t="array" ref="W17">SUMPRODUCT(--(B17:S17=INT(B17:S17)),--(B17:S17&gt;0))/18*100%</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="18" ht="14" customHeight="1" spans="1:23">
-      <c r="A18" s="7">
+      <c r="X17" s="4">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="Y17" s="4">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="Z17" s="4">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" ht="14" customHeight="1" spans="1:26">
+      <c r="A18" s="9">
         <v>17</v>
       </c>
-      <c r="B18" s="11">
-        <v>1</v>
-      </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="11">
-        <v>1</v>
-      </c>
-      <c r="O18" s="7"/>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="7"/>
-      <c r="R18" s="8"/>
-      <c r="S18" s="9"/>
+      <c r="B18" s="13">
+        <v>1</v>
+      </c>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="13">
+        <v>1</v>
+      </c>
+      <c r="O18" s="9"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="9"/>
+      <c r="R18" s="10"/>
+      <c r="S18" s="11"/>
       <c r="T18" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="U18" s="3" cm="1">
@@ -4076,37 +4342,49 @@
         <f t="array" ref="V18">MAX(FREQUENCY(IF((B18:S18=INT(B18:S18))*(B18:S18&gt;0),COLUMN(B18:S18)),IF((B18:S18&lt;&gt;INT(B18:S18))+(B18:S18&lt;=0),COLUMN(B18:S18))))</f>
         <v>1</v>
       </c>
-      <c r="W18" s="10" t="str" cm="1">
-        <f t="array" ref="W18">TEXT(SUMPRODUCT(--(B18:S18=INT(B18:S18)),--(B18:S18&gt;0))/18*100%,0%)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="14" customHeight="1" spans="1:23">
-      <c r="A19" s="7">
+      <c r="W18" s="12" cm="1">
+        <f t="array" ref="W18">SUMPRODUCT(--(B18:S18=INT(B18:S18)),--(B18:S18&gt;0))/18*100%</f>
+        <v>0.111111111111111</v>
+      </c>
+      <c r="X18" s="4">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="Y18" s="4">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="Z18" s="4">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" ht="14" customHeight="1" spans="1:26">
+      <c r="A19" s="9">
         <v>18</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="11">
-        <v>1</v>
-      </c>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="7"/>
-      <c r="P19" s="7"/>
-      <c r="Q19" s="7"/>
-      <c r="R19" s="8"/>
-      <c r="S19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="13">
+        <v>1</v>
+      </c>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="9"/>
+      <c r="Q19" s="9"/>
+      <c r="R19" s="10"/>
+      <c r="S19" s="11"/>
       <c r="T19" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="U19" s="3" cm="1">
@@ -4117,39 +4395,51 @@
         <f t="array" ref="V19">MAX(FREQUENCY(IF((B19:S19=INT(B19:S19))*(B19:S19&gt;0),COLUMN(B19:S19)),IF((B19:S19&lt;&gt;INT(B19:S19))+(B19:S19&lt;=0),COLUMN(B19:S19))))</f>
         <v>1</v>
       </c>
-      <c r="W19" s="14" cm="1">
+      <c r="W19" s="12" cm="1">
         <f t="array" ref="W19">SUMPRODUCT(--(B19:S19=INT(B19:S19)),--(B19:S19&gt;0))/18*100%</f>
         <v>0.0555555555555556</v>
       </c>
-    </row>
-    <row r="20" ht="14" customHeight="1" spans="1:23">
-      <c r="A20" s="7">
+      <c r="X19" s="4">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="Y19" s="4">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="Z19" s="4">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" ht="14" customHeight="1" spans="1:26">
+      <c r="A20" s="9">
         <v>19</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="11">
-        <v>1</v>
-      </c>
-      <c r="K20" s="7"/>
-      <c r="L20" s="11">
-        <v>1</v>
-      </c>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
-      <c r="P20" s="7"/>
-      <c r="Q20" s="7"/>
-      <c r="R20" s="8"/>
-      <c r="S20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="13">
+        <v>1</v>
+      </c>
+      <c r="K20" s="9"/>
+      <c r="L20" s="13">
+        <v>1</v>
+      </c>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="9"/>
+      <c r="Q20" s="9"/>
+      <c r="R20" s="10"/>
+      <c r="S20" s="11"/>
       <c r="T20" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="U20" s="3" cm="1">
@@ -4160,80 +4450,106 @@
         <f t="array" ref="V20">MAX(FREQUENCY(IF((B20:S20=INT(B20:S20))*(B20:S20&gt;0),COLUMN(B20:S20)),IF((B20:S20&lt;&gt;INT(B20:S20))+(B20:S20&lt;=0),COLUMN(B20:S20))))</f>
         <v>1</v>
       </c>
-      <c r="W20" s="10" t="str" cm="1">
-        <f t="array" ref="W20">TEXT(SUMPRODUCT(--(B20:S20=INT(B20:S20)),--(B20:S20&gt;0))/18*100%,0%)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" ht="14" customHeight="1" spans="1:23">
-      <c r="A21" s="7">
+      <c r="W20" s="12" cm="1">
+        <f t="array" ref="W20">SUMPRODUCT(--(B20:S20=INT(B20:S20)),--(B20:S20&gt;0))/18*100%</f>
+        <v>0.111111111111111</v>
+      </c>
+      <c r="X20" s="4">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="11">
-        <v>1</v>
-      </c>
-      <c r="J21" s="11">
-        <v>1</v>
-      </c>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
-      <c r="P21" s="7"/>
-      <c r="Q21" s="11">
-        <v>1</v>
-      </c>
-      <c r="R21" s="12"/>
-      <c r="S21" s="13"/>
+      <c r="Y20" s="4">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="Z20" s="4">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" ht="14" customHeight="1" spans="1:26">
+      <c r="A21" s="9">
+        <v>20</v>
+      </c>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="13">
+        <v>1</v>
+      </c>
+      <c r="J21" s="13">
+        <v>1</v>
+      </c>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="9"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="13">
+        <v>1</v>
+      </c>
+      <c r="R21" s="13">
+        <v>1</v>
+      </c>
+      <c r="S21" s="11"/>
       <c r="T21" s="2">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f t="shared" si="3"/>
+        <v>4</v>
       </c>
       <c r="U21" s="3" cm="1">
         <f t="array" ref="U21">SUMPRODUCT(--(B21:S21=INT(B21:S21)),--(B21:S21&gt;0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V21" s="3" cm="1">
         <f t="array" ref="V21">MAX(FREQUENCY(IF((B21:S21=INT(B21:S21))*(B21:S21&gt;0),COLUMN(B21:S21)),IF((B21:S21&lt;&gt;INT(B21:S21))+(B21:S21&lt;=0),COLUMN(B21:S21))))</f>
         <v>2</v>
       </c>
-      <c r="W21" s="14" cm="1">
+      <c r="W21" s="12" cm="1">
         <f t="array" ref="W21">SUMPRODUCT(--(B21:S21=INT(B21:S21)),--(B21:S21&gt;0))/18*100%</f>
-        <v>0.166666666666667</v>
-      </c>
-    </row>
-    <row r="22" ht="14" customHeight="1" spans="1:23">
-      <c r="A22" s="7">
+        <v>0.222222222222222</v>
+      </c>
+      <c r="X21" s="4">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="Y21" s="4">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="Z21" s="4">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" ht="14" customHeight="1" spans="1:26">
+      <c r="A22" s="9">
         <v>21</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
-      <c r="P22" s="7"/>
-      <c r="Q22" s="7"/>
-      <c r="R22" s="8"/>
-      <c r="S22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="9"/>
+      <c r="Q22" s="9"/>
+      <c r="R22" s="10"/>
+      <c r="S22" s="11"/>
       <c r="T22" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U22" s="3" cm="1">
@@ -4244,45 +4560,57 @@
         <f t="array" ref="V22">MAX(FREQUENCY(IF((B22:S22=INT(B22:S22))*(B22:S22&gt;0),COLUMN(B22:S22)),IF((B22:S22&lt;&gt;INT(B22:S22))+(B22:S22&lt;=0),COLUMN(B22:S22))))</f>
         <v>0</v>
       </c>
-      <c r="W22" s="10" t="str" cm="1">
-        <f t="array" ref="W22">TEXT(SUMPRODUCT(--(B22:S22=INT(B22:S22)),--(B22:S22&gt;0))/18*100%,0%)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" ht="14" customHeight="1" spans="1:23">
-      <c r="A23" s="7">
+      <c r="W22" s="12" cm="1">
+        <f t="array" ref="W22">SUMPRODUCT(--(B22:S22=INT(B22:S22)),--(B22:S22&gt;0))/18*100%</f>
+        <v>0</v>
+      </c>
+      <c r="X22" s="4">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="Y22" s="4">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="Z22" s="4">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" ht="14" customHeight="1" spans="1:26">
+      <c r="A23" s="9">
         <v>22</v>
       </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="11">
-        <v>1</v>
-      </c>
-      <c r="D23" s="11">
-        <v>1</v>
-      </c>
-      <c r="E23" s="11">
-        <v>1</v>
-      </c>
-      <c r="F23" s="7"/>
-      <c r="G23" s="11">
-        <v>1</v>
-      </c>
-      <c r="H23" s="7"/>
-      <c r="I23" s="11">
-        <v>1</v>
-      </c>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
-      <c r="O23" s="7"/>
-      <c r="P23" s="7"/>
-      <c r="Q23" s="7"/>
-      <c r="R23" s="8"/>
-      <c r="S23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="13">
+        <v>1</v>
+      </c>
+      <c r="D23" s="13">
+        <v>1</v>
+      </c>
+      <c r="E23" s="13">
+        <v>1</v>
+      </c>
+      <c r="F23" s="9"/>
+      <c r="G23" s="13">
+        <v>1</v>
+      </c>
+      <c r="H23" s="9"/>
+      <c r="I23" s="13">
+        <v>1</v>
+      </c>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="9"/>
+      <c r="O23" s="9"/>
+      <c r="P23" s="9"/>
+      <c r="Q23" s="9"/>
+      <c r="R23" s="10"/>
+      <c r="S23" s="11"/>
       <c r="T23" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="U23" s="3" cm="1">
@@ -4293,35 +4621,47 @@
         <f t="array" ref="V23">MAX(FREQUENCY(IF((B23:S23=INT(B23:S23))*(B23:S23&gt;0),COLUMN(B23:S23)),IF((B23:S23&lt;&gt;INT(B23:S23))+(B23:S23&lt;=0),COLUMN(B23:S23))))</f>
         <v>3</v>
       </c>
-      <c r="W23" s="14" cm="1">
+      <c r="W23" s="12" cm="1">
         <f t="array" ref="W23">SUMPRODUCT(--(B23:S23=INT(B23:S23)),--(B23:S23&gt;0))/18*100%</f>
         <v>0.277777777777778</v>
       </c>
-    </row>
-    <row r="24" ht="14" customHeight="1" spans="1:23">
-      <c r="A24" s="7">
+      <c r="X23" s="4">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="Y23" s="4">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="Z23" s="4">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" ht="14" customHeight="1" spans="1:26">
+      <c r="A24" s="9">
         <v>23</v>
       </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
-      <c r="O24" s="7"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="7"/>
-      <c r="R24" s="8"/>
-      <c r="S24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="9"/>
+      <c r="O24" s="9"/>
+      <c r="P24" s="9"/>
+      <c r="Q24" s="9"/>
+      <c r="R24" s="10"/>
+      <c r="S24" s="11"/>
       <c r="T24" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U24" s="3" cm="1">
@@ -4332,35 +4672,47 @@
         <f t="array" ref="V24">MAX(FREQUENCY(IF((B24:S24=INT(B24:S24))*(B24:S24&gt;0),COLUMN(B24:S24)),IF((B24:S24&lt;&gt;INT(B24:S24))+(B24:S24&lt;=0),COLUMN(B24:S24))))</f>
         <v>0</v>
       </c>
-      <c r="W24" s="10" t="str" cm="1">
-        <f t="array" ref="W24">TEXT(SUMPRODUCT(--(B24:S24=INT(B24:S24)),--(B24:S24&gt;0))/18*100%,0%)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" ht="14" customHeight="1" spans="1:23">
-      <c r="A25" s="7">
+      <c r="W24" s="12" cm="1">
+        <f t="array" ref="W24">SUMPRODUCT(--(B24:S24=INT(B24:S24)),--(B24:S24&gt;0))/18*100%</f>
+        <v>0</v>
+      </c>
+      <c r="X24" s="4">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="Y24" s="4">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="Z24" s="4">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" ht="14" customHeight="1" spans="1:26">
+      <c r="A25" s="9">
         <v>24</v>
       </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="7"/>
-      <c r="O25" s="7"/>
-      <c r="P25" s="7"/>
-      <c r="Q25" s="7"/>
-      <c r="R25" s="8"/>
-      <c r="S25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="9"/>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="9"/>
+      <c r="R25" s="10"/>
+      <c r="S25" s="11"/>
       <c r="T25" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U25" s="3" cm="1">
@@ -4371,35 +4723,47 @@
         <f t="array" ref="V25">MAX(FREQUENCY(IF((B25:S25=INT(B25:S25))*(B25:S25&gt;0),COLUMN(B25:S25)),IF((B25:S25&lt;&gt;INT(B25:S25))+(B25:S25&lt;=0),COLUMN(B25:S25))))</f>
         <v>0</v>
       </c>
-      <c r="W25" s="14" cm="1">
+      <c r="W25" s="12" cm="1">
         <f t="array" ref="W25">SUMPRODUCT(--(B25:S25=INT(B25:S25)),--(B25:S25&gt;0))/18*100%</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="26" ht="14" customHeight="1" spans="1:23">
-      <c r="A26" s="7">
+      <c r="X25" s="4">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="Y25" s="4">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="Z25" s="4">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" ht="14" customHeight="1" spans="1:26">
+      <c r="A26" s="9">
         <v>25</v>
       </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="7"/>
-      <c r="O26" s="7"/>
-      <c r="P26" s="7"/>
-      <c r="Q26" s="7"/>
-      <c r="R26" s="8"/>
-      <c r="S26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="9"/>
+      <c r="P26" s="9"/>
+      <c r="Q26" s="9"/>
+      <c r="R26" s="10"/>
+      <c r="S26" s="11"/>
       <c r="T26" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U26" s="3" cm="1">
@@ -4410,43 +4774,55 @@
         <f t="array" ref="V26">MAX(FREQUENCY(IF((B26:S26=INT(B26:S26))*(B26:S26&gt;0),COLUMN(B26:S26)),IF((B26:S26&lt;&gt;INT(B26:S26))+(B26:S26&lt;=0),COLUMN(B26:S26))))</f>
         <v>0</v>
       </c>
-      <c r="W26" s="10" t="str" cm="1">
-        <f t="array" ref="W26">TEXT(SUMPRODUCT(--(B26:S26=INT(B26:S26)),--(B26:S26&gt;0))/18*100%,0%)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" ht="14" customHeight="1" spans="1:23">
-      <c r="A27" s="7">
+      <c r="W26" s="12" cm="1">
+        <f t="array" ref="W26">SUMPRODUCT(--(B26:S26=INT(B26:S26)),--(B26:S26&gt;0))/18*100%</f>
+        <v>0</v>
+      </c>
+      <c r="X26" s="4">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="Y26" s="4">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="Z26" s="4">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" ht="14" customHeight="1" spans="1:26">
+      <c r="A27" s="9">
         <v>26</v>
       </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="11">
-        <v>1</v>
-      </c>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="11">
-        <v>1</v>
-      </c>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="11">
-        <v>1</v>
-      </c>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
-      <c r="N27" s="7"/>
-      <c r="O27" s="7"/>
-      <c r="P27" s="7"/>
-      <c r="Q27" s="11">
-        <v>1</v>
-      </c>
-      <c r="R27" s="12"/>
-      <c r="S27" s="13"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="13">
+        <v>1</v>
+      </c>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="13">
+        <v>1</v>
+      </c>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="13">
+        <v>1</v>
+      </c>
+      <c r="L27" s="9"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="9"/>
+      <c r="O27" s="9"/>
+      <c r="P27" s="9"/>
+      <c r="Q27" s="13">
+        <v>1</v>
+      </c>
+      <c r="R27" s="10"/>
+      <c r="S27" s="11"/>
       <c r="T27" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="U27" s="3" cm="1">
@@ -4457,39 +4833,51 @@
         <f t="array" ref="V27">MAX(FREQUENCY(IF((B27:S27=INT(B27:S27))*(B27:S27&gt;0),COLUMN(B27:S27)),IF((B27:S27&lt;&gt;INT(B27:S27))+(B27:S27&lt;=0),COLUMN(B27:S27))))</f>
         <v>1</v>
       </c>
-      <c r="W27" s="14" cm="1">
+      <c r="W27" s="12" cm="1">
         <f t="array" ref="W27">SUMPRODUCT(--(B27:S27=INT(B27:S27)),--(B27:S27&gt;0))/18*100%</f>
         <v>0.222222222222222</v>
       </c>
-    </row>
-    <row r="28" ht="14" customHeight="1" spans="1:23">
-      <c r="A28" s="7">
+      <c r="X27" s="4">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="Y27" s="4">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="Z27" s="4">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" ht="14" customHeight="1" spans="1:26">
+      <c r="A28" s="9">
         <v>27</v>
       </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="11">
-        <v>1</v>
-      </c>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="11">
-        <v>1</v>
-      </c>
-      <c r="N28" s="7"/>
-      <c r="O28" s="7"/>
-      <c r="P28" s="7"/>
-      <c r="Q28" s="7"/>
-      <c r="R28" s="8"/>
-      <c r="S28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="13">
+        <v>1</v>
+      </c>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="13">
+        <v>1</v>
+      </c>
+      <c r="N28" s="9"/>
+      <c r="O28" s="9"/>
+      <c r="P28" s="9"/>
+      <c r="Q28" s="9"/>
+      <c r="R28" s="10"/>
+      <c r="S28" s="11"/>
       <c r="T28" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="U28" s="3" cm="1">
@@ -4500,39 +4888,51 @@
         <f t="array" ref="V28">MAX(FREQUENCY(IF((B28:S28=INT(B28:S28))*(B28:S28&gt;0),COLUMN(B28:S28)),IF((B28:S28&lt;&gt;INT(B28:S28))+(B28:S28&lt;=0),COLUMN(B28:S28))))</f>
         <v>1</v>
       </c>
-      <c r="W28" s="10" t="str" cm="1">
-        <f t="array" ref="W28">TEXT(SUMPRODUCT(--(B28:S28=INT(B28:S28)),--(B28:S28&gt;0))/18*100%,0%)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" ht="14" customHeight="1" spans="1:23">
-      <c r="A29" s="7">
+      <c r="W28" s="12" cm="1">
+        <f t="array" ref="W28">SUMPRODUCT(--(B28:S28=INT(B28:S28)),--(B28:S28&gt;0))/18*100%</f>
+        <v>0.111111111111111</v>
+      </c>
+      <c r="X28" s="4">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="Y28" s="4">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="Z28" s="4">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" ht="14" customHeight="1" spans="1:26">
+      <c r="A29" s="9">
         <v>28</v>
       </c>
-      <c r="B29" s="11">
-        <v>1</v>
-      </c>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="11">
-        <v>1</v>
-      </c>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
-      <c r="N29" s="7"/>
-      <c r="O29" s="7"/>
-      <c r="P29" s="7"/>
-      <c r="Q29" s="7"/>
-      <c r="R29" s="8"/>
-      <c r="S29" s="9"/>
+      <c r="B29" s="13">
+        <v>1</v>
+      </c>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="13">
+        <v>1</v>
+      </c>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="9"/>
+      <c r="M29" s="9"/>
+      <c r="N29" s="9"/>
+      <c r="O29" s="9"/>
+      <c r="P29" s="9"/>
+      <c r="Q29" s="9"/>
+      <c r="R29" s="10"/>
+      <c r="S29" s="11"/>
       <c r="T29" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="U29" s="3" cm="1">
@@ -4543,43 +4943,55 @@
         <f t="array" ref="V29">MAX(FREQUENCY(IF((B29:S29=INT(B29:S29))*(B29:S29&gt;0),COLUMN(B29:S29)),IF((B29:S29&lt;&gt;INT(B29:S29))+(B29:S29&lt;=0),COLUMN(B29:S29))))</f>
         <v>1</v>
       </c>
-      <c r="W29" s="14" cm="1">
+      <c r="W29" s="12" cm="1">
         <f t="array" ref="W29">SUMPRODUCT(--(B29:S29=INT(B29:S29)),--(B29:S29&gt;0))/18*100%</f>
         <v>0.111111111111111</v>
       </c>
-    </row>
-    <row r="30" ht="14" customHeight="1" spans="1:23">
-      <c r="A30" s="7">
+      <c r="X29" s="4">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="Y29" s="4">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="Z29" s="4">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" ht="14" customHeight="1" spans="1:26">
+      <c r="A30" s="9">
         <v>29</v>
       </c>
-      <c r="B30" s="11">
-        <v>1</v>
-      </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="11">
-        <v>1</v>
-      </c>
-      <c r="I30" s="15">
+      <c r="B30" s="13">
+        <v>1</v>
+      </c>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="13">
+        <v>1</v>
+      </c>
+      <c r="I30" s="14">
         <v>2</v>
       </c>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
-      <c r="N30" s="7"/>
-      <c r="O30" s="7"/>
-      <c r="P30" s="7"/>
-      <c r="Q30" s="11">
-        <v>1</v>
-      </c>
-      <c r="R30" s="12"/>
-      <c r="S30" s="13"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
+      <c r="M30" s="9"/>
+      <c r="N30" s="9"/>
+      <c r="O30" s="9"/>
+      <c r="P30" s="9"/>
+      <c r="Q30" s="13">
+        <v>1</v>
+      </c>
+      <c r="R30" s="10"/>
+      <c r="S30" s="11"/>
       <c r="T30" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="U30" s="3" cm="1">
@@ -4590,86 +5002,112 @@
         <f t="array" ref="V30">MAX(FREQUENCY(IF((B30:S30=INT(B30:S30))*(B30:S30&gt;0),COLUMN(B30:S30)),IF((B30:S30&lt;&gt;INT(B30:S30))+(B30:S30&lt;=0),COLUMN(B30:S30))))</f>
         <v>2</v>
       </c>
-      <c r="W30" s="10" t="str" cm="1">
-        <f t="array" ref="W30">TEXT(SUMPRODUCT(--(B30:S30=INT(B30:S30)),--(B30:S30&gt;0))/18*100%,0%)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" ht="14" customHeight="1" spans="1:23">
-      <c r="A31" s="7">
+      <c r="W30" s="12" cm="1">
+        <f t="array" ref="W30">SUMPRODUCT(--(B30:S30=INT(B30:S30)),--(B30:S30&gt;0))/18*100%</f>
+        <v>0.222222222222222</v>
+      </c>
+      <c r="X30" s="4">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="Y30" s="4">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="Z30" s="4">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" ht="14" customHeight="1" spans="1:26">
+      <c r="A31" s="9">
         <v>30</v>
       </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="11">
-        <v>1</v>
-      </c>
-      <c r="D31" s="7"/>
-      <c r="E31" s="11">
-        <v>1</v>
-      </c>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="15">
+      <c r="B31" s="9"/>
+      <c r="C31" s="13">
+        <v>1</v>
+      </c>
+      <c r="D31" s="9"/>
+      <c r="E31" s="13">
+        <v>1</v>
+      </c>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="14">
         <v>2</v>
       </c>
-      <c r="J31" s="11">
-        <v>1</v>
-      </c>
-      <c r="K31" s="7"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7"/>
-      <c r="N31" s="11">
-        <v>1</v>
-      </c>
-      <c r="O31" s="7"/>
-      <c r="P31" s="7"/>
-      <c r="Q31" s="7"/>
-      <c r="R31" s="8"/>
-      <c r="S31" s="9"/>
+      <c r="J31" s="13">
+        <v>1</v>
+      </c>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
+      <c r="M31" s="9"/>
+      <c r="N31" s="13">
+        <v>1</v>
+      </c>
+      <c r="O31" s="9"/>
+      <c r="P31" s="9"/>
+      <c r="Q31" s="9"/>
+      <c r="R31" s="13">
+        <v>1</v>
+      </c>
+      <c r="S31" s="11"/>
       <c r="T31" s="2">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <f t="shared" si="3"/>
+        <v>7</v>
       </c>
       <c r="U31" s="3" cm="1">
         <f t="array" ref="U31">SUMPRODUCT(--(B31:S31=INT(B31:S31)),--(B31:S31&gt;0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V31" s="3" cm="1">
         <f t="array" ref="V31">MAX(FREQUENCY(IF((B31:S31=INT(B31:S31))*(B31:S31&gt;0),COLUMN(B31:S31)),IF((B31:S31&lt;&gt;INT(B31:S31))+(B31:S31&lt;=0),COLUMN(B31:S31))))</f>
         <v>2</v>
       </c>
-      <c r="W31" s="14" cm="1">
+      <c r="W31" s="12" cm="1">
         <f t="array" ref="W31">SUMPRODUCT(--(B31:S31=INT(B31:S31)),--(B31:S31&gt;0))/18*100%</f>
-        <v>0.277777777777778</v>
-      </c>
-    </row>
-    <row r="32" ht="14" customHeight="1" spans="1:23">
-      <c r="A32" s="7">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="X31" s="4">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="Y31" s="4">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="Z31" s="4">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" ht="14" customHeight="1" spans="1:26">
+      <c r="A32" s="9">
         <v>31</v>
       </c>
-      <c r="B32" s="11">
-        <v>1</v>
-      </c>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
-      <c r="N32" s="7"/>
-      <c r="O32" s="7"/>
-      <c r="P32" s="7"/>
-      <c r="Q32" s="7"/>
-      <c r="R32" s="8"/>
-      <c r="S32" s="9"/>
+      <c r="B32" s="13">
+        <v>1</v>
+      </c>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9"/>
+      <c r="M32" s="9"/>
+      <c r="N32" s="9"/>
+      <c r="O32" s="9"/>
+      <c r="P32" s="9"/>
+      <c r="Q32" s="9"/>
+      <c r="R32" s="10"/>
+      <c r="S32" s="11"/>
       <c r="T32" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="U32" s="3" cm="1">
@@ -4680,35 +5118,47 @@
         <f t="array" ref="V32">MAX(FREQUENCY(IF((B32:S32=INT(B32:S32))*(B32:S32&gt;0),COLUMN(B32:S32)),IF((B32:S32&lt;&gt;INT(B32:S32))+(B32:S32&lt;=0),COLUMN(B32:S32))))</f>
         <v>1</v>
       </c>
-      <c r="W32" s="10" t="str" cm="1">
-        <f t="array" ref="W32">TEXT(SUMPRODUCT(--(B32:S32=INT(B32:S32)),--(B32:S32&gt;0))/18*100%,0%)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" ht="14" customHeight="1" spans="1:23">
-      <c r="A33" s="7">
+      <c r="W32" s="12" cm="1">
+        <f t="array" ref="W32">SUMPRODUCT(--(B32:S32=INT(B32:S32)),--(B32:S32&gt;0))/18*100%</f>
+        <v>0.0555555555555556</v>
+      </c>
+      <c r="X32" s="4">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="Y32" s="4">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="Z32" s="4">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" ht="14" customHeight="1" spans="1:26">
+      <c r="A33" s="9">
         <v>32</v>
       </c>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
-      <c r="J33" s="7"/>
-      <c r="K33" s="7"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
-      <c r="N33" s="7"/>
-      <c r="O33" s="7"/>
-      <c r="P33" s="7"/>
-      <c r="Q33" s="7"/>
-      <c r="R33" s="8"/>
-      <c r="S33" s="9"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
+      <c r="M33" s="9"/>
+      <c r="N33" s="9"/>
+      <c r="O33" s="9"/>
+      <c r="P33" s="9"/>
+      <c r="Q33" s="9"/>
+      <c r="R33" s="10"/>
+      <c r="S33" s="11"/>
       <c r="T33" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U33" s="3" cm="1">
@@ -4719,35 +5169,47 @@
         <f t="array" ref="V33">MAX(FREQUENCY(IF((B33:S33=INT(B33:S33))*(B33:S33&gt;0),COLUMN(B33:S33)),IF((B33:S33&lt;&gt;INT(B33:S33))+(B33:S33&lt;=0),COLUMN(B33:S33))))</f>
         <v>0</v>
       </c>
-      <c r="W33" s="14" cm="1">
+      <c r="W33" s="12" cm="1">
         <f t="array" ref="W33">SUMPRODUCT(--(B33:S33=INT(B33:S33)),--(B33:S33&gt;0))/18*100%</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="34" ht="14" customHeight="1" spans="1:23">
-      <c r="A34" s="7">
+      <c r="X33" s="4">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="Y33" s="4">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="Z33" s="4">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34" ht="14" customHeight="1" spans="1:26">
+      <c r="A34" s="9">
         <v>33</v>
       </c>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="7"/>
-      <c r="K34" s="7"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="7"/>
-      <c r="N34" s="7"/>
-      <c r="O34" s="7"/>
-      <c r="P34" s="7"/>
-      <c r="Q34" s="7"/>
-      <c r="R34" s="8"/>
-      <c r="S34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="9"/>
+      <c r="M34" s="9"/>
+      <c r="N34" s="9"/>
+      <c r="O34" s="9"/>
+      <c r="P34" s="9"/>
+      <c r="Q34" s="9"/>
+      <c r="R34" s="10"/>
+      <c r="S34" s="11"/>
       <c r="T34" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U34" s="3" cm="1">
@@ -4758,35 +5220,47 @@
         <f t="array" ref="V34">MAX(FREQUENCY(IF((B34:S34=INT(B34:S34))*(B34:S34&gt;0),COLUMN(B34:S34)),IF((B34:S34&lt;&gt;INT(B34:S34))+(B34:S34&lt;=0),COLUMN(B34:S34))))</f>
         <v>0</v>
       </c>
-      <c r="W34" s="10" t="str" cm="1">
-        <f t="array" ref="W34">TEXT(SUMPRODUCT(--(B34:S34=INT(B34:S34)),--(B34:S34&gt;0))/18*100%,0%)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" ht="14" customHeight="1" spans="1:23">
-      <c r="A35" s="7">
+      <c r="W34" s="12" cm="1">
+        <f t="array" ref="W34">SUMPRODUCT(--(B34:S34=INT(B34:S34)),--(B34:S34&gt;0))/18*100%</f>
+        <v>0</v>
+      </c>
+      <c r="X34" s="4">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="Y34" s="4">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="Z34" s="4">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" ht="14" customHeight="1" spans="1:26">
+      <c r="A35" s="9">
         <v>34</v>
       </c>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="7"/>
-      <c r="K35" s="7"/>
-      <c r="L35" s="7"/>
-      <c r="M35" s="7"/>
-      <c r="N35" s="7"/>
-      <c r="O35" s="7"/>
-      <c r="P35" s="7"/>
-      <c r="Q35" s="7"/>
-      <c r="R35" s="8"/>
-      <c r="S35" s="9"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="9"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="9"/>
+      <c r="M35" s="9"/>
+      <c r="N35" s="9"/>
+      <c r="O35" s="9"/>
+      <c r="P35" s="9"/>
+      <c r="Q35" s="9"/>
+      <c r="R35" s="10"/>
+      <c r="S35" s="11"/>
       <c r="T35" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U35" s="3" cm="1">
@@ -4797,43 +5271,55 @@
         <f t="array" ref="V35">MAX(FREQUENCY(IF((B35:S35=INT(B35:S35))*(B35:S35&gt;0),COLUMN(B35:S35)),IF((B35:S35&lt;&gt;INT(B35:S35))+(B35:S35&lt;=0),COLUMN(B35:S35))))</f>
         <v>0</v>
       </c>
-      <c r="W35" s="14" cm="1">
+      <c r="W35" s="12" cm="1">
         <f t="array" ref="W35">SUMPRODUCT(--(B35:S35=INT(B35:S35)),--(B35:S35&gt;0))/18*100%</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="36" ht="14" customHeight="1" spans="1:23">
-      <c r="A36" s="7">
+      <c r="X35" s="4">
+        <f t="shared" ref="X35:X52" si="4">RANK(T35,T$2:T$52,0)</f>
         <v>35</v>
       </c>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="11">
-        <v>1</v>
-      </c>
-      <c r="I36" s="11">
-        <v>1</v>
-      </c>
-      <c r="J36" s="11">
-        <v>1</v>
-      </c>
-      <c r="K36" s="7"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="7"/>
-      <c r="N36" s="11">
-        <v>1</v>
-      </c>
-      <c r="O36" s="7"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="7"/>
-      <c r="R36" s="8"/>
-      <c r="S36" s="9"/>
+      <c r="Y35" s="4">
+        <f t="shared" ref="Y35:Y52" si="5">RANK(U35,U$2:U$52,0)</f>
+        <v>35</v>
+      </c>
+      <c r="Z35" s="4">
+        <f t="shared" ref="Z35:Z52" si="6">RANK(V35,V$2:V$52,0)</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" ht="14" customHeight="1" spans="1:26">
+      <c r="A36" s="9">
+        <v>35</v>
+      </c>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="13">
+        <v>1</v>
+      </c>
+      <c r="I36" s="13">
+        <v>1</v>
+      </c>
+      <c r="J36" s="13">
+        <v>1</v>
+      </c>
+      <c r="K36" s="9"/>
+      <c r="L36" s="9"/>
+      <c r="M36" s="9"/>
+      <c r="N36" s="13">
+        <v>1</v>
+      </c>
+      <c r="O36" s="9"/>
+      <c r="P36" s="9"/>
+      <c r="Q36" s="9"/>
+      <c r="R36" s="10"/>
+      <c r="S36" s="11"/>
       <c r="T36" s="2">
-        <f t="shared" ref="T36:T52" si="1">SUM(B36:S36)</f>
+        <f t="shared" ref="T36:T52" si="7">SUM(B36:S36)</f>
         <v>4</v>
       </c>
       <c r="U36" s="3" cm="1">
@@ -4844,37 +5330,49 @@
         <f t="array" ref="V36">MAX(FREQUENCY(IF((B36:S36=INT(B36:S36))*(B36:S36&gt;0),COLUMN(B36:S36)),IF((B36:S36&lt;&gt;INT(B36:S36))+(B36:S36&lt;=0),COLUMN(B36:S36))))</f>
         <v>3</v>
       </c>
-      <c r="W36" s="10" t="str" cm="1">
-        <f t="array" ref="W36">TEXT(SUMPRODUCT(--(B36:S36=INT(B36:S36)),--(B36:S36&gt;0))/18*100%,0%)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" ht="14" customHeight="1" spans="1:23">
-      <c r="A37" s="7">
+      <c r="W36" s="12" cm="1">
+        <f t="array" ref="W36">SUMPRODUCT(--(B36:S36=INT(B36:S36)),--(B36:S36&gt;0))/18*100%</f>
+        <v>0.222222222222222</v>
+      </c>
+      <c r="X36" s="4">
+        <f t="shared" si="4"/>
+        <v>13</v>
+      </c>
+      <c r="Y36" s="4">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="Z36" s="4">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" ht="14" customHeight="1" spans="1:26">
+      <c r="A37" s="9">
         <v>36</v>
       </c>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="15">
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="14">
         <v>2</v>
       </c>
-      <c r="J37" s="7"/>
-      <c r="K37" s="7"/>
-      <c r="L37" s="7"/>
-      <c r="M37" s="7"/>
-      <c r="N37" s="7"/>
-      <c r="O37" s="7"/>
-      <c r="P37" s="7"/>
-      <c r="Q37" s="7"/>
-      <c r="R37" s="8"/>
-      <c r="S37" s="9"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
+      <c r="M37" s="9"/>
+      <c r="N37" s="9"/>
+      <c r="O37" s="9"/>
+      <c r="P37" s="9"/>
+      <c r="Q37" s="9"/>
+      <c r="R37" s="10"/>
+      <c r="S37" s="11"/>
       <c r="T37" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="U37" s="3" cm="1">
@@ -4885,35 +5383,47 @@
         <f t="array" ref="V37">MAX(FREQUENCY(IF((B37:S37=INT(B37:S37))*(B37:S37&gt;0),COLUMN(B37:S37)),IF((B37:S37&lt;&gt;INT(B37:S37))+(B37:S37&lt;=0),COLUMN(B37:S37))))</f>
         <v>1</v>
       </c>
-      <c r="W37" s="14" cm="1">
+      <c r="W37" s="12" cm="1">
         <f t="array" ref="W37">SUMPRODUCT(--(B37:S37=INT(B37:S37)),--(B37:S37&gt;0))/18*100%</f>
         <v>0.0555555555555556</v>
       </c>
-    </row>
-    <row r="38" ht="14" customHeight="1" spans="1:23">
-      <c r="A38" s="7">
+      <c r="X37" s="4">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="Y37" s="4">
+        <f t="shared" si="5"/>
+        <v>27</v>
+      </c>
+      <c r="Z37" s="4">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" ht="14" customHeight="1" spans="1:26">
+      <c r="A38" s="9">
         <v>37</v>
       </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7"/>
-      <c r="J38" s="7"/>
-      <c r="K38" s="7"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="7"/>
-      <c r="N38" s="7"/>
-      <c r="O38" s="7"/>
-      <c r="P38" s="7"/>
-      <c r="Q38" s="7"/>
-      <c r="R38" s="8"/>
-      <c r="S38" s="9"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="9"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="9"/>
+      <c r="M38" s="9"/>
+      <c r="N38" s="9"/>
+      <c r="O38" s="9"/>
+      <c r="P38" s="9"/>
+      <c r="Q38" s="9"/>
+      <c r="R38" s="10"/>
+      <c r="S38" s="11"/>
       <c r="T38" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="U38" s="3" cm="1">
@@ -4924,96 +5434,122 @@
         <f t="array" ref="V38">MAX(FREQUENCY(IF((B38:S38=INT(B38:S38))*(B38:S38&gt;0),COLUMN(B38:S38)),IF((B38:S38&lt;&gt;INT(B38:S38))+(B38:S38&lt;=0),COLUMN(B38:S38))))</f>
         <v>0</v>
       </c>
-      <c r="W38" s="10" t="str" cm="1">
-        <f t="array" ref="W38">TEXT(SUMPRODUCT(--(B38:S38=INT(B38:S38)),--(B38:S38&gt;0))/18*100%,0%)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" ht="14" customHeight="1" spans="1:23">
-      <c r="A39" s="7">
+      <c r="W38" s="12" cm="1">
+        <f t="array" ref="W38">SUMPRODUCT(--(B38:S38=INT(B38:S38)),--(B38:S38&gt;0))/18*100%</f>
+        <v>0</v>
+      </c>
+      <c r="X38" s="4">
+        <f t="shared" si="4"/>
+        <v>35</v>
+      </c>
+      <c r="Y38" s="4">
+        <f t="shared" si="5"/>
+        <v>35</v>
+      </c>
+      <c r="Z38" s="4">
+        <f t="shared" si="6"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" ht="14" customHeight="1" spans="1:26">
+      <c r="A39" s="9">
         <v>38</v>
       </c>
-      <c r="B39" s="7"/>
-      <c r="C39" s="11">
-        <v>1</v>
-      </c>
-      <c r="D39" s="11">
-        <v>1</v>
-      </c>
-      <c r="E39" s="7"/>
-      <c r="F39" s="11">
-        <v>1</v>
-      </c>
-      <c r="G39" s="7"/>
-      <c r="H39" s="11">
-        <v>1</v>
-      </c>
-      <c r="I39" s="11">
-        <v>1</v>
-      </c>
-      <c r="J39" s="15">
+      <c r="B39" s="9"/>
+      <c r="C39" s="13">
+        <v>1</v>
+      </c>
+      <c r="D39" s="13">
+        <v>1</v>
+      </c>
+      <c r="E39" s="9"/>
+      <c r="F39" s="13">
+        <v>1</v>
+      </c>
+      <c r="G39" s="9"/>
+      <c r="H39" s="13">
+        <v>1</v>
+      </c>
+      <c r="I39" s="13">
+        <v>1</v>
+      </c>
+      <c r="J39" s="14">
         <v>2</v>
       </c>
-      <c r="K39" s="7"/>
-      <c r="L39" s="11">
-        <v>1</v>
-      </c>
-      <c r="M39" s="7"/>
-      <c r="N39" s="7"/>
-      <c r="O39" s="7"/>
-      <c r="P39" s="7"/>
-      <c r="Q39" s="11">
-        <v>1</v>
-      </c>
-      <c r="R39" s="12"/>
-      <c r="S39" s="13"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="13">
+        <v>1</v>
+      </c>
+      <c r="M39" s="9"/>
+      <c r="N39" s="9"/>
+      <c r="O39" s="9"/>
+      <c r="P39" s="9"/>
+      <c r="Q39" s="13">
+        <v>1</v>
+      </c>
+      <c r="R39" s="13">
+        <v>1</v>
+      </c>
+      <c r="S39" s="11"/>
       <c r="T39" s="2">
-        <f t="shared" si="1"/>
-        <v>9</v>
+        <f t="shared" si="7"/>
+        <v>10</v>
       </c>
       <c r="U39" s="3" cm="1">
         <f t="array" ref="U39">SUMPRODUCT(--(B39:S39=INT(B39:S39)),--(B39:S39&gt;0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V39" s="3" cm="1">
         <f t="array" ref="V39">MAX(FREQUENCY(IF((B39:S39=INT(B39:S39))*(B39:S39&gt;0),COLUMN(B39:S39)),IF((B39:S39&lt;&gt;INT(B39:S39))+(B39:S39&lt;=0),COLUMN(B39:S39))))</f>
         <v>3</v>
       </c>
-      <c r="W39" s="14" cm="1">
+      <c r="W39" s="12" cm="1">
         <f t="array" ref="W39">SUMPRODUCT(--(B39:S39=INT(B39:S39)),--(B39:S39&gt;0))/18*100%</f>
-        <v>0.444444444444444</v>
-      </c>
-    </row>
-    <row r="40" ht="14" customHeight="1" spans="1:23">
-      <c r="A40" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="X39" s="4">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="Y39" s="4">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="Z39" s="4">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" ht="14" customHeight="1" spans="1:26">
+      <c r="A40" s="9">
         <v>39</v>
       </c>
-      <c r="B40" s="11">
-        <v>1</v>
-      </c>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="7"/>
-      <c r="I40" s="7"/>
-      <c r="J40" s="11">
-        <v>1</v>
-      </c>
-      <c r="K40" s="7"/>
-      <c r="L40" s="7"/>
-      <c r="M40" s="7"/>
-      <c r="N40" s="7"/>
-      <c r="O40" s="7"/>
-      <c r="P40" s="7"/>
-      <c r="Q40" s="11">
-        <v>1</v>
-      </c>
-      <c r="R40" s="12"/>
-      <c r="S40" s="13"/>
+      <c r="B40" s="13">
+        <v>1</v>
+      </c>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="13">
+        <v>1</v>
+      </c>
+      <c r="K40" s="9"/>
+      <c r="L40" s="9"/>
+      <c r="M40" s="9"/>
+      <c r="N40" s="9"/>
+      <c r="O40" s="9"/>
+      <c r="P40" s="9"/>
+      <c r="Q40" s="13">
+        <v>1</v>
+      </c>
+      <c r="R40" s="10"/>
+      <c r="S40" s="11"/>
       <c r="T40" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="U40" s="3" cm="1">
@@ -5024,88 +5560,114 @@
         <f t="array" ref="V40">MAX(FREQUENCY(IF((B40:S40=INT(B40:S40))*(B40:S40&gt;0),COLUMN(B40:S40)),IF((B40:S40&lt;&gt;INT(B40:S40))+(B40:S40&lt;=0),COLUMN(B40:S40))))</f>
         <v>1</v>
       </c>
-      <c r="W40" s="10" t="str" cm="1">
-        <f t="array" ref="W40">TEXT(SUMPRODUCT(--(B40:S40=INT(B40:S40)),--(B40:S40&gt;0))/18*100%,0%)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" ht="14" customHeight="1" spans="1:23">
-      <c r="A41" s="7">
+      <c r="W40" s="12" cm="1">
+        <f t="array" ref="W40">SUMPRODUCT(--(B40:S40=INT(B40:S40)),--(B40:S40&gt;0))/18*100%</f>
+        <v>0.166666666666667</v>
+      </c>
+      <c r="X40" s="4">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="Y40" s="4">
+        <f t="shared" si="5"/>
+        <v>17</v>
+      </c>
+      <c r="Z40" s="4">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" ht="14" customHeight="1" spans="1:26">
+      <c r="A41" s="9">
         <v>40</v>
       </c>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="11">
-        <v>1</v>
-      </c>
-      <c r="I41" s="7"/>
-      <c r="J41" s="11">
-        <v>1</v>
-      </c>
-      <c r="K41" s="11">
-        <v>1</v>
-      </c>
-      <c r="L41" s="11">
-        <v>1</v>
-      </c>
-      <c r="M41" s="11">
-        <v>1</v>
-      </c>
-      <c r="N41" s="11">
-        <v>1</v>
-      </c>
-      <c r="O41" s="7"/>
-      <c r="P41" s="7"/>
-      <c r="Q41" s="11">
-        <v>1</v>
-      </c>
-      <c r="R41" s="12"/>
-      <c r="S41" s="13"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="13">
+        <v>1</v>
+      </c>
+      <c r="I41" s="9"/>
+      <c r="J41" s="13">
+        <v>1</v>
+      </c>
+      <c r="K41" s="13">
+        <v>1</v>
+      </c>
+      <c r="L41" s="13">
+        <v>1</v>
+      </c>
+      <c r="M41" s="13">
+        <v>1</v>
+      </c>
+      <c r="N41" s="13">
+        <v>1</v>
+      </c>
+      <c r="O41" s="9"/>
+      <c r="P41" s="9"/>
+      <c r="Q41" s="13">
+        <v>1</v>
+      </c>
+      <c r="R41" s="14">
+        <v>2</v>
+      </c>
+      <c r="S41" s="11"/>
       <c r="T41" s="2">
-        <f t="shared" si="1"/>
-        <v>7</v>
+        <f t="shared" si="7"/>
+        <v>9</v>
       </c>
       <c r="U41" s="3" cm="1">
         <f t="array" ref="U41">SUMPRODUCT(--(B41:S41=INT(B41:S41)),--(B41:S41&gt;0))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V41" s="3" cm="1">
         <f t="array" ref="V41">MAX(FREQUENCY(IF((B41:S41=INT(B41:S41))*(B41:S41&gt;0),COLUMN(B41:S41)),IF((B41:S41&lt;&gt;INT(B41:S41))+(B41:S41&lt;=0),COLUMN(B41:S41))))</f>
         <v>5</v>
       </c>
-      <c r="W41" s="14" cm="1">
+      <c r="W41" s="12" cm="1">
         <f t="array" ref="W41">SUMPRODUCT(--(B41:S41=INT(B41:S41)),--(B41:S41&gt;0))/18*100%</f>
-        <v>0.388888888888889</v>
-      </c>
-    </row>
-    <row r="42" ht="14" customHeight="1" spans="1:23">
-      <c r="A42" s="7">
+        <v>0.444444444444444</v>
+      </c>
+      <c r="X41" s="4">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="Y41" s="4">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="Z41" s="4">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" ht="14" customHeight="1" spans="1:26">
+      <c r="A42" s="9">
         <v>41</v>
       </c>
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="7"/>
-      <c r="I42" s="7"/>
-      <c r="J42" s="7"/>
-      <c r="K42" s="7"/>
-      <c r="L42" s="7"/>
-      <c r="M42" s="7"/>
-      <c r="N42" s="7"/>
-      <c r="O42" s="7"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="7"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="9"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
+      <c r="I42" s="9"/>
+      <c r="J42" s="9"/>
+      <c r="K42" s="9"/>
+      <c r="L42" s="9"/>
+      <c r="M42" s="9"/>
+      <c r="N42" s="9"/>
+      <c r="O42" s="9"/>
+      <c r="P42" s="9"/>
+      <c r="Q42" s="9"/>
+      <c r="R42" s="10"/>
+      <c r="S42" s="11"/>
       <c r="T42" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="U42" s="3" cm="1">
@@ -5116,92 +5678,118 @@
         <f t="array" ref="V42">MAX(FREQUENCY(IF((B42:S42=INT(B42:S42))*(B42:S42&gt;0),COLUMN(B42:S42)),IF((B42:S42&lt;&gt;INT(B42:S42))+(B42:S42&lt;=0),COLUMN(B42:S42))))</f>
         <v>0</v>
       </c>
-      <c r="W42" s="10" t="str" cm="1">
-        <f t="array" ref="W42">TEXT(SUMPRODUCT(--(B42:S42=INT(B42:S42)),--(B42:S42&gt;0))/18*100%,0%)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" ht="14" customHeight="1" spans="1:23">
-      <c r="A43" s="7">
+      <c r="W42" s="12" cm="1">
+        <f t="array" ref="W42">SUMPRODUCT(--(B42:S42=INT(B42:S42)),--(B42:S42&gt;0))/18*100%</f>
+        <v>0</v>
+      </c>
+      <c r="X42" s="4">
+        <f t="shared" si="4"/>
+        <v>35</v>
+      </c>
+      <c r="Y42" s="4">
+        <f t="shared" si="5"/>
+        <v>35</v>
+      </c>
+      <c r="Z42" s="4">
+        <f t="shared" si="6"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="43" ht="14" customHeight="1" spans="1:26">
+      <c r="A43" s="9">
         <v>42</v>
       </c>
-      <c r="B43" s="11">
-        <v>1</v>
-      </c>
-      <c r="C43" s="11">
-        <v>1</v>
-      </c>
-      <c r="D43" s="15">
+      <c r="B43" s="13">
+        <v>1</v>
+      </c>
+      <c r="C43" s="13">
+        <v>1</v>
+      </c>
+      <c r="D43" s="14">
         <v>2</v>
       </c>
-      <c r="E43" s="11">
-        <v>1</v>
-      </c>
-      <c r="F43" s="11">
-        <v>1</v>
-      </c>
-      <c r="G43" s="7"/>
-      <c r="H43" s="11">
-        <v>1</v>
-      </c>
-      <c r="I43" s="11">
-        <v>1</v>
-      </c>
-      <c r="J43" s="11">
-        <v>1</v>
-      </c>
-      <c r="K43" s="7"/>
-      <c r="L43" s="11">
-        <v>1</v>
-      </c>
-      <c r="M43" s="7"/>
-      <c r="N43" s="7"/>
-      <c r="O43" s="7"/>
-      <c r="P43" s="7"/>
-      <c r="Q43" s="7"/>
-      <c r="R43" s="8"/>
-      <c r="S43" s="9"/>
+      <c r="E43" s="13">
+        <v>1</v>
+      </c>
+      <c r="F43" s="13">
+        <v>1</v>
+      </c>
+      <c r="G43" s="9"/>
+      <c r="H43" s="13">
+        <v>1</v>
+      </c>
+      <c r="I43" s="13">
+        <v>1</v>
+      </c>
+      <c r="J43" s="13">
+        <v>1</v>
+      </c>
+      <c r="K43" s="9"/>
+      <c r="L43" s="13">
+        <v>1</v>
+      </c>
+      <c r="M43" s="9"/>
+      <c r="N43" s="9"/>
+      <c r="O43" s="9"/>
+      <c r="P43" s="9"/>
+      <c r="Q43" s="9"/>
+      <c r="R43" s="14">
+        <v>2</v>
+      </c>
+      <c r="S43" s="11"/>
       <c r="T43" s="2">
-        <f t="shared" si="1"/>
-        <v>10</v>
+        <f t="shared" si="7"/>
+        <v>12</v>
       </c>
       <c r="U43" s="3" cm="1">
         <f t="array" ref="U43">SUMPRODUCT(--(B43:S43=INT(B43:S43)),--(B43:S43&gt;0))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V43" s="3" cm="1">
         <f t="array" ref="V43">MAX(FREQUENCY(IF((B43:S43=INT(B43:S43))*(B43:S43&gt;0),COLUMN(B43:S43)),IF((B43:S43&lt;&gt;INT(B43:S43))+(B43:S43&lt;=0),COLUMN(B43:S43))))</f>
         <v>5</v>
       </c>
-      <c r="W43" s="14" cm="1">
+      <c r="W43" s="12" cm="1">
         <f t="array" ref="W43">SUMPRODUCT(--(B43:S43=INT(B43:S43)),--(B43:S43&gt;0))/18*100%</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="44" ht="14" customHeight="1" spans="1:23">
-      <c r="A44" s="7">
+        <v>0.555555555555556</v>
+      </c>
+      <c r="X43" s="4">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="Y43" s="4">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="Z43" s="4">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" ht="14" customHeight="1" spans="1:26">
+      <c r="A44" s="9">
         <v>43</v>
       </c>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
-      <c r="I44" s="7"/>
-      <c r="J44" s="7"/>
-      <c r="K44" s="7"/>
-      <c r="L44" s="7"/>
-      <c r="M44" s="7"/>
-      <c r="N44" s="7"/>
-      <c r="O44" s="7"/>
-      <c r="P44" s="7"/>
-      <c r="Q44" s="7"/>
-      <c r="R44" s="8"/>
-      <c r="S44" s="9"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+      <c r="J44" s="9"/>
+      <c r="K44" s="9"/>
+      <c r="L44" s="9"/>
+      <c r="M44" s="9"/>
+      <c r="N44" s="9"/>
+      <c r="O44" s="9"/>
+      <c r="P44" s="9"/>
+      <c r="Q44" s="9"/>
+      <c r="R44" s="10"/>
+      <c r="S44" s="11"/>
       <c r="T44" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="U44" s="3" cm="1">
@@ -5212,98 +5800,124 @@
         <f t="array" ref="V44">MAX(FREQUENCY(IF((B44:S44=INT(B44:S44))*(B44:S44&gt;0),COLUMN(B44:S44)),IF((B44:S44&lt;&gt;INT(B44:S44))+(B44:S44&lt;=0),COLUMN(B44:S44))))</f>
         <v>0</v>
       </c>
-      <c r="W44" s="10" t="str" cm="1">
-        <f t="array" ref="W44">TEXT(SUMPRODUCT(--(B44:S44=INT(B44:S44)),--(B44:S44&gt;0))/18*100%,0%)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" ht="14" customHeight="1" spans="1:23">
-      <c r="A45" s="7">
+      <c r="W44" s="12" cm="1">
+        <f t="array" ref="W44">SUMPRODUCT(--(B44:S44=INT(B44:S44)),--(B44:S44&gt;0))/18*100%</f>
+        <v>0</v>
+      </c>
+      <c r="X44" s="4">
+        <f t="shared" si="4"/>
+        <v>35</v>
+      </c>
+      <c r="Y44" s="4">
+        <f t="shared" si="5"/>
+        <v>35</v>
+      </c>
+      <c r="Z44" s="4">
+        <f t="shared" si="6"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="45" ht="14" customHeight="1" spans="1:26">
+      <c r="A45" s="9">
         <v>44</v>
       </c>
-      <c r="B45" s="11">
-        <v>1</v>
-      </c>
-      <c r="C45" s="11">
-        <v>1</v>
-      </c>
-      <c r="D45" s="11">
-        <v>1</v>
-      </c>
-      <c r="E45" s="11">
-        <v>1</v>
-      </c>
-      <c r="F45" s="7"/>
-      <c r="G45" s="17">
+      <c r="B45" s="13">
+        <v>1</v>
+      </c>
+      <c r="C45" s="13">
+        <v>1</v>
+      </c>
+      <c r="D45" s="13">
+        <v>1</v>
+      </c>
+      <c r="E45" s="13">
+        <v>1</v>
+      </c>
+      <c r="F45" s="9"/>
+      <c r="G45" s="15">
         <v>3</v>
       </c>
-      <c r="H45" s="11">
-        <v>1</v>
-      </c>
-      <c r="I45" s="11">
-        <v>1</v>
-      </c>
-      <c r="J45" s="15">
+      <c r="H45" s="13">
+        <v>1</v>
+      </c>
+      <c r="I45" s="13">
+        <v>1</v>
+      </c>
+      <c r="J45" s="14">
         <v>2</v>
       </c>
-      <c r="K45" s="15">
+      <c r="K45" s="14">
         <v>2</v>
       </c>
-      <c r="L45" s="11">
-        <v>1</v>
-      </c>
-      <c r="M45" s="15">
+      <c r="L45" s="13">
+        <v>1</v>
+      </c>
+      <c r="M45" s="14">
         <v>2</v>
       </c>
-      <c r="N45" s="15">
+      <c r="N45" s="14">
         <v>2</v>
       </c>
-      <c r="O45" s="7"/>
-      <c r="P45" s="7"/>
-      <c r="Q45" s="7"/>
-      <c r="R45" s="8"/>
-      <c r="S45" s="9"/>
+      <c r="O45" s="9"/>
+      <c r="P45" s="9"/>
+      <c r="Q45" s="9"/>
+      <c r="R45" s="13">
+        <v>1</v>
+      </c>
+      <c r="S45" s="11"/>
       <c r="T45" s="2">
-        <f t="shared" si="1"/>
-        <v>18</v>
+        <f t="shared" si="7"/>
+        <v>19</v>
       </c>
       <c r="U45" s="3" cm="1">
         <f t="array" ref="U45">SUMPRODUCT(--(B45:S45=INT(B45:S45)),--(B45:S45&gt;0))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V45" s="3" cm="1">
         <f t="array" ref="V45">MAX(FREQUENCY(IF((B45:S45=INT(B45:S45))*(B45:S45&gt;0),COLUMN(B45:S45)),IF((B45:S45&lt;&gt;INT(B45:S45))+(B45:S45&lt;=0),COLUMN(B45:S45))))</f>
         <v>8</v>
       </c>
-      <c r="W45" s="14" cm="1">
+      <c r="W45" s="12" cm="1">
         <f t="array" ref="W45">SUMPRODUCT(--(B45:S45=INT(B45:S45)),--(B45:S45&gt;0))/18*100%</f>
-        <v>0.666666666666667</v>
-      </c>
-    </row>
-    <row r="46" ht="14" customHeight="1" spans="1:23">
-      <c r="A46" s="7">
+        <v>0.722222222222222</v>
+      </c>
+      <c r="X45" s="4">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="Y45" s="4">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="Z45" s="4">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" ht="14" customHeight="1" spans="1:26">
+      <c r="A46" s="9">
         <v>45</v>
       </c>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="7"/>
-      <c r="I46" s="7"/>
-      <c r="J46" s="7"/>
-      <c r="K46" s="7"/>
-      <c r="L46" s="7"/>
-      <c r="M46" s="7"/>
-      <c r="N46" s="7"/>
-      <c r="O46" s="7"/>
-      <c r="P46" s="7"/>
-      <c r="Q46" s="7"/>
-      <c r="R46" s="8"/>
-      <c r="S46" s="9"/>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="9"/>
+      <c r="I46" s="9"/>
+      <c r="J46" s="9"/>
+      <c r="K46" s="9"/>
+      <c r="L46" s="9"/>
+      <c r="M46" s="9"/>
+      <c r="N46" s="9"/>
+      <c r="O46" s="9"/>
+      <c r="P46" s="9"/>
+      <c r="Q46" s="9"/>
+      <c r="R46" s="10"/>
+      <c r="S46" s="11"/>
       <c r="T46" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="U46" s="3" cm="1">
@@ -5314,84 +5928,110 @@
         <f t="array" ref="V46">MAX(FREQUENCY(IF((B46:S46=INT(B46:S46))*(B46:S46&gt;0),COLUMN(B46:S46)),IF((B46:S46&lt;&gt;INT(B46:S46))+(B46:S46&lt;=0),COLUMN(B46:S46))))</f>
         <v>0</v>
       </c>
-      <c r="W46" s="10" t="str" cm="1">
-        <f t="array" ref="W46">TEXT(SUMPRODUCT(--(B46:S46=INT(B46:S46)),--(B46:S46&gt;0))/18*100%,0%)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" ht="14" customHeight="1" spans="1:23">
-      <c r="A47" s="7">
+      <c r="W46" s="12" cm="1">
+        <f t="array" ref="W46">SUMPRODUCT(--(B46:S46=INT(B46:S46)),--(B46:S46&gt;0))/18*100%</f>
+        <v>0</v>
+      </c>
+      <c r="X46" s="4">
+        <f t="shared" si="4"/>
+        <v>35</v>
+      </c>
+      <c r="Y46" s="4">
+        <f t="shared" si="5"/>
+        <v>35</v>
+      </c>
+      <c r="Z46" s="4">
+        <f t="shared" si="6"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="47" ht="14" customHeight="1" spans="1:26">
+      <c r="A47" s="9">
         <v>46</v>
       </c>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="11">
-        <v>1</v>
-      </c>
-      <c r="H47" s="7"/>
-      <c r="I47" s="7"/>
-      <c r="J47" s="7"/>
-      <c r="K47" s="7"/>
-      <c r="L47" s="7"/>
-      <c r="M47" s="7"/>
-      <c r="N47" s="11">
-        <v>1</v>
-      </c>
-      <c r="O47" s="7"/>
-      <c r="P47" s="7"/>
-      <c r="Q47" s="11">
-        <v>1</v>
-      </c>
-      <c r="R47" s="12"/>
-      <c r="S47" s="13"/>
+      <c r="B47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="13">
+        <v>1</v>
+      </c>
+      <c r="H47" s="9"/>
+      <c r="I47" s="9"/>
+      <c r="J47" s="9"/>
+      <c r="K47" s="9"/>
+      <c r="L47" s="9"/>
+      <c r="M47" s="9"/>
+      <c r="N47" s="13">
+        <v>1</v>
+      </c>
+      <c r="O47" s="9"/>
+      <c r="P47" s="9"/>
+      <c r="Q47" s="13">
+        <v>1</v>
+      </c>
+      <c r="R47" s="13">
+        <v>1</v>
+      </c>
+      <c r="S47" s="11"/>
       <c r="T47" s="2">
-        <f t="shared" si="1"/>
-        <v>3</v>
+        <f t="shared" si="7"/>
+        <v>4</v>
       </c>
       <c r="U47" s="3" cm="1">
         <f t="array" ref="U47">SUMPRODUCT(--(B47:S47=INT(B47:S47)),--(B47:S47&gt;0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V47" s="3" cm="1">
         <f t="array" ref="V47">MAX(FREQUENCY(IF((B47:S47=INT(B47:S47))*(B47:S47&gt;0),COLUMN(B47:S47)),IF((B47:S47&lt;&gt;INT(B47:S47))+(B47:S47&lt;=0),COLUMN(B47:S47))))</f>
-        <v>1</v>
-      </c>
-      <c r="W47" s="14" cm="1">
+        <v>2</v>
+      </c>
+      <c r="W47" s="12" cm="1">
         <f t="array" ref="W47">SUMPRODUCT(--(B47:S47=INT(B47:S47)),--(B47:S47&gt;0))/18*100%</f>
-        <v>0.166666666666667</v>
-      </c>
-    </row>
-    <row r="48" ht="14" customHeight="1" spans="1:23">
-      <c r="A48" s="7">
+        <v>0.222222222222222</v>
+      </c>
+      <c r="X47" s="4">
+        <f t="shared" si="4"/>
+        <v>13</v>
+      </c>
+      <c r="Y47" s="4">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="Z47" s="4">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" ht="14" customHeight="1" spans="1:26">
+      <c r="A48" s="9">
         <v>47</v>
       </c>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="11">
-        <v>1</v>
-      </c>
-      <c r="I48" s="7"/>
-      <c r="J48" s="7"/>
-      <c r="K48" s="7"/>
-      <c r="L48" s="7"/>
-      <c r="M48" s="11">
-        <v>1</v>
-      </c>
-      <c r="N48" s="7"/>
-      <c r="O48" s="7"/>
-      <c r="P48" s="7"/>
-      <c r="Q48" s="7"/>
-      <c r="R48" s="8"/>
-      <c r="S48" s="9"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="13">
+        <v>1</v>
+      </c>
+      <c r="I48" s="9"/>
+      <c r="J48" s="9"/>
+      <c r="K48" s="9"/>
+      <c r="L48" s="9"/>
+      <c r="M48" s="13">
+        <v>1</v>
+      </c>
+      <c r="N48" s="9"/>
+      <c r="O48" s="9"/>
+      <c r="P48" s="9"/>
+      <c r="Q48" s="9"/>
+      <c r="R48" s="10"/>
+      <c r="S48" s="11"/>
       <c r="T48" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="U48" s="3" cm="1">
@@ -5402,76 +6042,102 @@
         <f t="array" ref="V48">MAX(FREQUENCY(IF((B48:S48=INT(B48:S48))*(B48:S48&gt;0),COLUMN(B48:S48)),IF((B48:S48&lt;&gt;INT(B48:S48))+(B48:S48&lt;=0),COLUMN(B48:S48))))</f>
         <v>1</v>
       </c>
-      <c r="W48" s="10" t="str" cm="1">
-        <f t="array" ref="W48">TEXT(SUMPRODUCT(--(B48:S48=INT(B48:S48)),--(B48:S48&gt;0))/18*100%,0%)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" ht="14" customHeight="1" spans="1:23">
-      <c r="A49" s="7">
+      <c r="W48" s="12" cm="1">
+        <f t="array" ref="W48">SUMPRODUCT(--(B48:S48=INT(B48:S48)),--(B48:S48&gt;0))/18*100%</f>
+        <v>0.111111111111111</v>
+      </c>
+      <c r="X48" s="4">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="Y48" s="4">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="Z48" s="4">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" ht="14" customHeight="1" spans="1:26">
+      <c r="A49" s="9">
         <v>48</v>
       </c>
-      <c r="B49" s="7"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="11">
-        <v>1</v>
-      </c>
-      <c r="F49" s="7"/>
-      <c r="G49" s="7"/>
-      <c r="H49" s="7"/>
-      <c r="I49" s="7"/>
-      <c r="J49" s="7"/>
-      <c r="K49" s="7"/>
-      <c r="L49" s="7"/>
-      <c r="M49" s="7"/>
-      <c r="N49" s="7"/>
-      <c r="O49" s="7"/>
-      <c r="P49" s="7"/>
-      <c r="Q49" s="7"/>
-      <c r="R49" s="7"/>
-      <c r="S49" s="18"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="13">
+        <v>1</v>
+      </c>
+      <c r="F49" s="9"/>
+      <c r="G49" s="9"/>
+      <c r="H49" s="9"/>
+      <c r="I49" s="9"/>
+      <c r="J49" s="9"/>
+      <c r="K49" s="9"/>
+      <c r="L49" s="9"/>
+      <c r="M49" s="9"/>
+      <c r="N49" s="9"/>
+      <c r="O49" s="9"/>
+      <c r="P49" s="9"/>
+      <c r="Q49" s="9"/>
+      <c r="R49" s="13">
+        <v>1</v>
+      </c>
+      <c r="S49" s="16"/>
       <c r="T49" s="2">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f t="shared" si="7"/>
+        <v>2</v>
       </c>
       <c r="U49" s="3" cm="1">
         <f t="array" ref="U49">SUMPRODUCT(--(B49:S49=INT(B49:S49)),--(B49:S49&gt;0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V49" s="3" cm="1">
         <f t="array" ref="V49">MAX(FREQUENCY(IF((B49:S49=INT(B49:S49))*(B49:S49&gt;0),COLUMN(B49:S49)),IF((B49:S49&lt;&gt;INT(B49:S49))+(B49:S49&lt;=0),COLUMN(B49:S49))))</f>
         <v>1</v>
       </c>
-      <c r="W49" s="14" cm="1">
+      <c r="W49" s="12" cm="1">
         <f t="array" ref="W49">SUMPRODUCT(--(B49:S49=INT(B49:S49)),--(B49:S49&gt;0))/18*100%</f>
-        <v>0.0555555555555556</v>
-      </c>
-    </row>
-    <row r="50" ht="14" customHeight="1" spans="1:23">
-      <c r="A50" s="7">
+        <v>0.111111111111111</v>
+      </c>
+      <c r="X49" s="4">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="Y49" s="4">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="Z49" s="4">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" ht="14" customHeight="1" spans="1:26">
+      <c r="A50" s="9">
         <v>49</v>
       </c>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="7"/>
-      <c r="I50" s="7"/>
-      <c r="J50" s="7"/>
-      <c r="K50" s="7"/>
-      <c r="L50" s="7"/>
-      <c r="M50" s="7"/>
-      <c r="N50" s="7"/>
-      <c r="O50" s="7"/>
-      <c r="P50" s="7"/>
-      <c r="Q50" s="7"/>
-      <c r="R50" s="7"/>
-      <c r="S50" s="18"/>
+      <c r="B50" s="9"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="9"/>
+      <c r="F50" s="9"/>
+      <c r="G50" s="9"/>
+      <c r="H50" s="9"/>
+      <c r="I50" s="9"/>
+      <c r="J50" s="9"/>
+      <c r="K50" s="9"/>
+      <c r="L50" s="9"/>
+      <c r="M50" s="9"/>
+      <c r="N50" s="9"/>
+      <c r="O50" s="9"/>
+      <c r="P50" s="9"/>
+      <c r="Q50" s="9"/>
+      <c r="R50" s="9"/>
+      <c r="S50" s="16"/>
       <c r="T50" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="U50" s="3" cm="1">
@@ -5482,35 +6148,47 @@
         <f t="array" ref="V50">MAX(FREQUENCY(IF((B50:S50=INT(B50:S50))*(B50:S50&gt;0),COLUMN(B50:S50)),IF((B50:S50&lt;&gt;INT(B50:S50))+(B50:S50&lt;=0),COLUMN(B50:S50))))</f>
         <v>0</v>
       </c>
-      <c r="W50" s="10" t="str" cm="1">
-        <f t="array" ref="W50">TEXT(SUMPRODUCT(--(B50:S50=INT(B50:S50)),--(B50:S50&gt;0))/18*100%,0%)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" ht="14" customHeight="1" spans="1:23">
-      <c r="A51" s="7">
+      <c r="W50" s="12" cm="1">
+        <f t="array" ref="W50">SUMPRODUCT(--(B50:S50=INT(B50:S50)),--(B50:S50&gt;0))/18*100%</f>
+        <v>0</v>
+      </c>
+      <c r="X50" s="4">
+        <f t="shared" si="4"/>
+        <v>35</v>
+      </c>
+      <c r="Y50" s="4">
+        <f t="shared" si="5"/>
+        <v>35</v>
+      </c>
+      <c r="Z50" s="4">
+        <f t="shared" si="6"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51" ht="14" customHeight="1" spans="1:26">
+      <c r="A51" s="9">
         <v>50</v>
       </c>
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="7"/>
-      <c r="I51" s="7"/>
-      <c r="J51" s="7"/>
-      <c r="K51" s="7"/>
-      <c r="L51" s="7"/>
-      <c r="M51" s="7"/>
-      <c r="N51" s="7"/>
-      <c r="O51" s="7"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="7"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="18"/>
+      <c r="B51" s="9"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="9"/>
+      <c r="F51" s="9"/>
+      <c r="G51" s="9"/>
+      <c r="H51" s="9"/>
+      <c r="I51" s="9"/>
+      <c r="J51" s="9"/>
+      <c r="K51" s="9"/>
+      <c r="L51" s="9"/>
+      <c r="M51" s="9"/>
+      <c r="N51" s="9"/>
+      <c r="O51" s="9"/>
+      <c r="P51" s="9"/>
+      <c r="Q51" s="9"/>
+      <c r="R51" s="9"/>
+      <c r="S51" s="16"/>
       <c r="T51" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="U51" s="3" cm="1">
@@ -5521,35 +6199,47 @@
         <f t="array" ref="V51">MAX(FREQUENCY(IF((B51:S51=INT(B51:S51))*(B51:S51&gt;0),COLUMN(B51:S51)),IF((B51:S51&lt;&gt;INT(B51:S51))+(B51:S51&lt;=0),COLUMN(B51:S51))))</f>
         <v>0</v>
       </c>
-      <c r="W51" s="14" cm="1">
+      <c r="W51" s="12" cm="1">
         <f t="array" ref="W51">SUMPRODUCT(--(B51:S51=INT(B51:S51)),--(B51:S51&gt;0))/18*100%</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="52" ht="14" customHeight="1" spans="1:23">
-      <c r="A52" s="7">
+      <c r="X51" s="4">
+        <f t="shared" si="4"/>
+        <v>35</v>
+      </c>
+      <c r="Y51" s="4">
+        <f t="shared" si="5"/>
+        <v>35</v>
+      </c>
+      <c r="Z51" s="4">
+        <f t="shared" si="6"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="52" ht="14" customHeight="1" spans="1:26">
+      <c r="A52" s="9">
         <v>51</v>
       </c>
-      <c r="B52" s="7"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="7"/>
-      <c r="I52" s="7"/>
-      <c r="J52" s="7"/>
-      <c r="K52" s="7"/>
-      <c r="L52" s="7"/>
-      <c r="M52" s="7"/>
-      <c r="N52" s="7"/>
-      <c r="O52" s="7"/>
-      <c r="P52" s="7"/>
-      <c r="Q52" s="7"/>
-      <c r="R52" s="7"/>
-      <c r="S52" s="18"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="9"/>
+      <c r="F52" s="9"/>
+      <c r="G52" s="9"/>
+      <c r="H52" s="9"/>
+      <c r="I52" s="9"/>
+      <c r="J52" s="9"/>
+      <c r="K52" s="9"/>
+      <c r="L52" s="9"/>
+      <c r="M52" s="9"/>
+      <c r="N52" s="9"/>
+      <c r="O52" s="9"/>
+      <c r="P52" s="9"/>
+      <c r="Q52" s="9"/>
+      <c r="R52" s="9"/>
+      <c r="S52" s="16"/>
       <c r="T52" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="U52" s="3" cm="1">
@@ -5560,13 +6250,28 @@
         <f t="array" ref="V52">MAX(FREQUENCY(IF((B52:S52=INT(B52:S52))*(B52:S52&gt;0),COLUMN(B52:S52)),IF((B52:S52&lt;&gt;INT(B52:S52))+(B52:S52&lt;=0),COLUMN(B52:S52))))</f>
         <v>0</v>
       </c>
-      <c r="W52" s="10" t="str" cm="1">
-        <f t="array" ref="W52">TEXT(SUMPRODUCT(--(B52:S52=INT(B52:S52)),--(B52:S52&gt;0))/18*100%,0%)</f>
-        <v>0</v>
+      <c r="W52" s="12" cm="1">
+        <f t="array" ref="W52">SUMPRODUCT(--(B52:S52=INT(B52:S52)),--(B52:S52&gt;0))/18*100%</f>
+        <v>0</v>
+      </c>
+      <c r="X52" s="4">
+        <f t="shared" si="4"/>
+        <v>35</v>
+      </c>
+      <c r="Y52" s="4">
+        <f t="shared" si="5"/>
+        <v>35</v>
+      </c>
+      <c r="Z52" s="4">
+        <f t="shared" si="6"/>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:V1 X1:Z1 A2:Z52" formulaRange="1" unlockedFormula="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10480" activeTab="4"/>
+    <workbookView windowWidth="20750" windowHeight="10480" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="学生、老师" sheetId="5" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="225">
   <si>
     <t>姓名</t>
   </si>
@@ -691,6 +691,15 @@
     <t>崔母将崔玩手机事情告诉刘老师，手机被收，次日谈话</t>
   </si>
   <si>
+    <t>历史上的冤狱</t>
+  </si>
+  <si>
+    <t>八上12.31</t>
+  </si>
+  <si>
+    <t>文艺汇演，孔转头被调换位置。理由：转到后面讲话。孔：没讲话，只是转到后面看了一眼。刘：闭嘴。随后请张佳欣“作证”：是那个女生吗？-是。</t>
+  </si>
+  <si>
     <t>政治啧</t>
   </si>
   <si>
@@ -700,25 +709,32 @@
     <t>12月</t>
   </si>
   <si>
-    <t>被请次数</t>
-  </si>
-  <si>
-    <t>被请节数</t>
-  </si>
-  <si>
-    <t>最高连击</t>
-  </si>
-  <si>
-    <t>被请概率</t>
-  </si>
-  <si>
-    <t>次数排名</t>
-  </si>
-  <si>
-    <t>节数排名</t>
-  </si>
-  <si>
-    <t>连击排名</t>
+    <t>被请
+次数</t>
+  </si>
+  <si>
+    <t>被请
+节数</t>
+  </si>
+  <si>
+    <t>最高
+连击</t>
+  </si>
+  <si>
+    <t>被请
+概率</t>
+  </si>
+  <si>
+    <t>次数
+排名</t>
+  </si>
+  <si>
+    <t>节数
+排名</t>
+  </si>
+  <si>
+    <t>连击
+排名</t>
   </si>
 </sst>
 </file>
@@ -911,7 +927,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="44">
+  <fills count="45">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -950,19 +966,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -987,12 +997,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1046,6 +1050,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1064,6 +1074,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1077,6 +1093,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1368,7 +1390,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1392,16 +1414,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1410,30 +1432,30 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -1443,52 +1465,52 @@
     <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
@@ -1504,14 +1526,14 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1521,36 +1543,43 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1583,64 +1612,58 @@
     <xf numFmtId="20" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2983,163 +3006,174 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="35.1818181818182" style="18" customWidth="1"/>
-    <col min="2" max="2" width="16.9090909090909" style="18" customWidth="1"/>
-    <col min="3" max="3" width="50.0909090909091" style="23" customWidth="1"/>
-    <col min="4" max="16384" width="8.72727272727273" style="18"/>
+    <col min="1" max="1" width="35.1818181818182" style="20" customWidth="1"/>
+    <col min="2" max="2" width="16.9090909090909" style="20" customWidth="1"/>
+    <col min="3" max="3" width="50.0909090909091" style="25" customWidth="1"/>
+    <col min="4" max="16384" width="8.72727272727273" style="20"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="25" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="25" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="25" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="4" ht="28" spans="1:3">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="25" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="5" ht="42" spans="1:3">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="26" t="s">
         <v>187</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="25" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="6" ht="56" spans="1:3">
-      <c r="A6" s="25"/>
-      <c r="B6" s="18" t="s">
+      <c r="A6" s="27"/>
+      <c r="B6" s="20" t="s">
         <v>190</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="25" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="7" ht="28" spans="1:3">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="25" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="8" ht="28" spans="1:3">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="20" t="s">
         <v>195</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="25" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="20" t="s">
         <v>199</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="25" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="20" t="s">
         <v>201</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="25" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="20" t="s">
         <v>204</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="28">
         <v>0.440972222222222</v>
       </c>
     </row>
     <row r="12" ht="28" spans="1:3">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="20" t="s">
         <v>206</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="25" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="28"/>
-      <c r="B13" s="18" t="s">
+      <c r="A13" s="24"/>
+      <c r="B13" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="25" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="20" t="s">
         <v>210</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="25" t="s">
         <v>211</v>
+      </c>
+    </row>
+    <row r="15" ht="42" spans="1:3">
+      <c r="A15" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -3158,135 +3192,135 @@
   <dimension ref="A1:D15"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="9.18181818181818" style="9"/>
-    <col min="2" max="2" width="3.54545454545455" style="17" customWidth="1"/>
-    <col min="3" max="16384" width="8.72727272727273" style="18"/>
+    <col min="1" max="1" width="9.18181818181818" style="13"/>
+    <col min="2" max="2" width="3.54545454545455" style="19" customWidth="1"/>
+    <col min="3" max="16384" width="8.72727272727273" style="20"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="C1" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>213</v>
+      <c r="C1" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="20">
+      <c r="A2" s="22">
         <v>2025.1</v>
       </c>
-      <c r="B2" s="17">
+      <c r="B2" s="19">
         <v>11</v>
       </c>
-      <c r="C2" s="19">
+      <c r="C2" s="21">
         <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="21"/>
-      <c r="B3" s="17">
+      <c r="A3" s="23"/>
+      <c r="B3" s="19">
         <v>15</v>
       </c>
-      <c r="C3" s="19">
+      <c r="C3" s="21">
         <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="21"/>
-      <c r="B4" s="17">
+      <c r="A4" s="23"/>
+      <c r="B4" s="19">
         <v>17</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="21">
         <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="21"/>
-      <c r="B5" s="17">
+      <c r="A5" s="23"/>
+      <c r="B5" s="19">
         <v>22</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="21">
         <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="21"/>
-      <c r="B6" s="17">
+      <c r="A6" s="23"/>
+      <c r="B6" s="19">
         <v>24</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="21">
         <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="21"/>
-      <c r="B7" s="17">
+      <c r="A7" s="23"/>
+      <c r="B7" s="19">
         <v>29</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="21">
         <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="22"/>
-      <c r="B8" s="17">
+      <c r="A8" s="24"/>
+      <c r="B8" s="19">
         <v>31</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="21">
         <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="20">
+      <c r="A9" s="22">
         <v>2025.11</v>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="19">
         <v>5</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="21">
         <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="21"/>
-      <c r="B10" s="17">
+      <c r="A10" s="23"/>
+      <c r="B10" s="19">
         <v>7</v>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="21">
         <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="22"/>
-      <c r="B11" s="17">
+      <c r="A11" s="24"/>
+      <c r="B11" s="19">
         <v>14</v>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="21">
         <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="9">
+      <c r="A12" s="13">
         <v>2025.12</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="19">
         <v>26</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="21">
         <v>225</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="20">
         <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="C13" s="19"/>
+      <c r="C13" s="21"/>
     </row>
     <row r="14" spans="1:4">
-      <c r="C14" s="19"/>
+      <c r="C14" s="21"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="C15" s="19"/>
+      <c r="C15" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3300,21 +3334,23 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:Z52"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="4.07272727272727" customWidth="1"/>
     <col min="2" max="19" width="5.14545454545455" customWidth="1"/>
-    <col min="20" max="20" width="8.72727272727273" style="2"/>
-    <col min="21" max="22" width="8.72727272727273" style="3"/>
-    <col min="23" max="23" width="8.53636363636364" style="3" customWidth="1"/>
-    <col min="24" max="26" width="8.72727272727273" style="4"/>
+    <col min="20" max="20" width="4.81818181818182" style="2" customWidth="1"/>
+    <col min="21" max="22" width="4.81818181818182" style="3" customWidth="1"/>
+    <col min="23" max="23" width="6.63636363636364" style="3" customWidth="1"/>
+    <col min="24" max="26" width="4.81818181818182" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="14" spans="1:26">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:26">
       <c r="A1" s="5" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B1" s="5">
         <v>5</v>
@@ -3371,47 +3407,47 @@
         <v>31</v>
       </c>
       <c r="T1" s="7" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="U1" s="7" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="V1" s="7" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="W1" s="7" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="X1" s="8" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Y1" s="8" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2" ht="14" customHeight="1" spans="1:26">
       <c r="A2" s="9">
         <v>1</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
       <c r="R2" s="10"/>
       <c r="S2" s="11"/>
       <c r="T2" s="2">
@@ -3444,48 +3480,50 @@
       </c>
     </row>
     <row r="3" ht="14" customHeight="1" spans="1:26">
-      <c r="A3" s="9">
+      <c r="A3" s="13">
         <v>2</v>
       </c>
-      <c r="B3" s="13">
-        <v>1</v>
-      </c>
-      <c r="C3" s="13">
-        <v>1</v>
-      </c>
-      <c r="D3" s="13">
-        <v>1</v>
-      </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="13">
-        <v>1</v>
-      </c>
-      <c r="J3" s="13">
-        <v>1</v>
-      </c>
-      <c r="K3" s="13">
-        <v>1</v>
-      </c>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="13">
+      <c r="B3" s="10">
+        <v>1</v>
+      </c>
+      <c r="C3" s="10">
+        <v>1</v>
+      </c>
+      <c r="D3" s="10">
+        <v>1</v>
+      </c>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10">
+        <v>1</v>
+      </c>
+      <c r="J3" s="10">
+        <v>1</v>
+      </c>
+      <c r="K3" s="10">
+        <v>1</v>
+      </c>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10">
         <v>1</v>
       </c>
       <c r="R3" s="10"/>
-      <c r="S3" s="11"/>
+      <c r="S3" s="11">
+        <v>2</v>
+      </c>
       <c r="T3" s="2">
         <f>SUM(B3:S3)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U3" s="3" cm="1">
         <f t="array" ref="U3">SUMPRODUCT(--(B3:S3=INT(B3:S3)),--(B3:S3&gt;0))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V3" s="3" cm="1">
         <f t="array" ref="V3">MAX(FREQUENCY(IF((B3:S3=INT(B3:S3))*(B3:S3&gt;0),COLUMN(B3:S3)),IF((B3:S3&lt;&gt;INT(B3:S3))+(B3:S3&lt;=0),COLUMN(B3:S3))))</f>
@@ -3493,15 +3531,15 @@
       </c>
       <c r="W3" s="12" cm="1">
         <f t="array" ref="W3">SUMPRODUCT(--(B3:S3=INT(B3:S3)),--(B3:S3&gt;0))/18*100%</f>
-        <v>0.388888888888889</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="X3" s="4">
         <f t="shared" ref="X3:X34" si="0">RANK(T3,T$2:T$52,0)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y3" s="4">
         <f t="shared" ref="Y3:Y34" si="1">RANK(U3,U$2:U$52,0)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z3" s="4">
         <f t="shared" ref="Z3:Z34" si="2">RANK(V3,V$2:V$52,0)</f>
@@ -3509,27 +3547,27 @@
       </c>
     </row>
     <row r="4" ht="14" customHeight="1" spans="1:26">
-      <c r="A4" s="9">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="13">
-        <v>1</v>
-      </c>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10">
+        <v>1</v>
+      </c>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
       <c r="R4" s="10"/>
       <c r="S4" s="11"/>
       <c r="T4" s="2">
@@ -3562,27 +3600,27 @@
       </c>
     </row>
     <row r="5" ht="14" customHeight="1" spans="1:26">
-      <c r="A5" s="9">
+      <c r="A5" s="13">
         <v>4</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="13">
-        <v>1</v>
-      </c>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="13">
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10">
+        <v>1</v>
+      </c>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10">
         <v>1</v>
       </c>
       <c r="R5" s="10"/>
@@ -3605,11 +3643,11 @@
       </c>
       <c r="X5" s="4">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y5" s="4">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Z5" s="4">
         <f t="shared" si="2"/>
@@ -3617,31 +3655,31 @@
       </c>
     </row>
     <row r="6" ht="14" customHeight="1" spans="1:26">
-      <c r="A6" s="9">
+      <c r="A6" s="13">
         <v>5</v>
       </c>
-      <c r="B6" s="13">
-        <v>1</v>
-      </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="14">
+      <c r="B6" s="10">
+        <v>1</v>
+      </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10">
         <v>2</v>
       </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="13">
-        <v>1</v>
-      </c>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="9"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10">
+        <v>1</v>
+      </c>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
       <c r="R6" s="10"/>
       <c r="S6" s="11"/>
       <c r="T6" s="2">
@@ -3662,7 +3700,7 @@
       </c>
       <c r="X6" s="4">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y6" s="4">
         <f t="shared" si="1"/>
@@ -3674,58 +3712,60 @@
       </c>
     </row>
     <row r="7" ht="14" customHeight="1" spans="1:26">
-      <c r="A7" s="9">
+      <c r="A7" s="13">
         <v>6</v>
       </c>
-      <c r="B7" s="13">
-        <v>1</v>
-      </c>
-      <c r="C7" s="13">
-        <v>1</v>
-      </c>
-      <c r="D7" s="13">
-        <v>1</v>
-      </c>
-      <c r="E7" s="13">
-        <v>1</v>
-      </c>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="13">
-        <v>1</v>
-      </c>
-      <c r="I7" s="13">
-        <v>1</v>
-      </c>
-      <c r="J7" s="13">
-        <v>1</v>
-      </c>
-      <c r="K7" s="9"/>
-      <c r="L7" s="13">
-        <v>1</v>
-      </c>
-      <c r="M7" s="9"/>
-      <c r="N7" s="13">
-        <v>1</v>
-      </c>
-      <c r="O7" s="9"/>
-      <c r="P7" s="13">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="13">
-        <v>1</v>
-      </c>
-      <c r="R7" s="13">
-        <v>1</v>
-      </c>
-      <c r="S7" s="11"/>
+      <c r="B7" s="10">
+        <v>1</v>
+      </c>
+      <c r="C7" s="10">
+        <v>1</v>
+      </c>
+      <c r="D7" s="10">
+        <v>1</v>
+      </c>
+      <c r="E7" s="10">
+        <v>1</v>
+      </c>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10">
+        <v>1</v>
+      </c>
+      <c r="I7" s="10">
+        <v>1</v>
+      </c>
+      <c r="J7" s="10">
+        <v>1</v>
+      </c>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10">
+        <v>1</v>
+      </c>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10">
+        <v>1</v>
+      </c>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="10">
+        <v>1</v>
+      </c>
+      <c r="R7" s="10">
+        <v>1</v>
+      </c>
+      <c r="S7" s="11">
+        <v>1</v>
+      </c>
       <c r="T7" s="2">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U7" s="3" cm="1">
         <f t="array" ref="U7">SUMPRODUCT(--(B7:S7=INT(B7:S7)),--(B7:S7&gt;0))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V7" s="3" cm="1">
         <f t="array" ref="V7">MAX(FREQUENCY(IF((B7:S7=INT(B7:S7))*(B7:S7&gt;0),COLUMN(B7:S7)),IF((B7:S7&lt;&gt;INT(B7:S7))+(B7:S7&lt;=0),COLUMN(B7:S7))))</f>
@@ -3733,7 +3773,7 @@
       </c>
       <c r="W7" s="12" cm="1">
         <f t="array" ref="W7">SUMPRODUCT(--(B7:S7=INT(B7:S7)),--(B7:S7&gt;0))/18*100%</f>
-        <v>0.666666666666667</v>
+        <v>0.722222222222222</v>
       </c>
       <c r="X7" s="4">
         <f t="shared" si="0"/>
@@ -3749,46 +3789,48 @@
       </c>
     </row>
     <row r="8" ht="14" customHeight="1" spans="1:26">
-      <c r="A8" s="9">
+      <c r="A8" s="13">
         <v>7</v>
       </c>
-      <c r="B8" s="13">
-        <v>1</v>
-      </c>
-      <c r="C8" s="9"/>
+      <c r="B8" s="10">
+        <v>1</v>
+      </c>
+      <c r="C8" s="10"/>
       <c r="D8" s="10"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="13">
-        <v>1</v>
-      </c>
-      <c r="I8" s="13">
-        <v>1</v>
-      </c>
-      <c r="J8" s="13">
-        <v>1</v>
-      </c>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="13">
-        <v>1</v>
-      </c>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="9"/>
-      <c r="Q8" s="9"/>
-      <c r="R8" s="13">
-        <v>1</v>
-      </c>
-      <c r="S8" s="11"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10">
+        <v>1</v>
+      </c>
+      <c r="I8" s="10">
+        <v>1</v>
+      </c>
+      <c r="J8" s="10">
+        <v>1</v>
+      </c>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10">
+        <v>1</v>
+      </c>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10">
+        <v>1</v>
+      </c>
+      <c r="S8" s="11">
+        <v>1</v>
+      </c>
       <c r="T8" s="2">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U8" s="3" cm="1">
         <f t="array" ref="U8">SUMPRODUCT(--(B8:S8=INT(B8:S8)),--(B8:S8&gt;0))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V8" s="3" cm="1">
         <f t="array" ref="V8">MAX(FREQUENCY(IF((B8:S8=INT(B8:S8))*(B8:S8&gt;0),COLUMN(B8:S8)),IF((B8:S8&lt;&gt;INT(B8:S8))+(B8:S8&lt;=0),COLUMN(B8:S8))))</f>
@@ -3796,7 +3838,7 @@
       </c>
       <c r="W8" s="12" cm="1">
         <f t="array" ref="W8">SUMPRODUCT(--(B8:S8=INT(B8:S8)),--(B8:S8&gt;0))/18*100%</f>
-        <v>0.333333333333333</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="X8" s="4">
         <f t="shared" si="0"/>
@@ -3815,22 +3857,22 @@
       <c r="A9" s="9">
         <v>8</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="9"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
       <c r="R9" s="10"/>
       <c r="S9" s="11"/>
       <c r="T9" s="2">
@@ -3863,29 +3905,29 @@
       </c>
     </row>
     <row r="10" ht="14" customHeight="1" spans="1:26">
-      <c r="A10" s="9">
+      <c r="A10" s="13">
         <v>9</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="13">
-        <v>1</v>
-      </c>
-      <c r="M10" s="9"/>
-      <c r="N10" s="13">
-        <v>1</v>
-      </c>
-      <c r="O10" s="9"/>
-      <c r="P10" s="9"/>
-      <c r="Q10" s="13">
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10">
+        <v>1</v>
+      </c>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10">
+        <v>1</v>
+      </c>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10">
         <v>1</v>
       </c>
       <c r="R10" s="10"/>
@@ -3908,7 +3950,7 @@
       </c>
       <c r="X10" s="4">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y10" s="4">
         <f t="shared" si="1"/>
@@ -3920,27 +3962,27 @@
       </c>
     </row>
     <row r="11" ht="14" customHeight="1" spans="1:26">
-      <c r="A11" s="9">
+      <c r="A11" s="13">
         <v>10</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="13">
-        <v>1</v>
-      </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="9"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10">
+        <v>1</v>
+      </c>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10"/>
       <c r="R11" s="10"/>
       <c r="S11" s="11"/>
       <c r="T11" s="2">
@@ -3973,33 +4015,33 @@
       </c>
     </row>
     <row r="12" ht="14" customHeight="1" spans="1:26">
-      <c r="A12" s="9">
+      <c r="A12" s="13">
         <v>11</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="13">
-        <v>1</v>
-      </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="13">
-        <v>1</v>
-      </c>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="13">
-        <v>1</v>
-      </c>
-      <c r="M12" s="9"/>
-      <c r="N12" s="13">
-        <v>1</v>
-      </c>
-      <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="13">
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10">
+        <v>1</v>
+      </c>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10">
+        <v>1</v>
+      </c>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10">
+        <v>1</v>
+      </c>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10">
+        <v>1</v>
+      </c>
+      <c r="O12" s="10"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10">
         <v>1</v>
       </c>
       <c r="R12" s="10"/>
@@ -4022,7 +4064,7 @@
       </c>
       <c r="X12" s="4">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Y12" s="4">
         <f t="shared" si="1"/>
@@ -4034,27 +4076,27 @@
       </c>
     </row>
     <row r="13" ht="14" customHeight="1" spans="1:26">
-      <c r="A13" s="9">
+      <c r="A13" s="13">
         <v>12</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="13">
-        <v>1</v>
-      </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="9"/>
-      <c r="Q13" s="9"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10">
+        <v>1</v>
+      </c>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10"/>
       <c r="R13" s="10"/>
       <c r="S13" s="11"/>
       <c r="T13" s="2">
@@ -4087,33 +4129,33 @@
       </c>
     </row>
     <row r="14" ht="14" customHeight="1" spans="1:26">
-      <c r="A14" s="9">
+      <c r="A14" s="13">
         <v>13</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="13">
-        <v>1</v>
-      </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="13">
-        <v>1</v>
-      </c>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="13">
-        <v>1</v>
-      </c>
-      <c r="M14" s="13">
-        <v>1</v>
-      </c>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="9"/>
-      <c r="Q14" s="13">
+      <c r="B14" s="10"/>
+      <c r="C14" s="10">
+        <v>1</v>
+      </c>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10">
+        <v>1</v>
+      </c>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10">
+        <v>1</v>
+      </c>
+      <c r="M14" s="10">
+        <v>1</v>
+      </c>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10">
         <v>1</v>
       </c>
       <c r="R14" s="10"/>
@@ -4136,7 +4178,7 @@
       </c>
       <c r="X14" s="4">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Y14" s="4">
         <f t="shared" si="1"/>
@@ -4144,31 +4186,31 @@
       </c>
       <c r="Z14" s="4">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" ht="14" customHeight="1" spans="1:26">
-      <c r="A15" s="9">
+      <c r="A15" s="13">
         <v>14</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="13">
-        <v>1</v>
-      </c>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
-      <c r="P15" s="9"/>
-      <c r="Q15" s="9"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10">
+        <v>1</v>
+      </c>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="10"/>
       <c r="R15" s="10"/>
       <c r="S15" s="11"/>
       <c r="T15" s="2">
@@ -4201,26 +4243,26 @@
       </c>
     </row>
     <row r="16" ht="14" customHeight="1" spans="1:26">
-      <c r="A16" s="9">
+      <c r="A16" s="13">
         <v>15</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="9"/>
-      <c r="Q16" s="9"/>
-      <c r="R16" s="13">
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10">
         <v>1</v>
       </c>
       <c r="S16" s="11"/>
@@ -4257,22 +4299,22 @@
       <c r="A17" s="9">
         <v>16</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="9"/>
-      <c r="Q17" s="9"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="10"/>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="10"/>
       <c r="R17" s="10"/>
       <c r="S17" s="11"/>
       <c r="T17" s="2">
@@ -4305,38 +4347,40 @@
       </c>
     </row>
     <row r="18" ht="14" customHeight="1" spans="1:26">
-      <c r="A18" s="9">
+      <c r="A18" s="13">
         <v>17</v>
       </c>
-      <c r="B18" s="13">
-        <v>1</v>
-      </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="13">
-        <v>1</v>
-      </c>
-      <c r="O18" s="9"/>
-      <c r="P18" s="9"/>
-      <c r="Q18" s="9"/>
+      <c r="B18" s="10">
+        <v>1</v>
+      </c>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10">
+        <v>1</v>
+      </c>
+      <c r="O18" s="10"/>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="10"/>
       <c r="R18" s="10"/>
-      <c r="S18" s="11"/>
+      <c r="S18" s="11">
+        <v>1</v>
+      </c>
       <c r="T18" s="2">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U18" s="3" cm="1">
         <f t="array" ref="U18">SUMPRODUCT(--(B18:S18=INT(B18:S18)),--(B18:S18&gt;0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V18" s="3" cm="1">
         <f t="array" ref="V18">MAX(FREQUENCY(IF((B18:S18=INT(B18:S18))*(B18:S18&gt;0),COLUMN(B18:S18)),IF((B18:S18&lt;&gt;INT(B18:S18))+(B18:S18&lt;=0),COLUMN(B18:S18))))</f>
@@ -4344,15 +4388,15 @@
       </c>
       <c r="W18" s="12" cm="1">
         <f t="array" ref="W18">SUMPRODUCT(--(B18:S18=INT(B18:S18)),--(B18:S18&gt;0))/18*100%</f>
-        <v>0.111111111111111</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="X18" s="4">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y18" s="4">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Z18" s="4">
         <f t="shared" si="2"/>
@@ -4360,27 +4404,27 @@
       </c>
     </row>
     <row r="19" ht="14" customHeight="1" spans="1:26">
-      <c r="A19" s="9">
+      <c r="A19" s="13">
         <v>18</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="13">
-        <v>1</v>
-      </c>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
-      <c r="P19" s="9"/>
-      <c r="Q19" s="9"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10">
+        <v>1</v>
+      </c>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="10"/>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="10"/>
       <c r="R19" s="10"/>
       <c r="S19" s="11"/>
       <c r="T19" s="2">
@@ -4413,29 +4457,29 @@
       </c>
     </row>
     <row r="20" ht="14" customHeight="1" spans="1:26">
-      <c r="A20" s="9">
+      <c r="A20" s="13">
         <v>19</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="13">
-        <v>1</v>
-      </c>
-      <c r="K20" s="9"/>
-      <c r="L20" s="13">
-        <v>1</v>
-      </c>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
-      <c r="P20" s="9"/>
-      <c r="Q20" s="9"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10">
+        <v>1</v>
+      </c>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10">
+        <v>1</v>
+      </c>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
       <c r="R20" s="10"/>
       <c r="S20" s="11"/>
       <c r="T20" s="2">
@@ -4456,11 +4500,11 @@
       </c>
       <c r="X20" s="4">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y20" s="4">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Z20" s="4">
         <f t="shared" si="2"/>
@@ -4468,84 +4512,86 @@
       </c>
     </row>
     <row r="21" ht="14" customHeight="1" spans="1:26">
-      <c r="A21" s="9">
+      <c r="A21" s="13">
         <v>20</v>
       </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="13">
-        <v>1</v>
-      </c>
-      <c r="J21" s="13">
-        <v>1</v>
-      </c>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="9"/>
-      <c r="P21" s="9"/>
-      <c r="Q21" s="13">
-        <v>1</v>
-      </c>
-      <c r="R21" s="13">
-        <v>1</v>
-      </c>
-      <c r="S21" s="11"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10">
+        <v>1</v>
+      </c>
+      <c r="J21" s="10">
+        <v>1</v>
+      </c>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="10">
+        <v>1</v>
+      </c>
+      <c r="R21" s="10">
+        <v>1</v>
+      </c>
+      <c r="S21" s="11">
+        <v>3</v>
+      </c>
       <c r="T21" s="2">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U21" s="3" cm="1">
         <f t="array" ref="U21">SUMPRODUCT(--(B21:S21=INT(B21:S21)),--(B21:S21&gt;0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V21" s="3" cm="1">
         <f t="array" ref="V21">MAX(FREQUENCY(IF((B21:S21=INT(B21:S21))*(B21:S21&gt;0),COLUMN(B21:S21)),IF((B21:S21&lt;&gt;INT(B21:S21))+(B21:S21&lt;=0),COLUMN(B21:S21))))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W21" s="12" cm="1">
         <f t="array" ref="W21">SUMPRODUCT(--(B21:S21=INT(B21:S21)),--(B21:S21&gt;0))/18*100%</f>
-        <v>0.222222222222222</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="X21" s="4">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Y21" s="4">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Z21" s="4">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" ht="14" customHeight="1" spans="1:26">
       <c r="A22" s="9">
         <v>21</v>
       </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
-      <c r="P22" s="9"/>
-      <c r="Q22" s="9"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="10"/>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="10"/>
       <c r="R22" s="10"/>
       <c r="S22" s="11"/>
       <c r="T22" s="2">
@@ -4578,35 +4624,35 @@
       </c>
     </row>
     <row r="23" ht="14" customHeight="1" spans="1:26">
-      <c r="A23" s="9">
+      <c r="A23" s="13">
         <v>22</v>
       </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="13">
-        <v>1</v>
-      </c>
-      <c r="D23" s="13">
-        <v>1</v>
-      </c>
-      <c r="E23" s="13">
-        <v>1</v>
-      </c>
-      <c r="F23" s="9"/>
-      <c r="G23" s="13">
-        <v>1</v>
-      </c>
-      <c r="H23" s="9"/>
-      <c r="I23" s="13">
-        <v>1</v>
-      </c>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="9"/>
-      <c r="P23" s="9"/>
-      <c r="Q23" s="9"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10">
+        <v>1</v>
+      </c>
+      <c r="D23" s="10">
+        <v>1</v>
+      </c>
+      <c r="E23" s="10">
+        <v>1</v>
+      </c>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10">
+        <v>1</v>
+      </c>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10">
+        <v>1</v>
+      </c>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="10"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
       <c r="S23" s="11"/>
       <c r="T23" s="2">
@@ -4627,7 +4673,7 @@
       </c>
       <c r="X23" s="4">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Y23" s="4">
         <f t="shared" si="1"/>
@@ -4642,22 +4688,22 @@
       <c r="A24" s="9">
         <v>23</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
-      <c r="P24" s="9"/>
-      <c r="Q24" s="9"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="10"/>
       <c r="R24" s="10"/>
       <c r="S24" s="11"/>
       <c r="T24" s="2">
@@ -4693,22 +4739,22 @@
       <c r="A25" s="9">
         <v>24</v>
       </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
-      <c r="P25" s="9"/>
-      <c r="Q25" s="9"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="10"/>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="11"/>
       <c r="T25" s="2">
@@ -4744,22 +4790,22 @@
       <c r="A26" s="9">
         <v>25</v>
       </c>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="9"/>
-      <c r="N26" s="9"/>
-      <c r="O26" s="9"/>
-      <c r="P26" s="9"/>
-      <c r="Q26" s="9"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="10"/>
+      <c r="P26" s="10"/>
+      <c r="Q26" s="10"/>
       <c r="R26" s="10"/>
       <c r="S26" s="11"/>
       <c r="T26" s="2">
@@ -4792,42 +4838,44 @@
       </c>
     </row>
     <row r="27" ht="14" customHeight="1" spans="1:26">
-      <c r="A27" s="9">
+      <c r="A27" s="13">
         <v>26</v>
       </c>
-      <c r="B27" s="9"/>
-      <c r="C27" s="13">
-        <v>1</v>
-      </c>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="13">
-        <v>1</v>
-      </c>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="13">
-        <v>1</v>
-      </c>
-      <c r="L27" s="9"/>
-      <c r="M27" s="9"/>
-      <c r="N27" s="9"/>
-      <c r="O27" s="9"/>
-      <c r="P27" s="9"/>
-      <c r="Q27" s="13">
+      <c r="B27" s="10"/>
+      <c r="C27" s="10">
+        <v>1</v>
+      </c>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10">
+        <v>1</v>
+      </c>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10">
+        <v>1</v>
+      </c>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="10"/>
+      <c r="P27" s="10"/>
+      <c r="Q27" s="10">
         <v>1</v>
       </c>
       <c r="R27" s="10"/>
-      <c r="S27" s="11"/>
+      <c r="S27" s="11">
+        <v>1</v>
+      </c>
       <c r="T27" s="2">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U27" s="3" cm="1">
         <f t="array" ref="U27">SUMPRODUCT(--(B27:S27=INT(B27:S27)),--(B27:S27&gt;0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V27" s="3" cm="1">
         <f t="array" ref="V27">MAX(FREQUENCY(IF((B27:S27=INT(B27:S27))*(B27:S27&gt;0),COLUMN(B27:S27)),IF((B27:S27&lt;&gt;INT(B27:S27))+(B27:S27&lt;=0),COLUMN(B27:S27))))</f>
@@ -4835,15 +4883,15 @@
       </c>
       <c r="W27" s="12" cm="1">
         <f t="array" ref="W27">SUMPRODUCT(--(B27:S27=INT(B27:S27)),--(B27:S27&gt;0))/18*100%</f>
-        <v>0.222222222222222</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="X27" s="4">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y27" s="4">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Z27" s="4">
         <f t="shared" si="2"/>
@@ -4851,29 +4899,29 @@
       </c>
     </row>
     <row r="28" ht="14" customHeight="1" spans="1:26">
-      <c r="A28" s="9">
+      <c r="A28" s="13">
         <v>27</v>
       </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="13">
-        <v>1</v>
-      </c>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="13">
-        <v>1</v>
-      </c>
-      <c r="N28" s="9"/>
-      <c r="O28" s="9"/>
-      <c r="P28" s="9"/>
-      <c r="Q28" s="9"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10">
+        <v>1</v>
+      </c>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10">
+        <v>1</v>
+      </c>
+      <c r="N28" s="10"/>
+      <c r="O28" s="10"/>
+      <c r="P28" s="10"/>
+      <c r="Q28" s="10"/>
       <c r="R28" s="10"/>
       <c r="S28" s="11"/>
       <c r="T28" s="2">
@@ -4894,11 +4942,11 @@
       </c>
       <c r="X28" s="4">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y28" s="4">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Z28" s="4">
         <f t="shared" si="2"/>
@@ -4906,38 +4954,40 @@
       </c>
     </row>
     <row r="29" ht="14" customHeight="1" spans="1:26">
-      <c r="A29" s="9">
+      <c r="A29" s="13">
         <v>28</v>
       </c>
-      <c r="B29" s="13">
-        <v>1</v>
-      </c>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="13">
-        <v>1</v>
-      </c>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9"/>
-      <c r="N29" s="9"/>
-      <c r="O29" s="9"/>
-      <c r="P29" s="9"/>
-      <c r="Q29" s="9"/>
+      <c r="B29" s="10">
+        <v>1</v>
+      </c>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10">
+        <v>1</v>
+      </c>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="10"/>
+      <c r="P29" s="10"/>
+      <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
-      <c r="S29" s="11"/>
+      <c r="S29" s="11">
+        <v>2</v>
+      </c>
       <c r="T29" s="2">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U29" s="3" cm="1">
         <f t="array" ref="U29">SUMPRODUCT(--(B29:S29=INT(B29:S29)),--(B29:S29&gt;0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V29" s="3" cm="1">
         <f t="array" ref="V29">MAX(FREQUENCY(IF((B29:S29=INT(B29:S29))*(B29:S29&gt;0),COLUMN(B29:S29)),IF((B29:S29&lt;&gt;INT(B29:S29))+(B29:S29&lt;=0),COLUMN(B29:S29))))</f>
@@ -4945,15 +4995,15 @@
       </c>
       <c r="W29" s="12" cm="1">
         <f t="array" ref="W29">SUMPRODUCT(--(B29:S29=INT(B29:S29)),--(B29:S29&gt;0))/18*100%</f>
-        <v>0.111111111111111</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="X29" s="4">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y29" s="4">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Z29" s="4">
         <f t="shared" si="2"/>
@@ -4961,42 +5011,44 @@
       </c>
     </row>
     <row r="30" ht="14" customHeight="1" spans="1:26">
-      <c r="A30" s="9">
+      <c r="A30" s="13">
         <v>29</v>
       </c>
-      <c r="B30" s="13">
-        <v>1</v>
-      </c>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="13">
-        <v>1</v>
-      </c>
-      <c r="I30" s="14">
+      <c r="B30" s="10">
+        <v>1</v>
+      </c>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10">
+        <v>1</v>
+      </c>
+      <c r="I30" s="10">
         <v>2</v>
       </c>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
-      <c r="P30" s="9"/>
-      <c r="Q30" s="13">
+      <c r="J30" s="10"/>
+      <c r="K30" s="10"/>
+      <c r="L30" s="10"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="10"/>
+      <c r="O30" s="10"/>
+      <c r="P30" s="10"/>
+      <c r="Q30" s="10">
         <v>1</v>
       </c>
       <c r="R30" s="10"/>
-      <c r="S30" s="11"/>
+      <c r="S30" s="11">
+        <v>1</v>
+      </c>
       <c r="T30" s="2">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U30" s="3" cm="1">
         <f t="array" ref="U30">SUMPRODUCT(--(B30:S30=INT(B30:S30)),--(B30:S30&gt;0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V30" s="3" cm="1">
         <f t="array" ref="V30">MAX(FREQUENCY(IF((B30:S30=INT(B30:S30))*(B30:S30&gt;0),COLUMN(B30:S30)),IF((B30:S30&lt;&gt;INT(B30:S30))+(B30:S30&lt;=0),COLUMN(B30:S30))))</f>
@@ -5004,62 +5056,64 @@
       </c>
       <c r="W30" s="12" cm="1">
         <f t="array" ref="W30">SUMPRODUCT(--(B30:S30=INT(B30:S30)),--(B30:S30&gt;0))/18*100%</f>
-        <v>0.222222222222222</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="X30" s="4">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y30" s="4">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Z30" s="4">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" ht="14" customHeight="1" spans="1:26">
-      <c r="A31" s="9">
+      <c r="A31" s="13">
         <v>30</v>
       </c>
-      <c r="B31" s="9"/>
-      <c r="C31" s="13">
-        <v>1</v>
-      </c>
-      <c r="D31" s="9"/>
-      <c r="E31" s="13">
-        <v>1</v>
-      </c>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="14">
+      <c r="B31" s="10"/>
+      <c r="C31" s="10">
+        <v>1</v>
+      </c>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10">
+        <v>1</v>
+      </c>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10">
         <v>2</v>
       </c>
-      <c r="J31" s="13">
-        <v>1</v>
-      </c>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9"/>
-      <c r="M31" s="9"/>
-      <c r="N31" s="13">
-        <v>1</v>
-      </c>
-      <c r="O31" s="9"/>
-      <c r="P31" s="9"/>
-      <c r="Q31" s="9"/>
-      <c r="R31" s="13">
-        <v>1</v>
-      </c>
-      <c r="S31" s="11"/>
+      <c r="J31" s="10">
+        <v>1</v>
+      </c>
+      <c r="K31" s="10"/>
+      <c r="L31" s="10"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="10">
+        <v>1</v>
+      </c>
+      <c r="O31" s="10"/>
+      <c r="P31" s="10"/>
+      <c r="Q31" s="10"/>
+      <c r="R31" s="10">
+        <v>1</v>
+      </c>
+      <c r="S31" s="11">
+        <v>1</v>
+      </c>
       <c r="T31" s="2">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U31" s="3" cm="1">
         <f t="array" ref="U31">SUMPRODUCT(--(B31:S31=INT(B31:S31)),--(B31:S31&gt;0))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V31" s="3" cm="1">
         <f t="array" ref="V31">MAX(FREQUENCY(IF((B31:S31=INT(B31:S31))*(B31:S31&gt;0),COLUMN(B31:S31)),IF((B31:S31&lt;&gt;INT(B31:S31))+(B31:S31&lt;=0),COLUMN(B31:S31))))</f>
@@ -5067,11 +5121,11 @@
       </c>
       <c r="W31" s="12" cm="1">
         <f t="array" ref="W31">SUMPRODUCT(--(B31:S31=INT(B31:S31)),--(B31:S31&gt;0))/18*100%</f>
-        <v>0.333333333333333</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="X31" s="4">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y31" s="4">
         <f t="shared" si="1"/>
@@ -5079,31 +5133,31 @@
       </c>
       <c r="Z31" s="4">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" ht="14" customHeight="1" spans="1:26">
-      <c r="A32" s="9">
+      <c r="A32" s="13">
         <v>31</v>
       </c>
-      <c r="B32" s="13">
-        <v>1</v>
-      </c>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9"/>
-      <c r="M32" s="9"/>
-      <c r="N32" s="9"/>
-      <c r="O32" s="9"/>
-      <c r="P32" s="9"/>
-      <c r="Q32" s="9"/>
+      <c r="B32" s="10">
+        <v>1</v>
+      </c>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="10"/>
+      <c r="J32" s="10"/>
+      <c r="K32" s="10"/>
+      <c r="L32" s="10"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="10"/>
+      <c r="O32" s="10"/>
+      <c r="P32" s="10"/>
+      <c r="Q32" s="10"/>
       <c r="R32" s="10"/>
       <c r="S32" s="11"/>
       <c r="T32" s="2">
@@ -5139,22 +5193,22 @@
       <c r="A33" s="9">
         <v>32</v>
       </c>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9"/>
-      <c r="K33" s="9"/>
-      <c r="L33" s="9"/>
-      <c r="M33" s="9"/>
-      <c r="N33" s="9"/>
-      <c r="O33" s="9"/>
-      <c r="P33" s="9"/>
-      <c r="Q33" s="9"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="10"/>
+      <c r="L33" s="10"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="10"/>
+      <c r="O33" s="10"/>
+      <c r="P33" s="10"/>
+      <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
       <c r="S33" s="11"/>
       <c r="T33" s="2">
@@ -5190,22 +5244,22 @@
       <c r="A34" s="9">
         <v>33</v>
       </c>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9"/>
-      <c r="M34" s="9"/>
-      <c r="N34" s="9"/>
-      <c r="O34" s="9"/>
-      <c r="P34" s="9"/>
-      <c r="Q34" s="9"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="10"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="10"/>
+      <c r="O34" s="10"/>
+      <c r="P34" s="10"/>
+      <c r="Q34" s="10"/>
       <c r="R34" s="10"/>
       <c r="S34" s="11"/>
       <c r="T34" s="2">
@@ -5241,22 +5295,22 @@
       <c r="A35" s="9">
         <v>34</v>
       </c>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="9"/>
-      <c r="K35" s="9"/>
-      <c r="L35" s="9"/>
-      <c r="M35" s="9"/>
-      <c r="N35" s="9"/>
-      <c r="O35" s="9"/>
-      <c r="P35" s="9"/>
-      <c r="Q35" s="9"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10"/>
+      <c r="K35" s="10"/>
+      <c r="L35" s="10"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="10"/>
+      <c r="P35" s="10"/>
+      <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
       <c r="S35" s="11"/>
       <c r="T35" s="2">
@@ -5289,33 +5343,33 @@
       </c>
     </row>
     <row r="36" ht="14" customHeight="1" spans="1:26">
-      <c r="A36" s="9">
+      <c r="A36" s="13">
         <v>35</v>
       </c>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="13">
-        <v>1</v>
-      </c>
-      <c r="I36" s="13">
-        <v>1</v>
-      </c>
-      <c r="J36" s="13">
-        <v>1</v>
-      </c>
-      <c r="K36" s="9"/>
-      <c r="L36" s="9"/>
-      <c r="M36" s="9"/>
-      <c r="N36" s="13">
-        <v>1</v>
-      </c>
-      <c r="O36" s="9"/>
-      <c r="P36" s="9"/>
-      <c r="Q36" s="9"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10">
+        <v>1</v>
+      </c>
+      <c r="I36" s="10">
+        <v>1</v>
+      </c>
+      <c r="J36" s="10">
+        <v>1</v>
+      </c>
+      <c r="K36" s="10"/>
+      <c r="L36" s="10"/>
+      <c r="M36" s="10"/>
+      <c r="N36" s="10">
+        <v>1</v>
+      </c>
+      <c r="O36" s="10"/>
+      <c r="P36" s="10"/>
+      <c r="Q36" s="10"/>
       <c r="R36" s="10"/>
       <c r="S36" s="11"/>
       <c r="T36" s="2">
@@ -5336,11 +5390,11 @@
       </c>
       <c r="X36" s="4">
         <f t="shared" si="4"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y36" s="4">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Z36" s="4">
         <f t="shared" si="6"/>
@@ -5348,27 +5402,27 @@
       </c>
     </row>
     <row r="37" ht="14" customHeight="1" spans="1:26">
-      <c r="A37" s="9">
+      <c r="A37" s="13">
         <v>36</v>
       </c>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="14">
+      <c r="B37" s="10"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10">
         <v>2</v>
       </c>
-      <c r="J37" s="9"/>
-      <c r="K37" s="9"/>
-      <c r="L37" s="9"/>
-      <c r="M37" s="9"/>
-      <c r="N37" s="9"/>
-      <c r="O37" s="9"/>
-      <c r="P37" s="9"/>
-      <c r="Q37" s="9"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="10"/>
+      <c r="P37" s="10"/>
+      <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
       <c r="S37" s="11"/>
       <c r="T37" s="2">
@@ -5389,7 +5443,7 @@
       </c>
       <c r="X37" s="4">
         <f t="shared" si="4"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y37" s="4">
         <f t="shared" si="5"/>
@@ -5401,103 +5455,105 @@
       </c>
     </row>
     <row r="38" ht="14" customHeight="1" spans="1:26">
-      <c r="A38" s="9">
+      <c r="A38" s="14">
         <v>37</v>
       </c>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
-      <c r="J38" s="9"/>
-      <c r="K38" s="9"/>
-      <c r="L38" s="9"/>
-      <c r="M38" s="9"/>
-      <c r="N38" s="9"/>
-      <c r="O38" s="9"/>
-      <c r="P38" s="9"/>
-      <c r="Q38" s="9"/>
-      <c r="R38" s="10"/>
-      <c r="S38" s="11"/>
-      <c r="T38" s="2">
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="14"/>
+      <c r="K38" s="14"/>
+      <c r="L38" s="14"/>
+      <c r="M38" s="14"/>
+      <c r="N38" s="14"/>
+      <c r="O38" s="14"/>
+      <c r="P38" s="14"/>
+      <c r="Q38" s="14"/>
+      <c r="R38" s="14"/>
+      <c r="S38" s="15"/>
+      <c r="T38" s="16">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U38" s="3" cm="1">
+      <c r="U38" s="17" cm="1">
         <f t="array" ref="U38">SUMPRODUCT(--(B38:S38=INT(B38:S38)),--(B38:S38&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="V38" s="3" cm="1">
+      <c r="V38" s="17" cm="1">
         <f t="array" ref="V38">MAX(FREQUENCY(IF((B38:S38=INT(B38:S38))*(B38:S38&gt;0),COLUMN(B38:S38)),IF((B38:S38&lt;&gt;INT(B38:S38))+(B38:S38&lt;=0),COLUMN(B38:S38))))</f>
         <v>0</v>
       </c>
-      <c r="W38" s="12" cm="1">
+      <c r="W38" s="18" cm="1">
         <f t="array" ref="W38">SUMPRODUCT(--(B38:S38=INT(B38:S38)),--(B38:S38&gt;0))/18*100%</f>
         <v>0</v>
       </c>
-      <c r="X38" s="4">
+      <c r="X38" s="17">
         <f t="shared" si="4"/>
         <v>35</v>
       </c>
-      <c r="Y38" s="4">
+      <c r="Y38" s="17">
         <f t="shared" si="5"/>
         <v>35</v>
       </c>
-      <c r="Z38" s="4">
+      <c r="Z38" s="17">
         <f t="shared" si="6"/>
         <v>35</v>
       </c>
     </row>
     <row r="39" ht="14" customHeight="1" spans="1:26">
-      <c r="A39" s="9">
+      <c r="A39" s="13">
         <v>38</v>
       </c>
-      <c r="B39" s="9"/>
-      <c r="C39" s="13">
-        <v>1</v>
-      </c>
-      <c r="D39" s="13">
-        <v>1</v>
-      </c>
-      <c r="E39" s="9"/>
-      <c r="F39" s="13">
-        <v>1</v>
-      </c>
-      <c r="G39" s="9"/>
-      <c r="H39" s="13">
-        <v>1</v>
-      </c>
-      <c r="I39" s="13">
-        <v>1</v>
-      </c>
-      <c r="J39" s="14">
+      <c r="B39" s="10"/>
+      <c r="C39" s="10">
+        <v>1</v>
+      </c>
+      <c r="D39" s="10">
+        <v>1</v>
+      </c>
+      <c r="E39" s="10"/>
+      <c r="F39" s="10">
+        <v>1</v>
+      </c>
+      <c r="G39" s="10"/>
+      <c r="H39" s="10">
+        <v>1</v>
+      </c>
+      <c r="I39" s="10">
+        <v>1</v>
+      </c>
+      <c r="J39" s="10">
         <v>2</v>
       </c>
-      <c r="K39" s="9"/>
-      <c r="L39" s="13">
-        <v>1</v>
-      </c>
-      <c r="M39" s="9"/>
-      <c r="N39" s="9"/>
-      <c r="O39" s="9"/>
-      <c r="P39" s="9"/>
-      <c r="Q39" s="13">
-        <v>1</v>
-      </c>
-      <c r="R39" s="13">
-        <v>1</v>
-      </c>
-      <c r="S39" s="11"/>
+      <c r="K39" s="10"/>
+      <c r="L39" s="10">
+        <v>1</v>
+      </c>
+      <c r="M39" s="10"/>
+      <c r="N39" s="10"/>
+      <c r="O39" s="10"/>
+      <c r="P39" s="10"/>
+      <c r="Q39" s="10">
+        <v>1</v>
+      </c>
+      <c r="R39" s="10">
+        <v>1</v>
+      </c>
+      <c r="S39" s="11">
+        <v>1</v>
+      </c>
       <c r="T39" s="2">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="U39" s="3" cm="1">
         <f t="array" ref="U39">SUMPRODUCT(--(B39:S39=INT(B39:S39)),--(B39:S39&gt;0))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V39" s="3" cm="1">
         <f t="array" ref="V39">MAX(FREQUENCY(IF((B39:S39=INT(B39:S39))*(B39:S39&gt;0),COLUMN(B39:S39)),IF((B39:S39&lt;&gt;INT(B39:S39))+(B39:S39&lt;=0),COLUMN(B39:S39))))</f>
@@ -5505,7 +5561,7 @@
       </c>
       <c r="W39" s="12" cm="1">
         <f t="array" ref="W39">SUMPRODUCT(--(B39:S39=INT(B39:S39)),--(B39:S39&gt;0))/18*100%</f>
-        <v>0.5</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="X39" s="4">
         <f t="shared" si="4"/>
@@ -5513,7 +5569,7 @@
       </c>
       <c r="Y39" s="4">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z39" s="4">
         <f t="shared" si="6"/>
@@ -5521,29 +5577,29 @@
       </c>
     </row>
     <row r="40" ht="14" customHeight="1" spans="1:26">
-      <c r="A40" s="9">
+      <c r="A40" s="13">
         <v>39</v>
       </c>
-      <c r="B40" s="13">
-        <v>1</v>
-      </c>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="9"/>
-      <c r="J40" s="13">
-        <v>1</v>
-      </c>
-      <c r="K40" s="9"/>
-      <c r="L40" s="9"/>
-      <c r="M40" s="9"/>
-      <c r="N40" s="9"/>
-      <c r="O40" s="9"/>
-      <c r="P40" s="9"/>
-      <c r="Q40" s="13">
+      <c r="B40" s="10">
+        <v>1</v>
+      </c>
+      <c r="C40" s="10"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="10"/>
+      <c r="H40" s="10"/>
+      <c r="I40" s="10"/>
+      <c r="J40" s="10">
+        <v>1</v>
+      </c>
+      <c r="K40" s="10"/>
+      <c r="L40" s="10"/>
+      <c r="M40" s="10"/>
+      <c r="N40" s="10"/>
+      <c r="O40" s="10"/>
+      <c r="P40" s="10"/>
+      <c r="Q40" s="10">
         <v>1</v>
       </c>
       <c r="R40" s="10"/>
@@ -5566,7 +5622,7 @@
       </c>
       <c r="X40" s="4">
         <f t="shared" si="4"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y40" s="4">
         <f t="shared" si="5"/>
@@ -5578,40 +5634,40 @@
       </c>
     </row>
     <row r="41" ht="14" customHeight="1" spans="1:26">
-      <c r="A41" s="9">
+      <c r="A41" s="13">
         <v>40</v>
       </c>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="13">
-        <v>1</v>
-      </c>
-      <c r="I41" s="9"/>
-      <c r="J41" s="13">
-        <v>1</v>
-      </c>
-      <c r="K41" s="13">
-        <v>1</v>
-      </c>
-      <c r="L41" s="13">
-        <v>1</v>
-      </c>
-      <c r="M41" s="13">
-        <v>1</v>
-      </c>
-      <c r="N41" s="13">
-        <v>1</v>
-      </c>
-      <c r="O41" s="9"/>
-      <c r="P41" s="9"/>
-      <c r="Q41" s="13">
-        <v>1</v>
-      </c>
-      <c r="R41" s="14">
+      <c r="B41" s="10"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="10">
+        <v>1</v>
+      </c>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10">
+        <v>1</v>
+      </c>
+      <c r="K41" s="10">
+        <v>1</v>
+      </c>
+      <c r="L41" s="10">
+        <v>1</v>
+      </c>
+      <c r="M41" s="10">
+        <v>1</v>
+      </c>
+      <c r="N41" s="10">
+        <v>1</v>
+      </c>
+      <c r="O41" s="10"/>
+      <c r="P41" s="10"/>
+      <c r="Q41" s="10">
+        <v>1</v>
+      </c>
+      <c r="R41" s="10">
         <v>2</v>
       </c>
       <c r="S41" s="11"/>
@@ -5648,22 +5704,22 @@
       <c r="A42" s="9">
         <v>41</v>
       </c>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="9"/>
-      <c r="J42" s="9"/>
-      <c r="K42" s="9"/>
-      <c r="L42" s="9"/>
-      <c r="M42" s="9"/>
-      <c r="N42" s="9"/>
-      <c r="O42" s="9"/>
-      <c r="P42" s="9"/>
-      <c r="Q42" s="9"/>
+      <c r="B42" s="10"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="10"/>
+      <c r="J42" s="10"/>
+      <c r="K42" s="10"/>
+      <c r="L42" s="10"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="10"/>
+      <c r="O42" s="10"/>
+      <c r="P42" s="10"/>
+      <c r="Q42" s="10"/>
       <c r="R42" s="10"/>
       <c r="S42" s="11"/>
       <c r="T42" s="2">
@@ -5696,44 +5752,44 @@
       </c>
     </row>
     <row r="43" ht="14" customHeight="1" spans="1:26">
-      <c r="A43" s="9">
+      <c r="A43" s="13">
         <v>42</v>
       </c>
-      <c r="B43" s="13">
-        <v>1</v>
-      </c>
-      <c r="C43" s="13">
-        <v>1</v>
-      </c>
-      <c r="D43" s="14">
+      <c r="B43" s="10">
+        <v>1</v>
+      </c>
+      <c r="C43" s="10">
+        <v>1</v>
+      </c>
+      <c r="D43" s="10">
         <v>2</v>
       </c>
-      <c r="E43" s="13">
-        <v>1</v>
-      </c>
-      <c r="F43" s="13">
-        <v>1</v>
-      </c>
-      <c r="G43" s="9"/>
-      <c r="H43" s="13">
-        <v>1</v>
-      </c>
-      <c r="I43" s="13">
-        <v>1</v>
-      </c>
-      <c r="J43" s="13">
-        <v>1</v>
-      </c>
-      <c r="K43" s="9"/>
-      <c r="L43" s="13">
-        <v>1</v>
-      </c>
-      <c r="M43" s="9"/>
-      <c r="N43" s="9"/>
-      <c r="O43" s="9"/>
-      <c r="P43" s="9"/>
-      <c r="Q43" s="9"/>
-      <c r="R43" s="14">
+      <c r="E43" s="10">
+        <v>1</v>
+      </c>
+      <c r="F43" s="10">
+        <v>1</v>
+      </c>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10">
+        <v>1</v>
+      </c>
+      <c r="I43" s="10">
+        <v>1</v>
+      </c>
+      <c r="J43" s="10">
+        <v>1</v>
+      </c>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10">
+        <v>1</v>
+      </c>
+      <c r="M43" s="10"/>
+      <c r="N43" s="10"/>
+      <c r="O43" s="10"/>
+      <c r="P43" s="10"/>
+      <c r="Q43" s="10"/>
+      <c r="R43" s="10">
         <v>2</v>
       </c>
       <c r="S43" s="11"/>
@@ -5755,7 +5811,7 @@
       </c>
       <c r="X43" s="4">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y43" s="4">
         <f t="shared" si="5"/>
@@ -5770,22 +5826,22 @@
       <c r="A44" s="9">
         <v>43</v>
       </c>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="9"/>
-      <c r="J44" s="9"/>
-      <c r="K44" s="9"/>
-      <c r="L44" s="9"/>
-      <c r="M44" s="9"/>
-      <c r="N44" s="9"/>
-      <c r="O44" s="9"/>
-      <c r="P44" s="9"/>
-      <c r="Q44" s="9"/>
+      <c r="B44" s="10"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="10"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="10"/>
+      <c r="G44" s="10"/>
+      <c r="H44" s="10"/>
+      <c r="I44" s="10"/>
+      <c r="J44" s="10"/>
+      <c r="K44" s="10"/>
+      <c r="L44" s="10"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="10"/>
+      <c r="O44" s="10"/>
+      <c r="P44" s="10"/>
+      <c r="Q44" s="10"/>
       <c r="R44" s="10"/>
       <c r="S44" s="11"/>
       <c r="T44" s="2">
@@ -5818,60 +5874,62 @@
       </c>
     </row>
     <row r="45" ht="14" customHeight="1" spans="1:26">
-      <c r="A45" s="9">
+      <c r="A45" s="13">
         <v>44</v>
       </c>
-      <c r="B45" s="13">
-        <v>1</v>
-      </c>
-      <c r="C45" s="13">
-        <v>1</v>
-      </c>
-      <c r="D45" s="13">
-        <v>1</v>
-      </c>
-      <c r="E45" s="13">
-        <v>1</v>
-      </c>
-      <c r="F45" s="9"/>
-      <c r="G45" s="15">
+      <c r="B45" s="10">
+        <v>1</v>
+      </c>
+      <c r="C45" s="10">
+        <v>1</v>
+      </c>
+      <c r="D45" s="10">
+        <v>1</v>
+      </c>
+      <c r="E45" s="10">
+        <v>1</v>
+      </c>
+      <c r="F45" s="10"/>
+      <c r="G45" s="10">
         <v>3</v>
       </c>
-      <c r="H45" s="13">
-        <v>1</v>
-      </c>
-      <c r="I45" s="13">
-        <v>1</v>
-      </c>
-      <c r="J45" s="14">
+      <c r="H45" s="10">
+        <v>1</v>
+      </c>
+      <c r="I45" s="10">
+        <v>1</v>
+      </c>
+      <c r="J45" s="10">
         <v>2</v>
       </c>
-      <c r="K45" s="14">
+      <c r="K45" s="10">
         <v>2</v>
       </c>
-      <c r="L45" s="13">
-        <v>1</v>
-      </c>
-      <c r="M45" s="14">
+      <c r="L45" s="10">
+        <v>1</v>
+      </c>
+      <c r="M45" s="10">
         <v>2</v>
       </c>
-      <c r="N45" s="14">
+      <c r="N45" s="10">
         <v>2</v>
       </c>
-      <c r="O45" s="9"/>
-      <c r="P45" s="9"/>
-      <c r="Q45" s="9"/>
-      <c r="R45" s="13">
-        <v>1</v>
-      </c>
-      <c r="S45" s="11"/>
+      <c r="O45" s="10"/>
+      <c r="P45" s="10"/>
+      <c r="Q45" s="10"/>
+      <c r="R45" s="10">
+        <v>1</v>
+      </c>
+      <c r="S45" s="11">
+        <v>1</v>
+      </c>
       <c r="T45" s="2">
         <f t="shared" si="7"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U45" s="3" cm="1">
         <f t="array" ref="U45">SUMPRODUCT(--(B45:S45=INT(B45:S45)),--(B45:S45&gt;0))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V45" s="3" cm="1">
         <f t="array" ref="V45">MAX(FREQUENCY(IF((B45:S45=INT(B45:S45))*(B45:S45&gt;0),COLUMN(B45:S45)),IF((B45:S45&lt;&gt;INT(B45:S45))+(B45:S45&lt;=0),COLUMN(B45:S45))))</f>
@@ -5879,7 +5937,7 @@
       </c>
       <c r="W45" s="12" cm="1">
         <f t="array" ref="W45">SUMPRODUCT(--(B45:S45=INT(B45:S45)),--(B45:S45&gt;0))/18*100%</f>
-        <v>0.722222222222222</v>
+        <v>0.777777777777778</v>
       </c>
       <c r="X45" s="4">
         <f t="shared" si="4"/>
@@ -5898,22 +5956,22 @@
       <c r="A46" s="9">
         <v>45</v>
       </c>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
-      <c r="I46" s="9"/>
-      <c r="J46" s="9"/>
-      <c r="K46" s="9"/>
-      <c r="L46" s="9"/>
-      <c r="M46" s="9"/>
-      <c r="N46" s="9"/>
-      <c r="O46" s="9"/>
-      <c r="P46" s="9"/>
-      <c r="Q46" s="9"/>
+      <c r="B46" s="10"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="10"/>
+      <c r="G46" s="10"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10"/>
+      <c r="K46" s="10"/>
+      <c r="L46" s="10"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="10"/>
+      <c r="O46" s="10"/>
+      <c r="P46" s="10"/>
+      <c r="Q46" s="10"/>
       <c r="R46" s="10"/>
       <c r="S46" s="11"/>
       <c r="T46" s="2">
@@ -5946,32 +6004,32 @@
       </c>
     </row>
     <row r="47" ht="14" customHeight="1" spans="1:26">
-      <c r="A47" s="9">
+      <c r="A47" s="13">
         <v>46</v>
       </c>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="13">
-        <v>1</v>
-      </c>
-      <c r="H47" s="9"/>
-      <c r="I47" s="9"/>
-      <c r="J47" s="9"/>
-      <c r="K47" s="9"/>
-      <c r="L47" s="9"/>
-      <c r="M47" s="9"/>
-      <c r="N47" s="13">
-        <v>1</v>
-      </c>
-      <c r="O47" s="9"/>
-      <c r="P47" s="9"/>
-      <c r="Q47" s="13">
-        <v>1</v>
-      </c>
-      <c r="R47" s="13">
+      <c r="B47" s="10"/>
+      <c r="C47" s="10"/>
+      <c r="D47" s="10"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="10">
+        <v>1</v>
+      </c>
+      <c r="H47" s="10"/>
+      <c r="I47" s="10"/>
+      <c r="J47" s="10"/>
+      <c r="K47" s="10"/>
+      <c r="L47" s="10"/>
+      <c r="M47" s="10"/>
+      <c r="N47" s="10">
+        <v>1</v>
+      </c>
+      <c r="O47" s="10"/>
+      <c r="P47" s="10"/>
+      <c r="Q47" s="10">
+        <v>1</v>
+      </c>
+      <c r="R47" s="10">
         <v>1</v>
       </c>
       <c r="S47" s="11"/>
@@ -5993,41 +6051,41 @@
       </c>
       <c r="X47" s="4">
         <f t="shared" si="4"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y47" s="4">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Z47" s="4">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48" ht="14" customHeight="1" spans="1:26">
-      <c r="A48" s="9">
+      <c r="A48" s="13">
         <v>47</v>
       </c>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="9"/>
-      <c r="H48" s="13">
-        <v>1</v>
-      </c>
-      <c r="I48" s="9"/>
-      <c r="J48" s="9"/>
-      <c r="K48" s="9"/>
-      <c r="L48" s="9"/>
-      <c r="M48" s="13">
-        <v>1</v>
-      </c>
-      <c r="N48" s="9"/>
-      <c r="O48" s="9"/>
-      <c r="P48" s="9"/>
-      <c r="Q48" s="9"/>
+      <c r="B48" s="10"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="10"/>
+      <c r="H48" s="10">
+        <v>1</v>
+      </c>
+      <c r="I48" s="10"/>
+      <c r="J48" s="10"/>
+      <c r="K48" s="10"/>
+      <c r="L48" s="10"/>
+      <c r="M48" s="10">
+        <v>1</v>
+      </c>
+      <c r="N48" s="10"/>
+      <c r="O48" s="10"/>
+      <c r="P48" s="10"/>
+      <c r="Q48" s="10"/>
       <c r="R48" s="10"/>
       <c r="S48" s="11"/>
       <c r="T48" s="2">
@@ -6048,11 +6106,11 @@
       </c>
       <c r="X48" s="4">
         <f t="shared" si="4"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y48" s="4">
         <f t="shared" si="5"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Z48" s="4">
         <f t="shared" si="6"/>
@@ -6060,31 +6118,31 @@
       </c>
     </row>
     <row r="49" ht="14" customHeight="1" spans="1:26">
-      <c r="A49" s="9">
+      <c r="A49" s="13">
         <v>48</v>
       </c>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="13">
-        <v>1</v>
-      </c>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
-      <c r="H49" s="9"/>
-      <c r="I49" s="9"/>
-      <c r="J49" s="9"/>
-      <c r="K49" s="9"/>
-      <c r="L49" s="9"/>
-      <c r="M49" s="9"/>
-      <c r="N49" s="9"/>
-      <c r="O49" s="9"/>
-      <c r="P49" s="9"/>
-      <c r="Q49" s="9"/>
-      <c r="R49" s="13">
-        <v>1</v>
-      </c>
-      <c r="S49" s="16"/>
+      <c r="B49" s="10"/>
+      <c r="C49" s="10"/>
+      <c r="D49" s="10"/>
+      <c r="E49" s="10">
+        <v>1</v>
+      </c>
+      <c r="F49" s="10"/>
+      <c r="G49" s="10"/>
+      <c r="H49" s="10"/>
+      <c r="I49" s="10"/>
+      <c r="J49" s="10"/>
+      <c r="K49" s="10"/>
+      <c r="L49" s="10"/>
+      <c r="M49" s="10"/>
+      <c r="N49" s="10"/>
+      <c r="O49" s="10"/>
+      <c r="P49" s="10"/>
+      <c r="Q49" s="10"/>
+      <c r="R49" s="10">
+        <v>1</v>
+      </c>
+      <c r="S49" s="11"/>
       <c r="T49" s="2">
         <f t="shared" si="7"/>
         <v>2</v>
@@ -6103,11 +6161,11 @@
       </c>
       <c r="X49" s="4">
         <f t="shared" si="4"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y49" s="4">
         <f t="shared" si="5"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Z49" s="4">
         <f t="shared" si="6"/>
@@ -6118,24 +6176,24 @@
       <c r="A50" s="9">
         <v>49</v>
       </c>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9"/>
-      <c r="H50" s="9"/>
-      <c r="I50" s="9"/>
-      <c r="J50" s="9"/>
-      <c r="K50" s="9"/>
-      <c r="L50" s="9"/>
-      <c r="M50" s="9"/>
-      <c r="N50" s="9"/>
-      <c r="O50" s="9"/>
-      <c r="P50" s="9"/>
-      <c r="Q50" s="9"/>
-      <c r="R50" s="9"/>
-      <c r="S50" s="16"/>
+      <c r="B50" s="10"/>
+      <c r="C50" s="10"/>
+      <c r="D50" s="10"/>
+      <c r="E50" s="10"/>
+      <c r="F50" s="10"/>
+      <c r="G50" s="10"/>
+      <c r="H50" s="10"/>
+      <c r="I50" s="10"/>
+      <c r="J50" s="10"/>
+      <c r="K50" s="10"/>
+      <c r="L50" s="10"/>
+      <c r="M50" s="10"/>
+      <c r="N50" s="10"/>
+      <c r="O50" s="10"/>
+      <c r="P50" s="10"/>
+      <c r="Q50" s="10"/>
+      <c r="R50" s="10"/>
+      <c r="S50" s="11"/>
       <c r="T50" s="2">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -6169,24 +6227,24 @@
       <c r="A51" s="9">
         <v>50</v>
       </c>
-      <c r="B51" s="9"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="9"/>
-      <c r="H51" s="9"/>
-      <c r="I51" s="9"/>
-      <c r="J51" s="9"/>
-      <c r="K51" s="9"/>
-      <c r="L51" s="9"/>
-      <c r="M51" s="9"/>
-      <c r="N51" s="9"/>
-      <c r="O51" s="9"/>
-      <c r="P51" s="9"/>
-      <c r="Q51" s="9"/>
-      <c r="R51" s="9"/>
-      <c r="S51" s="16"/>
+      <c r="B51" s="10"/>
+      <c r="C51" s="10"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="10"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="10"/>
+      <c r="J51" s="10"/>
+      <c r="K51" s="10"/>
+      <c r="L51" s="10"/>
+      <c r="M51" s="10"/>
+      <c r="N51" s="10"/>
+      <c r="O51" s="10"/>
+      <c r="P51" s="10"/>
+      <c r="Q51" s="10"/>
+      <c r="R51" s="10"/>
+      <c r="S51" s="11"/>
       <c r="T51" s="2">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -6220,24 +6278,24 @@
       <c r="A52" s="9">
         <v>51</v>
       </c>
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="9"/>
-      <c r="H52" s="9"/>
-      <c r="I52" s="9"/>
-      <c r="J52" s="9"/>
-      <c r="K52" s="9"/>
-      <c r="L52" s="9"/>
-      <c r="M52" s="9"/>
-      <c r="N52" s="9"/>
-      <c r="O52" s="9"/>
-      <c r="P52" s="9"/>
-      <c r="Q52" s="9"/>
-      <c r="R52" s="9"/>
-      <c r="S52" s="16"/>
+      <c r="B52" s="10"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="10"/>
+      <c r="E52" s="10"/>
+      <c r="F52" s="10"/>
+      <c r="G52" s="10"/>
+      <c r="H52" s="10"/>
+      <c r="I52" s="10"/>
+      <c r="J52" s="10"/>
+      <c r="K52" s="10"/>
+      <c r="L52" s="10"/>
+      <c r="M52" s="10"/>
+      <c r="N52" s="10"/>
+      <c r="O52" s="10"/>
+      <c r="P52" s="10"/>
+      <c r="Q52" s="10"/>
+      <c r="R52" s="10"/>
+      <c r="S52" s="11"/>
       <c r="T52" s="2">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -6268,10 +6326,67 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="X2:X52">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF7128"/>
+        <color rgb="FFFFEF9C"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="9" tint="-0.5"/>
+        <color theme="9" tint="0.8"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y2:Y52">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="9" tint="-0.5"/>
+        <color theme="9" tint="0.8"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z2:Z52">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="9" tint="-0.5"/>
+        <color theme="9" tint="0.8"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:S52">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="-0.25"/>
+        <color theme="4" tint="0.8"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="0.8"/>
+        <color theme="4" tint="-0.25"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="0" bottom="0" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="80" orientation="landscape"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:V1 X1:Z1 A2:Z52" formulaRange="1" unlockedFormula="1"/>
+    <ignoredError sqref="G1:S1 A1:E1 A46:Z52 T45:Z45 A45:R45 A40:Z44 T39:Z39 A39:R39 A32:Z38 T29:Z31 A29:R31 A28:Z28 T27:Z27 A27:R27 A22:Z26 T21:Z21 A21:R21 A19:Z20 T18:Z18 A18:R18 A9:Z17 T7:Z8 A7:R8 A4:Z6 T3:Z3 A3:R3 A2:Z2" formulaRange="1" unlockedFormula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10480" activeTab="2"/>
+    <workbookView windowWidth="7790" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="学生、老师" sheetId="5" r:id="rId1"/>
@@ -397,7 +397,7 @@
     <t>语3</t>
   </si>
   <si>
-    <t>微信窗口藏下面、C读“系”、我的天哪、周末作业（周记、好段、读书笔记）、以行践言、崇拜</t>
+    <t>微信窗口藏下面、C读“系”、我的天哪、周末作业（周记、好段、读书笔记）、以行践言、崇拜、父亲</t>
   </si>
   <si>
     <t>数1</t>
@@ -6386,7 +6386,7 @@
   <pageSetup paperSize="9" scale="80" orientation="landscape"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="G1:S1 A1:E1 A46:Z52 T45:Z45 A45:R45 A40:Z44 T39:Z39 A39:R39 A32:Z38 T29:Z31 A29:R31 A28:Z28 T27:Z27 A27:R27 A22:Z26 T21:Z21 A21:R21 A19:Z20 T18:Z18 A18:R18 A9:Z17 T7:Z8 A7:R8 A4:Z6 T3:Z3 A3:R3 A2:Z2" formulaRange="1" unlockedFormula="1"/>
+    <ignoredError sqref="A2:Z2 A3:R3 T3:Z3 A4:Z6 A7:R8 T7:Z8 A9:Z17 A18:R18 T18:Z18 A19:Z20 A21:R21 T21:Z21 A22:Z26 A27:R27 T27:Z27 A28:Z28 A29:R31 T29:Z31 A32:Z38 A39:R39 T39:Z39 A40:Z44 A45:R45 T45:Z45 A46:Z52 A1:E1 G1:S1" formulaRange="1" unlockedFormula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="7790" windowHeight="10480"/>
+    <workbookView windowWidth="20750" windowHeight="10030" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="学生、老师" sheetId="5" r:id="rId1"/>
@@ -3341,7 +3341,7 @@
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="4.07272727272727" customWidth="1"/>
-    <col min="2" max="19" width="5.14545454545455" customWidth="1"/>
+    <col min="2" max="19" width="3.23636363636364" customWidth="1"/>
     <col min="20" max="20" width="4.81818181818182" style="2" customWidth="1"/>
     <col min="21" max="22" width="4.81818181818182" style="3" customWidth="1"/>
     <col min="23" max="23" width="6.63636363636364" style="3" customWidth="1"/>
@@ -6386,7 +6386,7 @@
   <pageSetup paperSize="9" scale="80" orientation="landscape"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A2:Z2 A3:R3 T3:Z3 A4:Z6 A7:R8 T7:Z8 A9:Z17 A18:R18 T18:Z18 A19:Z20 A21:R21 T21:Z21 A22:Z26 A27:R27 T27:Z27 A28:Z28 A29:R31 T29:Z31 A32:Z38 A39:R39 T39:Z39 A40:Z44 A45:R45 T45:Z45 A46:Z52 A1:E1 G1:S1" formulaRange="1" unlockedFormula="1"/>
+    <ignoredError sqref="G1:S1 A1:E1 A46:Z52 T45:Z45 A45:R45 A40:Z44 T39:Z39 A39:R39 A32:Z38 T29:Z31 A29:R31 A28:Z28 T27:Z27 A27:R27 A22:Z26 T21:Z21 A21:R21 A19:Z20 T18:Z18 A18:R18 A9:Z17 T7:Z8 A7:R8 A4:Z6 T3:Z3 A3:R3 A2:Z2" formulaRange="1" unlockedFormula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10030" activeTab="4"/>
+    <workbookView windowWidth="20750" windowHeight="10030" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="学生、老师" sheetId="5" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="228">
   <si>
     <t>姓名</t>
   </si>
@@ -199,7 +199,7 @@
     <t>爆胎</t>
   </si>
   <si>
-    <t>踩桌子通行、对臭味敏感、头痛/腰痛/骨折/受伤、伙食、林奕扬来校吐槽/分享</t>
+    <t>踩桌子通行、对臭味敏感、头痛/腰痛/骨折/受伤、伙食、林奕扬来校吐槽/分享、座位下打球</t>
   </si>
   <si>
     <t>张桢烨</t>
@@ -583,6 +583,9 @@
     <t>零食饮料、背书、吃早餐</t>
   </si>
   <si>
+    <t>9班民族乐器</t>
+  </si>
+  <si>
     <t>日常</t>
   </si>
   <si>
@@ -689,6 +692,12 @@
   </si>
   <si>
     <t>崔母将崔玩手机事情告诉刘老师，手机被收，次日谈话</t>
+  </si>
+  <si>
+    <t>八上1.4</t>
+  </si>
+  <si>
+    <t>小测多人不过关，刘老师局部调查手机使用</t>
   </si>
   <si>
     <t>历史上的冤狱</t>
@@ -1517,7 +1526,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1611,6 +1620,12 @@
     </xf>
     <xf numFmtId="20" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1999,729 +2014,729 @@
   <dimension ref="A1:G78"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="7.59090909090909" style="39" customWidth="1"/>
-    <col min="2" max="7" width="25.8727272727273" style="40" customWidth="1"/>
+    <col min="1" max="1" width="7.59090909090909" style="41" customWidth="1"/>
+    <col min="2" max="7" width="25.8727272727273" style="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="38" customFormat="1" spans="1:7">
-      <c r="A1" s="41" t="s">
+    <row r="1" s="40" customFormat="1" spans="1:7">
+      <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="42" t="s">
+      <c r="B1" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="E1" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="42" t="s">
+      <c r="F1" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="42" t="s">
+      <c r="G1" s="44" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="C2" s="42" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" ht="39" spans="1:7">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="40" t="s">
+      <c r="D3" s="42" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="43" t="s">
+      <c r="A4" s="45" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="40" t="s">
+      <c r="C5" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="40" t="s">
+      <c r="D5" s="42" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="43" t="s">
+      <c r="A6" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="42" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" ht="208" spans="1:7">
-      <c r="A7" s="43" t="s">
+      <c r="A7" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="40" t="s">
+      <c r="C7" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="40" t="s">
+      <c r="D7" s="42" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="43" t="s">
+      <c r="A8" s="45" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="43" t="s">
+      <c r="A9" s="45" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="43" t="s">
+      <c r="A10" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="42" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="43" t="s">
+      <c r="A11" s="45" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="43" t="s">
+      <c r="A12" s="45" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="13" ht="39" spans="1:7">
-      <c r="A13" s="43" t="s">
+      <c r="A13" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="40" t="s">
+      <c r="D13" s="42" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="43" t="s">
+      <c r="A14" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="43" t="s">
+      <c r="A15" s="45" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="43" t="s">
+      <c r="A16" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="40" t="s">
+      <c r="C16" s="42" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="17" ht="26" spans="1:4">
-      <c r="A17" s="43" t="s">
+      <c r="A17" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="40" t="s">
+      <c r="C17" s="42" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="43" t="s">
+      <c r="A18" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="40" t="s">
+      <c r="D18" s="42" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="43" t="s">
+      <c r="A19" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="40" t="s">
+      <c r="D19" s="42" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="20" ht="26" spans="1:4">
-      <c r="A20" s="43" t="s">
+      <c r="A20" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="40" t="s">
+      <c r="B20" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="40" t="s">
+      <c r="C20" s="42" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="21" ht="39" spans="1:4">
-      <c r="A21" s="43" t="s">
+    <row r="21" ht="52" spans="1:4">
+      <c r="A21" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="B21" s="40" t="s">
+      <c r="B21" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="40" t="s">
+      <c r="C21" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="40" t="s">
+      <c r="D21" s="42" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="43" t="s">
+      <c r="A22" s="45" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="23" ht="26" spans="1:4">
-      <c r="A23" s="43" t="s">
+      <c r="A23" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="B23" s="40" t="s">
+      <c r="B23" s="42" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="24" ht="52" spans="1:4">
-      <c r="A24" s="43" t="s">
+      <c r="A24" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="40" t="s">
+      <c r="B24" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="C24" s="40" t="s">
+      <c r="C24" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="40" t="s">
+      <c r="D24" s="42" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="43" t="s">
+      <c r="A25" s="45" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="43" t="s">
+      <c r="A26" s="45" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="43" t="s">
+      <c r="A27" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="B27" s="40" t="s">
+      <c r="B27" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="C27" s="40" t="s">
+      <c r="C27" s="42" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="28" ht="91" spans="1:4">
-      <c r="A28" s="43" t="s">
+      <c r="A28" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="B28" s="40" t="s">
+      <c r="B28" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="C28" s="40" t="s">
+      <c r="C28" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="D28" s="40" t="s">
+      <c r="D28" s="42" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="43" t="s">
+      <c r="A29" s="45" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="43" t="s">
+      <c r="A30" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="B30" s="40" t="s">
+      <c r="B30" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="C30" s="40" t="s">
+      <c r="C30" s="42" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="43" t="s">
+      <c r="A31" s="45" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="43" t="s">
+      <c r="A32" s="45" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="43" t="s">
+      <c r="A33" s="45" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="43" t="s">
+      <c r="A34" s="45" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="43" t="s">
+      <c r="A35" s="45" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="43" t="s">
+      <c r="A36" s="45" t="s">
         <v>73</v>
       </c>
-      <c r="B36" s="40" t="s">
+      <c r="B36" s="42" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="37" ht="26" spans="1:7">
-      <c r="A37" s="43" t="s">
+      <c r="A37" s="45" t="s">
         <v>75</v>
       </c>
-      <c r="C37" s="40" t="s">
+      <c r="C37" s="42" t="s">
         <v>76</v>
       </c>
-      <c r="D37" s="40" t="s">
+      <c r="D37" s="42" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="43" t="s">
+      <c r="A38" s="45" t="s">
         <v>78</v>
       </c>
-      <c r="B38" s="40" t="s">
+      <c r="B38" s="42" t="s">
         <v>79</v>
       </c>
-      <c r="C38" s="44"/>
-      <c r="D38" s="44"/>
-      <c r="E38" s="44"/>
-      <c r="F38" s="44"/>
-      <c r="G38" s="44"/>
+      <c r="C38" s="46"/>
+      <c r="D38" s="46"/>
+      <c r="E38" s="46"/>
+      <c r="F38" s="46"/>
+      <c r="G38" s="46"/>
     </row>
     <row r="39" ht="26" spans="1:7">
-      <c r="A39" s="43" t="s">
+      <c r="A39" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="C39" s="40" t="s">
+      <c r="C39" s="42" t="s">
         <v>81</v>
       </c>
-      <c r="D39" s="40" t="s">
+      <c r="D39" s="42" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="43" t="s">
+      <c r="A40" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="B40" s="40" t="s">
+      <c r="B40" s="42" t="s">
         <v>84</v>
       </c>
-      <c r="C40" s="40" t="s">
+      <c r="C40" s="42" t="s">
         <v>85</v>
       </c>
-      <c r="D40" s="40" t="s">
+      <c r="D40" s="42" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="41" ht="195" spans="1:7">
-      <c r="A41" s="43" t="s">
+      <c r="A41" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="C41" s="40" t="s">
+      <c r="C41" s="42" t="s">
         <v>88</v>
       </c>
-      <c r="D41" s="40" t="s">
+      <c r="D41" s="42" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="43" t="s">
+      <c r="A42" s="45" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="43" t="s">
+      <c r="A43" s="45" t="s">
         <v>91</v>
       </c>
-      <c r="B43" s="40" t="s">
+      <c r="B43" s="42" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="44" ht="26" spans="1:7">
-      <c r="A44" s="43" t="s">
+      <c r="A44" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="B44" s="40" t="s">
+      <c r="B44" s="42" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="43" t="s">
+      <c r="A45" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="D45" s="40" t="s">
+      <c r="D45" s="42" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="43" t="s">
+      <c r="A46" s="45" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="43" t="s">
+      <c r="A47" s="45" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="43" t="s">
+      <c r="A48" s="45" t="s">
         <v>99</v>
       </c>
-      <c r="C48" s="40" t="s">
+      <c r="C48" s="42" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="43" t="s">
+      <c r="A49" s="45" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="50" ht="78" spans="1:7">
-      <c r="A50" s="43" t="s">
+      <c r="A50" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="C50" s="40" t="s">
+      <c r="C50" s="42" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="43" t="s">
+      <c r="A51" s="45" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="52" ht="26" spans="1:7">
-      <c r="A52" s="43" t="s">
+      <c r="A52" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="B52" s="40" t="s">
+      <c r="B52" s="42" t="s">
         <v>106</v>
       </c>
-      <c r="C52" s="40" t="s">
+      <c r="C52" s="42" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="53" ht="26" spans="1:7">
-      <c r="A53" s="39" t="s">
+      <c r="A53" s="41" t="s">
         <v>108</v>
       </c>
-      <c r="B53" s="40" t="s">
+      <c r="B53" s="42" t="s">
         <v>109</v>
       </c>
-      <c r="D53" s="44"/>
-      <c r="E53" s="44"/>
-      <c r="F53" s="44"/>
-      <c r="G53" s="44"/>
+      <c r="D53" s="46"/>
+      <c r="E53" s="46"/>
+      <c r="F53" s="46"/>
+      <c r="G53" s="46"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="39" t="s">
+      <c r="A54" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="B54" s="40" t="s">
+      <c r="B54" s="42" t="s">
         <v>111</v>
       </c>
-      <c r="C54" s="40" t="s">
+      <c r="C54" s="42" t="s">
         <v>112</v>
       </c>
-      <c r="D54" s="44"/>
-      <c r="E54" s="44"/>
-      <c r="F54" s="44"/>
-      <c r="G54" s="44"/>
+      <c r="D54" s="46"/>
+      <c r="E54" s="46"/>
+      <c r="F54" s="46"/>
+      <c r="G54" s="46"/>
     </row>
     <row r="55" ht="52" spans="1:7">
-      <c r="A55" s="39" t="s">
+      <c r="A55" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="B55" s="44"/>
-      <c r="C55" s="44"/>
-      <c r="D55" s="40" t="s">
+      <c r="B55" s="46"/>
+      <c r="C55" s="46"/>
+      <c r="D55" s="42" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="56" ht="65" spans="1:7">
-      <c r="A56" s="39" t="s">
+      <c r="A56" s="41" t="s">
         <v>115</v>
       </c>
-      <c r="B56" s="36" t="s">
+      <c r="B56" s="38" t="s">
         <v>116</v>
       </c>
-      <c r="C56" s="36"/>
-      <c r="D56" s="40" t="s">
+      <c r="C56" s="38"/>
+      <c r="D56" s="42" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="57" ht="117" spans="1:7">
-      <c r="A57" s="39" t="s">
+      <c r="A57" s="41" t="s">
         <v>118</v>
       </c>
-      <c r="B57" s="36" t="s">
+      <c r="B57" s="38" t="s">
         <v>119</v>
       </c>
-      <c r="C57" s="36" t="s">
+      <c r="C57" s="38" t="s">
         <v>120</v>
       </c>
-      <c r="D57" s="40" t="s">
+      <c r="D57" s="42" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="39" t="s">
+      <c r="A58" s="41" t="s">
         <v>122</v>
       </c>
-      <c r="B58" s="40" t="s">
+      <c r="B58" s="42" t="s">
         <v>123</v>
       </c>
-      <c r="C58" s="44"/>
-      <c r="D58" s="44"/>
-      <c r="E58" s="44"/>
-      <c r="F58" s="44"/>
-      <c r="G58" s="44"/>
+      <c r="C58" s="46"/>
+      <c r="D58" s="46"/>
+      <c r="E58" s="46"/>
+      <c r="F58" s="46"/>
+      <c r="G58" s="46"/>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="39" t="s">
+      <c r="A59" s="41" t="s">
         <v>124</v>
       </c>
-      <c r="B59" s="44"/>
-      <c r="C59" s="40" t="s">
+      <c r="B59" s="46"/>
+      <c r="C59" s="42" t="s">
         <v>125</v>
       </c>
-      <c r="D59" s="44"/>
-      <c r="E59" s="44"/>
-      <c r="F59" s="44"/>
-      <c r="G59" s="44"/>
+      <c r="D59" s="46"/>
+      <c r="E59" s="46"/>
+      <c r="F59" s="46"/>
+      <c r="G59" s="46"/>
     </row>
     <row r="60" ht="52" spans="1:7">
-      <c r="A60" s="39" t="s">
+      <c r="A60" s="41" t="s">
         <v>126</v>
       </c>
-      <c r="B60" s="44"/>
-      <c r="C60" s="44"/>
-      <c r="D60" s="40" t="s">
+      <c r="B60" s="46"/>
+      <c r="C60" s="46"/>
+      <c r="D60" s="42" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="39" t="s">
+      <c r="A61" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="B61" s="36" t="s">
+      <c r="B61" s="38" t="s">
         <v>129</v>
       </c>
-      <c r="C61" s="36"/>
-      <c r="D61" s="44"/>
-      <c r="E61" s="44"/>
-      <c r="F61" s="44"/>
-      <c r="G61" s="44"/>
+      <c r="C61" s="38"/>
+      <c r="D61" s="46"/>
+      <c r="E61" s="46"/>
+      <c r="F61" s="46"/>
+      <c r="G61" s="46"/>
     </row>
     <row r="62" ht="39" spans="1:7">
-      <c r="A62" s="39" t="s">
+      <c r="A62" s="41" t="s">
         <v>130</v>
       </c>
-      <c r="B62" s="44"/>
-      <c r="C62" s="44"/>
-      <c r="D62" s="40" t="s">
+      <c r="B62" s="46"/>
+      <c r="C62" s="46"/>
+      <c r="D62" s="42" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="63" ht="26" spans="1:7">
-      <c r="A63" s="39" t="s">
+      <c r="A63" s="41" t="s">
         <v>132</v>
       </c>
-      <c r="B63" s="36" t="s">
+      <c r="B63" s="38" t="s">
         <v>133</v>
       </c>
-      <c r="C63" s="36" t="s">
+      <c r="C63" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="D63" s="44"/>
-      <c r="E63" s="44"/>
-      <c r="F63" s="44"/>
-      <c r="G63" s="44"/>
+      <c r="D63" s="46"/>
+      <c r="E63" s="46"/>
+      <c r="F63" s="46"/>
+      <c r="G63" s="46"/>
     </row>
     <row r="64" ht="26" spans="1:7">
-      <c r="A64" s="39" t="s">
+      <c r="A64" s="41" t="s">
         <v>135</v>
       </c>
-      <c r="B64" s="44"/>
-      <c r="C64" s="44"/>
-      <c r="D64" s="40" t="s">
+      <c r="B64" s="46"/>
+      <c r="C64" s="46"/>
+      <c r="D64" s="42" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="65" ht="26" spans="1:7">
-      <c r="A65" s="39" t="s">
+      <c r="A65" s="41" t="s">
         <v>137</v>
       </c>
-      <c r="B65" s="45" t="s">
+      <c r="B65" s="47" t="s">
         <v>138</v>
       </c>
-      <c r="C65" s="44"/>
-      <c r="D65" s="44"/>
-      <c r="E65" s="44"/>
-      <c r="F65" s="44"/>
-      <c r="G65" s="44"/>
+      <c r="C65" s="46"/>
+      <c r="D65" s="46"/>
+      <c r="E65" s="46"/>
+      <c r="F65" s="46"/>
+      <c r="G65" s="46"/>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="39" t="s">
+      <c r="A66" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="B66" s="44"/>
-      <c r="C66" s="40" t="s">
+      <c r="B66" s="46"/>
+      <c r="C66" s="42" t="s">
         <v>140</v>
       </c>
-      <c r="D66" s="44"/>
-      <c r="E66" s="44"/>
-      <c r="F66" s="44"/>
-      <c r="G66" s="44"/>
+      <c r="D66" s="46"/>
+      <c r="E66" s="46"/>
+      <c r="F66" s="46"/>
+      <c r="G66" s="46"/>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="39" t="s">
+      <c r="A67" s="41" t="s">
         <v>141</v>
       </c>
-      <c r="B67" s="44"/>
-      <c r="C67" s="44"/>
+      <c r="B67" s="46"/>
+      <c r="C67" s="46"/>
     </row>
     <row r="68" ht="26" spans="1:7">
-      <c r="A68" s="39" t="s">
+      <c r="A68" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="B68" s="44"/>
-      <c r="C68" s="44"/>
-      <c r="D68" s="40" t="s">
+      <c r="B68" s="46"/>
+      <c r="C68" s="46"/>
+      <c r="D68" s="42" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="39" t="s">
+      <c r="A69" s="41" t="s">
         <v>144</v>
       </c>
-      <c r="B69" s="36" t="s">
+      <c r="B69" s="38" t="s">
         <v>145</v>
       </c>
-      <c r="C69" s="36"/>
+      <c r="C69" s="38"/>
     </row>
     <row r="70" ht="26" spans="1:7">
-      <c r="A70" s="39" t="s">
+      <c r="A70" s="41" t="s">
         <v>146</v>
       </c>
-      <c r="B70" s="36" t="s">
+      <c r="B70" s="38" t="s">
         <v>147</v>
       </c>
-      <c r="C70" s="36"/>
-      <c r="D70" s="44"/>
-      <c r="E70" s="44"/>
-      <c r="F70" s="44"/>
-      <c r="G70" s="44"/>
+      <c r="C70" s="38"/>
+      <c r="D70" s="46"/>
+      <c r="E70" s="46"/>
+      <c r="F70" s="46"/>
+      <c r="G70" s="46"/>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="39" t="s">
+      <c r="A71" s="41" t="s">
         <v>148</v>
       </c>
-      <c r="B71" s="44"/>
-      <c r="C71" s="44"/>
+      <c r="B71" s="46"/>
+      <c r="C71" s="46"/>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="39" t="s">
+      <c r="A72" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="B72" s="40" t="s">
+      <c r="B72" s="42" t="s">
         <v>150</v>
       </c>
-      <c r="C72" s="40" t="s">
+      <c r="C72" s="42" t="s">
         <v>151</v>
       </c>
-      <c r="D72" s="44"/>
-      <c r="E72" s="44"/>
-      <c r="F72" s="44"/>
-      <c r="G72" s="44"/>
+      <c r="D72" s="46"/>
+      <c r="E72" s="46"/>
+      <c r="F72" s="46"/>
+      <c r="G72" s="46"/>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="39" t="s">
+      <c r="A73" s="41" t="s">
         <v>152</v>
       </c>
-      <c r="B73" s="44"/>
-      <c r="C73" s="40" t="s">
+      <c r="B73" s="46"/>
+      <c r="C73" s="42" t="s">
         <v>153</v>
       </c>
-      <c r="D73" s="44"/>
-      <c r="E73" s="44"/>
-      <c r="F73" s="44"/>
-      <c r="G73" s="44"/>
+      <c r="D73" s="46"/>
+      <c r="E73" s="46"/>
+      <c r="F73" s="46"/>
+      <c r="G73" s="46"/>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="39" t="s">
+      <c r="A74" s="41" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="39" t="s">
+      <c r="A75" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="D75" s="44"/>
-      <c r="E75" s="44"/>
-      <c r="F75" s="44"/>
-      <c r="G75" s="44"/>
+      <c r="D75" s="46"/>
+      <c r="E75" s="46"/>
+      <c r="F75" s="46"/>
+      <c r="G75" s="46"/>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="39" t="s">
+      <c r="A76" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="B76" s="44"/>
-      <c r="C76" s="44"/>
-      <c r="D76" s="40" t="s">
+      <c r="B76" s="46"/>
+      <c r="C76" s="46"/>
+      <c r="D76" s="42" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="39" t="s">
+      <c r="A77" s="41" t="s">
         <v>158</v>
       </c>
-      <c r="B77" s="36"/>
-      <c r="C77" s="36"/>
+      <c r="B77" s="38"/>
+      <c r="C77" s="38"/>
     </row>
     <row r="78" ht="26" spans="1:7">
-      <c r="A78" s="46" t="s">
+      <c r="A78" s="48" t="s">
         <v>159</v>
       </c>
-      <c r="B78" s="40" t="s">
+      <c r="B78" s="42" t="s">
         <v>160</v>
       </c>
     </row>
@@ -2765,237 +2780,240 @@
   <dimension ref="A1:G51"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="6.64545454545455" style="30" customWidth="1"/>
-    <col min="2" max="7" width="16.4909090909091" style="31" customWidth="1"/>
-    <col min="8" max="16384" width="8.72727272727273" style="32"/>
+    <col min="1" max="1" width="6.64545454545455" style="32" customWidth="1"/>
+    <col min="2" max="7" width="16.4909090909091" style="33" customWidth="1"/>
+    <col min="8" max="16384" width="8.72727272727273" style="34"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="33"/>
-      <c r="B1" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="34" t="s">
+      <c r="A1" s="35"/>
+      <c r="B1" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="34" t="s">
+      <c r="E1" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="34" t="s">
+      <c r="F1" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="34" t="s">
+      <c r="G1" s="36" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="29" customFormat="1" ht="39" spans="1:7">
-      <c r="A2" s="35" t="s">
+    <row r="2" s="31" customFormat="1" ht="39" spans="1:7">
+      <c r="A2" s="37" t="s">
         <v>161</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36" t="s">
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38" t="s">
         <v>162</v>
       </c>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="39" t="s">
         <v>163</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="33" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="39" t="s">
         <v>165</v>
       </c>
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="33" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="39" t="s">
         <v>167</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="33" t="s">
         <v>168</v>
       </c>
-      <c r="D5" s="31" t="s">
+      <c r="D5" s="33" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="39" t="s">
         <v>170</v>
       </c>
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="33" t="s">
         <v>171</v>
       </c>
-      <c r="D6" s="31" t="s">
+      <c r="D6" s="33" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="39" t="s">
         <v>173</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="33" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="37"/>
-      <c r="D8" s="31" t="s">
+      <c r="A8" s="39"/>
+      <c r="D8" s="33" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="37"/>
+      <c r="A9" s="39"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="37"/>
+      <c r="A10" s="39"/>
+      <c r="B10" s="33" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="37"/>
+      <c r="A11" s="39"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="37"/>
+      <c r="A12" s="39"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="37"/>
+      <c r="A13" s="39"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="37"/>
+      <c r="A14" s="39"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="37"/>
+      <c r="A15" s="39"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="37"/>
+      <c r="A16" s="39"/>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="37"/>
+      <c r="A17" s="39"/>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="37"/>
+      <c r="A18" s="39"/>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="37"/>
+      <c r="A19" s="39"/>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="37"/>
+      <c r="A20" s="39"/>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="37"/>
+      <c r="A21" s="39"/>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="37"/>
+      <c r="A22" s="39"/>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="37"/>
+      <c r="A23" s="39"/>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="37"/>
+      <c r="A24" s="39"/>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="37"/>
+      <c r="A25" s="39"/>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="37"/>
+      <c r="A26" s="39"/>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="37"/>
+      <c r="A27" s="39"/>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="37"/>
+      <c r="A28" s="39"/>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="37"/>
+      <c r="A29" s="39"/>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="37"/>
+      <c r="A30" s="39"/>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="37"/>
+      <c r="A31" s="39"/>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="37"/>
+      <c r="A32" s="39"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="37"/>
+      <c r="A33" s="39"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="37"/>
+      <c r="A34" s="39"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="37"/>
+      <c r="A35" s="39"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="37"/>
+      <c r="A36" s="39"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="37"/>
+      <c r="A37" s="39"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="37"/>
-      <c r="B38" s="36"/>
-      <c r="C38" s="36"/>
-      <c r="D38" s="36"/>
-      <c r="E38" s="36"/>
-      <c r="F38" s="36"/>
-      <c r="G38" s="36"/>
+      <c r="A38" s="39"/>
+      <c r="B38" s="38"/>
+      <c r="C38" s="38"/>
+      <c r="D38" s="38"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="38"/>
+      <c r="G38" s="38"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="37"/>
-      <c r="B39" s="36"/>
-      <c r="C39" s="36"/>
-      <c r="D39" s="36"/>
-      <c r="E39" s="36"/>
-      <c r="F39" s="36"/>
-      <c r="G39" s="36"/>
+      <c r="A39" s="39"/>
+      <c r="B39" s="38"/>
+      <c r="C39" s="38"/>
+      <c r="D39" s="38"/>
+      <c r="E39" s="38"/>
+      <c r="F39" s="38"/>
+      <c r="G39" s="38"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="37"/>
+      <c r="A40" s="39"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="37"/>
+      <c r="A41" s="39"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="37"/>
+      <c r="A42" s="39"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="37"/>
+      <c r="A43" s="39"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="37"/>
+      <c r="A44" s="39"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="37"/>
+      <c r="A45" s="39"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="37"/>
+      <c r="A46" s="39"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="37"/>
+      <c r="A47" s="39"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="37"/>
+      <c r="A48" s="39"/>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="37"/>
+      <c r="A49" s="39"/>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="37"/>
+      <c r="A50" s="39"/>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="37"/>
+      <c r="A51" s="39"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3006,7 +3024,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="35.1818181818182" style="20" customWidth="1"/>
@@ -3017,118 +3035,118 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="20" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="20" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="20" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" ht="28" spans="1:3">
       <c r="A4" s="20" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" ht="42" spans="1:3">
       <c r="A5" s="26" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" ht="56" spans="1:3">
       <c r="A6" s="27"/>
       <c r="B6" s="20" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" ht="28" spans="1:3">
       <c r="A7" s="20" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" ht="28" spans="1:3">
       <c r="A8" s="20" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="20" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="20" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="20" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C11" s="28">
         <v>0.440972222222222</v>
@@ -3139,36 +3157,34 @@
         <v>60</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="24"/>
       <c r="B13" s="20" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C13" s="25" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="29" t="s">
+        <v>211</v>
+      </c>
+      <c r="B14" s="20" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="20" t="s">
-        <v>210</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>208</v>
-      </c>
       <c r="C14" s="25" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="15" ht="42" spans="1:3">
-      <c r="A15" s="20" t="s">
         <v>212</v>
       </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="30"/>
       <c r="B15" s="20" t="s">
         <v>213</v>
       </c>
@@ -3176,10 +3192,22 @@
         <v>214</v>
       </c>
     </row>
+    <row r="16" ht="42" spans="1:3">
+      <c r="A16" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>217</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -3199,10 +3227,10 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="C1" s="21" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -3337,20 +3365,21 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z52"/>
+  <dimension ref="A1:AM52"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="4.07272727272727" customWidth="1"/>
     <col min="2" max="19" width="3.23636363636364" customWidth="1"/>
-    <col min="20" max="20" width="4.81818181818182" style="2" customWidth="1"/>
-    <col min="21" max="22" width="4.81818181818182" style="3" customWidth="1"/>
+    <col min="20" max="20" width="5.23636363636364" style="2" customWidth="1"/>
+    <col min="21" max="22" width="5.23636363636364" style="3" customWidth="1"/>
     <col min="23" max="23" width="6.63636363636364" style="3" customWidth="1"/>
-    <col min="24" max="26" width="4.81818181818182" style="4" customWidth="1"/>
+    <col min="24" max="26" width="5.23636363636364" style="4" customWidth="1"/>
+    <col min="27" max="39" width="3.23636363636364" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28" spans="1:26">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:39">
       <c r="A1" s="5" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B1" s="5">
         <v>5</v>
@@ -3407,28 +3436,67 @@
         <v>31</v>
       </c>
       <c r="T1" s="7" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="U1" s="7" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="V1" s="7" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="W1" s="7" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="X1" s="8" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Y1" s="8" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="2" ht="14" customHeight="1" spans="1:26">
+        <v>227</v>
+      </c>
+      <c r="AA1" s="5">
+        <v>4</v>
+      </c>
+      <c r="AB1" s="5">
+        <v>5</v>
+      </c>
+      <c r="AC1" s="5">
+        <v>6</v>
+      </c>
+      <c r="AD1" s="5">
+        <v>7</v>
+      </c>
+      <c r="AE1" s="5">
+        <v>8</v>
+      </c>
+      <c r="AF1" s="5">
+        <v>9</v>
+      </c>
+      <c r="AG1" s="5">
+        <v>12</v>
+      </c>
+      <c r="AH1" s="5">
+        <v>13</v>
+      </c>
+      <c r="AI1" s="5">
+        <v>14</v>
+      </c>
+      <c r="AJ1" s="5">
+        <v>15</v>
+      </c>
+      <c r="AK1" s="5">
+        <v>16</v>
+      </c>
+      <c r="AL1" s="5">
+        <v>19</v>
+      </c>
+      <c r="AM1" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" ht="14" customHeight="1" spans="1:39">
       <c r="A2" s="9">
         <v>1</v>
       </c>
@@ -3478,8 +3546,21 @@
         <f>RANK(V2,V$2:V$52,0)</f>
         <v>35</v>
       </c>
-    </row>
-    <row r="3" ht="14" customHeight="1" spans="1:26">
+      <c r="AA2" s="10"/>
+      <c r="AB2" s="10"/>
+      <c r="AC2" s="10"/>
+      <c r="AD2" s="10"/>
+      <c r="AE2" s="10"/>
+      <c r="AF2" s="10"/>
+      <c r="AG2" s="10"/>
+      <c r="AH2" s="10"/>
+      <c r="AI2" s="10"/>
+      <c r="AJ2" s="10"/>
+      <c r="AK2" s="10"/>
+      <c r="AL2" s="10"/>
+      <c r="AM2" s="10"/>
+    </row>
+    <row r="3" ht="14" customHeight="1" spans="1:39">
       <c r="A3" s="13">
         <v>2</v>
       </c>
@@ -3545,8 +3626,23 @@
         <f t="shared" ref="Z3:Z34" si="2">RANK(V3,V$2:V$52,0)</f>
         <v>5</v>
       </c>
-    </row>
-    <row r="4" ht="14" customHeight="1" spans="1:26">
+      <c r="AA3" s="10">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="10"/>
+      <c r="AC3" s="10"/>
+      <c r="AD3" s="10"/>
+      <c r="AE3" s="10"/>
+      <c r="AF3" s="10"/>
+      <c r="AG3" s="10"/>
+      <c r="AH3" s="10"/>
+      <c r="AI3" s="10"/>
+      <c r="AJ3" s="10"/>
+      <c r="AK3" s="10"/>
+      <c r="AL3" s="10"/>
+      <c r="AM3" s="10"/>
+    </row>
+    <row r="4" ht="14" customHeight="1" spans="1:39">
       <c r="A4" s="13">
         <v>3</v>
       </c>
@@ -3598,8 +3694,23 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="5" ht="14" customHeight="1" spans="1:26">
+      <c r="AA4" s="10">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="10"/>
+      <c r="AC4" s="10"/>
+      <c r="AD4" s="10"/>
+      <c r="AE4" s="10"/>
+      <c r="AF4" s="10"/>
+      <c r="AG4" s="10"/>
+      <c r="AH4" s="10"/>
+      <c r="AI4" s="10"/>
+      <c r="AJ4" s="10"/>
+      <c r="AK4" s="10"/>
+      <c r="AL4" s="10"/>
+      <c r="AM4" s="10"/>
+    </row>
+    <row r="5" ht="14" customHeight="1" spans="1:39">
       <c r="A5" s="13">
         <v>4</v>
       </c>
@@ -3653,8 +3764,21 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="6" ht="14" customHeight="1" spans="1:26">
+      <c r="AA5" s="10"/>
+      <c r="AB5" s="10"/>
+      <c r="AC5" s="10"/>
+      <c r="AD5" s="10"/>
+      <c r="AE5" s="10"/>
+      <c r="AF5" s="10"/>
+      <c r="AG5" s="10"/>
+      <c r="AH5" s="10"/>
+      <c r="AI5" s="10"/>
+      <c r="AJ5" s="10"/>
+      <c r="AK5" s="10"/>
+      <c r="AL5" s="10"/>
+      <c r="AM5" s="10"/>
+    </row>
+    <row r="6" ht="14" customHeight="1" spans="1:39">
       <c r="A6" s="13">
         <v>5</v>
       </c>
@@ -3710,8 +3834,21 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="7" ht="14" customHeight="1" spans="1:26">
+      <c r="AA6" s="10"/>
+      <c r="AB6" s="10"/>
+      <c r="AC6" s="10"/>
+      <c r="AD6" s="10"/>
+      <c r="AE6" s="10"/>
+      <c r="AF6" s="10"/>
+      <c r="AG6" s="10"/>
+      <c r="AH6" s="10"/>
+      <c r="AI6" s="10"/>
+      <c r="AJ6" s="10"/>
+      <c r="AK6" s="10"/>
+      <c r="AL6" s="10"/>
+      <c r="AM6" s="10"/>
+    </row>
+    <row r="7" ht="14" customHeight="1" spans="1:39">
       <c r="A7" s="13">
         <v>6</v>
       </c>
@@ -3787,8 +3924,23 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="8" ht="14" customHeight="1" spans="1:26">
+      <c r="AA7" s="10">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="10"/>
+      <c r="AC7" s="10"/>
+      <c r="AD7" s="10"/>
+      <c r="AE7" s="10"/>
+      <c r="AF7" s="10"/>
+      <c r="AG7" s="10"/>
+      <c r="AH7" s="10"/>
+      <c r="AI7" s="10"/>
+      <c r="AJ7" s="10"/>
+      <c r="AK7" s="10"/>
+      <c r="AL7" s="10"/>
+      <c r="AM7" s="10"/>
+    </row>
+    <row r="8" ht="14" customHeight="1" spans="1:39">
       <c r="A8" s="13">
         <v>7</v>
       </c>
@@ -3852,8 +4004,23 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-    </row>
-    <row r="9" ht="14" customHeight="1" spans="1:26">
+      <c r="AA8" s="10">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="10"/>
+      <c r="AC8" s="10"/>
+      <c r="AD8" s="10"/>
+      <c r="AE8" s="10"/>
+      <c r="AF8" s="10"/>
+      <c r="AG8" s="10"/>
+      <c r="AH8" s="10"/>
+      <c r="AI8" s="10"/>
+      <c r="AJ8" s="10"/>
+      <c r="AK8" s="10"/>
+      <c r="AL8" s="10"/>
+      <c r="AM8" s="10"/>
+    </row>
+    <row r="9" ht="14" customHeight="1" spans="1:39">
       <c r="A9" s="9">
         <v>8</v>
       </c>
@@ -3903,8 +4070,21 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-    </row>
-    <row r="10" ht="14" customHeight="1" spans="1:26">
+      <c r="AA9" s="10"/>
+      <c r="AB9" s="10"/>
+      <c r="AC9" s="10"/>
+      <c r="AD9" s="10"/>
+      <c r="AE9" s="10"/>
+      <c r="AF9" s="10"/>
+      <c r="AG9" s="10"/>
+      <c r="AH9" s="10"/>
+      <c r="AI9" s="10"/>
+      <c r="AJ9" s="10"/>
+      <c r="AK9" s="10"/>
+      <c r="AL9" s="10"/>
+      <c r="AM9" s="10"/>
+    </row>
+    <row r="10" ht="14" customHeight="1" spans="1:39">
       <c r="A10" s="13">
         <v>9</v>
       </c>
@@ -3960,8 +4140,21 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="11" ht="14" customHeight="1" spans="1:26">
+      <c r="AA10" s="10"/>
+      <c r="AB10" s="10"/>
+      <c r="AC10" s="10"/>
+      <c r="AD10" s="10"/>
+      <c r="AE10" s="10"/>
+      <c r="AF10" s="10"/>
+      <c r="AG10" s="10"/>
+      <c r="AH10" s="10"/>
+      <c r="AI10" s="10"/>
+      <c r="AJ10" s="10"/>
+      <c r="AK10" s="10"/>
+      <c r="AL10" s="10"/>
+      <c r="AM10" s="10"/>
+    </row>
+    <row r="11" ht="14" customHeight="1" spans="1:39">
       <c r="A11" s="13">
         <v>10</v>
       </c>
@@ -4013,8 +4206,21 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="12" ht="14" customHeight="1" spans="1:26">
+      <c r="AA11" s="10"/>
+      <c r="AB11" s="10"/>
+      <c r="AC11" s="10"/>
+      <c r="AD11" s="10"/>
+      <c r="AE11" s="10"/>
+      <c r="AF11" s="10"/>
+      <c r="AG11" s="10"/>
+      <c r="AH11" s="10"/>
+      <c r="AI11" s="10"/>
+      <c r="AJ11" s="10"/>
+      <c r="AK11" s="10"/>
+      <c r="AL11" s="10"/>
+      <c r="AM11" s="10"/>
+    </row>
+    <row r="12" ht="14" customHeight="1" spans="1:39">
       <c r="A12" s="13">
         <v>11</v>
       </c>
@@ -4074,8 +4280,23 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="13" ht="14" customHeight="1" spans="1:26">
+      <c r="AA12" s="10">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="10"/>
+      <c r="AC12" s="10"/>
+      <c r="AD12" s="10"/>
+      <c r="AE12" s="10"/>
+      <c r="AF12" s="10"/>
+      <c r="AG12" s="10"/>
+      <c r="AH12" s="10"/>
+      <c r="AI12" s="10"/>
+      <c r="AJ12" s="10"/>
+      <c r="AK12" s="10"/>
+      <c r="AL12" s="10"/>
+      <c r="AM12" s="10"/>
+    </row>
+    <row r="13" ht="14" customHeight="1" spans="1:39">
       <c r="A13" s="13">
         <v>12</v>
       </c>
@@ -4127,8 +4348,21 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="14" ht="14" customHeight="1" spans="1:26">
+      <c r="AA13" s="10"/>
+      <c r="AB13" s="10"/>
+      <c r="AC13" s="10"/>
+      <c r="AD13" s="10"/>
+      <c r="AE13" s="10"/>
+      <c r="AF13" s="10"/>
+      <c r="AG13" s="10"/>
+      <c r="AH13" s="10"/>
+      <c r="AI13" s="10"/>
+      <c r="AJ13" s="10"/>
+      <c r="AK13" s="10"/>
+      <c r="AL13" s="10"/>
+      <c r="AM13" s="10"/>
+    </row>
+    <row r="14" ht="14" customHeight="1" spans="1:39">
       <c r="A14" s="13">
         <v>13</v>
       </c>
@@ -4188,8 +4422,23 @@
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-    </row>
-    <row r="15" ht="14" customHeight="1" spans="1:26">
+      <c r="AA14" s="10">
+        <v>2</v>
+      </c>
+      <c r="AB14" s="10"/>
+      <c r="AC14" s="10"/>
+      <c r="AD14" s="10"/>
+      <c r="AE14" s="10"/>
+      <c r="AF14" s="10"/>
+      <c r="AG14" s="10"/>
+      <c r="AH14" s="10"/>
+      <c r="AI14" s="10"/>
+      <c r="AJ14" s="10"/>
+      <c r="AK14" s="10"/>
+      <c r="AL14" s="10"/>
+      <c r="AM14" s="10"/>
+    </row>
+    <row r="15" ht="14" customHeight="1" spans="1:39">
       <c r="A15" s="13">
         <v>14</v>
       </c>
@@ -4241,8 +4490,23 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="16" ht="14" customHeight="1" spans="1:26">
+      <c r="AA15" s="10">
+        <v>1</v>
+      </c>
+      <c r="AB15" s="10"/>
+      <c r="AC15" s="10"/>
+      <c r="AD15" s="10"/>
+      <c r="AE15" s="10"/>
+      <c r="AF15" s="10"/>
+      <c r="AG15" s="10"/>
+      <c r="AH15" s="10"/>
+      <c r="AI15" s="10"/>
+      <c r="AJ15" s="10"/>
+      <c r="AK15" s="10"/>
+      <c r="AL15" s="10"/>
+      <c r="AM15" s="10"/>
+    </row>
+    <row r="16" ht="14" customHeight="1" spans="1:39">
       <c r="A16" s="13">
         <v>15</v>
       </c>
@@ -4294,8 +4558,21 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="17" ht="14" customHeight="1" spans="1:26">
+      <c r="AA16" s="10"/>
+      <c r="AB16" s="10"/>
+      <c r="AC16" s="10"/>
+      <c r="AD16" s="10"/>
+      <c r="AE16" s="10"/>
+      <c r="AF16" s="10"/>
+      <c r="AG16" s="10"/>
+      <c r="AH16" s="10"/>
+      <c r="AI16" s="10"/>
+      <c r="AJ16" s="10"/>
+      <c r="AK16" s="10"/>
+      <c r="AL16" s="10"/>
+      <c r="AM16" s="10"/>
+    </row>
+    <row r="17" ht="14" customHeight="1" spans="1:39">
       <c r="A17" s="9">
         <v>16</v>
       </c>
@@ -4345,8 +4622,21 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-    </row>
-    <row r="18" ht="14" customHeight="1" spans="1:26">
+      <c r="AA17" s="10"/>
+      <c r="AB17" s="10"/>
+      <c r="AC17" s="10"/>
+      <c r="AD17" s="10"/>
+      <c r="AE17" s="10"/>
+      <c r="AF17" s="10"/>
+      <c r="AG17" s="10"/>
+      <c r="AH17" s="10"/>
+      <c r="AI17" s="10"/>
+      <c r="AJ17" s="10"/>
+      <c r="AK17" s="10"/>
+      <c r="AL17" s="10"/>
+      <c r="AM17" s="10"/>
+    </row>
+    <row r="18" ht="14" customHeight="1" spans="1:39">
       <c r="A18" s="13">
         <v>17</v>
       </c>
@@ -4402,8 +4692,23 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="19" ht="14" customHeight="1" spans="1:26">
+      <c r="AA18" s="10">
+        <v>1</v>
+      </c>
+      <c r="AB18" s="10"/>
+      <c r="AC18" s="10"/>
+      <c r="AD18" s="10"/>
+      <c r="AE18" s="10"/>
+      <c r="AF18" s="10"/>
+      <c r="AG18" s="10"/>
+      <c r="AH18" s="10"/>
+      <c r="AI18" s="10"/>
+      <c r="AJ18" s="10"/>
+      <c r="AK18" s="10"/>
+      <c r="AL18" s="10"/>
+      <c r="AM18" s="10"/>
+    </row>
+    <row r="19" ht="14" customHeight="1" spans="1:39">
       <c r="A19" s="13">
         <v>18</v>
       </c>
@@ -4455,8 +4760,21 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="20" ht="14" customHeight="1" spans="1:26">
+      <c r="AA19" s="10"/>
+      <c r="AB19" s="10"/>
+      <c r="AC19" s="10"/>
+      <c r="AD19" s="10"/>
+      <c r="AE19" s="10"/>
+      <c r="AF19" s="10"/>
+      <c r="AG19" s="10"/>
+      <c r="AH19" s="10"/>
+      <c r="AI19" s="10"/>
+      <c r="AJ19" s="10"/>
+      <c r="AK19" s="10"/>
+      <c r="AL19" s="10"/>
+      <c r="AM19" s="10"/>
+    </row>
+    <row r="20" ht="14" customHeight="1" spans="1:39">
       <c r="A20" s="13">
         <v>19</v>
       </c>
@@ -4510,8 +4828,21 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="21" ht="14" customHeight="1" spans="1:26">
+      <c r="AA20" s="10"/>
+      <c r="AB20" s="10"/>
+      <c r="AC20" s="10"/>
+      <c r="AD20" s="10"/>
+      <c r="AE20" s="10"/>
+      <c r="AF20" s="10"/>
+      <c r="AG20" s="10"/>
+      <c r="AH20" s="10"/>
+      <c r="AI20" s="10"/>
+      <c r="AJ20" s="10"/>
+      <c r="AK20" s="10"/>
+      <c r="AL20" s="10"/>
+      <c r="AM20" s="10"/>
+    </row>
+    <row r="21" ht="14" customHeight="1" spans="1:39">
       <c r="A21" s="13">
         <v>20</v>
       </c>
@@ -4571,8 +4902,23 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-    </row>
-    <row r="22" ht="14" customHeight="1" spans="1:26">
+      <c r="AA21" s="10">
+        <v>1</v>
+      </c>
+      <c r="AB21" s="10"/>
+      <c r="AC21" s="10"/>
+      <c r="AD21" s="10"/>
+      <c r="AE21" s="10"/>
+      <c r="AF21" s="10"/>
+      <c r="AG21" s="10"/>
+      <c r="AH21" s="10"/>
+      <c r="AI21" s="10"/>
+      <c r="AJ21" s="10"/>
+      <c r="AK21" s="10"/>
+      <c r="AL21" s="10"/>
+      <c r="AM21" s="10"/>
+    </row>
+    <row r="22" ht="14" customHeight="1" spans="1:39">
       <c r="A22" s="9">
         <v>21</v>
       </c>
@@ -4622,8 +4968,21 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-    </row>
-    <row r="23" ht="14" customHeight="1" spans="1:26">
+      <c r="AA22" s="10"/>
+      <c r="AB22" s="10"/>
+      <c r="AC22" s="10"/>
+      <c r="AD22" s="10"/>
+      <c r="AE22" s="10"/>
+      <c r="AF22" s="10"/>
+      <c r="AG22" s="10"/>
+      <c r="AH22" s="10"/>
+      <c r="AI22" s="10"/>
+      <c r="AJ22" s="10"/>
+      <c r="AK22" s="10"/>
+      <c r="AL22" s="10"/>
+      <c r="AM22" s="10"/>
+    </row>
+    <row r="23" ht="14" customHeight="1" spans="1:39">
       <c r="A23" s="13">
         <v>22</v>
       </c>
@@ -4683,8 +5042,23 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-    </row>
-    <row r="24" ht="14" customHeight="1" spans="1:26">
+      <c r="AA23" s="10">
+        <v>1</v>
+      </c>
+      <c r="AB23" s="10"/>
+      <c r="AC23" s="10"/>
+      <c r="AD23" s="10"/>
+      <c r="AE23" s="10"/>
+      <c r="AF23" s="10"/>
+      <c r="AG23" s="10"/>
+      <c r="AH23" s="10"/>
+      <c r="AI23" s="10"/>
+      <c r="AJ23" s="10"/>
+      <c r="AK23" s="10"/>
+      <c r="AL23" s="10"/>
+      <c r="AM23" s="10"/>
+    </row>
+    <row r="24" ht="14" customHeight="1" spans="1:39">
       <c r="A24" s="9">
         <v>23</v>
       </c>
@@ -4734,8 +5108,21 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-    </row>
-    <row r="25" ht="14" customHeight="1" spans="1:26">
+      <c r="AA24" s="10"/>
+      <c r="AB24" s="10"/>
+      <c r="AC24" s="10"/>
+      <c r="AD24" s="10"/>
+      <c r="AE24" s="10"/>
+      <c r="AF24" s="10"/>
+      <c r="AG24" s="10"/>
+      <c r="AH24" s="10"/>
+      <c r="AI24" s="10"/>
+      <c r="AJ24" s="10"/>
+      <c r="AK24" s="10"/>
+      <c r="AL24" s="10"/>
+      <c r="AM24" s="10"/>
+    </row>
+    <row r="25" ht="14" customHeight="1" spans="1:39">
       <c r="A25" s="9">
         <v>24</v>
       </c>
@@ -4785,8 +5172,21 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-    </row>
-    <row r="26" ht="14" customHeight="1" spans="1:26">
+      <c r="AA25" s="10"/>
+      <c r="AB25" s="10"/>
+      <c r="AC25" s="10"/>
+      <c r="AD25" s="10"/>
+      <c r="AE25" s="10"/>
+      <c r="AF25" s="10"/>
+      <c r="AG25" s="10"/>
+      <c r="AH25" s="10"/>
+      <c r="AI25" s="10"/>
+      <c r="AJ25" s="10"/>
+      <c r="AK25" s="10"/>
+      <c r="AL25" s="10"/>
+      <c r="AM25" s="10"/>
+    </row>
+    <row r="26" ht="14" customHeight="1" spans="1:39">
       <c r="A26" s="9">
         <v>25</v>
       </c>
@@ -4836,8 +5236,21 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-    </row>
-    <row r="27" ht="14" customHeight="1" spans="1:26">
+      <c r="AA26" s="10"/>
+      <c r="AB26" s="10"/>
+      <c r="AC26" s="10"/>
+      <c r="AD26" s="10"/>
+      <c r="AE26" s="10"/>
+      <c r="AF26" s="10"/>
+      <c r="AG26" s="10"/>
+      <c r="AH26" s="10"/>
+      <c r="AI26" s="10"/>
+      <c r="AJ26" s="10"/>
+      <c r="AK26" s="10"/>
+      <c r="AL26" s="10"/>
+      <c r="AM26" s="10"/>
+    </row>
+    <row r="27" ht="14" customHeight="1" spans="1:39">
       <c r="A27" s="13">
         <v>26</v>
       </c>
@@ -4897,8 +5310,23 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="28" ht="14" customHeight="1" spans="1:26">
+      <c r="AA27" s="10">
+        <v>1</v>
+      </c>
+      <c r="AB27" s="10"/>
+      <c r="AC27" s="10"/>
+      <c r="AD27" s="10"/>
+      <c r="AE27" s="10"/>
+      <c r="AF27" s="10"/>
+      <c r="AG27" s="10"/>
+      <c r="AH27" s="10"/>
+      <c r="AI27" s="10"/>
+      <c r="AJ27" s="10"/>
+      <c r="AK27" s="10"/>
+      <c r="AL27" s="10"/>
+      <c r="AM27" s="10"/>
+    </row>
+    <row r="28" ht="14" customHeight="1" spans="1:39">
       <c r="A28" s="13">
         <v>27</v>
       </c>
@@ -4952,8 +5380,21 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="29" ht="14" customHeight="1" spans="1:26">
+      <c r="AA28" s="10"/>
+      <c r="AB28" s="10"/>
+      <c r="AC28" s="10"/>
+      <c r="AD28" s="10"/>
+      <c r="AE28" s="10"/>
+      <c r="AF28" s="10"/>
+      <c r="AG28" s="10"/>
+      <c r="AH28" s="10"/>
+      <c r="AI28" s="10"/>
+      <c r="AJ28" s="10"/>
+      <c r="AK28" s="10"/>
+      <c r="AL28" s="10"/>
+      <c r="AM28" s="10"/>
+    </row>
+    <row r="29" ht="14" customHeight="1" spans="1:39">
       <c r="A29" s="13">
         <v>28</v>
       </c>
@@ -5009,8 +5450,23 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="30" ht="14" customHeight="1" spans="1:26">
+      <c r="AA29" s="10">
+        <v>1</v>
+      </c>
+      <c r="AB29" s="10"/>
+      <c r="AC29" s="10"/>
+      <c r="AD29" s="10"/>
+      <c r="AE29" s="10"/>
+      <c r="AF29" s="10"/>
+      <c r="AG29" s="10"/>
+      <c r="AH29" s="10"/>
+      <c r="AI29" s="10"/>
+      <c r="AJ29" s="10"/>
+      <c r="AK29" s="10"/>
+      <c r="AL29" s="10"/>
+      <c r="AM29" s="10"/>
+    </row>
+    <row r="30" ht="14" customHeight="1" spans="1:39">
       <c r="A30" s="13">
         <v>29</v>
       </c>
@@ -5070,8 +5526,23 @@
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-    </row>
-    <row r="31" ht="14" customHeight="1" spans="1:26">
+      <c r="AA30" s="10">
+        <v>1</v>
+      </c>
+      <c r="AB30" s="10"/>
+      <c r="AC30" s="10"/>
+      <c r="AD30" s="10"/>
+      <c r="AE30" s="10"/>
+      <c r="AF30" s="10"/>
+      <c r="AG30" s="10"/>
+      <c r="AH30" s="10"/>
+      <c r="AI30" s="10"/>
+      <c r="AJ30" s="10"/>
+      <c r="AK30" s="10"/>
+      <c r="AL30" s="10"/>
+      <c r="AM30" s="10"/>
+    </row>
+    <row r="31" ht="14" customHeight="1" spans="1:39">
       <c r="A31" s="13">
         <v>30</v>
       </c>
@@ -5135,8 +5606,23 @@
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-    </row>
-    <row r="32" ht="14" customHeight="1" spans="1:26">
+      <c r="AA31" s="10">
+        <v>1</v>
+      </c>
+      <c r="AB31" s="10"/>
+      <c r="AC31" s="10"/>
+      <c r="AD31" s="10"/>
+      <c r="AE31" s="10"/>
+      <c r="AF31" s="10"/>
+      <c r="AG31" s="10"/>
+      <c r="AH31" s="10"/>
+      <c r="AI31" s="10"/>
+      <c r="AJ31" s="10"/>
+      <c r="AK31" s="10"/>
+      <c r="AL31" s="10"/>
+      <c r="AM31" s="10"/>
+    </row>
+    <row r="32" ht="14" customHeight="1" spans="1:39">
       <c r="A32" s="13">
         <v>31</v>
       </c>
@@ -5188,8 +5674,23 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="33" ht="14" customHeight="1" spans="1:26">
+      <c r="AA32" s="10">
+        <v>1</v>
+      </c>
+      <c r="AB32" s="10"/>
+      <c r="AC32" s="10"/>
+      <c r="AD32" s="10"/>
+      <c r="AE32" s="10"/>
+      <c r="AF32" s="10"/>
+      <c r="AG32" s="10"/>
+      <c r="AH32" s="10"/>
+      <c r="AI32" s="10"/>
+      <c r="AJ32" s="10"/>
+      <c r="AK32" s="10"/>
+      <c r="AL32" s="10"/>
+      <c r="AM32" s="10"/>
+    </row>
+    <row r="33" ht="14" customHeight="1" spans="1:39">
       <c r="A33" s="9">
         <v>32</v>
       </c>
@@ -5239,8 +5740,21 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-    </row>
-    <row r="34" ht="14" customHeight="1" spans="1:26">
+      <c r="AA33" s="10"/>
+      <c r="AB33" s="10"/>
+      <c r="AC33" s="10"/>
+      <c r="AD33" s="10"/>
+      <c r="AE33" s="10"/>
+      <c r="AF33" s="10"/>
+      <c r="AG33" s="10"/>
+      <c r="AH33" s="10"/>
+      <c r="AI33" s="10"/>
+      <c r="AJ33" s="10"/>
+      <c r="AK33" s="10"/>
+      <c r="AL33" s="10"/>
+      <c r="AM33" s="10"/>
+    </row>
+    <row r="34" ht="14" customHeight="1" spans="1:39">
       <c r="A34" s="9">
         <v>33</v>
       </c>
@@ -5290,8 +5804,21 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-    </row>
-    <row r="35" ht="14" customHeight="1" spans="1:26">
+      <c r="AA34" s="10"/>
+      <c r="AB34" s="10"/>
+      <c r="AC34" s="10"/>
+      <c r="AD34" s="10"/>
+      <c r="AE34" s="10"/>
+      <c r="AF34" s="10"/>
+      <c r="AG34" s="10"/>
+      <c r="AH34" s="10"/>
+      <c r="AI34" s="10"/>
+      <c r="AJ34" s="10"/>
+      <c r="AK34" s="10"/>
+      <c r="AL34" s="10"/>
+      <c r="AM34" s="10"/>
+    </row>
+    <row r="35" ht="14" customHeight="1" spans="1:39">
       <c r="A35" s="9">
         <v>34</v>
       </c>
@@ -5341,8 +5868,21 @@
         <f t="shared" ref="Z35:Z52" si="6">RANK(V35,V$2:V$52,0)</f>
         <v>35</v>
       </c>
-    </row>
-    <row r="36" ht="14" customHeight="1" spans="1:26">
+      <c r="AA35" s="10"/>
+      <c r="AB35" s="10"/>
+      <c r="AC35" s="10"/>
+      <c r="AD35" s="10"/>
+      <c r="AE35" s="10"/>
+      <c r="AF35" s="10"/>
+      <c r="AG35" s="10"/>
+      <c r="AH35" s="10"/>
+      <c r="AI35" s="10"/>
+      <c r="AJ35" s="10"/>
+      <c r="AK35" s="10"/>
+      <c r="AL35" s="10"/>
+      <c r="AM35" s="10"/>
+    </row>
+    <row r="36" ht="14" customHeight="1" spans="1:39">
       <c r="A36" s="13">
         <v>35</v>
       </c>
@@ -5400,8 +5940,23 @@
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-    </row>
-    <row r="37" ht="14" customHeight="1" spans="1:26">
+      <c r="AA36" s="10">
+        <v>1</v>
+      </c>
+      <c r="AB36" s="10"/>
+      <c r="AC36" s="10"/>
+      <c r="AD36" s="10"/>
+      <c r="AE36" s="10"/>
+      <c r="AF36" s="10"/>
+      <c r="AG36" s="10"/>
+      <c r="AH36" s="10"/>
+      <c r="AI36" s="10"/>
+      <c r="AJ36" s="10"/>
+      <c r="AK36" s="10"/>
+      <c r="AL36" s="10"/>
+      <c r="AM36" s="10"/>
+    </row>
+    <row r="37" ht="14" customHeight="1" spans="1:39">
       <c r="A37" s="13">
         <v>36</v>
       </c>
@@ -5453,8 +6008,21 @@
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="38" ht="14" customHeight="1" spans="1:26">
+      <c r="AA37" s="10"/>
+      <c r="AB37" s="10"/>
+      <c r="AC37" s="10"/>
+      <c r="AD37" s="10"/>
+      <c r="AE37" s="10"/>
+      <c r="AF37" s="10"/>
+      <c r="AG37" s="10"/>
+      <c r="AH37" s="10"/>
+      <c r="AI37" s="10"/>
+      <c r="AJ37" s="10"/>
+      <c r="AK37" s="10"/>
+      <c r="AL37" s="10"/>
+      <c r="AM37" s="10"/>
+    </row>
+    <row r="38" ht="14" customHeight="1" spans="1:39">
       <c r="A38" s="14">
         <v>37</v>
       </c>
@@ -5504,8 +6072,21 @@
         <f t="shared" si="6"/>
         <v>35</v>
       </c>
-    </row>
-    <row r="39" ht="14" customHeight="1" spans="1:26">
+      <c r="AA38" s="14"/>
+      <c r="AB38" s="14"/>
+      <c r="AC38" s="14"/>
+      <c r="AD38" s="14"/>
+      <c r="AE38" s="14"/>
+      <c r="AF38" s="14"/>
+      <c r="AG38" s="14"/>
+      <c r="AH38" s="14"/>
+      <c r="AI38" s="14"/>
+      <c r="AJ38" s="14"/>
+      <c r="AK38" s="14"/>
+      <c r="AL38" s="14"/>
+      <c r="AM38" s="14"/>
+    </row>
+    <row r="39" ht="14" customHeight="1" spans="1:39">
       <c r="A39" s="13">
         <v>38</v>
       </c>
@@ -5575,8 +6156,23 @@
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-    </row>
-    <row r="40" ht="14" customHeight="1" spans="1:26">
+      <c r="AA39" s="10">
+        <v>1</v>
+      </c>
+      <c r="AB39" s="10"/>
+      <c r="AC39" s="10"/>
+      <c r="AD39" s="10"/>
+      <c r="AE39" s="10"/>
+      <c r="AF39" s="10"/>
+      <c r="AG39" s="10"/>
+      <c r="AH39" s="10"/>
+      <c r="AI39" s="10"/>
+      <c r="AJ39" s="10"/>
+      <c r="AK39" s="10"/>
+      <c r="AL39" s="10"/>
+      <c r="AM39" s="10"/>
+    </row>
+    <row r="40" ht="14" customHeight="1" spans="1:39">
       <c r="A40" s="13">
         <v>39</v>
       </c>
@@ -5632,8 +6228,23 @@
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="41" ht="14" customHeight="1" spans="1:26">
+      <c r="AA40" s="10">
+        <v>2</v>
+      </c>
+      <c r="AB40" s="10"/>
+      <c r="AC40" s="10"/>
+      <c r="AD40" s="10"/>
+      <c r="AE40" s="10"/>
+      <c r="AF40" s="10"/>
+      <c r="AG40" s="10"/>
+      <c r="AH40" s="10"/>
+      <c r="AI40" s="10"/>
+      <c r="AJ40" s="10"/>
+      <c r="AK40" s="10"/>
+      <c r="AL40" s="10"/>
+      <c r="AM40" s="10"/>
+    </row>
+    <row r="41" ht="14" customHeight="1" spans="1:39">
       <c r="A41" s="13">
         <v>40</v>
       </c>
@@ -5699,8 +6310,23 @@
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="42" ht="14" customHeight="1" spans="1:26">
+      <c r="AA41" s="10">
+        <v>2</v>
+      </c>
+      <c r="AB41" s="10"/>
+      <c r="AC41" s="10"/>
+      <c r="AD41" s="10"/>
+      <c r="AE41" s="10"/>
+      <c r="AF41" s="10"/>
+      <c r="AG41" s="10"/>
+      <c r="AH41" s="10"/>
+      <c r="AI41" s="10"/>
+      <c r="AJ41" s="10"/>
+      <c r="AK41" s="10"/>
+      <c r="AL41" s="10"/>
+      <c r="AM41" s="10"/>
+    </row>
+    <row r="42" ht="14" customHeight="1" spans="1:39">
       <c r="A42" s="9">
         <v>41</v>
       </c>
@@ -5750,8 +6376,21 @@
         <f t="shared" si="6"/>
         <v>35</v>
       </c>
-    </row>
-    <row r="43" ht="14" customHeight="1" spans="1:26">
+      <c r="AA42" s="10"/>
+      <c r="AB42" s="10"/>
+      <c r="AC42" s="10"/>
+      <c r="AD42" s="10"/>
+      <c r="AE42" s="10"/>
+      <c r="AF42" s="10"/>
+      <c r="AG42" s="10"/>
+      <c r="AH42" s="10"/>
+      <c r="AI42" s="10"/>
+      <c r="AJ42" s="10"/>
+      <c r="AK42" s="10"/>
+      <c r="AL42" s="10"/>
+      <c r="AM42" s="10"/>
+    </row>
+    <row r="43" ht="14" customHeight="1" spans="1:39">
       <c r="A43" s="13">
         <v>42</v>
       </c>
@@ -5821,8 +6460,23 @@
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="44" ht="14" customHeight="1" spans="1:26">
+      <c r="AA43" s="10">
+        <v>1</v>
+      </c>
+      <c r="AB43" s="10"/>
+      <c r="AC43" s="10"/>
+      <c r="AD43" s="10"/>
+      <c r="AE43" s="10"/>
+      <c r="AF43" s="10"/>
+      <c r="AG43" s="10"/>
+      <c r="AH43" s="10"/>
+      <c r="AI43" s="10"/>
+      <c r="AJ43" s="10"/>
+      <c r="AK43" s="10"/>
+      <c r="AL43" s="10"/>
+      <c r="AM43" s="10"/>
+    </row>
+    <row r="44" ht="14" customHeight="1" spans="1:39">
       <c r="A44" s="9">
         <v>43</v>
       </c>
@@ -5872,8 +6526,21 @@
         <f t="shared" si="6"/>
         <v>35</v>
       </c>
-    </row>
-    <row r="45" ht="14" customHeight="1" spans="1:26">
+      <c r="AA44" s="10"/>
+      <c r="AB44" s="10"/>
+      <c r="AC44" s="10"/>
+      <c r="AD44" s="10"/>
+      <c r="AE44" s="10"/>
+      <c r="AF44" s="10"/>
+      <c r="AG44" s="10"/>
+      <c r="AH44" s="10"/>
+      <c r="AI44" s="10"/>
+      <c r="AJ44" s="10"/>
+      <c r="AK44" s="10"/>
+      <c r="AL44" s="10"/>
+      <c r="AM44" s="10"/>
+    </row>
+    <row r="45" ht="14" customHeight="1" spans="1:39">
       <c r="A45" s="13">
         <v>44</v>
       </c>
@@ -5951,8 +6618,23 @@
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="46" ht="14" customHeight="1" spans="1:26">
+      <c r="AA45" s="10">
+        <v>3</v>
+      </c>
+      <c r="AB45" s="10"/>
+      <c r="AC45" s="10"/>
+      <c r="AD45" s="10"/>
+      <c r="AE45" s="10"/>
+      <c r="AF45" s="10"/>
+      <c r="AG45" s="10"/>
+      <c r="AH45" s="10"/>
+      <c r="AI45" s="10"/>
+      <c r="AJ45" s="10"/>
+      <c r="AK45" s="10"/>
+      <c r="AL45" s="10"/>
+      <c r="AM45" s="10"/>
+    </row>
+    <row r="46" ht="14" customHeight="1" spans="1:39">
       <c r="A46" s="9">
         <v>45</v>
       </c>
@@ -6002,8 +6684,21 @@
         <f t="shared" si="6"/>
         <v>35</v>
       </c>
-    </row>
-    <row r="47" ht="14" customHeight="1" spans="1:26">
+      <c r="AA46" s="10"/>
+      <c r="AB46" s="10"/>
+      <c r="AC46" s="10"/>
+      <c r="AD46" s="10"/>
+      <c r="AE46" s="10"/>
+      <c r="AF46" s="10"/>
+      <c r="AG46" s="10"/>
+      <c r="AH46" s="10"/>
+      <c r="AI46" s="10"/>
+      <c r="AJ46" s="10"/>
+      <c r="AK46" s="10"/>
+      <c r="AL46" s="10"/>
+      <c r="AM46" s="10"/>
+    </row>
+    <row r="47" ht="14" customHeight="1" spans="1:39">
       <c r="A47" s="13">
         <v>46</v>
       </c>
@@ -6061,8 +6756,23 @@
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
-    </row>
-    <row r="48" ht="14" customHeight="1" spans="1:26">
+      <c r="AA47" s="10">
+        <v>1</v>
+      </c>
+      <c r="AB47" s="10"/>
+      <c r="AC47" s="10"/>
+      <c r="AD47" s="10"/>
+      <c r="AE47" s="10"/>
+      <c r="AF47" s="10"/>
+      <c r="AG47" s="10"/>
+      <c r="AH47" s="10"/>
+      <c r="AI47" s="10"/>
+      <c r="AJ47" s="10"/>
+      <c r="AK47" s="10"/>
+      <c r="AL47" s="10"/>
+      <c r="AM47" s="10"/>
+    </row>
+    <row r="48" ht="14" customHeight="1" spans="1:39">
       <c r="A48" s="13">
         <v>47</v>
       </c>
@@ -6116,8 +6826,21 @@
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="49" ht="14" customHeight="1" spans="1:26">
+      <c r="AA48" s="10"/>
+      <c r="AB48" s="10"/>
+      <c r="AC48" s="10"/>
+      <c r="AD48" s="10"/>
+      <c r="AE48" s="10"/>
+      <c r="AF48" s="10"/>
+      <c r="AG48" s="10"/>
+      <c r="AH48" s="10"/>
+      <c r="AI48" s="10"/>
+      <c r="AJ48" s="10"/>
+      <c r="AK48" s="10"/>
+      <c r="AL48" s="10"/>
+      <c r="AM48" s="10"/>
+    </row>
+    <row r="49" ht="14" customHeight="1" spans="1:39">
       <c r="A49" s="13">
         <v>48</v>
       </c>
@@ -6171,8 +6894,23 @@
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="50" ht="14" customHeight="1" spans="1:26">
+      <c r="AA49" s="10">
+        <v>1</v>
+      </c>
+      <c r="AB49" s="10"/>
+      <c r="AC49" s="10"/>
+      <c r="AD49" s="10"/>
+      <c r="AE49" s="10"/>
+      <c r="AF49" s="10"/>
+      <c r="AG49" s="10"/>
+      <c r="AH49" s="10"/>
+      <c r="AI49" s="10"/>
+      <c r="AJ49" s="10"/>
+      <c r="AK49" s="10"/>
+      <c r="AL49" s="10"/>
+      <c r="AM49" s="10"/>
+    </row>
+    <row r="50" ht="14" customHeight="1" spans="1:39">
       <c r="A50" s="9">
         <v>49</v>
       </c>
@@ -6222,8 +6960,21 @@
         <f t="shared" si="6"/>
         <v>35</v>
       </c>
-    </row>
-    <row r="51" ht="14" customHeight="1" spans="1:26">
+      <c r="AA50" s="10"/>
+      <c r="AB50" s="10"/>
+      <c r="AC50" s="10"/>
+      <c r="AD50" s="10"/>
+      <c r="AE50" s="10"/>
+      <c r="AF50" s="10"/>
+      <c r="AG50" s="10"/>
+      <c r="AH50" s="10"/>
+      <c r="AI50" s="10"/>
+      <c r="AJ50" s="10"/>
+      <c r="AK50" s="10"/>
+      <c r="AL50" s="10"/>
+      <c r="AM50" s="10"/>
+    </row>
+    <row r="51" ht="14" customHeight="1" spans="1:39">
       <c r="A51" s="9">
         <v>50</v>
       </c>
@@ -6273,8 +7024,21 @@
         <f t="shared" si="6"/>
         <v>35</v>
       </c>
-    </row>
-    <row r="52" ht="14" customHeight="1" spans="1:26">
+      <c r="AA51" s="10"/>
+      <c r="AB51" s="10"/>
+      <c r="AC51" s="10"/>
+      <c r="AD51" s="10"/>
+      <c r="AE51" s="10"/>
+      <c r="AF51" s="10"/>
+      <c r="AG51" s="10"/>
+      <c r="AH51" s="10"/>
+      <c r="AI51" s="10"/>
+      <c r="AJ51" s="10"/>
+      <c r="AK51" s="10"/>
+      <c r="AL51" s="10"/>
+      <c r="AM51" s="10"/>
+    </row>
+    <row r="52" ht="14" customHeight="1" spans="1:39">
       <c r="A52" s="9">
         <v>51</v>
       </c>
@@ -6324,10 +7088,23 @@
         <f t="shared" si="6"/>
         <v>35</v>
       </c>
+      <c r="AA52" s="10"/>
+      <c r="AB52" s="10"/>
+      <c r="AC52" s="10"/>
+      <c r="AD52" s="10"/>
+      <c r="AE52" s="10"/>
+      <c r="AF52" s="10"/>
+      <c r="AG52" s="10"/>
+      <c r="AH52" s="10"/>
+      <c r="AI52" s="10"/>
+      <c r="AJ52" s="10"/>
+      <c r="AK52" s="10"/>
+      <c r="AL52" s="10"/>
+      <c r="AM52" s="10"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="X2:X52">
-    <cfRule type="colorScale" priority="6">
+    <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -6335,7 +7112,7 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="5">
+    <cfRule type="colorScale" priority="31">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -6345,7 +7122,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y52">
-    <cfRule type="colorScale" priority="4">
+    <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -6355,7 +7132,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z2:Z52">
-    <cfRule type="colorScale" priority="3">
+    <cfRule type="colorScale" priority="29">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -6364,8 +7141,224 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:S52">
+  <conditionalFormatting sqref="AA2:AA52">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="-0.25"/>
+        <color theme="4" tint="0.8"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="0.8"/>
+        <color theme="4" tint="-0.25"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB2:AB52">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="-0.25"/>
+        <color theme="4" tint="0.8"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="0.8"/>
+        <color theme="4" tint="-0.25"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC2:AC52">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="-0.25"/>
+        <color theme="4" tint="0.8"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="0.8"/>
+        <color theme="4" tint="-0.25"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD2:AD52">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="-0.25"/>
+        <color theme="4" tint="0.8"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="0.8"/>
+        <color theme="4" tint="-0.25"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE2:AE52">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="-0.25"/>
+        <color theme="4" tint="0.8"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="0.8"/>
+        <color theme="4" tint="-0.25"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF2:AF52">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="-0.25"/>
+        <color theme="4" tint="0.8"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="0.8"/>
+        <color theme="4" tint="-0.25"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG2:AG52">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="-0.25"/>
+        <color theme="4" tint="0.8"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="0.8"/>
+        <color theme="4" tint="-0.25"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH2:AH52">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="-0.25"/>
+        <color theme="4" tint="0.8"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="0.8"/>
+        <color theme="4" tint="-0.25"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI2:AI52">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="-0.25"/>
+        <color theme="4" tint="0.8"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="0.8"/>
+        <color theme="4" tint="-0.25"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ2:AJ52">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="-0.25"/>
+        <color theme="4" tint="0.8"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="0.8"/>
+        <color theme="4" tint="-0.25"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK2:AK52">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="-0.25"/>
+        <color theme="4" tint="0.8"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="0.8"/>
+        <color theme="4" tint="-0.25"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL2:AL52">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="-0.25"/>
+        <color theme="4" tint="0.8"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="0.8"/>
+        <color theme="4" tint="-0.25"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AM2:AM52">
+    <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -6382,11 +7375,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B2:S52">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="-0.25"/>
+        <color theme="4" tint="0.8"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="0.8"/>
+        <color theme="4" tint="-0.25"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="0" bottom="0" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="80" orientation="landscape"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="G1:S1 A1:E1 A46:Z52 T45:Z45 A45:R45 A40:Z44 T39:Z39 A39:R39 A32:Z38 T29:Z31 A29:R31 A28:Z28 T27:Z27 A27:R27 A22:Z26 T21:Z21 A21:R21 A19:Z20 T18:Z18 A18:R18 A9:Z17 T7:Z8 A7:R8 A4:Z6 T3:Z3 A3:R3 A2:Z2" formulaRange="1" unlockedFormula="1"/>
+    <ignoredError sqref="A2:Z2 A3:R3 T3:Z3 A4:Z6 A7:R8 T7:Z8 A9:Z17 A18:R18 T18:Z18 A19:Z20 A21:R21 T21:Z21 A22:Z26 A27:R27 T27:Z27 A28:Z28 A29:R31 T29:Z31 A32:Z38 A39:R39 T39:Z39 A40:Z44 A45:R45 T45:Z45 A46:Z52 A1:E1 G1:S1" formulaRange="1" unlockedFormula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10030" activeTab="2"/>
+    <workbookView windowWidth="20750" windowHeight="10030" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="学生、老师" sheetId="5" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="230">
   <si>
     <t>姓名</t>
   </si>
@@ -322,7 +322,14 @@
     <t>早读（劝学/磨刀霍霍向鑫洋）、生物30分、记笔记</t>
   </si>
   <si>
-    <t>孺子、反思（我也老了、相见时难别亦难，东风无力百花残、未来是你们，但现在未必、革命尚未成功）（一旬老人）、哲学（旁观者：学地理要以旁观者视角、水循环：逆水行舟，退到极点就是进）、装（问第几题有问题，体现自己做得快、费马点）、考进班级前10、种地（初二第三次月考、打赌八上期末物理自己和郑永泽考的低者种地）、因错题争论、嫂子（47）、三江口（小宝）、问问题（秦岭山顶的人）</t>
+    <t>孺子、反思（我也老了、相见时难别亦难，东风无力百花残、未来是你们，但现在未必、革命尚未成功）（一旬老人）、哲学（旁观者：学地理要以旁观者视角、水循环：逆水行舟，退到极点就是进）、装（问第几题有问题，体现自己做得快、费马点）、考进班级前10、种地（初二第三次月考、打赌八上期末物理自己和郑永泽考的低者种地）、因错题争论、嫂子（47）、三江口（小宝）（江怡佳、江允儿、江雨晴）、问问题（秦岭山顶的人）</t>
+  </si>
+  <si>
+    <t>洪鑫洋名言：
+我努力学习就是为了装……我就装怎么了？
+我要考年段前30
+我一天24小时都在看手机，从没看过书
+我要去参加奥数比赛</t>
   </si>
   <si>
     <t>游武毅</t>
@@ -584,6 +591,9 @@
   </si>
   <si>
     <t>9班民族乐器</t>
+  </si>
+  <si>
+    <t>26.1.5周一特色餐</t>
   </si>
   <si>
     <t>日常</t>
@@ -1526,7 +1536,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1621,12 +1631,6 @@
     <xf numFmtId="20" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1674,6 +1678,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2011,733 +2018,736 @@
   <sheetPr>
     <tabColor theme="7" tint="0.8"/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
+  <dimension ref="A1:H78"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="7.59090909090909" style="41" customWidth="1"/>
-    <col min="2" max="7" width="25.8727272727273" style="42" customWidth="1"/>
+    <col min="1" max="1" width="7.59090909090909" style="39" customWidth="1"/>
+    <col min="2" max="7" width="25.8727272727273" style="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="40" customFormat="1" spans="1:7">
-      <c r="A1" s="43" t="s">
+    <row r="1" s="38" customFormat="1" spans="1:7">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="44" t="s">
+      <c r="B1" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="E1" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="44" t="s">
+      <c r="F1" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="44" t="s">
+      <c r="G1" s="42" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="42" t="s">
+      <c r="C2" s="40" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" ht="39" spans="1:7">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="42" t="s">
+      <c r="C3" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="42" t="s">
+      <c r="D3" s="40" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="43" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="45" t="s">
+      <c r="A5" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="42" t="s">
+      <c r="C5" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="42" t="s">
+      <c r="D5" s="40" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="45" t="s">
+      <c r="A6" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="42" t="s">
+      <c r="C6" s="40" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" ht="208" spans="1:7">
-      <c r="A7" s="45" t="s">
+      <c r="A7" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="42" t="s">
+      <c r="C7" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="42" t="s">
+      <c r="D7" s="40" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="45" t="s">
+      <c r="A8" s="43" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="45" t="s">
+      <c r="A9" s="43" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="45" t="s">
+      <c r="A10" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="40" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="45" t="s">
+      <c r="A11" s="43" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="45" t="s">
+      <c r="A12" s="43" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="13" ht="39" spans="1:7">
-      <c r="A13" s="45" t="s">
+      <c r="A13" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="42" t="s">
+      <c r="D13" s="40" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="45" t="s">
+      <c r="A14" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="42" t="s">
+      <c r="B14" s="40" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="45" t="s">
+      <c r="A15" s="43" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="45" t="s">
+      <c r="A16" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="42" t="s">
+      <c r="C16" s="40" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="17" ht="26" spans="1:4">
-      <c r="A17" s="45" t="s">
+      <c r="A17" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="42" t="s">
+      <c r="C17" s="40" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="45" t="s">
+      <c r="A18" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="42" t="s">
+      <c r="D18" s="40" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="45" t="s">
+      <c r="A19" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="42" t="s">
+      <c r="D19" s="40" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="20" ht="26" spans="1:4">
-      <c r="A20" s="45" t="s">
+      <c r="A20" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="42" t="s">
+      <c r="B20" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="42" t="s">
+      <c r="C20" s="40" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="21" ht="52" spans="1:4">
-      <c r="A21" s="45" t="s">
+      <c r="A21" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="B21" s="42" t="s">
+      <c r="B21" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="42" t="s">
+      <c r="C21" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="42" t="s">
+      <c r="D21" s="40" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="45" t="s">
+      <c r="A22" s="43" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="23" ht="26" spans="1:4">
-      <c r="A23" s="45" t="s">
+      <c r="A23" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="B23" s="42" t="s">
+      <c r="B23" s="40" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="24" ht="52" spans="1:4">
-      <c r="A24" s="45" t="s">
+      <c r="A24" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="42" t="s">
+      <c r="B24" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="C24" s="42" t="s">
+      <c r="C24" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="42" t="s">
+      <c r="D24" s="40" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="45" t="s">
+      <c r="A25" s="43" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="45" t="s">
+      <c r="A26" s="43" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="45" t="s">
+      <c r="A27" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="B27" s="42" t="s">
+      <c r="B27" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="C27" s="42" t="s">
+      <c r="C27" s="40" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="28" ht="91" spans="1:4">
-      <c r="A28" s="45" t="s">
+      <c r="A28" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="B28" s="42" t="s">
+      <c r="B28" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="C28" s="42" t="s">
+      <c r="C28" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="D28" s="42" t="s">
+      <c r="D28" s="40" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="45" t="s">
+      <c r="A29" s="43" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="45" t="s">
+      <c r="A30" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="B30" s="42" t="s">
+      <c r="B30" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="C30" s="42" t="s">
+      <c r="C30" s="40" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="45" t="s">
+      <c r="A31" s="43" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="45" t="s">
+      <c r="A32" s="43" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="45" t="s">
+    <row r="33" spans="1:8">
+      <c r="A33" s="43" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="45" t="s">
+    <row r="34" spans="1:8">
+      <c r="A34" s="43" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="45" t="s">
+    <row r="35" spans="1:8">
+      <c r="A35" s="43" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
-      <c r="A36" s="45" t="s">
+    <row r="36" spans="1:8">
+      <c r="A36" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="B36" s="42" t="s">
+      <c r="B36" s="40" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="37" ht="26" spans="1:7">
-      <c r="A37" s="45" t="s">
+    <row r="37" ht="26" spans="1:8">
+      <c r="A37" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="C37" s="42" t="s">
+      <c r="C37" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="D37" s="42" t="s">
+      <c r="D37" s="40" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
-      <c r="A38" s="45" t="s">
+    <row r="38" spans="1:8">
+      <c r="A38" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="B38" s="42" t="s">
+      <c r="B38" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="C38" s="46"/>
-      <c r="D38" s="46"/>
-      <c r="E38" s="46"/>
-      <c r="F38" s="46"/>
-      <c r="G38" s="46"/>
-    </row>
-    <row r="39" ht="26" spans="1:7">
-      <c r="A39" s="45" t="s">
+      <c r="C38" s="44"/>
+      <c r="D38" s="44"/>
+      <c r="E38" s="44"/>
+      <c r="F38" s="44"/>
+      <c r="G38" s="44"/>
+    </row>
+    <row r="39" ht="26" spans="1:8">
+      <c r="A39" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="C39" s="42" t="s">
+      <c r="C39" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="D39" s="42" t="s">
+      <c r="D39" s="40" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
-      <c r="A40" s="45" t="s">
+    <row r="40" spans="1:8">
+      <c r="A40" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="B40" s="42" t="s">
+      <c r="B40" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="C40" s="42" t="s">
+      <c r="C40" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="D40" s="42" t="s">
+      <c r="D40" s="40" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="41" ht="195" spans="1:7">
-      <c r="A41" s="45" t="s">
+    <row r="41" ht="238" spans="1:8">
+      <c r="A41" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="C41" s="42" t="s">
+      <c r="C41" s="40" t="s">
         <v>88</v>
       </c>
-      <c r="D41" s="42" t="s">
+      <c r="D41" s="40" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42" s="45" t="s">
+      <c r="H41" s="45" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
-      <c r="A43" s="45" t="s">
+    <row r="42" spans="1:8">
+      <c r="A42" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="B43" s="42" t="s">
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="43" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="44" ht="26" spans="1:7">
-      <c r="A44" s="45" t="s">
+      <c r="B43" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="B44" s="42" t="s">
+    </row>
+    <row r="44" ht="26" spans="1:8">
+      <c r="A44" s="43" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45" s="45" t="s">
+      <c r="B44" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="D45" s="42" t="s">
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="43" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46" s="45" t="s">
+      <c r="D45" s="40" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
-      <c r="A47" s="45" t="s">
+    <row r="46" spans="1:8">
+      <c r="A46" s="43" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
-      <c r="A48" s="45" t="s">
+    <row r="47" spans="1:8">
+      <c r="A47" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="C48" s="42" t="s">
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="43" t="s">
         <v>100</v>
       </c>
+      <c r="C48" s="40" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="45" t="s">
-        <v>101</v>
+      <c r="A49" s="43" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="50" ht="78" spans="1:7">
-      <c r="A50" s="45" t="s">
-        <v>102</v>
-      </c>
-      <c r="C50" s="42" t="s">
+      <c r="A50" s="43" t="s">
         <v>103</v>
       </c>
+      <c r="C50" s="40" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="45" t="s">
-        <v>104</v>
+      <c r="A51" s="43" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="52" ht="26" spans="1:7">
-      <c r="A52" s="45" t="s">
-        <v>105</v>
-      </c>
-      <c r="B52" s="42" t="s">
+      <c r="A52" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="C52" s="42" t="s">
+      <c r="B52" s="40" t="s">
         <v>107</v>
       </c>
+      <c r="C52" s="40" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="53" ht="26" spans="1:7">
-      <c r="A53" s="41" t="s">
-        <v>108</v>
-      </c>
-      <c r="B53" s="42" t="s">
+      <c r="A53" s="39" t="s">
         <v>109</v>
       </c>
-      <c r="D53" s="46"/>
-      <c r="E53" s="46"/>
-      <c r="F53" s="46"/>
-      <c r="G53" s="46"/>
+      <c r="B53" s="40" t="s">
+        <v>110</v>
+      </c>
+      <c r="D53" s="44"/>
+      <c r="E53" s="44"/>
+      <c r="F53" s="44"/>
+      <c r="G53" s="44"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="41" t="s">
-        <v>110</v>
-      </c>
-      <c r="B54" s="42" t="s">
+      <c r="A54" s="39" t="s">
         <v>111</v>
       </c>
-      <c r="C54" s="42" t="s">
+      <c r="B54" s="40" t="s">
         <v>112</v>
       </c>
-      <c r="D54" s="46"/>
-      <c r="E54" s="46"/>
-      <c r="F54" s="46"/>
-      <c r="G54" s="46"/>
+      <c r="C54" s="40" t="s">
+        <v>113</v>
+      </c>
+      <c r="D54" s="44"/>
+      <c r="E54" s="44"/>
+      <c r="F54" s="44"/>
+      <c r="G54" s="44"/>
     </row>
     <row r="55" ht="52" spans="1:7">
-      <c r="A55" s="41" t="s">
-        <v>113</v>
-      </c>
-      <c r="B55" s="46"/>
-      <c r="C55" s="46"/>
-      <c r="D55" s="42" t="s">
+      <c r="A55" s="39" t="s">
         <v>114</v>
       </c>
+      <c r="B55" s="44"/>
+      <c r="C55" s="44"/>
+      <c r="D55" s="40" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="56" ht="65" spans="1:7">
-      <c r="A56" s="41" t="s">
-        <v>115</v>
-      </c>
-      <c r="B56" s="38" t="s">
+      <c r="A56" s="39" t="s">
         <v>116</v>
       </c>
-      <c r="C56" s="38"/>
-      <c r="D56" s="42" t="s">
+      <c r="B56" s="36" t="s">
         <v>117</v>
       </c>
+      <c r="C56" s="36"/>
+      <c r="D56" s="40" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="57" ht="117" spans="1:7">
-      <c r="A57" s="41" t="s">
-        <v>118</v>
-      </c>
-      <c r="B57" s="38" t="s">
+      <c r="A57" s="39" t="s">
         <v>119</v>
       </c>
-      <c r="C57" s="38" t="s">
+      <c r="B57" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="D57" s="42" t="s">
+      <c r="C57" s="36" t="s">
         <v>121</v>
       </c>
+      <c r="D57" s="40" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="41" t="s">
-        <v>122</v>
-      </c>
-      <c r="B58" s="42" t="s">
+      <c r="A58" s="39" t="s">
         <v>123</v>
       </c>
-      <c r="C58" s="46"/>
-      <c r="D58" s="46"/>
-      <c r="E58" s="46"/>
-      <c r="F58" s="46"/>
-      <c r="G58" s="46"/>
+      <c r="B58" s="40" t="s">
+        <v>124</v>
+      </c>
+      <c r="C58" s="44"/>
+      <c r="D58" s="44"/>
+      <c r="E58" s="44"/>
+      <c r="F58" s="44"/>
+      <c r="G58" s="44"/>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="41" t="s">
-        <v>124</v>
-      </c>
-      <c r="B59" s="46"/>
-      <c r="C59" s="42" t="s">
+      <c r="A59" s="39" t="s">
         <v>125</v>
       </c>
-      <c r="D59" s="46"/>
-      <c r="E59" s="46"/>
-      <c r="F59" s="46"/>
-      <c r="G59" s="46"/>
+      <c r="B59" s="44"/>
+      <c r="C59" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="D59" s="44"/>
+      <c r="E59" s="44"/>
+      <c r="F59" s="44"/>
+      <c r="G59" s="44"/>
     </row>
     <row r="60" ht="52" spans="1:7">
-      <c r="A60" s="41" t="s">
-        <v>126</v>
-      </c>
-      <c r="B60" s="46"/>
-      <c r="C60" s="46"/>
-      <c r="D60" s="42" t="s">
+      <c r="A60" s="39" t="s">
         <v>127</v>
       </c>
+      <c r="B60" s="44"/>
+      <c r="C60" s="44"/>
+      <c r="D60" s="40" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="B61" s="38" t="s">
+      <c r="A61" s="39" t="s">
         <v>129</v>
       </c>
-      <c r="C61" s="38"/>
-      <c r="D61" s="46"/>
-      <c r="E61" s="46"/>
-      <c r="F61" s="46"/>
-      <c r="G61" s="46"/>
+      <c r="B61" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="C61" s="36"/>
+      <c r="D61" s="44"/>
+      <c r="E61" s="44"/>
+      <c r="F61" s="44"/>
+      <c r="G61" s="44"/>
     </row>
     <row r="62" ht="39" spans="1:7">
-      <c r="A62" s="41" t="s">
-        <v>130</v>
-      </c>
-      <c r="B62" s="46"/>
-      <c r="C62" s="46"/>
-      <c r="D62" s="42" t="s">
+      <c r="A62" s="39" t="s">
         <v>131</v>
       </c>
+      <c r="B62" s="44"/>
+      <c r="C62" s="44"/>
+      <c r="D62" s="40" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="63" ht="26" spans="1:7">
-      <c r="A63" s="41" t="s">
-        <v>132</v>
-      </c>
-      <c r="B63" s="38" t="s">
+      <c r="A63" s="39" t="s">
         <v>133</v>
       </c>
-      <c r="C63" s="38" t="s">
+      <c r="B63" s="36" t="s">
         <v>134</v>
       </c>
-      <c r="D63" s="46"/>
-      <c r="E63" s="46"/>
-      <c r="F63" s="46"/>
-      <c r="G63" s="46"/>
+      <c r="C63" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="D63" s="44"/>
+      <c r="E63" s="44"/>
+      <c r="F63" s="44"/>
+      <c r="G63" s="44"/>
     </row>
     <row r="64" ht="26" spans="1:7">
-      <c r="A64" s="41" t="s">
-        <v>135</v>
-      </c>
-      <c r="B64" s="46"/>
-      <c r="C64" s="46"/>
-      <c r="D64" s="42" t="s">
+      <c r="A64" s="39" t="s">
         <v>136</v>
       </c>
+      <c r="B64" s="44"/>
+      <c r="C64" s="44"/>
+      <c r="D64" s="40" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="65" ht="26" spans="1:7">
-      <c r="A65" s="41" t="s">
-        <v>137</v>
-      </c>
-      <c r="B65" s="47" t="s">
+      <c r="A65" s="39" t="s">
         <v>138</v>
       </c>
-      <c r="C65" s="46"/>
-      <c r="D65" s="46"/>
-      <c r="E65" s="46"/>
-      <c r="F65" s="46"/>
-      <c r="G65" s="46"/>
+      <c r="B65" s="46" t="s">
+        <v>139</v>
+      </c>
+      <c r="C65" s="44"/>
+      <c r="D65" s="44"/>
+      <c r="E65" s="44"/>
+      <c r="F65" s="44"/>
+      <c r="G65" s="44"/>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="41" t="s">
-        <v>139</v>
-      </c>
-      <c r="B66" s="46"/>
-      <c r="C66" s="42" t="s">
+      <c r="A66" s="39" t="s">
         <v>140</v>
       </c>
-      <c r="D66" s="46"/>
-      <c r="E66" s="46"/>
-      <c r="F66" s="46"/>
-      <c r="G66" s="46"/>
+      <c r="B66" s="44"/>
+      <c r="C66" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="D66" s="44"/>
+      <c r="E66" s="44"/>
+      <c r="F66" s="44"/>
+      <c r="G66" s="44"/>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="41" t="s">
-        <v>141</v>
-      </c>
-      <c r="B67" s="46"/>
-      <c r="C67" s="46"/>
+      <c r="A67" s="39" t="s">
+        <v>142</v>
+      </c>
+      <c r="B67" s="44"/>
+      <c r="C67" s="44"/>
     </row>
     <row r="68" ht="26" spans="1:7">
-      <c r="A68" s="41" t="s">
-        <v>142</v>
-      </c>
-      <c r="B68" s="46"/>
-      <c r="C68" s="46"/>
-      <c r="D68" s="42" t="s">
+      <c r="A68" s="39" t="s">
         <v>143</v>
       </c>
+      <c r="B68" s="44"/>
+      <c r="C68" s="44"/>
+      <c r="D68" s="40" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="41" t="s">
-        <v>144</v>
-      </c>
-      <c r="B69" s="38" t="s">
+      <c r="A69" s="39" t="s">
         <v>145</v>
       </c>
-      <c r="C69" s="38"/>
+      <c r="B69" s="36" t="s">
+        <v>146</v>
+      </c>
+      <c r="C69" s="36"/>
     </row>
     <row r="70" ht="26" spans="1:7">
-      <c r="A70" s="41" t="s">
-        <v>146</v>
-      </c>
-      <c r="B70" s="38" t="s">
+      <c r="A70" s="39" t="s">
         <v>147</v>
       </c>
-      <c r="C70" s="38"/>
-      <c r="D70" s="46"/>
-      <c r="E70" s="46"/>
-      <c r="F70" s="46"/>
-      <c r="G70" s="46"/>
+      <c r="B70" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="C70" s="36"/>
+      <c r="D70" s="44"/>
+      <c r="E70" s="44"/>
+      <c r="F70" s="44"/>
+      <c r="G70" s="44"/>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="41" t="s">
-        <v>148</v>
-      </c>
-      <c r="B71" s="46"/>
-      <c r="C71" s="46"/>
+      <c r="A71" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="B71" s="44"/>
+      <c r="C71" s="44"/>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="B72" s="42" t="s">
+      <c r="A72" s="39" t="s">
         <v>150</v>
       </c>
-      <c r="C72" s="42" t="s">
+      <c r="B72" s="40" t="s">
         <v>151</v>
       </c>
-      <c r="D72" s="46"/>
-      <c r="E72" s="46"/>
-      <c r="F72" s="46"/>
-      <c r="G72" s="46"/>
+      <c r="C72" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="D72" s="44"/>
+      <c r="E72" s="44"/>
+      <c r="F72" s="44"/>
+      <c r="G72" s="44"/>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="41" t="s">
-        <v>152</v>
-      </c>
-      <c r="B73" s="46"/>
-      <c r="C73" s="42" t="s">
+      <c r="A73" s="39" t="s">
         <v>153</v>
       </c>
-      <c r="D73" s="46"/>
-      <c r="E73" s="46"/>
-      <c r="F73" s="46"/>
-      <c r="G73" s="46"/>
+      <c r="B73" s="44"/>
+      <c r="C73" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="D73" s="44"/>
+      <c r="E73" s="44"/>
+      <c r="F73" s="44"/>
+      <c r="G73" s="44"/>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="41" t="s">
-        <v>154</v>
+      <c r="A74" s="39" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="41" t="s">
-        <v>155</v>
-      </c>
-      <c r="D75" s="46"/>
-      <c r="E75" s="46"/>
-      <c r="F75" s="46"/>
-      <c r="G75" s="46"/>
+      <c r="A75" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="D75" s="44"/>
+      <c r="E75" s="44"/>
+      <c r="F75" s="44"/>
+      <c r="G75" s="44"/>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="41" t="s">
-        <v>156</v>
-      </c>
-      <c r="B76" s="46"/>
-      <c r="C76" s="46"/>
-      <c r="D76" s="42" t="s">
+      <c r="A76" s="39" t="s">
         <v>157</v>
       </c>
+      <c r="B76" s="44"/>
+      <c r="C76" s="44"/>
+      <c r="D76" s="40" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="41" t="s">
-        <v>158</v>
-      </c>
-      <c r="B77" s="38"/>
-      <c r="C77" s="38"/>
+      <c r="A77" s="39" t="s">
+        <v>159</v>
+      </c>
+      <c r="B77" s="36"/>
+      <c r="C77" s="36"/>
     </row>
     <row r="78" ht="26" spans="1:7">
-      <c r="A78" s="48" t="s">
-        <v>159</v>
-      </c>
-      <c r="B78" s="42" t="s">
+      <c r="A78" s="47" t="s">
         <v>160</v>
+      </c>
+      <c r="B78" s="40" t="s">
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -2780,240 +2790,243 @@
   <dimension ref="A1:G51"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="6.64545454545455" style="32" customWidth="1"/>
-    <col min="2" max="7" width="16.4909090909091" style="33" customWidth="1"/>
-    <col min="8" max="16384" width="8.72727272727273" style="34"/>
+    <col min="1" max="1" width="6.64545454545455" style="30" customWidth="1"/>
+    <col min="2" max="7" width="16.4909090909091" style="31" customWidth="1"/>
+    <col min="8" max="16384" width="8.72727272727273" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="35"/>
-      <c r="B1" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="36" t="s">
+      <c r="A1" s="33"/>
+      <c r="B1" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="36" t="s">
+      <c r="E1" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="36" t="s">
+      <c r="G1" s="34" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="31" customFormat="1" ht="39" spans="1:7">
-      <c r="A2" s="37" t="s">
-        <v>161</v>
-      </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38" t="s">
+    <row r="2" s="29" customFormat="1" ht="39" spans="1:7">
+      <c r="A2" s="35" t="s">
         <v>162</v>
       </c>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="C3" s="33" t="s">
+      <c r="A3" s="37" t="s">
         <v>164</v>
       </c>
+      <c r="C3" s="31" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="B4" s="33" t="s">
+      <c r="A4" s="37" t="s">
         <v>166</v>
       </c>
+      <c r="B4" s="31" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="C5" s="33" t="s">
+      <c r="A5" s="37" t="s">
         <v>168</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="C5" s="31" t="s">
         <v>169</v>
       </c>
+      <c r="D5" s="31" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="39" t="s">
-        <v>170</v>
-      </c>
-      <c r="B6" s="33" t="s">
+      <c r="A6" s="37" t="s">
         <v>171</v>
       </c>
-      <c r="D6" s="33" t="s">
+      <c r="B6" s="31" t="s">
         <v>172</v>
       </c>
+      <c r="D6" s="31" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="39" t="s">
-        <v>173</v>
-      </c>
-      <c r="B7" s="33" t="s">
+      <c r="A7" s="37" t="s">
         <v>174</v>
       </c>
+      <c r="B7" s="31" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="39"/>
-      <c r="D8" s="33" t="s">
-        <v>175</v>
+      <c r="A8" s="37"/>
+      <c r="D8" s="31" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="39"/>
+      <c r="A9" s="37"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="39"/>
-      <c r="B10" s="33" t="s">
-        <v>176</v>
+      <c r="A10" s="37"/>
+      <c r="B10" s="31" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="39"/>
+      <c r="A11" s="37"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="39"/>
+      <c r="A12" s="37"/>
+      <c r="B12" s="31" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="39"/>
+      <c r="A13" s="37"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="39"/>
+      <c r="A14" s="37"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="39"/>
+      <c r="A15" s="37"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="39"/>
+      <c r="A16" s="37"/>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="39"/>
+      <c r="A17" s="37"/>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="39"/>
+      <c r="A18" s="37"/>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="39"/>
+      <c r="A19" s="37"/>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="39"/>
+      <c r="A20" s="37"/>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="39"/>
+      <c r="A21" s="37"/>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="39"/>
+      <c r="A22" s="37"/>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="39"/>
+      <c r="A23" s="37"/>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="39"/>
+      <c r="A24" s="37"/>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="39"/>
+      <c r="A25" s="37"/>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="39"/>
+      <c r="A26" s="37"/>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="39"/>
+      <c r="A27" s="37"/>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="39"/>
+      <c r="A28" s="37"/>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="39"/>
+      <c r="A29" s="37"/>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="39"/>
+      <c r="A30" s="37"/>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="39"/>
+      <c r="A31" s="37"/>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="39"/>
+      <c r="A32" s="37"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="39"/>
+      <c r="A33" s="37"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="39"/>
+      <c r="A34" s="37"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="39"/>
+      <c r="A35" s="37"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="39"/>
+      <c r="A36" s="37"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="39"/>
+      <c r="A37" s="37"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="39"/>
-      <c r="B38" s="38"/>
-      <c r="C38" s="38"/>
-      <c r="D38" s="38"/>
-      <c r="E38" s="38"/>
-      <c r="F38" s="38"/>
-      <c r="G38" s="38"/>
+      <c r="A38" s="37"/>
+      <c r="B38" s="36"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="36"/>
+      <c r="F38" s="36"/>
+      <c r="G38" s="36"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="39"/>
-      <c r="B39" s="38"/>
-      <c r="C39" s="38"/>
-      <c r="D39" s="38"/>
-      <c r="E39" s="38"/>
-      <c r="F39" s="38"/>
-      <c r="G39" s="38"/>
+      <c r="A39" s="37"/>
+      <c r="B39" s="36"/>
+      <c r="C39" s="36"/>
+      <c r="D39" s="36"/>
+      <c r="E39" s="36"/>
+      <c r="F39" s="36"/>
+      <c r="G39" s="36"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="39"/>
+      <c r="A40" s="37"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="39"/>
+      <c r="A41" s="37"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="39"/>
+      <c r="A42" s="37"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="39"/>
+      <c r="A43" s="37"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="39"/>
+      <c r="A44" s="37"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="39"/>
+      <c r="A45" s="37"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="39"/>
+      <c r="A46" s="37"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="39"/>
+      <c r="A47" s="37"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="39"/>
+      <c r="A48" s="37"/>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="39"/>
+      <c r="A49" s="37"/>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="39"/>
+      <c r="A50" s="37"/>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="39"/>
+      <c r="A51" s="37"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3035,118 +3048,118 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="20" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="20" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="20" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" ht="28" spans="1:3">
       <c r="A4" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="B4" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="B4" s="20" t="s">
-        <v>184</v>
-      </c>
       <c r="C4" s="25" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" ht="42" spans="1:3">
       <c r="A5" s="26" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" ht="56" spans="1:3">
       <c r="A6" s="27"/>
       <c r="B6" s="20" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" ht="28" spans="1:3">
       <c r="A7" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8" ht="28" spans="1:3">
       <c r="A8" s="20" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="20" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="20" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="20" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C11" s="28">
         <v>0.440972222222222</v>
@@ -3157,50 +3170,50 @@
         <v>60</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="24"/>
       <c r="B13" s="20" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="29" t="s">
+      <c r="A14" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="B14" s="20" t="s">
         <v>211</v>
       </c>
-      <c r="B14" s="20" t="s">
-        <v>209</v>
-      </c>
       <c r="C14" s="25" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="30"/>
+      <c r="A15" s="24"/>
       <c r="B15" s="20" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16" ht="42" spans="1:3">
       <c r="A16" s="20" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -3227,10 +3240,10 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="C1" s="21" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -3379,7 +3392,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="28" spans="1:39">
       <c r="A1" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B1" s="5">
         <v>5</v>
@@ -3436,25 +3449,25 @@
         <v>31</v>
       </c>
       <c r="T1" s="7" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="U1" s="7" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="V1" s="7" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="W1" s="7" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="X1" s="8" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Y1" s="8" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AA1" s="5">
         <v>4</v>
@@ -7397,7 +7410,7 @@
   <pageSetup paperSize="9" scale="80" orientation="landscape"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A2:Z2 A3:R3 T3:Z3 A4:Z6 A7:R8 T7:Z8 A9:Z17 A18:R18 T18:Z18 A19:Z20 A21:R21 T21:Z21 A22:Z26 A27:R27 T27:Z27 A28:Z28 A29:R31 T29:Z31 A32:Z38 A39:R39 T39:Z39 A40:Z44 A45:R45 T45:Z45 A46:Z52 A1:E1 G1:S1" formulaRange="1" unlockedFormula="1"/>
+    <ignoredError sqref="G1:S1 A1:E1 A46:Z52 T45:Z45 A45:R45 A40:Z44 T39:Z39 A39:R39 A32:Z38 T29:Z31 A29:R31 A28:Z28 T27:Z27 A27:R27 A22:Z26 T21:Z21 A21:R21 A19:Z20 T18:Z18 A18:R18 A9:Z17 T7:Z8 A7:R8 A4:Z6 T3:Z3 A3:R3 A2:Z2" formulaRange="1" unlockedFormula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/c/9班资料（关键词）.xlsx
+++ b/c/9班资料（关键词）.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10030" activeTab="4"/>
+    <workbookView windowWidth="20750" windowHeight="10030"/>
   </bookViews>
   <sheets>
     <sheet name="学生、老师" sheetId="5" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="234">
   <si>
     <t>姓名</t>
   </si>
@@ -720,6 +720,12 @@
   </si>
   <si>
     <t>文艺汇演，孔转头被调换位置。理由：转到后面讲话。孔：没讲话，只是转到后面看了一眼。刘：闭嘴。随后请张佳欣“作证”：是那个女生吗？-是。</t>
+  </si>
+  <si>
+    <t>跑操喊口号</t>
+  </si>
+  <si>
+    <t>八上1.7 留下跑4圈</t>
   </si>
   <si>
     <t>政治啧</t>
@@ -3074,7 +3080,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="35.1818181818182" style="20" customWidth="1"/>
@@ -3251,6 +3257,14 @@
       </c>
       <c r="C16" s="25" t="s">
         <v>220</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -3277,10 +3291,10 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="C1" s="21" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -3427,7 +3441,7 @@
   <sheetData>
     <row r="1" spans="1:39">
       <c r="A1" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B1" s="3">
         <v>45992</v>
@@ -3465,7 +3479,7 @@
       <c r="AE1" s="4"/>
       <c r="AF1" s="4"/>
       <c r="AG1" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AH1" s="6"/>
       <c r="AI1" s="6"/>
@@ -3570,25 +3584,25 @@
         <v>20</v>
       </c>
       <c r="AG2" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AH2" s="9" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AI2" s="9" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AJ2" s="9" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AK2" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AL2" s="10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AM2" s="10" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:39">
@@ -3998,7 +4012,9 @@
       <c r="V8" s="12">
         <v>1</v>
       </c>
-      <c r="W8" s="12"/>
+      <c r="W8" s="12">
+        <v>1</v>
+      </c>
       <c r="X8" s="12"/>
       <c r="Y8" s="12"/>
       <c r="Z8" s="12"/>
@@ -4010,11 +4026,11 @@
       <c r="AF8" s="12"/>
       <c r="AG8" s="13">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH8" s="14" cm="1">
         <f t="array" ref="AH8">SUMPRODUCT(--(B8:AF8=INT(B8:AF8)),--(B8:AF8&gt;0))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI8" s="14" cm="1">
         <f t="array" ref="AI8">MAX(FREQUENCY(IF((B8:AF8=INT(B8:AF8))*(B8:AF8&gt;0),COLUMN(B8:AF8)),IF((B8:AF8&lt;&gt;INT(B8:AF8))+(B8:AF8&lt;=0),COLUMN(B8:AF8))))</f>
@@ -4022,7 +4038,7 @@
       </c>
       <c r="AJ8" s="15" cm="1">
         <f t="array" ref="AJ8">SUMPRODUCT(--(B8:AF8=INT(B8:AF8)),--(B8:AF8&gt;0))/30*100%</f>
-        <v>0.5</v>
+        <v>0.533333333333333</v>
       </c>
       <c r="AK8" s="16">
         <f t="shared" ref="AK8:AM8" si="5">RANK(AG8,AG$3:AG$53,0)</f>
@@ -4246,7 +4262,7 @@
       </c>
       <c r="AL11" s="16">
         <f t="shared" si="8"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM11" s="16">
         <f t="shared" si="8"/>
@@ -4800,7 +4816,7 @@
       </c>
       <c r="AK19" s="16">
         <f t="shared" ref="AK19:AM19" si="16">RANK(AG19,AG$3:AG$53,0)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL19" s="16">
         <f t="shared" si="16"/>
@@ -5059,7 +5075,7 @@
       <c r="AE23" s="12"/>
       <c r="AF23" s="12"/>
       <c r="AG23" s="13">
-        <f>SUM(B23:AF23)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AH23" s="14" cm="1">
@@ -6254,7 +6270,9 @@
       <c r="V40" s="12">
         <v>1</v>
       </c>
-      <c r="W40" s="12"/>
+      <c r="W40" s="12">
+        <v>1</v>
+      </c>
       <c r="X40" s="12"/>
       <c r="Y40" s="12"/>
       <c r="Z40" s="12"/>
@@ -6266,19 +6284,19 @@
       <c r="AF40" s="12"/>
       <c r="AG40" s="13">
         <f t="shared" si="33"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH40" s="14" cm="1">
         <f t="array" ref="AH40">SUMPRODUCT(--(B40:AF40=INT(B40:AF40)),--(B40:AF40&gt;0))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI40" s="14" cm="1">
         <f t="array" ref="AI40">MAX(FREQUENCY(IF((B40:AF40=INT(B40:AF40))*(B40:AF40&gt;0),COLUMN(B40:AF40)),IF((B40:AF40&lt;&gt;INT(B40:AF40))+(B40:AF40&lt;=0),COLUMN(B40:AF40))))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ40" s="15" cm="1">
         <f t="array" ref="AJ40">SUMPRODUCT(--(B40:AF40=INT(B40:AF40)),--(B40:AF40&gt;0))/30*100%</f>
-        <v>0.433333333333333</v>
+        <v>0.466666666666667</v>
       </c>
       <c r="AK40" s="16">
         <f t="shared" ref="AK40:AM40" si="38">RANK(AG40,AG$3:AG$53,0)</f>
@@ -6326,7 +6344,9 @@
       </c>
       <c r="U41" s="12"/>
       <c r="V41" s="12"/>
-      <c r="W41" s="12"/>
+      <c r="W41" s="12">
+        <v>1</v>
+      </c>
       <c r="X41" s="12"/>
       <c r="Y41" s="12"/>
       <c r="Z41" s="12"/>
@@ -6338,11 +6358,11 @@
       <c r="AF41" s="12"/>
       <c r="AG41" s="13">
         <f t="shared" si="33"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH41" s="14" cm="1">
         <f t="array" ref="AH41">SUMPRODUCT(--(B41:AF41=INT(B41:AF41)),--(B41:AF41&gt;0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI41" s="14" cm="1">
         <f t="array" ref="AI41">MAX(FREQUENCY(IF((B41:AF41=INT(B41:AF41))*(B41:AF41&gt;0),COLUMN(B41:AF41)),IF((B41:AF41&lt;&gt;INT(B41:AF41))+(B41:AF41&lt;=0),COLUMN(B41:AF41))))</f>
@@ -6350,15 +6370,15 @@
       </c>
       <c r="AJ41" s="15" cm="1">
         <f t="array" ref="AJ41">SUMPRODUCT(--(B41:AF41=INT(B41:AF41)),--(B41:AF41&gt;0))/30*100%</f>
-        <v>0.133333333333333</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="AK41" s="16">
         <f t="shared" ref="AK41:AM41" si="39">RANK(AG41,AG$3:AG$53,0)</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL41" s="16">
         <f t="shared" si="39"/>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AM41" s="16">
         <f t="shared" si="39"/>
@@ -6888,7 +6908,7 @@
       </c>
       <c r="AK48" s="16">
         <f t="shared" ref="AK48:AM48" si="46">RANK(AG48,AG$3:AG$53,0)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL48" s="16">
         <f t="shared" si="46"/>
@@ -7548,7 +7568,7 @@
   <pageSetup paperSize="9" scale="80" orientation="landscape"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AM53" formulaRange="1" unlockedFormula="1"/>
+    <ignoredError sqref="A1:AM7 A8:V8 X8:AM8 A9:AM39 A40:V41 X40:AM41 A42:AM53" formulaRange="1" unlockedFormula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>